--- a/Base_Consolidada_SIAFI.xlsx
+++ b/Base_Consolidada_SIAFI.xlsx
@@ -25182,11 +25182,11 @@
     </row>
     <row r="322">
       <c r="A322" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -25259,11 +25259,11 @@
     </row>
     <row r="323">
       <c r="A323" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -25336,11 +25336,11 @@
     </row>
     <row r="324">
       <c r="A324" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -25413,11 +25413,11 @@
     </row>
     <row r="325">
       <c r="A325" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -25490,11 +25490,11 @@
     </row>
     <row r="326">
       <c r="A326" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -25567,11 +25567,11 @@
     </row>
     <row r="327">
       <c r="A327" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -25644,11 +25644,11 @@
     </row>
     <row r="328">
       <c r="A328" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -25721,11 +25721,11 @@
     </row>
     <row r="329">
       <c r="A329" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -25798,11 +25798,11 @@
     </row>
     <row r="330">
       <c r="A330" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -25875,11 +25875,11 @@
     </row>
     <row r="331">
       <c r="A331" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -25952,11 +25952,11 @@
     </row>
     <row r="332">
       <c r="A332" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -26029,11 +26029,11 @@
     </row>
     <row r="333">
       <c r="A333" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -26106,11 +26106,11 @@
     </row>
     <row r="334">
       <c r="A334" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -26163,16 +26163,16 @@
         <v>197714</v>
       </c>
       <c r="P334" t="n">
-        <v>120857</v>
+        <v>124857</v>
       </c>
       <c r="Q334" t="n">
-        <v>76857</v>
+        <v>72857</v>
       </c>
       <c r="R334" t="n">
         <v>75428.5</v>
       </c>
       <c r="S334" t="n">
-        <v>45428.5</v>
+        <v>49428.5</v>
       </c>
       <c r="T334" t="n">
         <v>0</v>
@@ -26183,11 +26183,11 @@
     </row>
     <row r="335">
       <c r="A335" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -26260,11 +26260,11 @@
     </row>
     <row r="336">
       <c r="A336" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -26337,11 +26337,11 @@
     </row>
     <row r="337">
       <c r="A337" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -26414,11 +26414,11 @@
     </row>
     <row r="338">
       <c r="A338" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -26491,11 +26491,11 @@
     </row>
     <row r="339">
       <c r="A339" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -26568,11 +26568,11 @@
     </row>
     <row r="340">
       <c r="A340" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -26645,11 +26645,11 @@
     </row>
     <row r="341">
       <c r="A341" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -26702,16 +26702,16 @@
         <v>19428.5</v>
       </c>
       <c r="P341" t="n">
-        <v>43428.5</v>
+        <v>47428.5</v>
       </c>
       <c r="Q341" t="n">
-        <v>-24000</v>
+        <v>-28000</v>
       </c>
       <c r="R341" t="n">
         <v>23428.5</v>
       </c>
       <c r="S341" t="n">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="T341" t="n">
         <v>0</v>
@@ -26722,11 +26722,11 @@
     </row>
     <row r="342">
       <c r="A342" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -26799,11 +26799,11 @@
     </row>
     <row r="343">
       <c r="A343" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -26876,11 +26876,11 @@
     </row>
     <row r="344">
       <c r="A344" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -26933,16 +26933,16 @@
         <v>8333.32</v>
       </c>
       <c r="P344" t="n">
-        <v>2253112</v>
+        <v>2580876.33</v>
       </c>
       <c r="Q344" t="n">
-        <v>-2244778.68</v>
+        <v>-2572543.01</v>
       </c>
       <c r="R344" t="n">
         <v>3731947.25</v>
       </c>
       <c r="S344" t="n">
-        <v>-1478835.25</v>
+        <v>-1151070.92</v>
       </c>
       <c r="T344" t="n">
         <v>725340</v>
@@ -26953,11 +26953,11 @@
     </row>
     <row r="345">
       <c r="A345" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -27010,31 +27010,31 @@
         <v>161054.2</v>
       </c>
       <c r="P345" t="n">
-        <v>437815.74</v>
+        <v>511836.91</v>
       </c>
       <c r="Q345" t="n">
-        <v>-276761.54</v>
+        <v>-350782.71</v>
       </c>
       <c r="R345" t="n">
         <v>295383.5</v>
       </c>
       <c r="S345" t="n">
-        <v>142432.24</v>
+        <v>216453.41</v>
       </c>
       <c r="T345" t="n">
-        <v>312185.7</v>
+        <v>415791.82</v>
       </c>
       <c r="U345" t="n">
-        <v>-473239.9</v>
+        <v>-576846.02</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -27107,11 +27107,11 @@
     </row>
     <row r="347">
       <c r="A347" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -27164,16 +27164,16 @@
         <v>13410211.52</v>
       </c>
       <c r="P347" t="n">
-        <v>8622057.49</v>
+        <v>8949821.82</v>
       </c>
       <c r="Q347" t="n">
-        <v>4788154.029999999</v>
+        <v>4460389.699999999</v>
       </c>
       <c r="R347" t="n">
         <v>6636057.49</v>
       </c>
       <c r="S347" t="n">
-        <v>1986000</v>
+        <v>2313764.33</v>
       </c>
       <c r="T347" t="n">
         <v>6724744.79</v>
@@ -27184,11 +27184,11 @@
     </row>
     <row r="348">
       <c r="A348" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -27261,11 +27261,11 @@
     </row>
     <row r="349">
       <c r="A349" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -27338,11 +27338,11 @@
     </row>
     <row r="350">
       <c r="A350" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -27415,11 +27415,11 @@
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -27492,11 +27492,11 @@
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -27569,11 +27569,11 @@
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -27626,31 +27626,31 @@
         <v>1257262.46</v>
       </c>
       <c r="P353" t="n">
-        <v>441322.08</v>
+        <v>515343.25</v>
       </c>
       <c r="Q353" t="n">
-        <v>815940.3799999999</v>
+        <v>741919.21</v>
       </c>
       <c r="R353" t="n">
         <v>295383.5</v>
       </c>
       <c r="S353" t="n">
-        <v>145938.58</v>
+        <v>219959.75</v>
       </c>
       <c r="T353" t="n">
-        <v>312185.7</v>
+        <v>415791.82</v>
       </c>
       <c r="U353" t="n">
-        <v>430551.84</v>
+        <v>326945.72</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -27723,11 +27723,11 @@
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -27800,11 +27800,11 @@
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -27877,11 +27877,11 @@
     </row>
     <row r="357">
       <c r="A357" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -27954,11 +27954,11 @@
     </row>
     <row r="358">
       <c r="A358" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -28031,11 +28031,11 @@
     </row>
     <row r="359">
       <c r="A359" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -28108,11 +28108,11 @@
     </row>
     <row r="360">
       <c r="A360" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -28185,11 +28185,11 @@
     </row>
     <row r="361">
       <c r="A361" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -28262,11 +28262,11 @@
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -28339,11 +28339,11 @@
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -28416,11 +28416,11 @@
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -28493,11 +28493,11 @@
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -28570,11 +28570,11 @@
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -28647,11 +28647,11 @@
     </row>
     <row r="367">
       <c r="A367" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -28704,16 +28704,16 @@
         <v>10000</v>
       </c>
       <c r="P367" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q367" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="R367" t="n">
         <v>0</v>
       </c>
       <c r="S367" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T367" t="n">
         <v>0</v>
@@ -28724,11 +28724,11 @@
     </row>
     <row r="368">
       <c r="A368" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -28781,16 +28781,16 @@
         <v>10000</v>
       </c>
       <c r="P368" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q368" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="R368" t="n">
         <v>0</v>
       </c>
       <c r="S368" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T368" t="n">
         <v>0</v>
@@ -28801,11 +28801,11 @@
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -28878,11 +28878,11 @@
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -28955,11 +28955,11 @@
     </row>
     <row r="371">
       <c r="A371" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -29032,11 +29032,11 @@
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -29109,11 +29109,11 @@
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -29186,11 +29186,11 @@
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -29263,11 +29263,11 @@
     </row>
     <row r="375">
       <c r="A375" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -29340,11 +29340,11 @@
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -29417,11 +29417,11 @@
     </row>
     <row r="377">
       <c r="A377" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -29474,16 +29474,16 @@
         <v>20000</v>
       </c>
       <c r="P377" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Q377" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="R377" t="n">
         <v>0</v>
       </c>
       <c r="S377" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T377" t="n">
         <v>0</v>
@@ -29494,11 +29494,11 @@
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -29551,16 +29551,16 @@
         <v>20000</v>
       </c>
       <c r="P378" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Q378" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="R378" t="n">
         <v>0</v>
       </c>
       <c r="S378" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T378" t="n">
         <v>0</v>
@@ -29571,11 +29571,11 @@
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -29648,11 +29648,11 @@
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -29725,11 +29725,11 @@
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -29802,11 +29802,11 @@
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -29879,11 +29879,11 @@
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -29956,11 +29956,11 @@
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -30033,11 +30033,11 @@
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -30110,11 +30110,11 @@
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -30187,11 +30187,11 @@
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -30264,11 +30264,11 @@
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -30341,11 +30341,11 @@
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -30418,11 +30418,11 @@
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -30495,11 +30495,11 @@
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -30572,11 +30572,11 @@
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -30649,11 +30649,11 @@
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -30726,11 +30726,11 @@
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -30803,11 +30803,11 @@
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -30860,16 +30860,16 @@
         <v>0</v>
       </c>
       <c r="P395" t="n">
-        <v>460330.88</v>
+        <v>640609.77</v>
       </c>
       <c r="Q395" t="n">
-        <v>-460330.88</v>
+        <v>-640609.77</v>
       </c>
       <c r="R395" t="n">
         <v>854970.39</v>
       </c>
       <c r="S395" t="n">
-        <v>-394639.51</v>
+        <v>-214360.62</v>
       </c>
       <c r="T395" t="n">
         <v>0</v>
@@ -30880,11 +30880,11 @@
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -30937,16 +30937,16 @@
         <v>2601132.4</v>
       </c>
       <c r="P396" t="n">
-        <v>1736690.42</v>
+        <v>1916969.31</v>
       </c>
       <c r="Q396" t="n">
-        <v>864441.98</v>
+        <v>684163.0899999999</v>
       </c>
       <c r="R396" t="n">
         <v>1278789.54</v>
       </c>
       <c r="S396" t="n">
-        <v>457900.88</v>
+        <v>638179.77</v>
       </c>
       <c r="T396" t="n">
         <v>1000000</v>
@@ -30957,11 +30957,11 @@
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -31034,11 +31034,11 @@
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -31111,11 +31111,11 @@
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -31188,11 +31188,11 @@
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -31265,11 +31265,11 @@
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -31322,16 +31322,16 @@
         <v>45591</v>
       </c>
       <c r="P401" t="n">
-        <v>0</v>
+        <v>45591</v>
       </c>
       <c r="Q401" t="n">
-        <v>45591</v>
+        <v>0</v>
       </c>
       <c r="R401" t="n">
         <v>13382.4</v>
       </c>
       <c r="S401" t="n">
-        <v>-13382.4</v>
+        <v>32208.6</v>
       </c>
       <c r="T401" t="n">
         <v>0</v>
@@ -31342,11 +31342,11 @@
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -31399,16 +31399,16 @@
         <v>76815.89999999999</v>
       </c>
       <c r="P402" t="n">
-        <v>31224.9</v>
+        <v>76815.89999999999</v>
       </c>
       <c r="Q402" t="n">
-        <v>45590.99999999999</v>
+        <v>0</v>
       </c>
       <c r="R402" t="n">
         <v>31224.9</v>
       </c>
       <c r="S402" t="n">
-        <v>0</v>
+        <v>45591</v>
       </c>
       <c r="T402" t="n">
         <v>0</v>
@@ -31419,11 +31419,11 @@
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -31496,11 +31496,11 @@
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -31573,11 +31573,11 @@
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -31650,11 +31650,11 @@
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -31727,11 +31727,11 @@
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -31804,11 +31804,11 @@
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -31881,11 +31881,11 @@
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -31935,13 +31935,13 @@
         <v>0</v>
       </c>
       <c r="O409" t="n">
-        <v>980482.8199999999</v>
+        <v>716482.8199999999</v>
       </c>
       <c r="P409" t="n">
         <v>284107.44</v>
       </c>
       <c r="Q409" t="n">
-        <v>696375.3799999999</v>
+        <v>432375.3799999999</v>
       </c>
       <c r="R409" t="n">
         <v>94702.48</v>
@@ -31953,16 +31953,16 @@
         <v>0</v>
       </c>
       <c r="U409" t="n">
-        <v>-980482.8199999999</v>
+        <v>-716482.8199999999</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -32012,13 +32012,13 @@
         <v>2990500.28</v>
       </c>
       <c r="O410" t="n">
-        <v>1075185.3</v>
+        <v>811185.3</v>
       </c>
       <c r="P410" t="n">
         <v>284107.44</v>
       </c>
       <c r="Q410" t="n">
-        <v>791077.8600000001</v>
+        <v>527077.8600000001</v>
       </c>
       <c r="R410" t="n">
         <v>94702.48</v>
@@ -32030,16 +32030,16 @@
         <v>0</v>
       </c>
       <c r="U410" t="n">
-        <v>1915314.98</v>
+        <v>2179314.98</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -32112,11 +32112,11 @@
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -32189,11 +32189,11 @@
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -32266,11 +32266,11 @@
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -32343,11 +32343,11 @@
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -32420,11 +32420,11 @@
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -32497,11 +32497,11 @@
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -32574,11 +32574,11 @@
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -32651,11 +32651,11 @@
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -32728,11 +32728,11 @@
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -32805,11 +32805,11 @@
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -32882,11 +32882,11 @@
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -32959,11 +32959,11 @@
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -33036,11 +33036,11 @@
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -33113,11 +33113,11 @@
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -33190,11 +33190,11 @@
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -33267,11 +33267,11 @@
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -33344,11 +33344,11 @@
     </row>
     <row r="428">
       <c r="A428" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -33421,11 +33421,11 @@
     </row>
     <row r="429">
       <c r="A429" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -33484,10 +33484,10 @@
         <v>0</v>
       </c>
       <c r="R429" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="S429" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="T429" t="n">
         <v>0</v>
@@ -33498,11 +33498,11 @@
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -33575,11 +33575,11 @@
     </row>
     <row r="431">
       <c r="A431" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -33652,11 +33652,11 @@
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -33729,11 +33729,11 @@
     </row>
     <row r="433">
       <c r="A433" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -33806,11 +33806,11 @@
     </row>
     <row r="434">
       <c r="A434" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -33863,16 +33863,16 @@
         <v>0</v>
       </c>
       <c r="P434" t="n">
-        <v>267500</v>
+        <v>929634.22</v>
       </c>
       <c r="Q434" t="n">
-        <v>-267500</v>
+        <v>-929634.22</v>
       </c>
       <c r="R434" t="n">
         <v>0</v>
       </c>
       <c r="S434" t="n">
-        <v>267500</v>
+        <v>929634.22</v>
       </c>
       <c r="T434" t="n">
         <v>1640638.11</v>
@@ -33883,11 +33883,11 @@
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -33940,16 +33940,16 @@
         <v>929634.22</v>
       </c>
       <c r="P435" t="n">
-        <v>267500</v>
+        <v>929634.22</v>
       </c>
       <c r="Q435" t="n">
-        <v>662134.22</v>
+        <v>0</v>
       </c>
       <c r="R435" t="n">
         <v>0</v>
       </c>
       <c r="S435" t="n">
-        <v>267500</v>
+        <v>929634.22</v>
       </c>
       <c r="T435" t="n">
         <v>1640638.11</v>
@@ -33960,11 +33960,11 @@
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -34037,11 +34037,11 @@
     </row>
     <row r="437">
       <c r="A437" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -34114,11 +34114,11 @@
     </row>
     <row r="438">
       <c r="A438" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -34191,11 +34191,11 @@
     </row>
     <row r="439">
       <c r="A439" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -34268,11 +34268,11 @@
     </row>
     <row r="440">
       <c r="A440" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -34345,11 +34345,11 @@
     </row>
     <row r="441">
       <c r="A441" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -34422,11 +34422,11 @@
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -34499,11 +34499,11 @@
     </row>
     <row r="443">
       <c r="A443" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -34562,10 +34562,10 @@
         <v>0</v>
       </c>
       <c r="R443" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="S443" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="T443" t="n">
         <v>0</v>
@@ -34576,11 +34576,11 @@
     </row>
     <row r="444">
       <c r="A444" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -34653,11 +34653,11 @@
     </row>
     <row r="445">
       <c r="A445" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -34710,16 +34710,16 @@
         <v>243324.6</v>
       </c>
       <c r="P445" t="n">
-        <v>27156</v>
+        <v>29532</v>
       </c>
       <c r="Q445" t="n">
-        <v>216168.6</v>
+        <v>213792.6</v>
       </c>
       <c r="R445" t="n">
-        <v>6204</v>
+        <v>21756</v>
       </c>
       <c r="S445" t="n">
-        <v>20952</v>
+        <v>7776</v>
       </c>
       <c r="T445" t="n">
         <v>0</v>
@@ -34730,11 +34730,11 @@
     </row>
     <row r="446">
       <c r="A446" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -34807,11 +34807,11 @@
     </row>
     <row r="447">
       <c r="A447" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -34884,11 +34884,11 @@
     </row>
     <row r="448">
       <c r="A448" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -34961,11 +34961,11 @@
     </row>
     <row r="449">
       <c r="A449" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -35038,11 +35038,11 @@
     </row>
     <row r="450">
       <c r="A450" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -35115,11 +35115,11 @@
     </row>
     <row r="451">
       <c r="A451" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -35192,11 +35192,11 @@
     </row>
     <row r="452">
       <c r="A452" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -35269,11 +35269,11 @@
     </row>
     <row r="453">
       <c r="A453" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -35326,16 +35326,16 @@
         <v>9860.91</v>
       </c>
       <c r="P453" t="n">
-        <v>0</v>
+        <v>8783.26</v>
       </c>
       <c r="Q453" t="n">
-        <v>9860.91</v>
+        <v>1077.65</v>
       </c>
       <c r="R453" t="n">
         <v>0</v>
       </c>
       <c r="S453" t="n">
-        <v>0</v>
+        <v>8783.26</v>
       </c>
       <c r="T453" t="n">
         <v>0</v>
@@ -35346,11 +35346,11 @@
     </row>
     <row r="454">
       <c r="A454" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -35403,16 +35403,16 @@
         <v>9860.91</v>
       </c>
       <c r="P454" t="n">
-        <v>0</v>
+        <v>8783.26</v>
       </c>
       <c r="Q454" t="n">
-        <v>9860.91</v>
+        <v>1077.65</v>
       </c>
       <c r="R454" t="n">
         <v>0</v>
       </c>
       <c r="S454" t="n">
-        <v>0</v>
+        <v>8783.26</v>
       </c>
       <c r="T454" t="n">
         <v>0</v>
@@ -35423,11 +35423,11 @@
     </row>
     <row r="455">
       <c r="A455" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -35500,11 +35500,11 @@
     </row>
     <row r="456">
       <c r="A456" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -35577,11 +35577,11 @@
     </row>
     <row r="457">
       <c r="A457" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -35654,11 +35654,11 @@
     </row>
     <row r="458">
       <c r="A458" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -35731,11 +35731,11 @@
     </row>
     <row r="459">
       <c r="A459" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -35808,11 +35808,11 @@
     </row>
     <row r="460">
       <c r="A460" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -35885,11 +35885,11 @@
     </row>
     <row r="461">
       <c r="A461" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -35927,7 +35927,7 @@
         <v>0</v>
       </c>
       <c r="K461" t="n">
-        <v>0</v>
+        <v>413526.97</v>
       </c>
       <c r="L461" t="n">
         <v>0</v>
@@ -35936,7 +35936,7 @@
         <v>0</v>
       </c>
       <c r="N461" t="n">
-        <v>0</v>
+        <v>-413526.97</v>
       </c>
       <c r="O461" t="n">
         <v>0</v>
@@ -35948,13 +35948,13 @@
         <v>-1141288.71</v>
       </c>
       <c r="R461" t="n">
-        <v>1088656.75</v>
+        <v>1141288.71</v>
       </c>
       <c r="S461" t="n">
-        <v>52631.96</v>
+        <v>0</v>
       </c>
       <c r="T461" t="n">
-        <v>413526.97</v>
+        <v>0</v>
       </c>
       <c r="U461" t="n">
         <v>-413526.97</v>
@@ -35962,11 +35962,11 @@
     </row>
     <row r="462">
       <c r="A462" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -36004,7 +36004,7 @@
         <v>0</v>
       </c>
       <c r="K462" t="n">
-        <v>38678.68</v>
+        <v>452205.65</v>
       </c>
       <c r="L462" t="n">
         <v>0</v>
@@ -36013,7 +36013,7 @@
         <v>0</v>
       </c>
       <c r="N462" t="n">
-        <v>13961321.32</v>
+        <v>13547794.35</v>
       </c>
       <c r="O462" t="n">
         <v>4215393.26</v>
@@ -36025,13 +36025,13 @@
         <v>2423508.25</v>
       </c>
       <c r="R462" t="n">
-        <v>1739253.05</v>
+        <v>1791885.01</v>
       </c>
       <c r="S462" t="n">
-        <v>52631.96</v>
+        <v>0</v>
       </c>
       <c r="T462" t="n">
-        <v>413526.97</v>
+        <v>0</v>
       </c>
       <c r="U462" t="n">
         <v>9332401.09</v>
@@ -36039,11 +36039,11 @@
     </row>
     <row r="463">
       <c r="A463" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -36075,7 +36075,7 @@
         <v>0</v>
       </c>
       <c r="I463" t="n">
-        <v>0</v>
+        <v>413526.97</v>
       </c>
       <c r="J463" t="n">
         <v>0</v>
@@ -36090,7 +36090,7 @@
         <v>0</v>
       </c>
       <c r="N463" t="n">
-        <v>0</v>
+        <v>413526.97</v>
       </c>
       <c r="O463" t="n">
         <v>0</v>
@@ -36111,16 +36111,16 @@
         <v>0</v>
       </c>
       <c r="U463" t="n">
-        <v>0</v>
+        <v>413526.97</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -36152,7 +36152,7 @@
         <v>0</v>
       </c>
       <c r="I464" t="n">
-        <v>38678.68</v>
+        <v>452205.65</v>
       </c>
       <c r="J464" t="n">
         <v>0</v>
@@ -36167,7 +36167,7 @@
         <v>0</v>
       </c>
       <c r="N464" t="n">
-        <v>38678.68</v>
+        <v>452205.65</v>
       </c>
       <c r="O464" t="n">
         <v>0</v>
@@ -36188,16 +36188,16 @@
         <v>0</v>
       </c>
       <c r="U464" t="n">
-        <v>38678.68</v>
+        <v>452205.65</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -36270,11 +36270,11 @@
     </row>
     <row r="466">
       <c r="A466" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -36347,11 +36347,11 @@
     </row>
     <row r="467">
       <c r="A467" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -36424,11 +36424,11 @@
     </row>
     <row r="468">
       <c r="A468" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -36501,11 +36501,11 @@
     </row>
     <row r="469">
       <c r="A469" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -36578,11 +36578,11 @@
     </row>
     <row r="470">
       <c r="A470" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -36655,11 +36655,11 @@
     </row>
     <row r="471">
       <c r="A471" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -36732,11 +36732,11 @@
     </row>
     <row r="472">
       <c r="A472" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -36809,11 +36809,11 @@
     </row>
     <row r="473">
       <c r="A473" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -36886,11 +36886,11 @@
     </row>
     <row r="474">
       <c r="A474" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -36963,11 +36963,11 @@
     </row>
     <row r="475">
       <c r="A475" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -37040,11 +37040,11 @@
     </row>
     <row r="476">
       <c r="A476" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -37117,11 +37117,11 @@
     </row>
     <row r="477">
       <c r="A477" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -37174,16 +37174,16 @@
         <v>92674</v>
       </c>
       <c r="P477" t="n">
-        <v>0</v>
+        <v>73024</v>
       </c>
       <c r="Q477" t="n">
-        <v>92674</v>
+        <v>19650</v>
       </c>
       <c r="R477" t="n">
         <v>0</v>
       </c>
       <c r="S477" t="n">
-        <v>0</v>
+        <v>73024</v>
       </c>
       <c r="T477" t="n">
         <v>0</v>
@@ -37194,11 +37194,11 @@
     </row>
     <row r="478">
       <c r="A478" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -37271,11 +37271,11 @@
     </row>
     <row r="479">
       <c r="A479" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -37348,11 +37348,11 @@
     </row>
     <row r="480">
       <c r="A480" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -37425,11 +37425,11 @@
     </row>
     <row r="481">
       <c r="A481" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -37488,10 +37488,10 @@
         <v>0</v>
       </c>
       <c r="R481" t="n">
-        <v>0</v>
+        <v>2588</v>
       </c>
       <c r="S481" t="n">
-        <v>2588</v>
+        <v>0</v>
       </c>
       <c r="T481" t="n">
         <v>0</v>
@@ -37502,11 +37502,11 @@
     </row>
     <row r="482">
       <c r="A482" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -37565,10 +37565,10 @@
         <v>0</v>
       </c>
       <c r="R482" t="n">
-        <v>0</v>
+        <v>2588</v>
       </c>
       <c r="S482" t="n">
-        <v>2588</v>
+        <v>0</v>
       </c>
       <c r="T482" t="n">
         <v>150000</v>
@@ -37579,11 +37579,11 @@
     </row>
     <row r="483">
       <c r="A483" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -37636,16 +37636,16 @@
         <v>115000</v>
       </c>
       <c r="P483" t="n">
+        <v>90000</v>
+      </c>
+      <c r="Q483" t="n">
+        <v>25000</v>
+      </c>
+      <c r="R483" t="n">
         <v>85000</v>
       </c>
-      <c r="Q483" t="n">
-        <v>30000</v>
-      </c>
-      <c r="R483" t="n">
-        <v>0</v>
-      </c>
       <c r="S483" t="n">
-        <v>85000</v>
+        <v>5000</v>
       </c>
       <c r="T483" t="n">
         <v>0</v>
@@ -37656,11 +37656,11 @@
     </row>
     <row r="484">
       <c r="A484" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -37713,16 +37713,16 @@
         <v>115000</v>
       </c>
       <c r="P484" t="n">
+        <v>90000</v>
+      </c>
+      <c r="Q484" t="n">
+        <v>25000</v>
+      </c>
+      <c r="R484" t="n">
         <v>85000</v>
       </c>
-      <c r="Q484" t="n">
-        <v>30000</v>
-      </c>
-      <c r="R484" t="n">
-        <v>0</v>
-      </c>
       <c r="S484" t="n">
-        <v>85000</v>
+        <v>5000</v>
       </c>
       <c r="T484" t="n">
         <v>0</v>
@@ -37733,11 +37733,11 @@
     </row>
     <row r="485">
       <c r="A485" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -37790,16 +37790,16 @@
         <v>0</v>
       </c>
       <c r="P485" t="n">
-        <v>398357.88</v>
+        <v>494710.02</v>
       </c>
       <c r="Q485" t="n">
-        <v>-398357.88</v>
+        <v>-494710.02</v>
       </c>
       <c r="R485" t="n">
         <v>251135.01</v>
       </c>
       <c r="S485" t="n">
-        <v>147222.87</v>
+        <v>243575.01</v>
       </c>
       <c r="T485" t="n">
         <v>0</v>
@@ -37810,11 +37810,11 @@
     </row>
     <row r="486">
       <c r="A486" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -37867,16 +37867,16 @@
         <v>1405964.1</v>
       </c>
       <c r="P486" t="n">
-        <v>429266.06</v>
+        <v>525618.2</v>
       </c>
       <c r="Q486" t="n">
-        <v>976698.04</v>
+        <v>880345.9000000001</v>
       </c>
       <c r="R486" t="n">
         <v>251135.01</v>
       </c>
       <c r="S486" t="n">
-        <v>178131.05</v>
+        <v>274483.19</v>
       </c>
       <c r="T486" t="n">
         <v>1500000</v>
@@ -37887,11 +37887,11 @@
     </row>
     <row r="487">
       <c r="A487" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -37964,11 +37964,11 @@
     </row>
     <row r="488">
       <c r="A488" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -38041,11 +38041,11 @@
     </row>
     <row r="489">
       <c r="A489" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -38104,10 +38104,10 @@
         <v>0</v>
       </c>
       <c r="R489" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="S489" t="n">
-        <v>2367</v>
+        <v>1863</v>
       </c>
       <c r="T489" t="n">
         <v>0</v>
@@ -38118,11 +38118,11 @@
     </row>
     <row r="490">
       <c r="A490" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -38181,10 +38181,10 @@
         <v>1863</v>
       </c>
       <c r="R490" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="S490" t="n">
-        <v>2367</v>
+        <v>1863</v>
       </c>
       <c r="T490" t="n">
         <v>0</v>
@@ -38195,11 +38195,11 @@
     </row>
     <row r="491">
       <c r="A491" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -38252,16 +38252,16 @@
         <v>4864097.58</v>
       </c>
       <c r="P491" t="n">
-        <v>3310792.4</v>
+        <v>4140580.15</v>
       </c>
       <c r="Q491" t="n">
-        <v>1553305.18</v>
+        <v>723517.4300000002</v>
       </c>
       <c r="R491" t="n">
         <v>6367841.19</v>
       </c>
       <c r="S491" t="n">
-        <v>-3057048.79</v>
+        <v>-2227261.04</v>
       </c>
       <c r="T491" t="n">
         <v>9799876.32</v>
@@ -38272,11 +38272,11 @@
     </row>
     <row r="492">
       <c r="A492" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -38329,16 +38329,16 @@
         <v>20471388.76</v>
       </c>
       <c r="P492" t="n">
-        <v>9603235.9</v>
+        <v>10433023.65</v>
       </c>
       <c r="Q492" t="n">
-        <v>10868152.86</v>
+        <v>10038365.11</v>
       </c>
       <c r="R492" t="n">
         <v>9603235.9</v>
       </c>
       <c r="S492" t="n">
-        <v>0</v>
+        <v>829787.75</v>
       </c>
       <c r="T492" t="n">
         <v>46382823.26</v>
@@ -38349,11 +38349,11 @@
     </row>
     <row r="493">
       <c r="A493" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -38406,16 +38406,16 @@
         <v>1235048.49</v>
       </c>
       <c r="P493" t="n">
-        <v>3199404.62</v>
+        <v>3425435.03</v>
       </c>
       <c r="Q493" t="n">
-        <v>-1964356.13</v>
+        <v>-2190386.54</v>
       </c>
       <c r="R493" t="n">
-        <v>3847433.72</v>
+        <v>3937090.32</v>
       </c>
       <c r="S493" t="n">
-        <v>-648029.1</v>
+        <v>-511655.29</v>
       </c>
       <c r="T493" t="n">
         <v>0</v>
@@ -38426,11 +38426,11 @@
     </row>
     <row r="494">
       <c r="A494" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -38483,16 +38483,16 @@
         <v>15381287.32</v>
       </c>
       <c r="P494" t="n">
-        <v>5553098.35</v>
+        <v>5779128.76</v>
       </c>
       <c r="Q494" t="n">
-        <v>9828188.970000001</v>
+        <v>9602158.560000001</v>
       </c>
       <c r="R494" t="n">
-        <v>4036593.73</v>
+        <v>4126250.33</v>
       </c>
       <c r="S494" t="n">
-        <v>1516504.62</v>
+        <v>1652878.43</v>
       </c>
       <c r="T494" t="n">
         <v>20045600</v>
@@ -38503,11 +38503,11 @@
     </row>
     <row r="495">
       <c r="A495" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -38560,16 +38560,16 @@
         <v>0</v>
       </c>
       <c r="P495" t="n">
-        <v>4584726.16</v>
+        <v>9878393.66</v>
       </c>
       <c r="Q495" t="n">
-        <v>-4584726.16</v>
+        <v>-9878393.66</v>
       </c>
       <c r="R495" t="n">
         <v>6481664.09</v>
       </c>
       <c r="S495" t="n">
-        <v>-1896937.93</v>
+        <v>3396729.57</v>
       </c>
       <c r="T495" t="n">
         <v>0</v>
@@ -38580,11 +38580,11 @@
     </row>
     <row r="496">
       <c r="A496" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -38637,16 +38637,16 @@
         <v>24377681.76</v>
       </c>
       <c r="P496" t="n">
-        <v>12895559.51</v>
+        <v>18189227.01</v>
       </c>
       <c r="Q496" t="n">
-        <v>11482122.25</v>
+        <v>6188454.75</v>
       </c>
       <c r="R496" t="n">
         <v>12799492.77</v>
       </c>
       <c r="S496" t="n">
-        <v>96066.74000000001</v>
+        <v>5389734.24</v>
       </c>
       <c r="T496" t="n">
         <v>44414000</v>
@@ -38657,11 +38657,11 @@
     </row>
     <row r="497">
       <c r="A497" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -38734,11 +38734,11 @@
     </row>
     <row r="498">
       <c r="A498" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -38811,11 +38811,11 @@
     </row>
     <row r="499">
       <c r="A499" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -38868,16 +38868,16 @@
         <v>7103038.78</v>
       </c>
       <c r="P499" t="n">
-        <v>8863509</v>
+        <v>9160932.08</v>
       </c>
       <c r="Q499" t="n">
-        <v>-1760470.22</v>
+        <v>-2057893.3</v>
       </c>
       <c r="R499" t="n">
         <v>4772145.95</v>
       </c>
       <c r="S499" t="n">
-        <v>4091363.05</v>
+        <v>4388786.13</v>
       </c>
       <c r="T499" t="n">
         <v>0</v>
@@ -38888,11 +38888,11 @@
     </row>
     <row r="500">
       <c r="A500" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -38945,16 +38945,16 @@
         <v>16324067.68</v>
       </c>
       <c r="P500" t="n">
-        <v>15757075.25</v>
+        <v>16054498.33</v>
       </c>
       <c r="Q500" t="n">
-        <v>566992.4299999997</v>
+        <v>269569.3499999996</v>
       </c>
       <c r="R500" t="n">
         <v>8877566.25</v>
       </c>
       <c r="S500" t="n">
-        <v>6879509</v>
+        <v>7176932.08</v>
       </c>
       <c r="T500" t="n">
         <v>0</v>
@@ -38965,11 +38965,11 @@
     </row>
     <row r="501">
       <c r="A501" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -39022,16 +39022,16 @@
         <v>1423291.02</v>
       </c>
       <c r="P501" t="n">
-        <v>558375.9</v>
+        <v>1423291.02</v>
       </c>
       <c r="Q501" t="n">
-        <v>864915.12</v>
+        <v>0</v>
       </c>
       <c r="R501" t="n">
         <v>474375.9</v>
       </c>
       <c r="S501" t="n">
-        <v>84000</v>
+        <v>948915.12</v>
       </c>
       <c r="T501" t="n">
         <v>0</v>
@@ -39042,11 +39042,11 @@
     </row>
     <row r="502">
       <c r="A502" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -39099,16 +39099,16 @@
         <v>1897666.92</v>
       </c>
       <c r="P502" t="n">
-        <v>1032751.8</v>
+        <v>1897666.92</v>
       </c>
       <c r="Q502" t="n">
-        <v>864915.1199999999</v>
+        <v>0</v>
       </c>
       <c r="R502" t="n">
         <v>474375.9</v>
       </c>
       <c r="S502" t="n">
-        <v>558375.9</v>
+        <v>1423291.02</v>
       </c>
       <c r="T502" t="n">
         <v>0</v>
@@ -39119,11 +39119,11 @@
     </row>
     <row r="503">
       <c r="A503" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -39196,11 +39196,11 @@
     </row>
     <row r="504">
       <c r="A504" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -39273,11 +39273,11 @@
     </row>
     <row r="505">
       <c r="A505" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -39330,16 +39330,16 @@
         <v>92674</v>
       </c>
       <c r="P505" t="n">
-        <v>0</v>
+        <v>73024</v>
       </c>
       <c r="Q505" t="n">
-        <v>92674</v>
+        <v>19650</v>
       </c>
       <c r="R505" t="n">
         <v>0</v>
       </c>
       <c r="S505" t="n">
-        <v>0</v>
+        <v>73024</v>
       </c>
       <c r="T505" t="n">
         <v>0</v>
@@ -39350,11 +39350,11 @@
     </row>
     <row r="506">
       <c r="A506" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -39427,11 +39427,11 @@
     </row>
     <row r="507">
       <c r="A507" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -39504,11 +39504,11 @@
     </row>
     <row r="508">
       <c r="A508" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -39581,11 +39581,11 @@
     </row>
     <row r="509">
       <c r="A509" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -39658,11 +39658,11 @@
     </row>
     <row r="510">
       <c r="A510" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -39735,11 +39735,11 @@
     </row>
     <row r="511">
       <c r="A511" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -39812,11 +39812,11 @@
     </row>
     <row r="512">
       <c r="A512" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -39889,11 +39889,11 @@
     </row>
     <row r="513">
       <c r="A513" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -39966,11 +39966,11 @@
     </row>
     <row r="514">
       <c r="A514" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -40043,11 +40043,11 @@
     </row>
     <row r="515">
       <c r="A515" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -40120,11 +40120,11 @@
     </row>
     <row r="516">
       <c r="A516" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -40197,11 +40197,11 @@
     </row>
     <row r="517">
       <c r="A517" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -40254,16 +40254,16 @@
         <v>61472.5</v>
       </c>
       <c r="P517" t="n">
-        <v>35342.5</v>
+        <v>39027.5</v>
       </c>
       <c r="Q517" t="n">
-        <v>26130</v>
+        <v>22445</v>
       </c>
       <c r="R517" t="n">
         <v>54437.5</v>
       </c>
       <c r="S517" t="n">
-        <v>-19095</v>
+        <v>-15410</v>
       </c>
       <c r="T517" t="n">
         <v>0</v>
@@ -40274,11 +40274,11 @@
     </row>
     <row r="518">
       <c r="A518" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -40331,16 +40331,16 @@
         <v>123950</v>
       </c>
       <c r="P518" t="n">
-        <v>89780</v>
+        <v>93465</v>
       </c>
       <c r="Q518" t="n">
-        <v>34170</v>
+        <v>30485</v>
       </c>
       <c r="R518" t="n">
         <v>54437.5</v>
       </c>
       <c r="S518" t="n">
-        <v>35342.5</v>
+        <v>39027.5</v>
       </c>
       <c r="T518" t="n">
         <v>0</v>
@@ -40351,11 +40351,11 @@
     </row>
     <row r="519">
       <c r="A519" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -40405,13 +40405,13 @@
         <v>0</v>
       </c>
       <c r="O519" t="n">
-        <v>52427.5</v>
+        <v>56447.5</v>
       </c>
       <c r="P519" t="n">
         <v>31657.5</v>
       </c>
       <c r="Q519" t="n">
-        <v>20770</v>
+        <v>24790</v>
       </c>
       <c r="R519" t="n">
         <v>37520</v>
@@ -40423,16 +40423,16 @@
         <v>0</v>
       </c>
       <c r="U519" t="n">
-        <v>-6793.9</v>
+        <v>-10813.9</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -40482,13 +40482,13 @@
         <v>0</v>
       </c>
       <c r="O520" t="n">
-        <v>93967.5</v>
+        <v>97987.5</v>
       </c>
       <c r="P520" t="n">
         <v>69177.5</v>
       </c>
       <c r="Q520" t="n">
-        <v>24790</v>
+        <v>28810</v>
       </c>
       <c r="R520" t="n">
         <v>37520</v>
@@ -40500,16 +40500,16 @@
         <v>0</v>
       </c>
       <c r="U520" t="n">
-        <v>25087.7</v>
+        <v>21067.7</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -40562,16 +40562,16 @@
         <v>10000</v>
       </c>
       <c r="P521" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q521" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="R521" t="n">
         <v>0</v>
       </c>
       <c r="S521" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T521" t="n">
         <v>0</v>
@@ -40582,11 +40582,11 @@
     </row>
     <row r="522">
       <c r="A522" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -40639,16 +40639,16 @@
         <v>10000</v>
       </c>
       <c r="P522" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q522" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="R522" t="n">
         <v>0</v>
       </c>
       <c r="S522" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T522" t="n">
         <v>0</v>
@@ -40659,11 +40659,11 @@
     </row>
     <row r="523">
       <c r="A523" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -40716,16 +40716,16 @@
         <v>10000</v>
       </c>
       <c r="P523" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q523" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="R523" t="n">
         <v>0</v>
       </c>
       <c r="S523" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T523" t="n">
         <v>0</v>
@@ -40736,11 +40736,11 @@
     </row>
     <row r="524">
       <c r="A524" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -40793,16 +40793,16 @@
         <v>10000</v>
       </c>
       <c r="P524" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q524" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="R524" t="n">
         <v>0</v>
       </c>
       <c r="S524" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T524" t="n">
         <v>0</v>
@@ -40813,11 +40813,11 @@
     </row>
     <row r="525">
       <c r="A525" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -40867,13 +40867,13 @@
         <v>20000</v>
       </c>
       <c r="O525" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="P525" t="n">
         <v>0</v>
       </c>
       <c r="Q525" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="R525" t="n">
         <v>0</v>
@@ -40885,16 +40885,16 @@
         <v>0</v>
       </c>
       <c r="U525" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -40944,13 +40944,13 @@
         <v>20000</v>
       </c>
       <c r="O526" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="P526" t="n">
         <v>0</v>
       </c>
       <c r="Q526" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="R526" t="n">
         <v>0</v>
@@ -40962,16 +40962,16 @@
         <v>0</v>
       </c>
       <c r="U526" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -41021,13 +41021,13 @@
         <v>20000</v>
       </c>
       <c r="O527" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="P527" t="n">
         <v>0</v>
       </c>
       <c r="Q527" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="R527" t="n">
         <v>0</v>
@@ -41039,16 +41039,16 @@
         <v>0</v>
       </c>
       <c r="U527" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -41098,13 +41098,13 @@
         <v>20000</v>
       </c>
       <c r="O528" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="P528" t="n">
         <v>0</v>
       </c>
       <c r="Q528" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="R528" t="n">
         <v>0</v>
@@ -41116,16 +41116,16 @@
         <v>0</v>
       </c>
       <c r="U528" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -41175,13 +41175,13 @@
         <v>15000</v>
       </c>
       <c r="O529" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="P529" t="n">
         <v>0</v>
       </c>
       <c r="Q529" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="R529" t="n">
         <v>0</v>
@@ -41193,16 +41193,16 @@
         <v>0</v>
       </c>
       <c r="U529" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -41252,13 +41252,13 @@
         <v>15000</v>
       </c>
       <c r="O530" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="P530" t="n">
         <v>0</v>
       </c>
       <c r="Q530" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="R530" t="n">
         <v>0</v>
@@ -41270,16 +41270,16 @@
         <v>0</v>
       </c>
       <c r="U530" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -41329,13 +41329,13 @@
         <v>15000</v>
       </c>
       <c r="O531" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="P531" t="n">
         <v>0</v>
       </c>
       <c r="Q531" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="R531" t="n">
         <v>0</v>
@@ -41347,16 +41347,16 @@
         <v>0</v>
       </c>
       <c r="U531" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -41406,13 +41406,13 @@
         <v>15000</v>
       </c>
       <c r="O532" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="P532" t="n">
         <v>0</v>
       </c>
       <c r="Q532" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="R532" t="n">
         <v>0</v>
@@ -41424,16 +41424,16 @@
         <v>0</v>
       </c>
       <c r="U532" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -41486,16 +41486,16 @@
         <v>5000</v>
       </c>
       <c r="P533" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q533" t="n">
+        <v>0</v>
+      </c>
+      <c r="R533" t="n">
+        <v>0</v>
+      </c>
+      <c r="S533" t="n">
         <v>5000</v>
-      </c>
-      <c r="R533" t="n">
-        <v>0</v>
-      </c>
-      <c r="S533" t="n">
-        <v>0</v>
       </c>
       <c r="T533" t="n">
         <v>0</v>
@@ -41506,11 +41506,11 @@
     </row>
     <row r="534">
       <c r="A534" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -41563,16 +41563,16 @@
         <v>5000</v>
       </c>
       <c r="P534" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q534" t="n">
+        <v>0</v>
+      </c>
+      <c r="R534" t="n">
+        <v>0</v>
+      </c>
+      <c r="S534" t="n">
         <v>5000</v>
-      </c>
-      <c r="R534" t="n">
-        <v>0</v>
-      </c>
-      <c r="S534" t="n">
-        <v>0</v>
       </c>
       <c r="T534" t="n">
         <v>0</v>
@@ -41583,11 +41583,11 @@
     </row>
     <row r="535">
       <c r="A535" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -41660,11 +41660,11 @@
     </row>
     <row r="536">
       <c r="A536" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -41737,11 +41737,11 @@
     </row>
     <row r="537">
       <c r="A537" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -41814,11 +41814,11 @@
     </row>
     <row r="538">
       <c r="A538" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -41891,11 +41891,11 @@
     </row>
     <row r="539">
       <c r="A539" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -41968,11 +41968,11 @@
     </row>
     <row r="540">
       <c r="A540" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -42045,11 +42045,11 @@
     </row>
     <row r="541">
       <c r="A541" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -42122,11 +42122,11 @@
     </row>
     <row r="542">
       <c r="A542" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -42199,11 +42199,11 @@
     </row>
     <row r="543">
       <c r="A543" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -42276,11 +42276,11 @@
     </row>
     <row r="544">
       <c r="A544" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -42353,11 +42353,11 @@
     </row>
     <row r="545">
       <c r="A545" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -42430,11 +42430,11 @@
     </row>
     <row r="546">
       <c r="A546" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -42507,11 +42507,11 @@
     </row>
     <row r="547">
       <c r="A547" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -42564,16 +42564,16 @@
         <v>340017</v>
       </c>
       <c r="P547" t="n">
-        <v>313086.45</v>
+        <v>314891.85</v>
       </c>
       <c r="Q547" t="n">
-        <v>26930.54999999999</v>
+        <v>25125.15000000002</v>
       </c>
       <c r="R547" t="n">
         <v>49648.5</v>
       </c>
       <c r="S547" t="n">
-        <v>263437.95</v>
+        <v>265243.35</v>
       </c>
       <c r="T547" t="n">
         <v>0</v>
@@ -42584,11 +42584,11 @@
     </row>
     <row r="548">
       <c r="A548" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -42641,16 +42641,16 @@
         <v>340017</v>
       </c>
       <c r="P548" t="n">
-        <v>313086.45</v>
+        <v>314891.85</v>
       </c>
       <c r="Q548" t="n">
-        <v>26930.54999999999</v>
+        <v>25125.15000000002</v>
       </c>
       <c r="R548" t="n">
         <v>49648.5</v>
       </c>
       <c r="S548" t="n">
-        <v>263437.95</v>
+        <v>265243.35</v>
       </c>
       <c r="T548" t="n">
         <v>0</v>
@@ -42661,11 +42661,11 @@
     </row>
     <row r="549">
       <c r="A549" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -42738,11 +42738,11 @@
     </row>
     <row r="550">
       <c r="A550" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -42815,11 +42815,11 @@
     </row>
     <row r="551">
       <c r="A551" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -42869,34 +42869,34 @@
         <v>0</v>
       </c>
       <c r="O551" t="n">
-        <v>150077</v>
+        <v>148097</v>
       </c>
       <c r="P551" t="n">
-        <v>89126</v>
+        <v>107054</v>
       </c>
       <c r="Q551" t="n">
-        <v>60951</v>
+        <v>41043</v>
       </c>
       <c r="R551" t="n">
-        <v>8388</v>
+        <v>93038</v>
       </c>
       <c r="S551" t="n">
-        <v>80738</v>
+        <v>14016</v>
       </c>
       <c r="T551" t="n">
         <v>0</v>
       </c>
       <c r="U551" t="n">
-        <v>-150077</v>
+        <v>-148097</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -42946,34 +42946,34 @@
         <v>800000</v>
       </c>
       <c r="O552" t="n">
-        <v>186563</v>
+        <v>184583</v>
       </c>
       <c r="P552" t="n">
-        <v>125612</v>
+        <v>143540</v>
       </c>
       <c r="Q552" t="n">
-        <v>60951</v>
+        <v>41043</v>
       </c>
       <c r="R552" t="n">
-        <v>38400</v>
+        <v>123050</v>
       </c>
       <c r="S552" t="n">
-        <v>87212</v>
+        <v>20490</v>
       </c>
       <c r="T552" t="n">
         <v>400000</v>
       </c>
       <c r="U552" t="n">
-        <v>213437</v>
+        <v>215417</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -43046,11 +43046,11 @@
     </row>
     <row r="554">
       <c r="A554" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -43123,11 +43123,11 @@
     </row>
     <row r="555">
       <c r="A555" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -43200,11 +43200,11 @@
     </row>
     <row r="556">
       <c r="A556" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -43277,11 +43277,11 @@
     </row>
     <row r="557">
       <c r="A557" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -43334,16 +43334,16 @@
         <v>170949</v>
       </c>
       <c r="P557" t="n">
-        <v>20952</v>
+        <v>23328</v>
       </c>
       <c r="Q557" t="n">
-        <v>149997</v>
+        <v>147621</v>
       </c>
       <c r="R557" t="n">
-        <v>3564</v>
+        <v>19116</v>
       </c>
       <c r="S557" t="n">
-        <v>17388</v>
+        <v>4212</v>
       </c>
       <c r="T557" t="n">
         <v>0</v>
@@ -43354,11 +43354,11 @@
     </row>
     <row r="558">
       <c r="A558" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -43431,11 +43431,11 @@
     </row>
     <row r="559">
       <c r="A559" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -43508,11 +43508,11 @@
     </row>
     <row r="560">
       <c r="A560" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -43571,10 +43571,10 @@
         <v>-1472601.98</v>
       </c>
       <c r="R560" t="n">
-        <v>3425052.05</v>
+        <v>3430052.05</v>
       </c>
       <c r="S560" t="n">
-        <v>-1902240.23</v>
+        <v>-1907240.23</v>
       </c>
       <c r="T560" t="n">
         <v>0</v>
@@ -43585,11 +43585,11 @@
     </row>
     <row r="561">
       <c r="A561" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -43648,10 +43648,10 @@
         <v>3637236.02</v>
       </c>
       <c r="R561" t="n">
-        <v>3615195.66</v>
+        <v>3620195.66</v>
       </c>
       <c r="S561" t="n">
-        <v>1522811.82</v>
+        <v>1517811.82</v>
       </c>
       <c r="T561" t="n">
         <v>2000000</v>
@@ -43662,11 +43662,11 @@
     </row>
     <row r="562">
       <c r="A562" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -43739,11 +43739,11 @@
     </row>
     <row r="563">
       <c r="A563" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -43816,11 +43816,11 @@
     </row>
     <row r="564">
       <c r="A564" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -43893,11 +43893,11 @@
     </row>
     <row r="565">
       <c r="A565" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -43970,11 +43970,11 @@
     </row>
     <row r="566">
       <c r="A566" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -44047,11 +44047,11 @@
     </row>
     <row r="567">
       <c r="A567" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -44124,11 +44124,11 @@
     </row>
     <row r="568">
       <c r="A568" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -44201,11 +44201,11 @@
     </row>
     <row r="569">
       <c r="A569" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>RELEXORC_25-03-2026.csv</t>
+          <t>RELEXORC_26-03-2026.csv</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -44427,7 +44427,7 @@
         <v>46080</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>46080</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -44579,10 +44579,10 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2588</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2588</v>
       </c>
       <c r="X3" t="n">
         <v>100000</v>
@@ -44599,7 +44599,7 @@
         <v>46080</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>46080</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -44742,19 +44742,19 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>85000</v>
       </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
         <v>85000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -44771,7 +44771,7 @@
         <v>46080</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -44828,10 +44828,10 @@
         <v>30908.18</v>
       </c>
       <c r="S6" t="n">
-        <v>429266.06</v>
+        <v>525618.2</v>
       </c>
       <c r="T6" t="n">
-        <v>398357.88</v>
+        <v>494710.02</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -44857,7 +44857,7 @@
         <v>46080</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>46080</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>46080</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -45095,10 +45095,10 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -45115,7 +45115,7 @@
         <v>46080</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -45172,10 +45172,10 @@
         <v>6292443.5</v>
       </c>
       <c r="S10" t="n">
-        <v>9603235.9</v>
+        <v>10433023.65</v>
       </c>
       <c r="T10" t="n">
-        <v>3310792.4</v>
+        <v>4140580.15</v>
       </c>
       <c r="U10" t="n">
         <v>3235394.71</v>
@@ -45201,7 +45201,7 @@
         <v>46080</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -45258,19 +45258,19 @@
         <v>2353693.73</v>
       </c>
       <c r="S11" t="n">
-        <v>5553098.35</v>
+        <v>5779128.76</v>
       </c>
       <c r="T11" t="n">
-        <v>3199404.62</v>
+        <v>3425435.03</v>
       </c>
       <c r="U11" t="n">
         <v>189160.01</v>
       </c>
       <c r="V11" t="n">
-        <v>4036593.73</v>
+        <v>4126250.33</v>
       </c>
       <c r="W11" t="n">
-        <v>3847433.72</v>
+        <v>3937090.32</v>
       </c>
       <c r="X11" t="n">
         <v>36138010.7</v>
@@ -45287,7 +45287,7 @@
         <v>46080</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -45344,10 +45344,10 @@
         <v>8310833.35</v>
       </c>
       <c r="S12" t="n">
-        <v>12895559.51</v>
+        <v>18189227.01</v>
       </c>
       <c r="T12" t="n">
-        <v>4584726.16</v>
+        <v>9878393.660000002</v>
       </c>
       <c r="U12" t="n">
         <v>6317828.68</v>
@@ -45373,7 +45373,7 @@
         <v>46080</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>46080</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -45516,10 +45516,10 @@
         <v>6356261.81</v>
       </c>
       <c r="S14" t="n">
-        <v>15757075.25</v>
+        <v>16054498.33</v>
       </c>
       <c r="T14" t="n">
-        <v>9400813.440000001</v>
+        <v>9698236.52</v>
       </c>
       <c r="U14" t="n">
         <v>4105420.3</v>
@@ -45545,7 +45545,7 @@
         <v>46080</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -45602,10 +45602,10 @@
         <v>474375.9</v>
       </c>
       <c r="S15" t="n">
-        <v>1032751.8</v>
+        <v>1897666.92</v>
       </c>
       <c r="T15" t="n">
-        <v>558375.9</v>
+        <v>1423291.02</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -45631,7 +45631,7 @@
         <v>46080</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>46080</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -45774,10 +45774,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>73024</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>73024</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -45803,7 +45803,7 @@
         <v>46080</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -45889,7 +45889,7 @@
         <v>46080</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -45975,7 +45975,7 @@
         <v>46080</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>46080</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -46147,7 +46147,7 @@
         <v>46080</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>46080</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -46319,7 +46319,7 @@
         <v>46080</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         <v>46080</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -46462,10 +46462,10 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>8783.26</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>8783.26</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -46491,7 +46491,7 @@
         <v>46080</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>46080</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -46663,7 +46663,7 @@
         <v>46080</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>46080</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -46779,19 +46779,19 @@
         <v>38678.68</v>
       </c>
       <c r="J29" t="n">
-        <v>38678.68</v>
+        <v>452205.65</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>413526.97</v>
       </c>
       <c r="L29" t="n">
         <v>13961321.32</v>
       </c>
       <c r="M29" t="n">
-        <v>13961321.32</v>
+        <v>13547794.35</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>-413526.9700000007</v>
       </c>
       <c r="O29" t="n">
         <v>4215393.26</v>
@@ -46815,10 +46815,10 @@
         <v>650596.3</v>
       </c>
       <c r="V29" t="n">
-        <v>1739253.05</v>
+        <v>1791885.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1088656.75</v>
+        <v>1141288.71</v>
       </c>
       <c r="X29" t="n">
         <v>9745928.060000001</v>
@@ -46835,7 +46835,7 @@
         <v>46080</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -46856,10 +46856,10 @@
         <v>38678.68</v>
       </c>
       <c r="G30" t="n">
-        <v>38678.68</v>
+        <v>452205.65</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>413526.97</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -46874,10 +46874,10 @@
         <v>38678.68</v>
       </c>
       <c r="M30" t="n">
-        <v>38678.68</v>
+        <v>452205.65</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>413526.97</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -46910,10 +46910,10 @@
         <v>38678.68</v>
       </c>
       <c r="Y30" t="n">
-        <v>38678.68</v>
+        <v>452205.65</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>413526.97</v>
       </c>
     </row>
     <row r="31">
@@ -46921,7 +46921,7 @@
         <v>46080</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -47007,7 +47007,7 @@
         <v>46080</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
         <v>46080</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -47179,7 +47179,7 @@
         <v>46080</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -47265,7 +47265,7 @@
         <v>46080</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>46080</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -47437,7 +47437,7 @@
         <v>46080</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -47523,7 +47523,7 @@
         <v>46080</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>46080</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -47695,7 +47695,7 @@
         <v>46080</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>46080</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -47838,10 +47838,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>313086.45</v>
+        <v>314891.85</v>
       </c>
       <c r="T41" t="n">
-        <v>313086.45</v>
+        <v>314891.85</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -47867,7 +47867,7 @@
         <v>46080</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>46080</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -48001,37 +48001,37 @@
         <v>36486</v>
       </c>
       <c r="P43" t="n">
-        <v>186563</v>
+        <v>184583</v>
       </c>
       <c r="Q43" t="n">
-        <v>150077</v>
+        <v>148097</v>
       </c>
       <c r="R43" t="n">
         <v>36486</v>
       </c>
       <c r="S43" t="n">
-        <v>125612</v>
+        <v>143540</v>
       </c>
       <c r="T43" t="n">
-        <v>89126</v>
+        <v>107054</v>
       </c>
       <c r="U43" t="n">
         <v>30012</v>
       </c>
       <c r="V43" t="n">
-        <v>38400</v>
+        <v>123050</v>
       </c>
       <c r="W43" t="n">
-        <v>8388</v>
+        <v>93038</v>
       </c>
       <c r="X43" t="n">
         <v>363514</v>
       </c>
       <c r="Y43" t="n">
-        <v>213437</v>
+        <v>215417</v>
       </c>
       <c r="Z43" t="n">
-        <v>-150077</v>
+        <v>-148097</v>
       </c>
     </row>
     <row r="44">
@@ -48039,7 +48039,7 @@
         <v>46080</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -48125,7 +48125,7 @@
         <v>46080</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>46080</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -48297,7 +48297,7 @@
         <v>46080</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -48354,19 +48354,19 @@
         <v>6204</v>
       </c>
       <c r="S47" t="n">
-        <v>27156</v>
+        <v>29532</v>
       </c>
       <c r="T47" t="n">
-        <v>20952</v>
+        <v>23328</v>
       </c>
       <c r="U47" t="n">
         <v>2640</v>
       </c>
       <c r="V47" t="n">
-        <v>6204</v>
+        <v>21756</v>
       </c>
       <c r="W47" t="n">
-        <v>3564</v>
+        <v>19116</v>
       </c>
       <c r="X47" t="n">
         <v>1427624.4</v>
@@ -48383,7 +48383,7 @@
         <v>46080</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -48469,7 +48469,7 @@
         <v>46080</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -48535,10 +48535,10 @@
         <v>190143.61</v>
       </c>
       <c r="V49" t="n">
-        <v>3615195.66</v>
+        <v>3620195.66</v>
       </c>
       <c r="W49" t="n">
-        <v>3425052.05</v>
+        <v>3430052.05</v>
       </c>
       <c r="X49" t="n">
         <v>7455173.6</v>
@@ -48555,7 +48555,7 @@
         <v>46080</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -48641,7 +48641,7 @@
         <v>46080</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -48727,7 +48727,7 @@
         <v>46080</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>46080</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -48899,7 +48899,7 @@
         <v>46080</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -48985,7 +48985,7 @@
         <v>46080</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -49071,7 +49071,7 @@
         <v>46080</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -49157,7 +49157,7 @@
         <v>46080</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -49243,7 +49243,7 @@
         <v>46080</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>46080</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -49472,10 +49472,10 @@
         <v>54437.5</v>
       </c>
       <c r="S60" t="n">
-        <v>89780</v>
+        <v>93465</v>
       </c>
       <c r="T60" t="n">
-        <v>35342.5</v>
+        <v>39027.5</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -49501,7 +49501,7 @@
         <v>46080</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -49549,10 +49549,10 @@
         <v>41540</v>
       </c>
       <c r="P61" t="n">
-        <v>93967.5</v>
+        <v>97987.5</v>
       </c>
       <c r="Q61" t="n">
-        <v>52427.5</v>
+        <v>56447.5</v>
       </c>
       <c r="R61" t="n">
         <v>37520</v>
@@ -49576,10 +49576,10 @@
         <v>31881.6</v>
       </c>
       <c r="Y61" t="n">
-        <v>25087.7</v>
+        <v>21067.7</v>
       </c>
       <c r="Z61" t="n">
-        <v>-6793.899999999998</v>
+        <v>-10813.9</v>
       </c>
     </row>
     <row r="62">
@@ -49587,7 +49587,7 @@
         <v>46080</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -49644,10 +49644,10 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -49673,7 +49673,7 @@
         <v>46080</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -49730,10 +49730,10 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -49759,7 +49759,7 @@
         <v>46080</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -49807,10 +49807,10 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="Q64" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -49834,10 +49834,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="Z64" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="65">
@@ -49845,7 +49845,7 @@
         <v>46080</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -49893,10 +49893,10 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="Q65" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -49920,10 +49920,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="Z65" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="66">
@@ -49931,7 +49931,7 @@
         <v>46080</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -49979,10 +49979,10 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="Q66" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -50006,10 +50006,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -50017,7 +50017,7 @@
         <v>46080</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -50065,10 +50065,10 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="Q67" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -50092,10 +50092,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -50103,7 +50103,7 @@
         <v>46080</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -50160,10 +50160,10 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -50189,7 +50189,7 @@
         <v>46080</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -50275,7 +50275,7 @@
         <v>46080</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -50361,7 +50361,7 @@
         <v>46080</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -50447,7 +50447,7 @@
         <v>46080</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -50533,7 +50533,7 @@
         <v>46080</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -50619,7 +50619,7 @@
         <v>46080</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -50705,7 +50705,7 @@
         <v>46080</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         <v>46080</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -50877,7 +50877,7 @@
         <v>46080</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -50963,7 +50963,7 @@
         <v>46080</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -51049,7 +51049,7 @@
         <v>46080</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -51106,10 +51106,10 @@
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -51135,7 +51135,7 @@
         <v>46080</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>46080</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -51307,7 +51307,7 @@
         <v>46080</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>46080</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -51479,7 +51479,7 @@
         <v>46080</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -51536,10 +51536,10 @@
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
@@ -51565,7 +51565,7 @@
         <v>46080</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -51651,7 +51651,7 @@
         <v>46080</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -51737,7 +51737,7 @@
         <v>46080</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -51823,7 +51823,7 @@
         <v>46080</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -51909,7 +51909,7 @@
         <v>46080</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -51995,7 +51995,7 @@
         <v>46080</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -52081,7 +52081,7 @@
         <v>46080</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -52167,7 +52167,7 @@
         <v>46080</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -52253,7 +52253,7 @@
         <v>46080</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -52339,7 +52339,7 @@
         <v>46080</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -52425,7 +52425,7 @@
         <v>46080</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>46080</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -52597,7 +52597,7 @@
         <v>46080</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -52654,10 +52654,10 @@
         <v>77428.5</v>
       </c>
       <c r="S97" t="n">
-        <v>120857</v>
+        <v>124857</v>
       </c>
       <c r="T97" t="n">
-        <v>43428.5</v>
+        <v>47428.5</v>
       </c>
       <c r="U97" t="n">
         <v>56000</v>
@@ -52683,7 +52683,7 @@
         <v>46080</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -52769,7 +52769,7 @@
         <v>46080</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -52855,7 +52855,7 @@
         <v>46080</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -52912,10 +52912,10 @@
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>8622057.49</v>
+        <v>8949821.82</v>
       </c>
       <c r="T100" t="n">
-        <v>8622057.49</v>
+        <v>8949821.82</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
@@ -52941,7 +52941,7 @@
         <v>46080</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -52998,10 +52998,10 @@
         <v>3506.34</v>
       </c>
       <c r="S101" t="n">
-        <v>441322.08</v>
+        <v>515343.25</v>
       </c>
       <c r="T101" t="n">
-        <v>437815.74</v>
+        <v>511836.91</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -53016,10 +53016,10 @@
         <v>903791.74</v>
       </c>
       <c r="Y101" t="n">
-        <v>430551.84</v>
+        <v>326945.72</v>
       </c>
       <c r="Z101" t="n">
-        <v>-473239.9</v>
+        <v>-576846.02</v>
       </c>
     </row>
     <row r="102">
@@ -53027,7 +53027,7 @@
         <v>46080</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -53113,7 +53113,7 @@
         <v>46080</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -53199,7 +53199,7 @@
         <v>46080</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -53285,7 +53285,7 @@
         <v>46080</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>46080</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -53457,7 +53457,7 @@
         <v>46080</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -53543,7 +53543,7 @@
         <v>46080</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>46080</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -53715,7 +53715,7 @@
         <v>46080</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -53781,10 +53781,10 @@
         <v>0</v>
       </c>
       <c r="V110" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="W110" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="X110" t="n">
         <v>250000</v>
@@ -53801,7 +53801,7 @@
         <v>46080</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -53887,7 +53887,7 @@
         <v>46080</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -53973,7 +53973,7 @@
         <v>46080</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -54030,10 +54030,10 @@
         <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>267500</v>
+        <v>929634.22</v>
       </c>
       <c r="T113" t="n">
-        <v>267500</v>
+        <v>929634.22</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
@@ -54059,7 +54059,7 @@
         <v>46080</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -54145,7 +54145,7 @@
         <v>46080</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -54231,7 +54231,7 @@
         <v>46080</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>46080</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -54403,7 +54403,7 @@
         <v>46080</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -54489,7 +54489,7 @@
         <v>46080</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -54575,7 +54575,7 @@
         <v>46080</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -54661,7 +54661,7 @@
         <v>46080</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -54747,7 +54747,7 @@
         <v>46080</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -54833,7 +54833,7 @@
         <v>46080</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>46080</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -55005,7 +55005,7 @@
         <v>46080</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -55091,7 +55091,7 @@
         <v>46080</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -55148,10 +55148,10 @@
         <v>1276359.54</v>
       </c>
       <c r="S126" t="n">
-        <v>1736690.42</v>
+        <v>1916969.31</v>
       </c>
       <c r="T126" t="n">
-        <v>460330.8799999999</v>
+        <v>640609.77</v>
       </c>
       <c r="U126" t="n">
         <v>423819.15</v>
@@ -55177,7 +55177,7 @@
         <v>46080</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -55263,7 +55263,7 @@
         <v>46080</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>46080</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -55435,7 +55435,7 @@
         <v>46080</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -55492,10 +55492,10 @@
         <v>31224.9</v>
       </c>
       <c r="S130" t="n">
-        <v>31224.9</v>
+        <v>76815.89999999999</v>
       </c>
       <c r="T130" t="n">
-        <v>0</v>
+        <v>45590.99999999999</v>
       </c>
       <c r="U130" t="n">
         <v>17842.5</v>
@@ -55521,7 +55521,7 @@
         <v>46080</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -55607,7 +55607,7 @@
         <v>46080</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -55693,7 +55693,7 @@
         <v>46080</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -55779,7 +55779,7 @@
         <v>46080</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -55827,10 +55827,10 @@
         <v>94702.48</v>
       </c>
       <c r="P134" t="n">
-        <v>1075185.3</v>
+        <v>811185.3</v>
       </c>
       <c r="Q134" t="n">
-        <v>980482.8200000001</v>
+        <v>716482.8200000001</v>
       </c>
       <c r="R134" t="n">
         <v>0</v>
@@ -55854,10 +55854,10 @@
         <v>2895797.8</v>
       </c>
       <c r="Y134" t="n">
-        <v>1915314.98</v>
+        <v>2179314.98</v>
       </c>
       <c r="Z134" t="n">
-        <v>-980482.8199999998</v>
+        <v>-716482.8199999998</v>
       </c>
     </row>
     <row r="135">
@@ -55865,7 +55865,7 @@
         <v>46080</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>

--- a/Base_Consolidada_SIAFI.xlsx
+++ b/Base_Consolidada_SIAFI.xlsx
@@ -25182,11 +25182,11 @@
     </row>
     <row r="322">
       <c r="A322" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -25259,11 +25259,11 @@
     </row>
     <row r="323">
       <c r="A323" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -25336,11 +25336,11 @@
     </row>
     <row r="324">
       <c r="A324" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -25413,11 +25413,11 @@
     </row>
     <row r="325">
       <c r="A325" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -25490,11 +25490,11 @@
     </row>
     <row r="326">
       <c r="A326" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -25567,11 +25567,11 @@
     </row>
     <row r="327">
       <c r="A327" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -25644,11 +25644,11 @@
     </row>
     <row r="328">
       <c r="A328" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -25721,11 +25721,11 @@
     </row>
     <row r="329">
       <c r="A329" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -25798,11 +25798,11 @@
     </row>
     <row r="330">
       <c r="A330" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -25875,11 +25875,11 @@
     </row>
     <row r="331">
       <c r="A331" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -25952,11 +25952,11 @@
     </row>
     <row r="332">
       <c r="A332" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -26029,11 +26029,11 @@
     </row>
     <row r="333">
       <c r="A333" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -26106,11 +26106,11 @@
     </row>
     <row r="334">
       <c r="A334" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -26183,11 +26183,11 @@
     </row>
     <row r="335">
       <c r="A335" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -26260,11 +26260,11 @@
     </row>
     <row r="336">
       <c r="A336" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -26337,11 +26337,11 @@
     </row>
     <row r="337">
       <c r="A337" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -26414,11 +26414,11 @@
     </row>
     <row r="338">
       <c r="A338" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -26491,11 +26491,11 @@
     </row>
     <row r="339">
       <c r="A339" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -26568,11 +26568,11 @@
     </row>
     <row r="340">
       <c r="A340" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -26631,10 +26631,10 @@
         <v>-28000</v>
       </c>
       <c r="R340" t="n">
-        <v>64857</v>
+        <v>63857</v>
       </c>
       <c r="S340" t="n">
-        <v>-17428.5</v>
+        <v>-16428.5</v>
       </c>
       <c r="T340" t="n">
         <v>0</v>
@@ -26645,11 +26645,11 @@
     </row>
     <row r="341">
       <c r="A341" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -26708,10 +26708,10 @@
         <v>72857</v>
       </c>
       <c r="R341" t="n">
-        <v>116857</v>
+        <v>115857</v>
       </c>
       <c r="S341" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="T341" t="n">
         <v>0</v>
@@ -26722,11 +26722,11 @@
     </row>
     <row r="342">
       <c r="A342" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -26799,11 +26799,11 @@
     </row>
     <row r="343">
       <c r="A343" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -26868,19 +26868,19 @@
         <v>-1037070.92</v>
       </c>
       <c r="T343" t="n">
-        <v>725340</v>
+        <v>332006.67</v>
       </c>
       <c r="U343" t="n">
-        <v>6921666.68</v>
+        <v>7315000.01</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -26945,19 +26945,19 @@
         <v>2427764.33</v>
       </c>
       <c r="T344" t="n">
-        <v>6724744.79</v>
+        <v>6331411.46</v>
       </c>
       <c r="U344" t="n">
-        <v>6961000.35</v>
+        <v>7354333.68</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -27010,16 +27010,16 @@
         <v>1257262.46</v>
       </c>
       <c r="P345" t="n">
-        <v>589893.25</v>
+        <v>664443.25</v>
       </c>
       <c r="Q345" t="n">
-        <v>667369.21</v>
+        <v>592819.21</v>
       </c>
       <c r="R345" t="n">
         <v>441322.08</v>
       </c>
       <c r="S345" t="n">
-        <v>148571.17</v>
+        <v>223121.17</v>
       </c>
       <c r="T345" t="n">
         <v>415791.82</v>
@@ -27030,11 +27030,11 @@
     </row>
     <row r="346">
       <c r="A346" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -27107,11 +27107,11 @@
     </row>
     <row r="347">
       <c r="A347" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -27164,16 +27164,16 @@
         <v>161054.2</v>
       </c>
       <c r="P347" t="n">
-        <v>586386.91</v>
+        <v>660936.91</v>
       </c>
       <c r="Q347" t="n">
-        <v>-425332.71</v>
+        <v>-499882.71</v>
       </c>
       <c r="R347" t="n">
         <v>441322.08</v>
       </c>
       <c r="S347" t="n">
-        <v>145064.83</v>
+        <v>219614.83</v>
       </c>
       <c r="T347" t="n">
         <v>415791.82</v>
@@ -27184,11 +27184,11 @@
     </row>
     <row r="348">
       <c r="A348" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -27261,11 +27261,11 @@
     </row>
     <row r="349">
       <c r="A349" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -27338,11 +27338,11 @@
     </row>
     <row r="350">
       <c r="A350" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -27415,11 +27415,11 @@
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -27492,11 +27492,11 @@
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -27569,11 +27569,11 @@
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -27646,11 +27646,11 @@
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -27723,11 +27723,11 @@
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -27800,11 +27800,11 @@
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -27877,11 +27877,11 @@
     </row>
     <row r="357">
       <c r="A357" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -27934,16 +27934,16 @@
         <v>5000</v>
       </c>
       <c r="P357" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q357" t="n">
+        <v>0</v>
+      </c>
+      <c r="R357" t="n">
+        <v>0</v>
+      </c>
+      <c r="S357" t="n">
         <v>5000</v>
-      </c>
-      <c r="R357" t="n">
-        <v>0</v>
-      </c>
-      <c r="S357" t="n">
-        <v>0</v>
       </c>
       <c r="T357" t="n">
         <v>0</v>
@@ -27954,11 +27954,11 @@
     </row>
     <row r="358">
       <c r="A358" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -28011,16 +28011,16 @@
         <v>5000</v>
       </c>
       <c r="P358" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q358" t="n">
+        <v>0</v>
+      </c>
+      <c r="R358" t="n">
+        <v>0</v>
+      </c>
+      <c r="S358" t="n">
         <v>5000</v>
-      </c>
-      <c r="R358" t="n">
-        <v>0</v>
-      </c>
-      <c r="S358" t="n">
-        <v>0</v>
       </c>
       <c r="T358" t="n">
         <v>0</v>
@@ -28031,11 +28031,11 @@
     </row>
     <row r="359">
       <c r="A359" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -28108,11 +28108,11 @@
     </row>
     <row r="360">
       <c r="A360" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -28185,11 +28185,11 @@
     </row>
     <row r="361">
       <c r="A361" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -28262,11 +28262,11 @@
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -28339,11 +28339,11 @@
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -28416,11 +28416,11 @@
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -28473,16 +28473,16 @@
         <v>10000</v>
       </c>
       <c r="P364" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q364" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="R364" t="n">
         <v>0</v>
       </c>
       <c r="S364" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T364" t="n">
         <v>0</v>
@@ -28493,11 +28493,11 @@
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -28570,11 +28570,11 @@
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -28627,16 +28627,16 @@
         <v>10000</v>
       </c>
       <c r="P366" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q366" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="R366" t="n">
         <v>0</v>
       </c>
       <c r="S366" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T366" t="n">
         <v>0</v>
@@ -28647,11 +28647,11 @@
     </row>
     <row r="367">
       <c r="A367" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -28724,11 +28724,11 @@
     </row>
     <row r="368">
       <c r="A368" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -28781,16 +28781,16 @@
         <v>10000</v>
       </c>
       <c r="P368" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q368" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="R368" t="n">
         <v>0</v>
       </c>
       <c r="S368" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T368" t="n">
         <v>0</v>
@@ -28801,11 +28801,11 @@
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -28858,16 +28858,16 @@
         <v>10000</v>
       </c>
       <c r="P369" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q369" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="R369" t="n">
         <v>0</v>
       </c>
       <c r="S369" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T369" t="n">
         <v>0</v>
@@ -28878,11 +28878,11 @@
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -28955,11 +28955,11 @@
     </row>
     <row r="371">
       <c r="A371" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -29032,11 +29032,11 @@
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -29109,11 +29109,11 @@
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -29186,11 +29186,11 @@
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -29243,16 +29243,16 @@
         <v>15000</v>
       </c>
       <c r="P374" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Q374" t="n">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="R374" t="n">
         <v>0</v>
       </c>
       <c r="S374" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T374" t="n">
         <v>0</v>
@@ -29263,11 +29263,11 @@
     </row>
     <row r="375">
       <c r="A375" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -29320,16 +29320,16 @@
         <v>15000</v>
       </c>
       <c r="P375" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Q375" t="n">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="R375" t="n">
         <v>0</v>
       </c>
       <c r="S375" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T375" t="n">
         <v>0</v>
@@ -29340,11 +29340,11 @@
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -29417,11 +29417,11 @@
     </row>
     <row r="377">
       <c r="A377" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -29494,11 +29494,11 @@
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -29571,11 +29571,11 @@
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -29648,11 +29648,11 @@
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -29725,11 +29725,11 @@
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -29802,11 +29802,11 @@
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -29879,11 +29879,11 @@
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -29956,11 +29956,11 @@
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -30033,11 +30033,11 @@
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -30110,11 +30110,11 @@
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -30173,10 +30173,10 @@
         <v>-771000</v>
       </c>
       <c r="R386" t="n">
-        <v>931000</v>
+        <v>930300</v>
       </c>
       <c r="S386" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="T386" t="n">
         <v>0</v>
@@ -30187,11 +30187,11 @@
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -30250,10 +30250,10 @@
         <v>2015000</v>
       </c>
       <c r="R387" t="n">
-        <v>1876000</v>
+        <v>1875300</v>
       </c>
       <c r="S387" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="T387" t="n">
         <v>0</v>
@@ -30264,11 +30264,11 @@
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -30341,11 +30341,11 @@
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -30418,11 +30418,11 @@
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -30495,11 +30495,11 @@
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -30572,11 +30572,11 @@
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -30649,11 +30649,11 @@
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -30726,11 +30726,11 @@
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -30803,11 +30803,11 @@
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -30880,11 +30880,11 @@
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -30937,16 +30937,16 @@
         <v>0</v>
       </c>
       <c r="P396" t="n">
-        <v>640609.77</v>
+        <v>643639.77</v>
       </c>
       <c r="Q396" t="n">
-        <v>-640609.77</v>
+        <v>-643639.77</v>
       </c>
       <c r="R396" t="n">
         <v>854970.39</v>
       </c>
       <c r="S396" t="n">
-        <v>-214360.62</v>
+        <v>-211330.62</v>
       </c>
       <c r="T396" t="n">
         <v>0</v>
@@ -30957,11 +30957,11 @@
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -31034,11 +31034,11 @@
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -31091,16 +31091,16 @@
         <v>2601132.4</v>
       </c>
       <c r="P398" t="n">
-        <v>1916969.31</v>
+        <v>1919999.31</v>
       </c>
       <c r="Q398" t="n">
-        <v>684163.0899999999</v>
+        <v>681133.0899999999</v>
       </c>
       <c r="R398" t="n">
         <v>1278789.54</v>
       </c>
       <c r="S398" t="n">
-        <v>638179.77</v>
+        <v>641209.77</v>
       </c>
       <c r="T398" t="n">
         <v>1000000</v>
@@ -31111,11 +31111,11 @@
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -31188,11 +31188,11 @@
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -31265,11 +31265,11 @@
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -31342,11 +31342,11 @@
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -31419,11 +31419,11 @@
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -31496,11 +31496,11 @@
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -31573,11 +31573,11 @@
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -31650,11 +31650,11 @@
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -31727,11 +31727,11 @@
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -31804,11 +31804,11 @@
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -31881,11 +31881,11 @@
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -31958,11 +31958,11 @@
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -32012,34 +32012,34 @@
         <v>0</v>
       </c>
       <c r="O410" t="n">
-        <v>716482.8199999999</v>
+        <v>1200203.82</v>
       </c>
       <c r="P410" t="n">
-        <v>378809.92</v>
+        <v>611433.92</v>
       </c>
       <c r="Q410" t="n">
-        <v>337672.9</v>
+        <v>588769.9</v>
       </c>
       <c r="R410" t="n">
         <v>94702.48</v>
       </c>
       <c r="S410" t="n">
-        <v>284107.44</v>
+        <v>516731.44</v>
       </c>
       <c r="T410" t="n">
         <v>0</v>
       </c>
       <c r="U410" t="n">
-        <v>-716482.8199999999</v>
+        <v>-1200203.82</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -32089,34 +32089,34 @@
         <v>2990500.28</v>
       </c>
       <c r="O411" t="n">
-        <v>811185.3</v>
+        <v>1294906.3</v>
       </c>
       <c r="P411" t="n">
-        <v>378809.92</v>
+        <v>611433.92</v>
       </c>
       <c r="Q411" t="n">
-        <v>432375.3800000001</v>
+        <v>683472.38</v>
       </c>
       <c r="R411" t="n">
         <v>94702.48</v>
       </c>
       <c r="S411" t="n">
-        <v>284107.44</v>
+        <v>516731.44</v>
       </c>
       <c r="T411" t="n">
         <v>0</v>
       </c>
       <c r="U411" t="n">
-        <v>2179314.98</v>
+        <v>1695593.98</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -32189,11 +32189,11 @@
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -32266,11 +32266,11 @@
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -32343,11 +32343,11 @@
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -32420,11 +32420,11 @@
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -32497,11 +32497,11 @@
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -32574,11 +32574,11 @@
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -32651,11 +32651,11 @@
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -32728,11 +32728,11 @@
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -32805,11 +32805,11 @@
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -32882,11 +32882,11 @@
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -32959,11 +32959,11 @@
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -33036,11 +33036,11 @@
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -33113,11 +33113,11 @@
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -33190,11 +33190,11 @@
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -33267,11 +33267,11 @@
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -33344,11 +33344,11 @@
     </row>
     <row r="428">
       <c r="A428" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -33421,11 +33421,11 @@
     </row>
     <row r="429">
       <c r="A429" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -33498,11 +33498,11 @@
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -33575,11 +33575,11 @@
     </row>
     <row r="431">
       <c r="A431" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -33652,11 +33652,11 @@
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -33729,11 +33729,11 @@
     </row>
     <row r="433">
       <c r="A433" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -33806,11 +33806,11 @@
     </row>
     <row r="434">
       <c r="A434" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -33883,11 +33883,11 @@
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -33960,11 +33960,11 @@
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -34037,11 +34037,11 @@
     </row>
     <row r="437">
       <c r="A437" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -34114,11 +34114,11 @@
     </row>
     <row r="438">
       <c r="A438" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -34191,11 +34191,11 @@
     </row>
     <row r="439">
       <c r="A439" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -34268,11 +34268,11 @@
     </row>
     <row r="440">
       <c r="A440" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -34345,11 +34345,11 @@
     </row>
     <row r="441">
       <c r="A441" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -34422,11 +34422,11 @@
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -34499,11 +34499,11 @@
     </row>
     <row r="443">
       <c r="A443" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -34576,11 +34576,11 @@
     </row>
     <row r="444">
       <c r="A444" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -34653,11 +34653,11 @@
     </row>
     <row r="445">
       <c r="A445" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -34730,11 +34730,11 @@
     </row>
     <row r="446">
       <c r="A446" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -34807,11 +34807,11 @@
     </row>
     <row r="447">
       <c r="A447" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -34864,16 +34864,16 @@
         <v>5000</v>
       </c>
       <c r="P447" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q447" t="n">
+        <v>0</v>
+      </c>
+      <c r="R447" t="n">
+        <v>0</v>
+      </c>
+      <c r="S447" t="n">
         <v>5000</v>
-      </c>
-      <c r="R447" t="n">
-        <v>0</v>
-      </c>
-      <c r="S447" t="n">
-        <v>0</v>
       </c>
       <c r="T447" t="n">
         <v>0</v>
@@ -34884,11 +34884,11 @@
     </row>
     <row r="448">
       <c r="A448" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -34961,11 +34961,11 @@
     </row>
     <row r="449">
       <c r="A449" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -35038,11 +35038,11 @@
     </row>
     <row r="450">
       <c r="A450" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -35115,11 +35115,11 @@
     </row>
     <row r="451">
       <c r="A451" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -35192,11 +35192,11 @@
     </row>
     <row r="452">
       <c r="A452" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -35269,11 +35269,11 @@
     </row>
     <row r="453">
       <c r="A453" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -35326,16 +35326,16 @@
         <v>9860.91</v>
       </c>
       <c r="P453" t="n">
-        <v>8783.26</v>
+        <v>9860.91</v>
       </c>
       <c r="Q453" t="n">
-        <v>1077.65</v>
+        <v>0</v>
       </c>
       <c r="R453" t="n">
         <v>0</v>
       </c>
       <c r="S453" t="n">
-        <v>8783.26</v>
+        <v>9860.91</v>
       </c>
       <c r="T453" t="n">
         <v>0</v>
@@ -35346,11 +35346,11 @@
     </row>
     <row r="454">
       <c r="A454" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -35403,16 +35403,16 @@
         <v>9860.91</v>
       </c>
       <c r="P454" t="n">
-        <v>8783.26</v>
+        <v>9860.91</v>
       </c>
       <c r="Q454" t="n">
-        <v>1077.65</v>
+        <v>0</v>
       </c>
       <c r="R454" t="n">
         <v>0</v>
       </c>
       <c r="S454" t="n">
-        <v>8783.26</v>
+        <v>9860.91</v>
       </c>
       <c r="T454" t="n">
         <v>0</v>
@@ -35423,11 +35423,11 @@
     </row>
     <row r="455">
       <c r="A455" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -35500,11 +35500,11 @@
     </row>
     <row r="456">
       <c r="A456" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -35577,11 +35577,11 @@
     </row>
     <row r="457">
       <c r="A457" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -35654,11 +35654,11 @@
     </row>
     <row r="458">
       <c r="A458" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -35731,11 +35731,11 @@
     </row>
     <row r="459">
       <c r="A459" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -35808,11 +35808,11 @@
     </row>
     <row r="460">
       <c r="A460" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -35885,11 +35885,11 @@
     </row>
     <row r="461">
       <c r="A461" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -35962,11 +35962,11 @@
     </row>
     <row r="462">
       <c r="A462" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -36039,11 +36039,11 @@
     </row>
     <row r="463">
       <c r="A463" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -36116,11 +36116,11 @@
     </row>
     <row r="464">
       <c r="A464" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -36193,11 +36193,11 @@
     </row>
     <row r="465">
       <c r="A465" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -36270,11 +36270,11 @@
     </row>
     <row r="466">
       <c r="A466" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -36347,11 +36347,11 @@
     </row>
     <row r="467">
       <c r="A467" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -36424,11 +36424,11 @@
     </row>
     <row r="468">
       <c r="A468" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -36501,11 +36501,11 @@
     </row>
     <row r="469">
       <c r="A469" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -36578,11 +36578,11 @@
     </row>
     <row r="470">
       <c r="A470" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -36655,11 +36655,11 @@
     </row>
     <row r="471">
       <c r="A471" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -36732,11 +36732,11 @@
     </row>
     <row r="472">
       <c r="A472" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -36809,11 +36809,11 @@
     </row>
     <row r="473">
       <c r="A473" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -36886,11 +36886,11 @@
     </row>
     <row r="474">
       <c r="A474" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -36963,11 +36963,11 @@
     </row>
     <row r="475">
       <c r="A475" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -37040,11 +37040,11 @@
     </row>
     <row r="476">
       <c r="A476" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -37117,11 +37117,11 @@
     </row>
     <row r="477">
       <c r="A477" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -37194,11 +37194,11 @@
     </row>
     <row r="478">
       <c r="A478" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -37271,11 +37271,11 @@
     </row>
     <row r="479">
       <c r="A479" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -37348,11 +37348,11 @@
     </row>
     <row r="480">
       <c r="A480" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -37425,11 +37425,11 @@
     </row>
     <row r="481">
       <c r="A481" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -37502,11 +37502,11 @@
     </row>
     <row r="482">
       <c r="A482" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -37579,11 +37579,11 @@
     </row>
     <row r="483">
       <c r="A483" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -37656,11 +37656,11 @@
     </row>
     <row r="484">
       <c r="A484" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -37713,16 +37713,16 @@
         <v>115000</v>
       </c>
       <c r="P484" t="n">
-        <v>90000</v>
+        <v>100000</v>
       </c>
       <c r="Q484" t="n">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="R484" t="n">
         <v>90000</v>
       </c>
       <c r="S484" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T484" t="n">
         <v>0</v>
@@ -37733,11 +37733,11 @@
     </row>
     <row r="485">
       <c r="A485" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -37790,16 +37790,16 @@
         <v>115000</v>
       </c>
       <c r="P485" t="n">
-        <v>90000</v>
+        <v>100000</v>
       </c>
       <c r="Q485" t="n">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="R485" t="n">
         <v>90000</v>
       </c>
       <c r="S485" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T485" t="n">
         <v>0</v>
@@ -37810,11 +37810,11 @@
     </row>
     <row r="486">
       <c r="A486" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -37867,16 +37867,16 @@
         <v>0</v>
       </c>
       <c r="P486" t="n">
-        <v>497626.12</v>
+        <v>575932.98</v>
       </c>
       <c r="Q486" t="n">
-        <v>-497626.12</v>
+        <v>-575932.98</v>
       </c>
       <c r="R486" t="n">
         <v>296021.27</v>
       </c>
       <c r="S486" t="n">
-        <v>201604.85</v>
+        <v>279911.71</v>
       </c>
       <c r="T486" t="n">
         <v>0</v>
@@ -37887,11 +37887,11 @@
     </row>
     <row r="487">
       <c r="A487" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -37944,16 +37944,16 @@
         <v>1405964.1</v>
       </c>
       <c r="P487" t="n">
-        <v>528534.3</v>
+        <v>606841.16</v>
       </c>
       <c r="Q487" t="n">
-        <v>877429.8</v>
+        <v>799122.9400000001</v>
       </c>
       <c r="R487" t="n">
         <v>296021.27</v>
       </c>
       <c r="S487" t="n">
-        <v>232513.03</v>
+        <v>310819.89</v>
       </c>
       <c r="T487" t="n">
         <v>1500000</v>
@@ -37964,11 +37964,11 @@
     </row>
     <row r="488">
       <c r="A488" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -38041,11 +38041,11 @@
     </row>
     <row r="489">
       <c r="A489" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -38118,11 +38118,11 @@
     </row>
     <row r="490">
       <c r="A490" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -38195,11 +38195,11 @@
     </row>
     <row r="491">
       <c r="A491" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -38272,11 +38272,11 @@
     </row>
     <row r="492">
       <c r="A492" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -38349,11 +38349,11 @@
     </row>
     <row r="493">
       <c r="A493" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -38426,11 +38426,11 @@
     </row>
     <row r="494">
       <c r="A494" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -38480,34 +38480,34 @@
         <v>-50000</v>
       </c>
       <c r="O494" t="n">
-        <v>1235048.49</v>
+        <v>1242648.49</v>
       </c>
       <c r="P494" t="n">
-        <v>3462275.03</v>
+        <v>3472275.03</v>
       </c>
       <c r="Q494" t="n">
-        <v>-2227226.54</v>
+        <v>-2229626.54</v>
       </c>
       <c r="R494" t="n">
         <v>3957789.63</v>
       </c>
       <c r="S494" t="n">
-        <v>-495514.6</v>
+        <v>-485514.6</v>
       </c>
       <c r="T494" t="n">
-        <v>0</v>
+        <v>-45600</v>
       </c>
       <c r="U494" t="n">
-        <v>-1285048.49</v>
+        <v>-1247048.49</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -38557,34 +38557,34 @@
         <v>64484793.39</v>
       </c>
       <c r="O495" t="n">
-        <v>15381287.32</v>
+        <v>15388887.32</v>
       </c>
       <c r="P495" t="n">
-        <v>5815968.76</v>
+        <v>5825968.76</v>
       </c>
       <c r="Q495" t="n">
-        <v>9565318.560000001</v>
+        <v>9562918.560000001</v>
       </c>
       <c r="R495" t="n">
         <v>4146949.64</v>
       </c>
       <c r="S495" t="n">
-        <v>1669019.12</v>
+        <v>1679019.12</v>
       </c>
       <c r="T495" t="n">
-        <v>20045600</v>
+        <v>20000000</v>
       </c>
       <c r="U495" t="n">
-        <v>29057906.07</v>
+        <v>29095906.07</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -38657,11 +38657,11 @@
     </row>
     <row r="497">
       <c r="A497" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -38734,11 +38734,11 @@
     </row>
     <row r="498">
       <c r="A498" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -38811,11 +38811,11 @@
     </row>
     <row r="499">
       <c r="A499" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -38888,11 +38888,11 @@
     </row>
     <row r="500">
       <c r="A500" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -38965,11 +38965,11 @@
     </row>
     <row r="501">
       <c r="A501" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -39042,11 +39042,11 @@
     </row>
     <row r="502">
       <c r="A502" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -39119,11 +39119,11 @@
     </row>
     <row r="503">
       <c r="A503" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -39196,11 +39196,11 @@
     </row>
     <row r="504">
       <c r="A504" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -39273,11 +39273,11 @@
     </row>
     <row r="505">
       <c r="A505" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -39350,11 +39350,11 @@
     </row>
     <row r="506">
       <c r="A506" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -39427,11 +39427,11 @@
     </row>
     <row r="507">
       <c r="A507" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -39504,11 +39504,11 @@
     </row>
     <row r="508">
       <c r="A508" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -39561,16 +39561,16 @@
         <v>5000</v>
       </c>
       <c r="P508" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q508" t="n">
+        <v>0</v>
+      </c>
+      <c r="R508" t="n">
+        <v>0</v>
+      </c>
+      <c r="S508" t="n">
         <v>5000</v>
-      </c>
-      <c r="R508" t="n">
-        <v>0</v>
-      </c>
-      <c r="S508" t="n">
-        <v>0</v>
       </c>
       <c r="T508" t="n">
         <v>0</v>
@@ -39581,11 +39581,11 @@
     </row>
     <row r="509">
       <c r="A509" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -39658,11 +39658,11 @@
     </row>
     <row r="510">
       <c r="A510" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -39735,11 +39735,11 @@
     </row>
     <row r="511">
       <c r="A511" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -39812,11 +39812,11 @@
     </row>
     <row r="512">
       <c r="A512" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -39889,11 +39889,11 @@
     </row>
     <row r="513">
       <c r="A513" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -39966,11 +39966,11 @@
     </row>
     <row r="514">
       <c r="A514" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -40020,13 +40020,13 @@
         <v>0</v>
       </c>
       <c r="O514" t="n">
-        <v>-135555.45</v>
+        <v>-133750.05</v>
       </c>
       <c r="P514" t="n">
         <v>0</v>
       </c>
       <c r="Q514" t="n">
-        <v>-135555.45</v>
+        <v>-133750.05</v>
       </c>
       <c r="R514" t="n">
         <v>63339.45</v>
@@ -40038,16 +40038,16 @@
         <v>0</v>
       </c>
       <c r="U514" t="n">
-        <v>135555.45</v>
+        <v>133750.05</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -40097,13 +40097,13 @@
         <v>0</v>
       </c>
       <c r="O515" t="n">
-        <v>63339.45</v>
+        <v>65144.85</v>
       </c>
       <c r="P515" t="n">
         <v>63339.45</v>
       </c>
       <c r="Q515" t="n">
-        <v>0</v>
+        <v>1805.400000000001</v>
       </c>
       <c r="R515" t="n">
         <v>63339.45</v>
@@ -40115,16 +40115,16 @@
         <v>0</v>
       </c>
       <c r="U515" t="n">
-        <v>155715.75</v>
+        <v>153910.35</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -40197,11 +40197,11 @@
     </row>
     <row r="517">
       <c r="A517" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -40274,11 +40274,11 @@
     </row>
     <row r="518">
       <c r="A518" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -40328,13 +40328,13 @@
         <v>0</v>
       </c>
       <c r="O518" t="n">
-        <v>61472.5</v>
+        <v>74537.5</v>
       </c>
       <c r="P518" t="n">
         <v>66162.5</v>
       </c>
       <c r="Q518" t="n">
-        <v>-4690</v>
+        <v>8375</v>
       </c>
       <c r="R518" t="n">
         <v>89780</v>
@@ -40346,16 +40346,16 @@
         <v>0</v>
       </c>
       <c r="U518" t="n">
-        <v>38527.5</v>
+        <v>25462.5</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -40405,13 +40405,13 @@
         <v>0</v>
       </c>
       <c r="O519" t="n">
-        <v>123950</v>
+        <v>137015</v>
       </c>
       <c r="P519" t="n">
         <v>120600</v>
       </c>
       <c r="Q519" t="n">
-        <v>3350</v>
+        <v>16415</v>
       </c>
       <c r="R519" t="n">
         <v>89780</v>
@@ -40423,16 +40423,16 @@
         <v>0</v>
       </c>
       <c r="U519" t="n">
-        <v>56994.8</v>
+        <v>43929.8</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -40482,13 +40482,13 @@
         <v>0</v>
       </c>
       <c r="O520" t="n">
-        <v>56447.5</v>
+        <v>60467.5</v>
       </c>
       <c r="P520" t="n">
         <v>52762.5</v>
       </c>
       <c r="Q520" t="n">
-        <v>3685</v>
+        <v>7705</v>
       </c>
       <c r="R520" t="n">
         <v>69177.5</v>
@@ -40500,16 +40500,16 @@
         <v>0</v>
       </c>
       <c r="U520" t="n">
-        <v>-10813.9</v>
+        <v>-14833.9</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -40559,13 +40559,13 @@
         <v>0</v>
       </c>
       <c r="O521" t="n">
-        <v>97987.5</v>
+        <v>102007.5</v>
       </c>
       <c r="P521" t="n">
         <v>90282.5</v>
       </c>
       <c r="Q521" t="n">
-        <v>7705</v>
+        <v>11725</v>
       </c>
       <c r="R521" t="n">
         <v>69177.5</v>
@@ -40577,16 +40577,16 @@
         <v>0</v>
       </c>
       <c r="U521" t="n">
-        <v>21067.7</v>
+        <v>17047.7</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -40659,11 +40659,11 @@
     </row>
     <row r="523">
       <c r="A523" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -40736,11 +40736,11 @@
     </row>
     <row r="524">
       <c r="A524" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -40813,11 +40813,11 @@
     </row>
     <row r="525">
       <c r="A525" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -40890,11 +40890,11 @@
     </row>
     <row r="526">
       <c r="A526" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -40947,16 +40947,16 @@
         <v>15000</v>
       </c>
       <c r="P526" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q526" t="n">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="R526" t="n">
         <v>0</v>
       </c>
       <c r="S526" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T526" t="n">
         <v>0</v>
@@ -40967,11 +40967,11 @@
     </row>
     <row r="527">
       <c r="A527" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -41024,16 +41024,16 @@
         <v>15000</v>
       </c>
       <c r="P527" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q527" t="n">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="R527" t="n">
         <v>0</v>
       </c>
       <c r="S527" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T527" t="n">
         <v>0</v>
@@ -41044,11 +41044,11 @@
     </row>
     <row r="528">
       <c r="A528" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -41101,16 +41101,16 @@
         <v>15000</v>
       </c>
       <c r="P528" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q528" t="n">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="R528" t="n">
         <v>0</v>
       </c>
       <c r="S528" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T528" t="n">
         <v>0</v>
@@ -41121,11 +41121,11 @@
     </row>
     <row r="529">
       <c r="A529" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -41178,16 +41178,16 @@
         <v>15000</v>
       </c>
       <c r="P529" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q529" t="n">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="R529" t="n">
         <v>0</v>
       </c>
       <c r="S529" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T529" t="n">
         <v>0</v>
@@ -41198,11 +41198,11 @@
     </row>
     <row r="530">
       <c r="A530" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -41275,11 +41275,11 @@
     </row>
     <row r="531">
       <c r="A531" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -41352,11 +41352,11 @@
     </row>
     <row r="532">
       <c r="A532" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -41429,11 +41429,11 @@
     </row>
     <row r="533">
       <c r="A533" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -41506,11 +41506,11 @@
     </row>
     <row r="534">
       <c r="A534" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -41583,11 +41583,11 @@
     </row>
     <row r="535">
       <c r="A535" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -41660,11 +41660,11 @@
     </row>
     <row r="536">
       <c r="A536" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -41717,16 +41717,16 @@
         <v>5000</v>
       </c>
       <c r="P536" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q536" t="n">
+        <v>0</v>
+      </c>
+      <c r="R536" t="n">
+        <v>0</v>
+      </c>
+      <c r="S536" t="n">
         <v>5000</v>
-      </c>
-      <c r="R536" t="n">
-        <v>0</v>
-      </c>
-      <c r="S536" t="n">
-        <v>0</v>
       </c>
       <c r="T536" t="n">
         <v>0</v>
@@ -41737,11 +41737,11 @@
     </row>
     <row r="537">
       <c r="A537" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -41794,16 +41794,16 @@
         <v>5000</v>
       </c>
       <c r="P537" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q537" t="n">
+        <v>0</v>
+      </c>
+      <c r="R537" t="n">
+        <v>0</v>
+      </c>
+      <c r="S537" t="n">
         <v>5000</v>
-      </c>
-      <c r="R537" t="n">
-        <v>0</v>
-      </c>
-      <c r="S537" t="n">
-        <v>0</v>
       </c>
       <c r="T537" t="n">
         <v>0</v>
@@ -41814,11 +41814,11 @@
     </row>
     <row r="538">
       <c r="A538" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -41891,11 +41891,11 @@
     </row>
     <row r="539">
       <c r="A539" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -41968,11 +41968,11 @@
     </row>
     <row r="540">
       <c r="A540" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -42045,11 +42045,11 @@
     </row>
     <row r="541">
       <c r="A541" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -42122,11 +42122,11 @@
     </row>
     <row r="542">
       <c r="A542" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -42199,11 +42199,11 @@
     </row>
     <row r="543">
       <c r="A543" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -42276,11 +42276,11 @@
     </row>
     <row r="544">
       <c r="A544" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -42353,11 +42353,11 @@
     </row>
     <row r="545">
       <c r="A545" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -42430,11 +42430,11 @@
     </row>
     <row r="546">
       <c r="A546" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -42507,11 +42507,11 @@
     </row>
     <row r="547">
       <c r="A547" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -42584,11 +42584,11 @@
     </row>
     <row r="548">
       <c r="A548" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -42661,11 +42661,11 @@
     </row>
     <row r="549">
       <c r="A549" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -42738,11 +42738,11 @@
     </row>
     <row r="550">
       <c r="A550" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -42815,11 +42815,11 @@
     </row>
     <row r="551">
       <c r="A551" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -42892,11 +42892,11 @@
     </row>
     <row r="552">
       <c r="A552" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -42949,16 +42949,16 @@
         <v>148097</v>
       </c>
       <c r="P552" t="n">
-        <v>107054</v>
+        <v>110558</v>
       </c>
       <c r="Q552" t="n">
-        <v>41043</v>
+        <v>37539</v>
       </c>
       <c r="R552" t="n">
         <v>105314</v>
       </c>
       <c r="S552" t="n">
-        <v>1740</v>
+        <v>5244</v>
       </c>
       <c r="T552" t="n">
         <v>0</v>
@@ -42969,11 +42969,11 @@
     </row>
     <row r="553">
       <c r="A553" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -43026,16 +43026,16 @@
         <v>184583</v>
       </c>
       <c r="P553" t="n">
-        <v>143540</v>
+        <v>147044</v>
       </c>
       <c r="Q553" t="n">
-        <v>41043</v>
+        <v>37539</v>
       </c>
       <c r="R553" t="n">
         <v>135326</v>
       </c>
       <c r="S553" t="n">
-        <v>8214</v>
+        <v>11718</v>
       </c>
       <c r="T553" t="n">
         <v>400000</v>
@@ -43046,11 +43046,11 @@
     </row>
     <row r="554">
       <c r="A554" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -43123,11 +43123,11 @@
     </row>
     <row r="555">
       <c r="A555" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -43200,11 +43200,11 @@
     </row>
     <row r="556">
       <c r="A556" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -43277,11 +43277,11 @@
     </row>
     <row r="557">
       <c r="A557" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -43354,11 +43354,11 @@
     </row>
     <row r="558">
       <c r="A558" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -43411,16 +43411,16 @@
         <v>170949</v>
       </c>
       <c r="P558" t="n">
-        <v>25896</v>
+        <v>27018</v>
       </c>
       <c r="Q558" t="n">
-        <v>145053</v>
+        <v>143931</v>
       </c>
       <c r="R558" t="n">
         <v>26892</v>
       </c>
       <c r="S558" t="n">
-        <v>-996</v>
+        <v>126</v>
       </c>
       <c r="T558" t="n">
         <v>0</v>
@@ -43431,11 +43431,11 @@
     </row>
     <row r="559">
       <c r="A559" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -43488,16 +43488,16 @@
         <v>243324.6</v>
       </c>
       <c r="P559" t="n">
-        <v>32100</v>
+        <v>33222</v>
       </c>
       <c r="Q559" t="n">
-        <v>211224.6</v>
+        <v>210102.6</v>
       </c>
       <c r="R559" t="n">
         <v>29532</v>
       </c>
       <c r="S559" t="n">
-        <v>2568</v>
+        <v>3690</v>
       </c>
       <c r="T559" t="n">
         <v>0</v>
@@ -43508,11 +43508,11 @@
     </row>
     <row r="560">
       <c r="A560" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -43585,11 +43585,11 @@
     </row>
     <row r="561">
       <c r="A561" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -43662,11 +43662,11 @@
     </row>
     <row r="562">
       <c r="A562" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -43739,11 +43739,11 @@
     </row>
     <row r="563">
       <c r="A563" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -43816,11 +43816,11 @@
     </row>
     <row r="564">
       <c r="A564" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -43893,11 +43893,11 @@
     </row>
     <row r="565">
       <c r="A565" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -43970,11 +43970,11 @@
     </row>
     <row r="566">
       <c r="A566" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -44047,11 +44047,11 @@
     </row>
     <row r="567">
       <c r="A567" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -44124,11 +44124,11 @@
     </row>
     <row r="568">
       <c r="A568" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -44201,11 +44201,11 @@
     </row>
     <row r="569">
       <c r="A569" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -44278,11 +44278,11 @@
     </row>
     <row r="570">
       <c r="A570" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -44355,11 +44355,11 @@
     </row>
     <row r="571">
       <c r="A571" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>RELEXORC_27-03-2026.csv</t>
+          <t>RELEXORC_30-03-2026.csv</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -44581,7 +44581,7 @@
         <v>46080</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -44667,7 +44667,7 @@
         <v>46080</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>46080</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -44839,7 +44839,7 @@
         <v>46080</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -44896,10 +44896,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>90000</v>
+        <v>100000</v>
       </c>
       <c r="T5" t="n">
-        <v>90000</v>
+        <v>100000</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -44925,7 +44925,7 @@
         <v>46080</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -44982,10 +44982,10 @@
         <v>30908.18</v>
       </c>
       <c r="S6" t="n">
-        <v>528534.3</v>
+        <v>606841.16</v>
       </c>
       <c r="T6" t="n">
-        <v>497626.1200000001</v>
+        <v>575932.98</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -45011,7 +45011,7 @@
         <v>46080</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>46080</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -45183,7 +45183,7 @@
         <v>46080</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>46080</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -45355,7 +45355,7 @@
         <v>46080</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -45403,19 +45403,19 @@
         <v>8351182.69</v>
       </c>
       <c r="P11" t="n">
-        <v>15381287.32</v>
+        <v>15388887.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>7030104.63</v>
+        <v>7037704.63</v>
       </c>
       <c r="R11" t="n">
         <v>2353693.73</v>
       </c>
       <c r="S11" t="n">
-        <v>5815968.76</v>
+        <v>5825968.76</v>
       </c>
       <c r="T11" t="n">
-        <v>3462275.03</v>
+        <v>3472275.03</v>
       </c>
       <c r="U11" t="n">
         <v>189160.01</v>
@@ -45430,10 +45430,10 @@
         <v>36138010.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>29057906.07</v>
+        <v>29095906.07</v>
       </c>
       <c r="Z11" t="n">
-        <v>-7080104.630000003</v>
+        <v>-7042104.630000003</v>
       </c>
     </row>
     <row r="12">
@@ -45441,7 +45441,7 @@
         <v>46080</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>46080</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>46080</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -45699,7 +45699,7 @@
         <v>46080</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -45785,7 +45785,7 @@
         <v>46080</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>46080</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -45957,7 +45957,7 @@
         <v>46080</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -46043,7 +46043,7 @@
         <v>46080</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -46129,7 +46129,7 @@
         <v>46080</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -46215,7 +46215,7 @@
         <v>46080</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -46301,7 +46301,7 @@
         <v>46080</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -46387,7 +46387,7 @@
         <v>46080</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>46080</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -46559,7 +46559,7 @@
         <v>46080</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -46616,10 +46616,10 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>8783.26</v>
+        <v>9860.91</v>
       </c>
       <c r="T25" t="n">
-        <v>8783.26</v>
+        <v>9860.91</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -46645,7 +46645,7 @@
         <v>46080</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>46080</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>46080</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -46903,7 +46903,7 @@
         <v>46080</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>46080</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -47075,7 +47075,7 @@
         <v>46080</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>46080</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>46080</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -47333,7 +47333,7 @@
         <v>46080</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -47419,7 +47419,7 @@
         <v>46080</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>46080</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -47591,7 +47591,7 @@
         <v>46080</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>46080</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -47763,7 +47763,7 @@
         <v>46080</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>46080</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -47935,7 +47935,7 @@
         <v>46080</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>46080</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -48107,7 +48107,7 @@
         <v>46080</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -48164,10 +48164,10 @@
         <v>36486</v>
       </c>
       <c r="S43" t="n">
-        <v>143540</v>
+        <v>147044</v>
       </c>
       <c r="T43" t="n">
-        <v>107054</v>
+        <v>110558</v>
       </c>
       <c r="U43" t="n">
         <v>30012</v>
@@ -48193,7 +48193,7 @@
         <v>46080</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -48279,7 +48279,7 @@
         <v>46080</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>46080</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -48451,7 +48451,7 @@
         <v>46080</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -48508,10 +48508,10 @@
         <v>6204</v>
       </c>
       <c r="S47" t="n">
-        <v>32100</v>
+        <v>33222</v>
       </c>
       <c r="T47" t="n">
-        <v>25896</v>
+        <v>27018</v>
       </c>
       <c r="U47" t="n">
         <v>2640</v>
@@ -48537,7 +48537,7 @@
         <v>46080</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -48623,7 +48623,7 @@
         <v>46080</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -48709,7 +48709,7 @@
         <v>46080</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -48795,7 +48795,7 @@
         <v>46080</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -48881,7 +48881,7 @@
         <v>46080</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -48967,7 +48967,7 @@
         <v>46080</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>46080</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>46080</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -49225,7 +49225,7 @@
         <v>46080</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -49311,7 +49311,7 @@
         <v>46080</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>46080</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -49445,10 +49445,10 @@
         <v>198894.9</v>
       </c>
       <c r="P58" t="n">
-        <v>63339.45</v>
+        <v>65144.85</v>
       </c>
       <c r="Q58" t="n">
-        <v>-135555.45</v>
+        <v>-133750.05</v>
       </c>
       <c r="R58" t="n">
         <v>198894.9</v>
@@ -49472,10 +49472,10 @@
         <v>20160.3</v>
       </c>
       <c r="Y58" t="n">
-        <v>155715.75</v>
+        <v>153910.35</v>
       </c>
       <c r="Z58" t="n">
-        <v>135555.45</v>
+        <v>133750.05</v>
       </c>
     </row>
     <row r="59">
@@ -49483,7 +49483,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -49569,7 +49569,7 @@
         <v>46080</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -49617,10 +49617,10 @@
         <v>62477.5</v>
       </c>
       <c r="P60" t="n">
-        <v>123950</v>
+        <v>137015</v>
       </c>
       <c r="Q60" t="n">
-        <v>61472.5</v>
+        <v>74537.5</v>
       </c>
       <c r="R60" t="n">
         <v>54437.5</v>
@@ -49644,10 +49644,10 @@
         <v>18467.3</v>
       </c>
       <c r="Y60" t="n">
-        <v>56994.8</v>
+        <v>43929.8</v>
       </c>
       <c r="Z60" t="n">
-        <v>38527.5</v>
+        <v>25462.5</v>
       </c>
     </row>
     <row r="61">
@@ -49655,7 +49655,7 @@
         <v>46080</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -49703,10 +49703,10 @@
         <v>41540</v>
       </c>
       <c r="P61" t="n">
-        <v>97987.5</v>
+        <v>102007.5</v>
       </c>
       <c r="Q61" t="n">
-        <v>56447.5</v>
+        <v>60467.5</v>
       </c>
       <c r="R61" t="n">
         <v>37520</v>
@@ -49730,10 +49730,10 @@
         <v>31881.6</v>
       </c>
       <c r="Y61" t="n">
-        <v>21067.7</v>
+        <v>17047.7</v>
       </c>
       <c r="Z61" t="n">
-        <v>-10813.9</v>
+        <v>-14833.9</v>
       </c>
     </row>
     <row r="62">
@@ -49741,7 +49741,7 @@
         <v>46080</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>46080</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         <v>46080</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -49970,10 +49970,10 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -49999,7 +49999,7 @@
         <v>46080</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -50056,10 +50056,10 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -50085,7 +50085,7 @@
         <v>46080</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -50171,7 +50171,7 @@
         <v>46080</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -50257,7 +50257,7 @@
         <v>46080</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -50343,7 +50343,7 @@
         <v>46080</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -50400,10 +50400,10 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -50429,7 +50429,7 @@
         <v>46080</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -50486,10 +50486,10 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -50515,7 +50515,7 @@
         <v>46080</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -50601,7 +50601,7 @@
         <v>46080</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -50687,7 +50687,7 @@
         <v>46080</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>46080</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -50830,10 +50830,10 @@
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -50859,7 +50859,7 @@
         <v>46080</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -50945,7 +50945,7 @@
         <v>46080</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -51031,7 +51031,7 @@
         <v>46080</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -51117,7 +51117,7 @@
         <v>46080</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -51174,10 +51174,10 @@
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -51203,7 +51203,7 @@
         <v>46080</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -51289,7 +51289,7 @@
         <v>46080</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -51346,10 +51346,10 @@
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -51375,7 +51375,7 @@
         <v>46080</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -51461,7 +51461,7 @@
         <v>46080</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>46080</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -51604,10 +51604,10 @@
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -51633,7 +51633,7 @@
         <v>46080</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -51719,7 +51719,7 @@
         <v>46080</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -51805,7 +51805,7 @@
         <v>46080</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>46080</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -51977,7 +51977,7 @@
         <v>46080</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -52063,7 +52063,7 @@
         <v>46080</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -52149,7 +52149,7 @@
         <v>46080</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>46080</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -52321,7 +52321,7 @@
         <v>46080</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -52407,7 +52407,7 @@
         <v>46080</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -52493,7 +52493,7 @@
         <v>46080</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>46080</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         <v>46080</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -52751,7 +52751,7 @@
         <v>46080</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -52817,10 +52817,10 @@
         <v>56000</v>
       </c>
       <c r="V97" t="n">
-        <v>116857</v>
+        <v>115857</v>
       </c>
       <c r="W97" t="n">
-        <v>60857</v>
+        <v>59857</v>
       </c>
       <c r="X97" t="n">
         <v>521714.5</v>
@@ -52837,7 +52837,7 @@
         <v>46080</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -52923,7 +52923,7 @@
         <v>46080</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>46080</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -53084,10 +53084,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>6961000.35</v>
+        <v>7354333.68</v>
       </c>
       <c r="Z100" t="n">
-        <v>6961000.35</v>
+        <v>7354333.68</v>
       </c>
     </row>
     <row r="101">
@@ -53095,7 +53095,7 @@
         <v>46080</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -53152,10 +53152,10 @@
         <v>3506.34</v>
       </c>
       <c r="S101" t="n">
-        <v>589893.25</v>
+        <v>664443.25</v>
       </c>
       <c r="T101" t="n">
-        <v>586386.91</v>
+        <v>660936.91</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -53181,7 +53181,7 @@
         <v>46080</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -53267,7 +53267,7 @@
         <v>46080</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -53353,7 +53353,7 @@
         <v>46080</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -53439,7 +53439,7 @@
         <v>46080</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -53525,7 +53525,7 @@
         <v>46080</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -53611,7 +53611,7 @@
         <v>46080</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -53697,7 +53697,7 @@
         <v>46080</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -53783,7 +53783,7 @@
         <v>46080</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -53869,7 +53869,7 @@
         <v>46080</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -53955,7 +53955,7 @@
         <v>46080</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -54041,7 +54041,7 @@
         <v>46080</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -54127,7 +54127,7 @@
         <v>46080</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>46080</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -54299,7 +54299,7 @@
         <v>46080</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -54385,7 +54385,7 @@
         <v>46080</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -54471,7 +54471,7 @@
         <v>46080</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -54557,7 +54557,7 @@
         <v>46080</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -54643,7 +54643,7 @@
         <v>46080</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -54729,7 +54729,7 @@
         <v>46080</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -54815,7 +54815,7 @@
         <v>46080</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -54901,7 +54901,7 @@
         <v>46080</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -54967,10 +54967,10 @@
         <v>945000</v>
       </c>
       <c r="V122" t="n">
-        <v>1876000</v>
+        <v>1875300</v>
       </c>
       <c r="W122" t="n">
-        <v>931000</v>
+        <v>930300</v>
       </c>
       <c r="X122" t="n">
         <v>8269000</v>
@@ -54987,7 +54987,7 @@
         <v>46080</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -55073,7 +55073,7 @@
         <v>46080</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -55159,7 +55159,7 @@
         <v>46080</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>46080</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -55331,7 +55331,7 @@
         <v>46080</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -55388,10 +55388,10 @@
         <v>1276359.54</v>
       </c>
       <c r="S127" t="n">
-        <v>1916969.31</v>
+        <v>1919999.31</v>
       </c>
       <c r="T127" t="n">
-        <v>640609.77</v>
+        <v>643639.77</v>
       </c>
       <c r="U127" t="n">
         <v>423819.15</v>
@@ -55417,7 +55417,7 @@
         <v>46080</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -55503,7 +55503,7 @@
         <v>46080</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -55589,7 +55589,7 @@
         <v>46080</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -55675,7 +55675,7 @@
         <v>46080</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -55761,7 +55761,7 @@
         <v>46080</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -55847,7 +55847,7 @@
         <v>46080</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -55933,7 +55933,7 @@
         <v>46080</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -56019,7 +56019,7 @@
         <v>46080</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -56067,19 +56067,19 @@
         <v>94702.48</v>
       </c>
       <c r="P135" t="n">
-        <v>811185.3</v>
+        <v>1294906.3</v>
       </c>
       <c r="Q135" t="n">
-        <v>716482.8200000001</v>
+        <v>1200203.82</v>
       </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
       <c r="S135" t="n">
-        <v>378809.92</v>
+        <v>611433.92</v>
       </c>
       <c r="T135" t="n">
-        <v>378809.92</v>
+        <v>611433.92</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
@@ -56094,10 +56094,10 @@
         <v>2895797.8</v>
       </c>
       <c r="Y135" t="n">
-        <v>2179314.98</v>
+        <v>1695593.98</v>
       </c>
       <c r="Z135" t="n">
-        <v>-716482.8199999998</v>
+        <v>-1200203.82</v>
       </c>
     </row>
     <row r="136">
@@ -56105,7 +56105,7 @@
         <v>46080</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>

--- a/Base_Consolidada_SIAFI.xlsx
+++ b/Base_Consolidada_SIAFI.xlsx
@@ -25182,11 +25182,11 @@
     </row>
     <row r="322">
       <c r="A322" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -25259,11 +25259,11 @@
     </row>
     <row r="323">
       <c r="A323" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -25336,11 +25336,11 @@
     </row>
     <row r="324">
       <c r="A324" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -25413,11 +25413,11 @@
     </row>
     <row r="325">
       <c r="A325" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -25490,11 +25490,11 @@
     </row>
     <row r="326">
       <c r="A326" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -25544,13 +25544,13 @@
         <v>0</v>
       </c>
       <c r="O326" t="n">
-        <v>0</v>
+        <v>9418</v>
       </c>
       <c r="P326" t="n">
         <v>0</v>
       </c>
       <c r="Q326" t="n">
-        <v>0</v>
+        <v>9418</v>
       </c>
       <c r="R326" t="n">
         <v>0</v>
@@ -25562,16 +25562,16 @@
         <v>0</v>
       </c>
       <c r="U326" t="n">
-        <v>9418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -25644,11 +25644,11 @@
     </row>
     <row r="328">
       <c r="A328" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -25698,13 +25698,13 @@
         <v>0</v>
       </c>
       <c r="O328" t="n">
-        <v>0</v>
+        <v>9418</v>
       </c>
       <c r="P328" t="n">
         <v>0</v>
       </c>
       <c r="Q328" t="n">
-        <v>0</v>
+        <v>9418</v>
       </c>
       <c r="R328" t="n">
         <v>0</v>
@@ -25716,16 +25716,16 @@
         <v>0</v>
       </c>
       <c r="U328" t="n">
-        <v>9418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -25798,11 +25798,11 @@
     </row>
     <row r="330">
       <c r="A330" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -25875,11 +25875,11 @@
     </row>
     <row r="331">
       <c r="A331" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -25952,11 +25952,11 @@
     </row>
     <row r="332">
       <c r="A332" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -26029,11 +26029,11 @@
     </row>
     <row r="333">
       <c r="A333" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -26106,11 +26106,11 @@
     </row>
     <row r="334">
       <c r="A334" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -26183,11 +26183,11 @@
     </row>
     <row r="335">
       <c r="A335" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -26260,11 +26260,11 @@
     </row>
     <row r="336">
       <c r="A336" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -26317,16 +26317,16 @@
         <v>0</v>
       </c>
       <c r="P336" t="n">
-        <v>268800</v>
+        <v>522800</v>
       </c>
       <c r="Q336" t="n">
-        <v>-268800</v>
+        <v>-522800</v>
       </c>
       <c r="R336" t="n">
         <v>302300</v>
       </c>
       <c r="S336" t="n">
-        <v>-33500</v>
+        <v>220500</v>
       </c>
       <c r="T336" t="n">
         <v>0</v>
@@ -26337,11 +26337,11 @@
     </row>
     <row r="337">
       <c r="A337" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -26394,16 +26394,16 @@
         <v>1305000</v>
       </c>
       <c r="P337" t="n">
-        <v>555600</v>
+        <v>809600</v>
       </c>
       <c r="Q337" t="n">
-        <v>749400</v>
+        <v>495400</v>
       </c>
       <c r="R337" t="n">
         <v>555600</v>
       </c>
       <c r="S337" t="n">
-        <v>0</v>
+        <v>254000</v>
       </c>
       <c r="T337" t="n">
         <v>0</v>
@@ -26414,11 +26414,11 @@
     </row>
     <row r="338">
       <c r="A338" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -26491,11 +26491,11 @@
     </row>
     <row r="339">
       <c r="A339" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -26568,11 +26568,11 @@
     </row>
     <row r="340">
       <c r="A340" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -26631,10 +26631,10 @@
         <v>-28000</v>
       </c>
       <c r="R340" t="n">
-        <v>63857</v>
+        <v>62857</v>
       </c>
       <c r="S340" t="n">
-        <v>-16428.5</v>
+        <v>-15428.5</v>
       </c>
       <c r="T340" t="n">
         <v>0</v>
@@ -26645,11 +26645,11 @@
     </row>
     <row r="341">
       <c r="A341" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -26708,10 +26708,10 @@
         <v>72857</v>
       </c>
       <c r="R341" t="n">
-        <v>115857</v>
+        <v>114857</v>
       </c>
       <c r="S341" t="n">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="T341" t="n">
         <v>0</v>
@@ -26722,11 +26722,11 @@
     </row>
     <row r="342">
       <c r="A342" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -26799,11 +26799,11 @@
     </row>
     <row r="343">
       <c r="A343" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -26876,11 +26876,11 @@
     </row>
     <row r="344">
       <c r="A344" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -26953,11 +26953,11 @@
     </row>
     <row r="345">
       <c r="A345" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -27030,11 +27030,11 @@
     </row>
     <row r="346">
       <c r="A346" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -27107,11 +27107,11 @@
     </row>
     <row r="347">
       <c r="A347" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -27184,11 +27184,11 @@
     </row>
     <row r="348">
       <c r="A348" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -27261,11 +27261,11 @@
     </row>
     <row r="349">
       <c r="A349" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -27338,11 +27338,11 @@
     </row>
     <row r="350">
       <c r="A350" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -27415,11 +27415,11 @@
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -27492,11 +27492,11 @@
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -27569,11 +27569,11 @@
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -27646,11 +27646,11 @@
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -27723,11 +27723,11 @@
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -27747,7 +27747,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>339030 - Material de Consumo</t>
+          <t>33903089 - Material de Consumo</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
@@ -27780,16 +27780,16 @@
         <v>10000</v>
       </c>
       <c r="P355" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Q355" t="n">
+        <v>0</v>
+      </c>
+      <c r="R355" t="n">
+        <v>0</v>
+      </c>
+      <c r="S355" t="n">
         <v>10000</v>
-      </c>
-      <c r="R355" t="n">
-        <v>0</v>
-      </c>
-      <c r="S355" t="n">
-        <v>0</v>
       </c>
       <c r="T355" t="n">
         <v>0</v>
@@ -27800,11 +27800,11 @@
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -27824,7 +27824,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>339030 - Material de Consumo</t>
+          <t>33903089 - Material de Consumo</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
@@ -27857,16 +27857,16 @@
         <v>10000</v>
       </c>
       <c r="P356" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Q356" t="n">
+        <v>0</v>
+      </c>
+      <c r="R356" t="n">
+        <v>0</v>
+      </c>
+      <c r="S356" t="n">
         <v>10000</v>
-      </c>
-      <c r="R356" t="n">
-        <v>0</v>
-      </c>
-      <c r="S356" t="n">
-        <v>0</v>
       </c>
       <c r="T356" t="n">
         <v>0</v>
@@ -27877,11 +27877,11 @@
     </row>
     <row r="357">
       <c r="A357" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -27954,11 +27954,11 @@
     </row>
     <row r="358">
       <c r="A358" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -28031,11 +28031,11 @@
     </row>
     <row r="359">
       <c r="A359" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -28108,11 +28108,11 @@
     </row>
     <row r="360">
       <c r="A360" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -28185,11 +28185,11 @@
     </row>
     <row r="361">
       <c r="A361" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -28262,11 +28262,11 @@
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -28339,11 +28339,11 @@
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -28416,11 +28416,11 @@
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -28493,11 +28493,11 @@
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -28570,11 +28570,11 @@
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -28647,11 +28647,11 @@
     </row>
     <row r="367">
       <c r="A367" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -28724,11 +28724,11 @@
     </row>
     <row r="368">
       <c r="A368" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -28781,16 +28781,16 @@
         <v>10000</v>
       </c>
       <c r="P368" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="Q368" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="R368" t="n">
         <v>0</v>
       </c>
       <c r="S368" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="T368" t="n">
         <v>0</v>
@@ -28801,11 +28801,11 @@
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -28858,16 +28858,16 @@
         <v>10000</v>
       </c>
       <c r="P369" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="Q369" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="R369" t="n">
         <v>0</v>
       </c>
       <c r="S369" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="T369" t="n">
         <v>0</v>
@@ -28878,11 +28878,11 @@
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -28935,16 +28935,16 @@
         <v>10000</v>
       </c>
       <c r="P370" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Q370" t="n">
+        <v>0</v>
+      </c>
+      <c r="R370" t="n">
+        <v>0</v>
+      </c>
+      <c r="S370" t="n">
         <v>10000</v>
-      </c>
-      <c r="R370" t="n">
-        <v>0</v>
-      </c>
-      <c r="S370" t="n">
-        <v>0</v>
       </c>
       <c r="T370" t="n">
         <v>0</v>
@@ -28955,11 +28955,11 @@
     </row>
     <row r="371">
       <c r="A371" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -29012,16 +29012,16 @@
         <v>10000</v>
       </c>
       <c r="P371" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Q371" t="n">
+        <v>0</v>
+      </c>
+      <c r="R371" t="n">
+        <v>0</v>
+      </c>
+      <c r="S371" t="n">
         <v>10000</v>
-      </c>
-      <c r="R371" t="n">
-        <v>0</v>
-      </c>
-      <c r="S371" t="n">
-        <v>0</v>
       </c>
       <c r="T371" t="n">
         <v>0</v>
@@ -29032,11 +29032,11 @@
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -29089,16 +29089,16 @@
         <v>15000</v>
       </c>
       <c r="P372" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="Q372" t="n">
+        <v>0</v>
+      </c>
+      <c r="R372" t="n">
+        <v>0</v>
+      </c>
+      <c r="S372" t="n">
         <v>15000</v>
-      </c>
-      <c r="R372" t="n">
-        <v>0</v>
-      </c>
-      <c r="S372" t="n">
-        <v>0</v>
       </c>
       <c r="T372" t="n">
         <v>0</v>
@@ -29109,11 +29109,11 @@
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -29166,16 +29166,16 @@
         <v>15000</v>
       </c>
       <c r="P373" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="Q373" t="n">
+        <v>0</v>
+      </c>
+      <c r="R373" t="n">
+        <v>0</v>
+      </c>
+      <c r="S373" t="n">
         <v>15000</v>
-      </c>
-      <c r="R373" t="n">
-        <v>0</v>
-      </c>
-      <c r="S373" t="n">
-        <v>0</v>
       </c>
       <c r="T373" t="n">
         <v>0</v>
@@ -29186,11 +29186,11 @@
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -29243,16 +29243,16 @@
         <v>15000</v>
       </c>
       <c r="P374" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="Q374" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="R374" t="n">
         <v>0</v>
       </c>
       <c r="S374" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="T374" t="n">
         <v>0</v>
@@ -29263,11 +29263,11 @@
     </row>
     <row r="375">
       <c r="A375" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -29320,16 +29320,16 @@
         <v>15000</v>
       </c>
       <c r="P375" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="Q375" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="R375" t="n">
         <v>0</v>
       </c>
       <c r="S375" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="T375" t="n">
         <v>0</v>
@@ -29340,11 +29340,11 @@
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -29397,16 +29397,16 @@
         <v>20000</v>
       </c>
       <c r="P376" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="Q376" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="R376" t="n">
         <v>10000</v>
       </c>
       <c r="S376" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T376" t="n">
         <v>0</v>
@@ -29417,11 +29417,11 @@
     </row>
     <row r="377">
       <c r="A377" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -29474,16 +29474,16 @@
         <v>20000</v>
       </c>
       <c r="P377" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="Q377" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="R377" t="n">
         <v>10000</v>
       </c>
       <c r="S377" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T377" t="n">
         <v>0</v>
@@ -29494,11 +29494,11 @@
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -29551,16 +29551,16 @@
         <v>20000</v>
       </c>
       <c r="P378" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="Q378" t="n">
+        <v>0</v>
+      </c>
+      <c r="R378" t="n">
+        <v>0</v>
+      </c>
+      <c r="S378" t="n">
         <v>20000</v>
-      </c>
-      <c r="R378" t="n">
-        <v>0</v>
-      </c>
-      <c r="S378" t="n">
-        <v>0</v>
       </c>
       <c r="T378" t="n">
         <v>0</v>
@@ -29571,11 +29571,11 @@
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -29628,16 +29628,16 @@
         <v>20000</v>
       </c>
       <c r="P379" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="Q379" t="n">
+        <v>0</v>
+      </c>
+      <c r="R379" t="n">
+        <v>0</v>
+      </c>
+      <c r="S379" t="n">
         <v>20000</v>
-      </c>
-      <c r="R379" t="n">
-        <v>0</v>
-      </c>
-      <c r="S379" t="n">
-        <v>0</v>
       </c>
       <c r="T379" t="n">
         <v>0</v>
@@ -29648,11 +29648,11 @@
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -29725,11 +29725,11 @@
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -29802,11 +29802,11 @@
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -29879,11 +29879,11 @@
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -29956,11 +29956,11 @@
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -30033,11 +30033,11 @@
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -30110,11 +30110,11 @@
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -30173,10 +30173,10 @@
         <v>-771000</v>
       </c>
       <c r="R386" t="n">
-        <v>930300</v>
+        <v>931000</v>
       </c>
       <c r="S386" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="T386" t="n">
         <v>0</v>
@@ -30187,11 +30187,11 @@
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -30250,10 +30250,10 @@
         <v>2015000</v>
       </c>
       <c r="R387" t="n">
-        <v>1875300</v>
+        <v>1876000</v>
       </c>
       <c r="S387" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="T387" t="n">
         <v>0</v>
@@ -30264,11 +30264,11 @@
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -30341,11 +30341,11 @@
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -30418,11 +30418,11 @@
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -30495,11 +30495,11 @@
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -30572,11 +30572,11 @@
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -30649,11 +30649,11 @@
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -30726,11 +30726,11 @@
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -30803,11 +30803,11 @@
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -30880,11 +30880,11 @@
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -30957,11 +30957,11 @@
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -31034,11 +31034,11 @@
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -31111,11 +31111,11 @@
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -31188,11 +31188,11 @@
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -31265,11 +31265,11 @@
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -31342,11 +31342,11 @@
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -31419,11 +31419,11 @@
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -31496,11 +31496,11 @@
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -31573,11 +31573,11 @@
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -31650,11 +31650,11 @@
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -31727,11 +31727,11 @@
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -31804,11 +31804,11 @@
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -31881,11 +31881,11 @@
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -31958,11 +31958,11 @@
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -32035,11 +32035,11 @@
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -32112,11 +32112,11 @@
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -32189,11 +32189,11 @@
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -32266,11 +32266,11 @@
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -32343,11 +32343,11 @@
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -32420,11 +32420,11 @@
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -32497,11 +32497,11 @@
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -32574,11 +32574,11 @@
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -32651,11 +32651,11 @@
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -32728,11 +32728,11 @@
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -32805,11 +32805,11 @@
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -32882,11 +32882,11 @@
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -32936,13 +32936,13 @@
         <v>817860.0600000001</v>
       </c>
       <c r="O422" t="n">
-        <v>59019.81</v>
+        <v>91019.71000000001</v>
       </c>
       <c r="P422" t="n">
         <v>0</v>
       </c>
       <c r="Q422" t="n">
-        <v>59019.81</v>
+        <v>91019.71000000001</v>
       </c>
       <c r="R422" t="n">
         <v>0</v>
@@ -32954,16 +32954,16 @@
         <v>0</v>
       </c>
       <c r="U422" t="n">
-        <v>758840.25</v>
+        <v>726840.35</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -33013,13 +33013,13 @@
         <v>817860.0600000001</v>
       </c>
       <c r="O423" t="n">
-        <v>59019.81</v>
+        <v>91019.71000000001</v>
       </c>
       <c r="P423" t="n">
         <v>0</v>
       </c>
       <c r="Q423" t="n">
-        <v>59019.81</v>
+        <v>91019.71000000001</v>
       </c>
       <c r="R423" t="n">
         <v>0</v>
@@ -33031,16 +33031,16 @@
         <v>0</v>
       </c>
       <c r="U423" t="n">
-        <v>758840.25</v>
+        <v>726840.35</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -33113,11 +33113,11 @@
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -33190,11 +33190,11 @@
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -33267,11 +33267,11 @@
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -33344,11 +33344,11 @@
     </row>
     <row r="428">
       <c r="A428" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -33421,11 +33421,11 @@
     </row>
     <row r="429">
       <c r="A429" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -33498,11 +33498,11 @@
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -33575,11 +33575,11 @@
     </row>
     <row r="431">
       <c r="A431" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -33652,11 +33652,11 @@
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -33729,11 +33729,11 @@
     </row>
     <row r="433">
       <c r="A433" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -33806,11 +33806,11 @@
     </row>
     <row r="434">
       <c r="A434" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -33883,11 +33883,11 @@
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -33960,11 +33960,11 @@
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -34037,11 +34037,11 @@
     </row>
     <row r="437">
       <c r="A437" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -34114,11 +34114,11 @@
     </row>
     <row r="438">
       <c r="A438" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -34191,11 +34191,11 @@
     </row>
     <row r="439">
       <c r="A439" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -34268,11 +34268,11 @@
     </row>
     <row r="440">
       <c r="A440" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -34345,11 +34345,11 @@
     </row>
     <row r="441">
       <c r="A441" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -34422,11 +34422,11 @@
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -34499,11 +34499,11 @@
     </row>
     <row r="443">
       <c r="A443" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -34576,11 +34576,11 @@
     </row>
     <row r="444">
       <c r="A444" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -34653,11 +34653,11 @@
     </row>
     <row r="445">
       <c r="A445" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -34730,11 +34730,11 @@
     </row>
     <row r="446">
       <c r="A446" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -34807,11 +34807,11 @@
     </row>
     <row r="447">
       <c r="A447" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -34884,11 +34884,11 @@
     </row>
     <row r="448">
       <c r="A448" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -34961,11 +34961,11 @@
     </row>
     <row r="449">
       <c r="A449" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -35024,10 +35024,10 @@
         <v>0</v>
       </c>
       <c r="R449" t="n">
-        <v>6047272.08</v>
+        <v>6144053.69</v>
       </c>
       <c r="S449" t="n">
-        <v>21489777.47</v>
+        <v>21392995.86</v>
       </c>
       <c r="T449" t="n">
         <v>0</v>
@@ -35038,11 +35038,11 @@
     </row>
     <row r="450">
       <c r="A450" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -35101,10 +35101,10 @@
         <v>0</v>
       </c>
       <c r="R450" t="n">
-        <v>60593868.57</v>
+        <v>60690650.18</v>
       </c>
       <c r="S450" t="n">
-        <v>27518687.16</v>
+        <v>27421905.55</v>
       </c>
       <c r="T450" t="n">
         <v>0</v>
@@ -35115,11 +35115,11 @@
     </row>
     <row r="451">
       <c r="A451" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -35192,11 +35192,11 @@
     </row>
     <row r="452">
       <c r="A452" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -35269,11 +35269,11 @@
     </row>
     <row r="453">
       <c r="A453" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -35346,11 +35346,11 @@
     </row>
     <row r="454">
       <c r="A454" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -35423,11 +35423,11 @@
     </row>
     <row r="455">
       <c r="A455" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -35500,11 +35500,11 @@
     </row>
     <row r="456">
       <c r="A456" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -35577,11 +35577,11 @@
     </row>
     <row r="457">
       <c r="A457" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -35654,11 +35654,11 @@
     </row>
     <row r="458">
       <c r="A458" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -35731,11 +35731,11 @@
     </row>
     <row r="459">
       <c r="A459" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -35808,11 +35808,11 @@
     </row>
     <row r="460">
       <c r="A460" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -35885,11 +35885,11 @@
     </row>
     <row r="461">
       <c r="A461" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -35962,11 +35962,11 @@
     </row>
     <row r="462">
       <c r="A462" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -36039,11 +36039,11 @@
     </row>
     <row r="463">
       <c r="A463" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -36116,11 +36116,11 @@
     </row>
     <row r="464">
       <c r="A464" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -36193,11 +36193,11 @@
     </row>
     <row r="465">
       <c r="A465" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -36270,11 +36270,11 @@
     </row>
     <row r="466">
       <c r="A466" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -36347,11 +36347,11 @@
     </row>
     <row r="467">
       <c r="A467" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -36424,11 +36424,11 @@
     </row>
     <row r="468">
       <c r="A468" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -36501,11 +36501,11 @@
     </row>
     <row r="469">
       <c r="A469" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -36578,11 +36578,11 @@
     </row>
     <row r="470">
       <c r="A470" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -36655,11 +36655,11 @@
     </row>
     <row r="471">
       <c r="A471" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -36732,11 +36732,11 @@
     </row>
     <row r="472">
       <c r="A472" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -36809,11 +36809,11 @@
     </row>
     <row r="473">
       <c r="A473" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -36886,11 +36886,11 @@
     </row>
     <row r="474">
       <c r="A474" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -36963,11 +36963,11 @@
     </row>
     <row r="475">
       <c r="A475" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -37040,11 +37040,11 @@
     </row>
     <row r="476">
       <c r="A476" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -37103,10 +37103,10 @@
         <v>0</v>
       </c>
       <c r="R476" t="n">
-        <v>4869001.05</v>
+        <v>4875485.05</v>
       </c>
       <c r="S476" t="n">
-        <v>4339959.46</v>
+        <v>4333475.46</v>
       </c>
       <c r="T476" t="n">
         <v>0</v>
@@ -37117,11 +37117,11 @@
     </row>
     <row r="477">
       <c r="A477" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -37180,10 +37180,10 @@
         <v>0</v>
       </c>
       <c r="R477" t="n">
-        <v>951673.5</v>
+        <v>958157.5</v>
       </c>
       <c r="S477" t="n">
-        <v>3372307.33</v>
+        <v>3365823.33</v>
       </c>
       <c r="T477" t="n">
         <v>0</v>
@@ -37194,11 +37194,11 @@
     </row>
     <row r="478">
       <c r="A478" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -37271,11 +37271,11 @@
     </row>
     <row r="479">
       <c r="A479" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -37348,11 +37348,11 @@
     </row>
     <row r="480">
       <c r="A480" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -37405,16 +37405,16 @@
         <v>526440</v>
       </c>
       <c r="P480" t="n">
-        <v>0</v>
+        <v>34440</v>
       </c>
       <c r="Q480" t="n">
-        <v>526440</v>
+        <v>492000</v>
       </c>
       <c r="R480" t="n">
         <v>0</v>
       </c>
       <c r="S480" t="n">
-        <v>0</v>
+        <v>34440</v>
       </c>
       <c r="T480" t="n">
         <v>0</v>
@@ -37425,11 +37425,11 @@
     </row>
     <row r="481">
       <c r="A481" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -37482,16 +37482,16 @@
         <v>526440</v>
       </c>
       <c r="P481" t="n">
-        <v>0</v>
+        <v>34440</v>
       </c>
       <c r="Q481" t="n">
-        <v>526440</v>
+        <v>492000</v>
       </c>
       <c r="R481" t="n">
         <v>0</v>
       </c>
       <c r="S481" t="n">
-        <v>0</v>
+        <v>34440</v>
       </c>
       <c r="T481" t="n">
         <v>0</v>
@@ -37502,11 +37502,11 @@
     </row>
     <row r="482">
       <c r="A482" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -37579,11 +37579,11 @@
     </row>
     <row r="483">
       <c r="A483" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -37656,11 +37656,11 @@
     </row>
     <row r="484">
       <c r="A484" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -37713,16 +37713,16 @@
         <v>115000</v>
       </c>
       <c r="P484" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="Q484" t="n">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="R484" t="n">
         <v>90000</v>
       </c>
       <c r="S484" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="T484" t="n">
         <v>0</v>
@@ -37733,11 +37733,11 @@
     </row>
     <row r="485">
       <c r="A485" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -37790,16 +37790,16 @@
         <v>115000</v>
       </c>
       <c r="P485" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="Q485" t="n">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="R485" t="n">
         <v>90000</v>
       </c>
       <c r="S485" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="T485" t="n">
         <v>0</v>
@@ -37810,11 +37810,11 @@
     </row>
     <row r="486">
       <c r="A486" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -37887,11 +37887,11 @@
     </row>
     <row r="487">
       <c r="A487" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -37964,11 +37964,11 @@
     </row>
     <row r="488">
       <c r="A488" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -38041,11 +38041,11 @@
     </row>
     <row r="489">
       <c r="A489" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -38118,11 +38118,11 @@
     </row>
     <row r="490">
       <c r="A490" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -38195,11 +38195,11 @@
     </row>
     <row r="491">
       <c r="A491" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -38272,11 +38272,11 @@
     </row>
     <row r="492">
       <c r="A492" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -38349,11 +38349,11 @@
     </row>
     <row r="493">
       <c r="A493" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -38406,16 +38406,16 @@
         <v>4864097.58</v>
       </c>
       <c r="P493" t="n">
-        <v>4568238.88</v>
+        <v>5371584.8</v>
       </c>
       <c r="Q493" t="n">
-        <v>295858.7000000002</v>
+        <v>-507487.2199999997</v>
       </c>
       <c r="R493" t="n">
         <v>6367841.19</v>
       </c>
       <c r="S493" t="n">
-        <v>-1799602.31</v>
+        <v>-996256.39</v>
       </c>
       <c r="T493" t="n">
         <v>9799876.32</v>
@@ -38426,11 +38426,11 @@
     </row>
     <row r="494">
       <c r="A494" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -38483,16 +38483,16 @@
         <v>1242648.49</v>
       </c>
       <c r="P494" t="n">
-        <v>3472275.03</v>
+        <v>3477275.03</v>
       </c>
       <c r="Q494" t="n">
-        <v>-2229626.54</v>
+        <v>-2234626.54</v>
       </c>
       <c r="R494" t="n">
         <v>3957789.63</v>
       </c>
       <c r="S494" t="n">
-        <v>-485514.6</v>
+        <v>-480514.6</v>
       </c>
       <c r="T494" t="n">
         <v>-45600</v>
@@ -38503,11 +38503,11 @@
     </row>
     <row r="495">
       <c r="A495" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -38560,16 +38560,16 @@
         <v>15388887.32</v>
       </c>
       <c r="P495" t="n">
-        <v>5825968.76</v>
+        <v>5830968.76</v>
       </c>
       <c r="Q495" t="n">
-        <v>9562918.560000001</v>
+        <v>9557918.560000001</v>
       </c>
       <c r="R495" t="n">
         <v>4146949.64</v>
       </c>
       <c r="S495" t="n">
-        <v>1679019.12</v>
+        <v>1684019.12</v>
       </c>
       <c r="T495" t="n">
         <v>20000000</v>
@@ -38580,11 +38580,11 @@
     </row>
     <row r="496">
       <c r="A496" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -38657,11 +38657,11 @@
     </row>
     <row r="497">
       <c r="A497" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -38734,11 +38734,11 @@
     </row>
     <row r="498">
       <c r="A498" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -38788,13 +38788,13 @@
         <v>0</v>
       </c>
       <c r="O498" t="n">
-        <v>26500.2</v>
+        <v>29560.2</v>
       </c>
       <c r="P498" t="n">
         <v>1452.6</v>
       </c>
       <c r="Q498" t="n">
-        <v>25047.6</v>
+        <v>28107.6</v>
       </c>
       <c r="R498" t="n">
         <v>372.6</v>
@@ -38806,16 +38806,16 @@
         <v>0</v>
       </c>
       <c r="U498" t="n">
-        <v>-26500.2</v>
+        <v>-29560.2</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -38865,13 +38865,13 @@
         <v>2788800</v>
       </c>
       <c r="O499" t="n">
-        <v>73395.60000000001</v>
+        <v>76455.60000000001</v>
       </c>
       <c r="P499" t="n">
         <v>37452.6</v>
       </c>
       <c r="Q499" t="n">
-        <v>35943.00000000001</v>
+        <v>39003.00000000001</v>
       </c>
       <c r="R499" t="n">
         <v>372.6</v>
@@ -38883,16 +38883,16 @@
         <v>0</v>
       </c>
       <c r="U499" t="n">
-        <v>2715404.4</v>
+        <v>2712344.4</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -38951,10 +38951,10 @@
         <v>-715737.6999999993</v>
       </c>
       <c r="R500" t="n">
-        <v>5627968.5</v>
+        <v>5642753.5</v>
       </c>
       <c r="S500" t="n">
-        <v>3532963.58</v>
+        <v>3518178.58</v>
       </c>
       <c r="T500" t="n">
         <v>0</v>
@@ -38965,11 +38965,11 @@
     </row>
     <row r="501">
       <c r="A501" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -39028,10 +39028,10 @@
         <v>1611724.950000001</v>
       </c>
       <c r="R501" t="n">
-        <v>9733388.800000001</v>
+        <v>9748173.800000001</v>
       </c>
       <c r="S501" t="n">
-        <v>6321109.53</v>
+        <v>6306324.53</v>
       </c>
       <c r="T501" t="n">
         <v>0</v>
@@ -39042,11 +39042,11 @@
     </row>
     <row r="502">
       <c r="A502" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -39119,11 +39119,11 @@
     </row>
     <row r="503">
       <c r="A503" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -39196,11 +39196,11 @@
     </row>
     <row r="504">
       <c r="A504" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -39273,11 +39273,11 @@
     </row>
     <row r="505">
       <c r="A505" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -39350,11 +39350,11 @@
     </row>
     <row r="506">
       <c r="A506" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -39427,11 +39427,11 @@
     </row>
     <row r="507">
       <c r="A507" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -39484,16 +39484,16 @@
         <v>20471388.76</v>
       </c>
       <c r="P507" t="n">
-        <v>10860682.38</v>
+        <v>11664028.3</v>
       </c>
       <c r="Q507" t="n">
-        <v>9610706.380000001</v>
+        <v>8807360.460000001</v>
       </c>
       <c r="R507" t="n">
         <v>9603235.9</v>
       </c>
       <c r="S507" t="n">
-        <v>1257446.48</v>
+        <v>2060792.4</v>
       </c>
       <c r="T507" t="n">
         <v>46382823.26</v>
@@ -39504,11 +39504,11 @@
     </row>
     <row r="508">
       <c r="A508" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -39581,11 +39581,11 @@
     </row>
     <row r="509">
       <c r="A509" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -39658,11 +39658,11 @@
     </row>
     <row r="510">
       <c r="A510" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -39735,11 +39735,11 @@
     </row>
     <row r="511">
       <c r="A511" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -39812,11 +39812,11 @@
     </row>
     <row r="512">
       <c r="A512" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -39889,11 +39889,11 @@
     </row>
     <row r="513">
       <c r="A513" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -39966,11 +39966,11 @@
     </row>
     <row r="514">
       <c r="A514" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -40020,13 +40020,13 @@
         <v>0</v>
       </c>
       <c r="O514" t="n">
-        <v>-133750.05</v>
+        <v>-121714.05</v>
       </c>
       <c r="P514" t="n">
         <v>0</v>
       </c>
       <c r="Q514" t="n">
-        <v>-133750.05</v>
+        <v>-121714.05</v>
       </c>
       <c r="R514" t="n">
         <v>63339.45</v>
@@ -40038,16 +40038,16 @@
         <v>0</v>
       </c>
       <c r="U514" t="n">
-        <v>133750.05</v>
+        <v>121714.05</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -40097,13 +40097,13 @@
         <v>0</v>
       </c>
       <c r="O515" t="n">
-        <v>65144.85</v>
+        <v>77180.85000000001</v>
       </c>
       <c r="P515" t="n">
         <v>63339.45</v>
       </c>
       <c r="Q515" t="n">
-        <v>1805.400000000001</v>
+        <v>13841.40000000001</v>
       </c>
       <c r="R515" t="n">
         <v>63339.45</v>
@@ -40115,16 +40115,16 @@
         <v>0</v>
       </c>
       <c r="U515" t="n">
-        <v>153910.35</v>
+        <v>141874.35</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -40197,11 +40197,11 @@
     </row>
     <row r="517">
       <c r="A517" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -40274,11 +40274,11 @@
     </row>
     <row r="518">
       <c r="A518" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -40328,34 +40328,34 @@
         <v>0</v>
       </c>
       <c r="O518" t="n">
-        <v>74537.5</v>
+        <v>91784</v>
       </c>
       <c r="P518" t="n">
-        <v>66162.5</v>
+        <v>69512.5</v>
       </c>
       <c r="Q518" t="n">
-        <v>8375</v>
+        <v>22271.5</v>
       </c>
       <c r="R518" t="n">
         <v>89780</v>
       </c>
       <c r="S518" t="n">
-        <v>-23617.5</v>
+        <v>-20267.5</v>
       </c>
       <c r="T518" t="n">
         <v>0</v>
       </c>
       <c r="U518" t="n">
-        <v>25462.5</v>
+        <v>8216</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -40405,34 +40405,34 @@
         <v>0</v>
       </c>
       <c r="O519" t="n">
-        <v>137015</v>
+        <v>154261.5</v>
       </c>
       <c r="P519" t="n">
-        <v>120600</v>
+        <v>123950</v>
       </c>
       <c r="Q519" t="n">
-        <v>16415</v>
+        <v>30311.5</v>
       </c>
       <c r="R519" t="n">
         <v>89780</v>
       </c>
       <c r="S519" t="n">
-        <v>30820</v>
+        <v>34170</v>
       </c>
       <c r="T519" t="n">
         <v>0</v>
       </c>
       <c r="U519" t="n">
-        <v>43929.8</v>
+        <v>26683.3</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -40505,11 +40505,11 @@
     </row>
     <row r="521">
       <c r="A521" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -40582,11 +40582,11 @@
     </row>
     <row r="522">
       <c r="A522" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -40659,11 +40659,11 @@
     </row>
     <row r="523">
       <c r="A523" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -40736,11 +40736,11 @@
     </row>
     <row r="524">
       <c r="A524" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -40813,11 +40813,11 @@
     </row>
     <row r="525">
       <c r="A525" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -40890,11 +40890,11 @@
     </row>
     <row r="526">
       <c r="A526" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -40947,16 +40947,16 @@
         <v>15000</v>
       </c>
       <c r="P526" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q526" t="n">
         <v>5000</v>
       </c>
-      <c r="Q526" t="n">
+      <c r="R526" t="n">
+        <v>0</v>
+      </c>
+      <c r="S526" t="n">
         <v>10000</v>
-      </c>
-      <c r="R526" t="n">
-        <v>0</v>
-      </c>
-      <c r="S526" t="n">
-        <v>5000</v>
       </c>
       <c r="T526" t="n">
         <v>0</v>
@@ -40967,11 +40967,11 @@
     </row>
     <row r="527">
       <c r="A527" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -41024,16 +41024,16 @@
         <v>15000</v>
       </c>
       <c r="P527" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q527" t="n">
         <v>5000</v>
       </c>
-      <c r="Q527" t="n">
+      <c r="R527" t="n">
+        <v>0</v>
+      </c>
+      <c r="S527" t="n">
         <v>10000</v>
-      </c>
-      <c r="R527" t="n">
-        <v>0</v>
-      </c>
-      <c r="S527" t="n">
-        <v>5000</v>
       </c>
       <c r="T527" t="n">
         <v>0</v>
@@ -41044,11 +41044,11 @@
     </row>
     <row r="528">
       <c r="A528" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -41101,16 +41101,16 @@
         <v>15000</v>
       </c>
       <c r="P528" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q528" t="n">
         <v>5000</v>
       </c>
-      <c r="Q528" t="n">
+      <c r="R528" t="n">
+        <v>0</v>
+      </c>
+      <c r="S528" t="n">
         <v>10000</v>
-      </c>
-      <c r="R528" t="n">
-        <v>0</v>
-      </c>
-      <c r="S528" t="n">
-        <v>5000</v>
       </c>
       <c r="T528" t="n">
         <v>0</v>
@@ -41121,11 +41121,11 @@
     </row>
     <row r="529">
       <c r="A529" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -41178,16 +41178,16 @@
         <v>15000</v>
       </c>
       <c r="P529" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q529" t="n">
         <v>5000</v>
       </c>
-      <c r="Q529" t="n">
+      <c r="R529" t="n">
+        <v>0</v>
+      </c>
+      <c r="S529" t="n">
         <v>10000</v>
-      </c>
-      <c r="R529" t="n">
-        <v>0</v>
-      </c>
-      <c r="S529" t="n">
-        <v>5000</v>
       </c>
       <c r="T529" t="n">
         <v>0</v>
@@ -41198,11 +41198,11 @@
     </row>
     <row r="530">
       <c r="A530" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -41255,16 +41255,16 @@
         <v>15000</v>
       </c>
       <c r="P530" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q530" t="n">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="R530" t="n">
         <v>0</v>
       </c>
       <c r="S530" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T530" t="n">
         <v>0</v>
@@ -41275,11 +41275,11 @@
     </row>
     <row r="531">
       <c r="A531" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -41332,16 +41332,16 @@
         <v>15000</v>
       </c>
       <c r="P531" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q531" t="n">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="R531" t="n">
         <v>0</v>
       </c>
       <c r="S531" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T531" t="n">
         <v>0</v>
@@ -41352,11 +41352,11 @@
     </row>
     <row r="532">
       <c r="A532" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -41409,16 +41409,16 @@
         <v>10000</v>
       </c>
       <c r="P532" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q532" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="R532" t="n">
         <v>0</v>
       </c>
       <c r="S532" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T532" t="n">
         <v>0</v>
@@ -41429,11 +41429,11 @@
     </row>
     <row r="533">
       <c r="A533" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -41486,16 +41486,16 @@
         <v>10000</v>
       </c>
       <c r="P533" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q533" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="R533" t="n">
         <v>0</v>
       </c>
       <c r="S533" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T533" t="n">
         <v>0</v>
@@ -41506,11 +41506,11 @@
     </row>
     <row r="534">
       <c r="A534" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -41583,11 +41583,11 @@
     </row>
     <row r="535">
       <c r="A535" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -41660,11 +41660,11 @@
     </row>
     <row r="536">
       <c r="A536" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -41737,11 +41737,11 @@
     </row>
     <row r="537">
       <c r="A537" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -41814,11 +41814,11 @@
     </row>
     <row r="538">
       <c r="A538" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -41891,11 +41891,11 @@
     </row>
     <row r="539">
       <c r="A539" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -41968,11 +41968,11 @@
     </row>
     <row r="540">
       <c r="A540" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -42045,11 +42045,11 @@
     </row>
     <row r="541">
       <c r="A541" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -42122,11 +42122,11 @@
     </row>
     <row r="542">
       <c r="A542" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -42199,11 +42199,11 @@
     </row>
     <row r="543">
       <c r="A543" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -42276,11 +42276,11 @@
     </row>
     <row r="544">
       <c r="A544" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -42353,11 +42353,11 @@
     </row>
     <row r="545">
       <c r="A545" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -42430,11 +42430,11 @@
     </row>
     <row r="546">
       <c r="A546" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -42507,11 +42507,11 @@
     </row>
     <row r="547">
       <c r="A547" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -42584,11 +42584,11 @@
     </row>
     <row r="548">
       <c r="A548" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -42661,11 +42661,11 @@
     </row>
     <row r="549">
       <c r="A549" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -42738,11 +42738,11 @@
     </row>
     <row r="550">
       <c r="A550" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -42815,11 +42815,11 @@
     </row>
     <row r="551">
       <c r="A551" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -42892,11 +42892,11 @@
     </row>
     <row r="552">
       <c r="A552" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -42949,16 +42949,16 @@
         <v>148097</v>
       </c>
       <c r="P552" t="n">
-        <v>110558</v>
+        <v>122912</v>
       </c>
       <c r="Q552" t="n">
-        <v>37539</v>
+        <v>25185</v>
       </c>
       <c r="R552" t="n">
         <v>105314</v>
       </c>
       <c r="S552" t="n">
-        <v>5244</v>
+        <v>17598</v>
       </c>
       <c r="T552" t="n">
         <v>0</v>
@@ -42969,11 +42969,11 @@
     </row>
     <row r="553">
       <c r="A553" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -43026,16 +43026,16 @@
         <v>184583</v>
       </c>
       <c r="P553" t="n">
-        <v>147044</v>
+        <v>159398</v>
       </c>
       <c r="Q553" t="n">
-        <v>37539</v>
+        <v>25185</v>
       </c>
       <c r="R553" t="n">
         <v>135326</v>
       </c>
       <c r="S553" t="n">
-        <v>11718</v>
+        <v>24072</v>
       </c>
       <c r="T553" t="n">
         <v>400000</v>
@@ -43046,11 +43046,11 @@
     </row>
     <row r="554">
       <c r="A554" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -43123,11 +43123,11 @@
     </row>
     <row r="555">
       <c r="A555" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -43200,11 +43200,11 @@
     </row>
     <row r="556">
       <c r="A556" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -43277,11 +43277,11 @@
     </row>
     <row r="557">
       <c r="A557" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -43354,11 +43354,11 @@
     </row>
     <row r="558">
       <c r="A558" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -43431,11 +43431,11 @@
     </row>
     <row r="559">
       <c r="A559" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -43508,11 +43508,11 @@
     </row>
     <row r="560">
       <c r="A560" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -43585,11 +43585,11 @@
     </row>
     <row r="561">
       <c r="A561" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -43662,11 +43662,11 @@
     </row>
     <row r="562">
       <c r="A562" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -43739,11 +43739,11 @@
     </row>
     <row r="563">
       <c r="A563" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -43816,11 +43816,11 @@
     </row>
     <row r="564">
       <c r="A564" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -43893,11 +43893,11 @@
     </row>
     <row r="565">
       <c r="A565" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -43970,11 +43970,11 @@
     </row>
     <row r="566">
       <c r="A566" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -44047,11 +44047,11 @@
     </row>
     <row r="567">
       <c r="A567" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -44124,11 +44124,11 @@
     </row>
     <row r="568">
       <c r="A568" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -44201,11 +44201,11 @@
     </row>
     <row r="569">
       <c r="A569" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -44278,11 +44278,11 @@
     </row>
     <row r="570">
       <c r="A570" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -44355,11 +44355,11 @@
     </row>
     <row r="571">
       <c r="A571" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>RELEXORC_30-03-2026.csv</t>
+          <t>RELEXORC_31-03-2026.csv</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -44581,7 +44581,7 @@
         <v>46080</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -44638,10 +44638,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>34440</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>34440</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -44667,7 +44667,7 @@
         <v>46080</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>46080</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -44839,7 +44839,7 @@
         <v>46080</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -44896,10 +44896,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="T5" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -44925,7 +44925,7 @@
         <v>46080</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>46080</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>46080</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -45183,7 +45183,7 @@
         <v>46080</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>46080</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -45326,10 +45326,10 @@
         <v>6292443.5</v>
       </c>
       <c r="S10" t="n">
-        <v>10860682.38</v>
+        <v>11664028.3</v>
       </c>
       <c r="T10" t="n">
-        <v>4568238.880000001</v>
+        <v>5371584.800000001</v>
       </c>
       <c r="U10" t="n">
         <v>3235394.71</v>
@@ -45355,7 +45355,7 @@
         <v>46080</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -45412,10 +45412,10 @@
         <v>2353693.73</v>
       </c>
       <c r="S11" t="n">
-        <v>5825968.76</v>
+        <v>5830968.76</v>
       </c>
       <c r="T11" t="n">
-        <v>3472275.03</v>
+        <v>3477275.03</v>
       </c>
       <c r="U11" t="n">
         <v>189160.01</v>
@@ -45441,7 +45441,7 @@
         <v>46080</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>46080</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -45575,10 +45575,10 @@
         <v>43977.6</v>
       </c>
       <c r="P13" t="n">
-        <v>73395.60000000001</v>
+        <v>76455.60000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>29418.00000000001</v>
+        <v>32478.00000000001</v>
       </c>
       <c r="R13" t="n">
         <v>36000</v>
@@ -45602,10 +45602,10 @@
         <v>2744822.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>2715404.4</v>
+        <v>2712344.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>-29418</v>
+        <v>-32478</v>
       </c>
     </row>
     <row r="14">
@@ -45613,7 +45613,7 @@
         <v>46080</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -45679,10 +45679,10 @@
         <v>4105420.3</v>
       </c>
       <c r="V14" t="n">
-        <v>9733388.800000001</v>
+        <v>9748173.800000001</v>
       </c>
       <c r="W14" t="n">
-        <v>5627968.500000001</v>
+        <v>5642753.500000001</v>
       </c>
       <c r="X14" t="n">
         <v>10048569.13</v>
@@ -45699,7 +45699,7 @@
         <v>46080</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -45785,7 +45785,7 @@
         <v>46080</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>46080</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -45957,7 +45957,7 @@
         <v>46080</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -46043,7 +46043,7 @@
         <v>46080</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -46109,10 +46109,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>4869001.05</v>
+        <v>4875485.05</v>
       </c>
       <c r="W19" t="n">
-        <v>4869001.05</v>
+        <v>4875485.05</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -46129,7 +46129,7 @@
         <v>46080</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -46215,7 +46215,7 @@
         <v>46080</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -46281,10 +46281,10 @@
         <v>54525368.63</v>
       </c>
       <c r="V21" t="n">
-        <v>60593868.57</v>
+        <v>60690650.18</v>
       </c>
       <c r="W21" t="n">
-        <v>6068499.939999998</v>
+        <v>6165281.549999997</v>
       </c>
       <c r="X21" t="n">
         <v>305981836.82</v>
@@ -46301,7 +46301,7 @@
         <v>46080</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -46387,7 +46387,7 @@
         <v>46080</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>46080</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -46559,7 +46559,7 @@
         <v>46080</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -46645,7 +46645,7 @@
         <v>46080</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>46080</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>46080</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -46903,7 +46903,7 @@
         <v>46080</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>46080</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -47075,7 +47075,7 @@
         <v>46080</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>46080</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>46080</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -47333,7 +47333,7 @@
         <v>46080</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -47419,7 +47419,7 @@
         <v>46080</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>46080</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -47591,7 +47591,7 @@
         <v>46080</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>46080</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -47763,7 +47763,7 @@
         <v>46080</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>46080</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -47935,7 +47935,7 @@
         <v>46080</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>46080</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -48107,7 +48107,7 @@
         <v>46080</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -48164,10 +48164,10 @@
         <v>36486</v>
       </c>
       <c r="S43" t="n">
-        <v>147044</v>
+        <v>159398</v>
       </c>
       <c r="T43" t="n">
-        <v>110558</v>
+        <v>122912</v>
       </c>
       <c r="U43" t="n">
         <v>30012</v>
@@ -48193,7 +48193,7 @@
         <v>46080</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -48279,7 +48279,7 @@
         <v>46080</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>46080</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -48451,7 +48451,7 @@
         <v>46080</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -48537,7 +48537,7 @@
         <v>46080</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -48623,7 +48623,7 @@
         <v>46080</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -48709,7 +48709,7 @@
         <v>46080</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -48795,7 +48795,7 @@
         <v>46080</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -48881,7 +48881,7 @@
         <v>46080</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -48967,7 +48967,7 @@
         <v>46080</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>46080</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>46080</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -49225,7 +49225,7 @@
         <v>46080</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -49311,7 +49311,7 @@
         <v>46080</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>46080</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -49445,10 +49445,10 @@
         <v>198894.9</v>
       </c>
       <c r="P58" t="n">
-        <v>65144.85</v>
+        <v>77180.85000000001</v>
       </c>
       <c r="Q58" t="n">
-        <v>-133750.05</v>
+        <v>-121714.05</v>
       </c>
       <c r="R58" t="n">
         <v>198894.9</v>
@@ -49472,10 +49472,10 @@
         <v>20160.3</v>
       </c>
       <c r="Y58" t="n">
-        <v>153910.35</v>
+        <v>141874.35</v>
       </c>
       <c r="Z58" t="n">
-        <v>133750.05</v>
+        <v>121714.05</v>
       </c>
     </row>
     <row r="59">
@@ -49483,7 +49483,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -49569,7 +49569,7 @@
         <v>46080</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -49617,19 +49617,19 @@
         <v>62477.5</v>
       </c>
       <c r="P60" t="n">
-        <v>137015</v>
+        <v>154261.5</v>
       </c>
       <c r="Q60" t="n">
-        <v>74537.5</v>
+        <v>91784</v>
       </c>
       <c r="R60" t="n">
         <v>54437.5</v>
       </c>
       <c r="S60" t="n">
-        <v>120600</v>
+        <v>123950</v>
       </c>
       <c r="T60" t="n">
-        <v>66162.5</v>
+        <v>69512.5</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -49644,10 +49644,10 @@
         <v>18467.3</v>
       </c>
       <c r="Y60" t="n">
-        <v>43929.8</v>
+        <v>26683.3</v>
       </c>
       <c r="Z60" t="n">
-        <v>25462.5</v>
+        <v>8216</v>
       </c>
     </row>
     <row r="61">
@@ -49655,7 +49655,7 @@
         <v>46080</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -49741,7 +49741,7 @@
         <v>46080</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>46080</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         <v>46080</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -49970,10 +49970,10 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="T64" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -49999,7 +49999,7 @@
         <v>46080</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -50056,10 +50056,10 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="T65" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -50085,7 +50085,7 @@
         <v>46080</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -50142,10 +50142,10 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -50171,7 +50171,7 @@
         <v>46080</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -50228,10 +50228,10 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -50257,7 +50257,7 @@
         <v>46080</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -50343,7 +50343,7 @@
         <v>46080</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>46080</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -50515,7 +50515,7 @@
         <v>46080</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -50601,7 +50601,7 @@
         <v>46080</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -50687,7 +50687,7 @@
         <v>46080</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>339030 - Material de Consumo</t>
+          <t>33903089 - Material de Consumo</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -50744,10 +50744,10 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
@@ -50773,7 +50773,7 @@
         <v>46080</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -50859,7 +50859,7 @@
         <v>46080</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -50945,7 +50945,7 @@
         <v>46080</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -51031,7 +51031,7 @@
         <v>46080</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -51117,7 +51117,7 @@
         <v>46080</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -51203,7 +51203,7 @@
         <v>46080</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -51289,7 +51289,7 @@
         <v>46080</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -51346,10 +51346,10 @@
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="T80" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -51375,7 +51375,7 @@
         <v>46080</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -51432,10 +51432,10 @@
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -51461,7 +51461,7 @@
         <v>46080</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -51518,10 +51518,10 @@
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -51547,7 +51547,7 @@
         <v>46080</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -51604,10 +51604,10 @@
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="T83" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -51633,7 +51633,7 @@
         <v>46080</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -51690,10 +51690,10 @@
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="T84" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
@@ -51719,7 +51719,7 @@
         <v>46080</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -51776,10 +51776,10 @@
         <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="U85" t="n">
         <v>0</v>
@@ -51805,7 +51805,7 @@
         <v>46080</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>46080</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -51977,7 +51977,7 @@
         <v>46080</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -52063,7 +52063,7 @@
         <v>46080</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -52111,10 +52111,10 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>9418</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>9418</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
@@ -52138,10 +52138,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>9418</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>9418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -52149,7 +52149,7 @@
         <v>46080</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>46080</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -52321,7 +52321,7 @@
         <v>46080</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -52407,7 +52407,7 @@
         <v>46080</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -52493,7 +52493,7 @@
         <v>46080</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>46080</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -52636,10 +52636,10 @@
         <v>286800</v>
       </c>
       <c r="S95" t="n">
-        <v>555600</v>
+        <v>809600</v>
       </c>
       <c r="T95" t="n">
-        <v>268800</v>
+        <v>522800</v>
       </c>
       <c r="U95" t="n">
         <v>256100</v>
@@ -52665,7 +52665,7 @@
         <v>46080</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -52751,7 +52751,7 @@
         <v>46080</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -52817,10 +52817,10 @@
         <v>56000</v>
       </c>
       <c r="V97" t="n">
-        <v>115857</v>
+        <v>114857</v>
       </c>
       <c r="W97" t="n">
-        <v>59857</v>
+        <v>58857</v>
       </c>
       <c r="X97" t="n">
         <v>521714.5</v>
@@ -52837,7 +52837,7 @@
         <v>46080</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -52923,7 +52923,7 @@
         <v>46080</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>46080</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -53095,7 +53095,7 @@
         <v>46080</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -53181,7 +53181,7 @@
         <v>46080</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -53267,7 +53267,7 @@
         <v>46080</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -53353,7 +53353,7 @@
         <v>46080</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -53439,7 +53439,7 @@
         <v>46080</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -53525,7 +53525,7 @@
         <v>46080</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -53611,7 +53611,7 @@
         <v>46080</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -53659,10 +53659,10 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>59019.81</v>
+        <v>91019.71000000001</v>
       </c>
       <c r="Q107" t="n">
-        <v>59019.81</v>
+        <v>91019.71000000001</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
@@ -53686,10 +53686,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>758840.25</v>
+        <v>726840.35</v>
       </c>
       <c r="Z107" t="n">
-        <v>758840.25</v>
+        <v>726840.35</v>
       </c>
     </row>
     <row r="108">
@@ -53697,7 +53697,7 @@
         <v>46080</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -53783,7 +53783,7 @@
         <v>46080</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -53869,7 +53869,7 @@
         <v>46080</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -53955,7 +53955,7 @@
         <v>46080</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -54041,7 +54041,7 @@
         <v>46080</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -54127,7 +54127,7 @@
         <v>46080</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>46080</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -54299,7 +54299,7 @@
         <v>46080</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -54385,7 +54385,7 @@
         <v>46080</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -54471,7 +54471,7 @@
         <v>46080</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -54557,7 +54557,7 @@
         <v>46080</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -54643,7 +54643,7 @@
         <v>46080</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -54729,7 +54729,7 @@
         <v>46080</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -54815,7 +54815,7 @@
         <v>46080</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -54901,7 +54901,7 @@
         <v>46080</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -54967,10 +54967,10 @@
         <v>945000</v>
       </c>
       <c r="V122" t="n">
-        <v>1875300</v>
+        <v>1876000</v>
       </c>
       <c r="W122" t="n">
-        <v>930300</v>
+        <v>931000</v>
       </c>
       <c r="X122" t="n">
         <v>8269000</v>
@@ -54987,7 +54987,7 @@
         <v>46080</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -55073,7 +55073,7 @@
         <v>46080</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -55159,7 +55159,7 @@
         <v>46080</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>46080</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -55331,7 +55331,7 @@
         <v>46080</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -55417,7 +55417,7 @@
         <v>46080</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -55503,7 +55503,7 @@
         <v>46080</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -55589,7 +55589,7 @@
         <v>46080</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -55675,7 +55675,7 @@
         <v>46080</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -55761,7 +55761,7 @@
         <v>46080</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -55847,7 +55847,7 @@
         <v>46080</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -55933,7 +55933,7 @@
         <v>46080</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -56019,7 +56019,7 @@
         <v>46080</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -56105,7 +56105,7 @@
         <v>46080</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>

--- a/Base_Consolidada_SIAFI.xlsx
+++ b/Base_Consolidada_SIAFI.xlsx
@@ -44432,11 +44432,11 @@
     </row>
     <row r="572">
       <c r="A572" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -44509,11 +44509,11 @@
     </row>
     <row r="573">
       <c r="A573" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -44586,11 +44586,11 @@
     </row>
     <row r="574">
       <c r="A574" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -44663,11 +44663,11 @@
     </row>
     <row r="575">
       <c r="A575" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -44740,11 +44740,11 @@
     </row>
     <row r="576">
       <c r="A576" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -44817,11 +44817,11 @@
     </row>
     <row r="577">
       <c r="A577" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -44894,11 +44894,11 @@
     </row>
     <row r="578">
       <c r="A578" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -44971,11 +44971,11 @@
     </row>
     <row r="579">
       <c r="A579" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -45048,11 +45048,11 @@
     </row>
     <row r="580">
       <c r="A580" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -45125,11 +45125,11 @@
     </row>
     <row r="581">
       <c r="A581" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -45202,11 +45202,11 @@
     </row>
     <row r="582">
       <c r="A582" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -45279,11 +45279,11 @@
     </row>
     <row r="583">
       <c r="A583" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -45356,11 +45356,11 @@
     </row>
     <row r="584">
       <c r="A584" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -45433,11 +45433,11 @@
     </row>
     <row r="585">
       <c r="A585" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -45510,11 +45510,11 @@
     </row>
     <row r="586">
       <c r="A586" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -45587,11 +45587,11 @@
     </row>
     <row r="587">
       <c r="A587" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -45664,11 +45664,11 @@
     </row>
     <row r="588">
       <c r="A588" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -45741,11 +45741,11 @@
     </row>
     <row r="589">
       <c r="A589" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -45818,11 +45818,11 @@
     </row>
     <row r="590">
       <c r="A590" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -45895,11 +45895,11 @@
     </row>
     <row r="591">
       <c r="A591" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -45972,11 +45972,11 @@
     </row>
     <row r="592">
       <c r="A592" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -46049,11 +46049,11 @@
     </row>
     <row r="593">
       <c r="A593" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -46126,11 +46126,11 @@
     </row>
     <row r="594">
       <c r="A594" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -46203,11 +46203,11 @@
     </row>
     <row r="595">
       <c r="A595" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -46280,11 +46280,11 @@
     </row>
     <row r="596">
       <c r="A596" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -46357,11 +46357,11 @@
     </row>
     <row r="597">
       <c r="A597" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -46434,11 +46434,11 @@
     </row>
     <row r="598">
       <c r="A598" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -46511,11 +46511,11 @@
     </row>
     <row r="599">
       <c r="A599" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -46588,11 +46588,11 @@
     </row>
     <row r="600">
       <c r="A600" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -46665,11 +46665,11 @@
     </row>
     <row r="601">
       <c r="A601" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -46742,11 +46742,11 @@
     </row>
     <row r="602">
       <c r="A602" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -46819,11 +46819,11 @@
     </row>
     <row r="603">
       <c r="A603" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -46896,11 +46896,11 @@
     </row>
     <row r="604">
       <c r="A604" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -46973,11 +46973,11 @@
     </row>
     <row r="605">
       <c r="A605" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -47050,11 +47050,11 @@
     </row>
     <row r="606">
       <c r="A606" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -47127,11 +47127,11 @@
     </row>
     <row r="607">
       <c r="A607" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -47204,11 +47204,11 @@
     </row>
     <row r="608">
       <c r="A608" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -47281,11 +47281,11 @@
     </row>
     <row r="609">
       <c r="A609" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -47358,11 +47358,11 @@
     </row>
     <row r="610">
       <c r="A610" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -47435,11 +47435,11 @@
     </row>
     <row r="611">
       <c r="A611" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -47512,11 +47512,11 @@
     </row>
     <row r="612">
       <c r="A612" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -47589,11 +47589,11 @@
     </row>
     <row r="613">
       <c r="A613" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -47666,11 +47666,11 @@
     </row>
     <row r="614">
       <c r="A614" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -47743,11 +47743,11 @@
     </row>
     <row r="615">
       <c r="A615" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -47820,11 +47820,11 @@
     </row>
     <row r="616">
       <c r="A616" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -47897,11 +47897,11 @@
     </row>
     <row r="617">
       <c r="A617" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -47974,11 +47974,11 @@
     </row>
     <row r="618">
       <c r="A618" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -48051,11 +48051,11 @@
     </row>
     <row r="619">
       <c r="A619" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -48128,11 +48128,11 @@
     </row>
     <row r="620">
       <c r="A620" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -48205,11 +48205,11 @@
     </row>
     <row r="621">
       <c r="A621" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -48282,11 +48282,11 @@
     </row>
     <row r="622">
       <c r="A622" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -48359,11 +48359,11 @@
     </row>
     <row r="623">
       <c r="A623" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -48436,11 +48436,11 @@
     </row>
     <row r="624">
       <c r="A624" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -48513,11 +48513,11 @@
     </row>
     <row r="625">
       <c r="A625" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -48590,11 +48590,11 @@
     </row>
     <row r="626">
       <c r="A626" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -48667,11 +48667,11 @@
     </row>
     <row r="627">
       <c r="A627" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -48744,11 +48744,11 @@
     </row>
     <row r="628">
       <c r="A628" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -48821,11 +48821,11 @@
     </row>
     <row r="629">
       <c r="A629" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -48898,11 +48898,11 @@
     </row>
     <row r="630">
       <c r="A630" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -48975,11 +48975,11 @@
     </row>
     <row r="631">
       <c r="A631" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -49052,11 +49052,11 @@
     </row>
     <row r="632">
       <c r="A632" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -49129,11 +49129,11 @@
     </row>
     <row r="633">
       <c r="A633" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -49206,11 +49206,11 @@
     </row>
     <row r="634">
       <c r="A634" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -49283,11 +49283,11 @@
     </row>
     <row r="635">
       <c r="A635" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -49360,11 +49360,11 @@
     </row>
     <row r="636">
       <c r="A636" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -49437,11 +49437,11 @@
     </row>
     <row r="637">
       <c r="A637" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -49514,11 +49514,11 @@
     </row>
     <row r="638">
       <c r="A638" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -49591,11 +49591,11 @@
     </row>
     <row r="639">
       <c r="A639" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -49668,11 +49668,11 @@
     </row>
     <row r="640">
       <c r="A640" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -49745,11 +49745,11 @@
     </row>
     <row r="641">
       <c r="A641" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -49822,11 +49822,11 @@
     </row>
     <row r="642">
       <c r="A642" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -49899,11 +49899,11 @@
     </row>
     <row r="643">
       <c r="A643" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -49976,11 +49976,11 @@
     </row>
     <row r="644">
       <c r="A644" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -50053,11 +50053,11 @@
     </row>
     <row r="645">
       <c r="A645" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -50130,11 +50130,11 @@
     </row>
     <row r="646">
       <c r="A646" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -50207,11 +50207,11 @@
     </row>
     <row r="647">
       <c r="A647" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -50284,11 +50284,11 @@
     </row>
     <row r="648">
       <c r="A648" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -50361,11 +50361,11 @@
     </row>
     <row r="649">
       <c r="A649" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -50438,11 +50438,11 @@
     </row>
     <row r="650">
       <c r="A650" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -50515,11 +50515,11 @@
     </row>
     <row r="651">
       <c r="A651" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -50592,11 +50592,11 @@
     </row>
     <row r="652">
       <c r="A652" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -50669,11 +50669,11 @@
     </row>
     <row r="653">
       <c r="A653" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -50746,11 +50746,11 @@
     </row>
     <row r="654">
       <c r="A654" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -50823,11 +50823,11 @@
     </row>
     <row r="655">
       <c r="A655" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -50900,11 +50900,11 @@
     </row>
     <row r="656">
       <c r="A656" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -50977,11 +50977,11 @@
     </row>
     <row r="657">
       <c r="A657" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -51054,11 +51054,11 @@
     </row>
     <row r="658">
       <c r="A658" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -51131,11 +51131,11 @@
     </row>
     <row r="659">
       <c r="A659" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -51188,16 +51188,16 @@
         <v>0</v>
       </c>
       <c r="P659" t="n">
-        <v>525588</v>
+        <v>777587.2</v>
       </c>
       <c r="Q659" t="n">
-        <v>-525588</v>
+        <v>-777587.2</v>
       </c>
       <c r="R659" t="n">
         <v>0</v>
       </c>
       <c r="S659" t="n">
-        <v>525588</v>
+        <v>777587.2</v>
       </c>
       <c r="T659" t="n">
         <v>0</v>
@@ -51208,11 +51208,11 @@
     </row>
     <row r="660">
       <c r="A660" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -51285,11 +51285,11 @@
     </row>
     <row r="661">
       <c r="A661" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -51362,11 +51362,11 @@
     </row>
     <row r="662">
       <c r="A662" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -51439,11 +51439,11 @@
     </row>
     <row r="663">
       <c r="A663" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -51516,11 +51516,11 @@
     </row>
     <row r="664">
       <c r="A664" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -51593,11 +51593,11 @@
     </row>
     <row r="665">
       <c r="A665" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -51670,11 +51670,11 @@
     </row>
     <row r="666">
       <c r="A666" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -51747,11 +51747,11 @@
     </row>
     <row r="667">
       <c r="A667" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -51824,11 +51824,11 @@
     </row>
     <row r="668">
       <c r="A668" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -51901,11 +51901,11 @@
     </row>
     <row r="669">
       <c r="A669" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -51978,11 +51978,11 @@
     </row>
     <row r="670">
       <c r="A670" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -52055,11 +52055,11 @@
     </row>
     <row r="671">
       <c r="A671" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -52132,11 +52132,11 @@
     </row>
     <row r="672">
       <c r="A672" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -52209,11 +52209,11 @@
     </row>
     <row r="673">
       <c r="A673" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -52286,11 +52286,11 @@
     </row>
     <row r="674">
       <c r="A674" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -52363,11 +52363,11 @@
     </row>
     <row r="675">
       <c r="A675" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -52440,11 +52440,11 @@
     </row>
     <row r="676">
       <c r="A676" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -52517,11 +52517,11 @@
     </row>
     <row r="677">
       <c r="A677" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -52594,11 +52594,11 @@
     </row>
     <row r="678">
       <c r="A678" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -52671,11 +52671,11 @@
     </row>
     <row r="679">
       <c r="A679" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -52748,11 +52748,11 @@
     </row>
     <row r="680">
       <c r="A680" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -52825,11 +52825,11 @@
     </row>
     <row r="681">
       <c r="A681" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -52902,11 +52902,11 @@
     </row>
     <row r="682">
       <c r="A682" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -52979,11 +52979,11 @@
     </row>
     <row r="683">
       <c r="A683" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -53056,11 +53056,11 @@
     </row>
     <row r="684">
       <c r="A684" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -53133,11 +53133,11 @@
     </row>
     <row r="685">
       <c r="A685" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -53210,11 +53210,11 @@
     </row>
     <row r="686">
       <c r="A686" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -53287,11 +53287,11 @@
     </row>
     <row r="687">
       <c r="A687" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -53364,11 +53364,11 @@
     </row>
     <row r="688">
       <c r="A688" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -53441,11 +53441,11 @@
     </row>
     <row r="689">
       <c r="A689" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -53518,11 +53518,11 @@
     </row>
     <row r="690">
       <c r="A690" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -53595,11 +53595,11 @@
     </row>
     <row r="691">
       <c r="A691" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -53672,11 +53672,11 @@
     </row>
     <row r="692">
       <c r="A692" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -53749,11 +53749,11 @@
     </row>
     <row r="693">
       <c r="A693" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -53826,11 +53826,11 @@
     </row>
     <row r="694">
       <c r="A694" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -53903,11 +53903,11 @@
     </row>
     <row r="695">
       <c r="A695" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -53980,11 +53980,11 @@
     </row>
     <row r="696">
       <c r="A696" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -54057,11 +54057,11 @@
     </row>
     <row r="697">
       <c r="A697" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -54134,11 +54134,11 @@
     </row>
     <row r="698">
       <c r="A698" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -54211,11 +54211,11 @@
     </row>
     <row r="699">
       <c r="A699" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -54274,10 +54274,10 @@
         <v>0</v>
       </c>
       <c r="R699" t="n">
-        <v>6531423.23</v>
+        <v>6550089.63</v>
       </c>
       <c r="S699" t="n">
-        <v>2677537.28</v>
+        <v>2658870.88</v>
       </c>
       <c r="T699" t="n">
         <v>0</v>
@@ -54288,11 +54288,11 @@
     </row>
     <row r="700">
       <c r="A700" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -54365,11 +54365,11 @@
     </row>
     <row r="701">
       <c r="A701" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -54442,11 +54442,11 @@
     </row>
     <row r="702">
       <c r="A702" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -54505,10 +54505,10 @@
         <v>0</v>
       </c>
       <c r="R702" t="n">
-        <v>17080063.73</v>
+        <v>18916647.74</v>
       </c>
       <c r="S702" t="n">
-        <v>-17080063.73</v>
+        <v>-18916647.74</v>
       </c>
       <c r="T702" t="n">
         <v>0</v>
@@ -54519,11 +54519,11 @@
     </row>
     <row r="703">
       <c r="A703" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -54582,10 +54582,10 @@
         <v>0</v>
       </c>
       <c r="R703" t="n">
-        <v>77798582.09999999</v>
+        <v>79635166.11</v>
       </c>
       <c r="S703" t="n">
-        <v>10313973.63</v>
+        <v>8477389.619999999</v>
       </c>
       <c r="T703" t="n">
         <v>0</v>
@@ -54596,11 +54596,11 @@
     </row>
     <row r="704">
       <c r="A704" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -54673,11 +54673,11 @@
     </row>
     <row r="705">
       <c r="A705" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -54750,11 +54750,11 @@
     </row>
     <row r="706">
       <c r="A706" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -54827,11 +54827,11 @@
     </row>
     <row r="707">
       <c r="A707" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -54904,11 +54904,11 @@
     </row>
     <row r="708">
       <c r="A708" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -54981,11 +54981,11 @@
     </row>
     <row r="709">
       <c r="A709" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -55058,11 +55058,11 @@
     </row>
     <row r="710">
       <c r="A710" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -55135,11 +55135,11 @@
     </row>
     <row r="711">
       <c r="A711" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -55212,11 +55212,11 @@
     </row>
     <row r="712">
       <c r="A712" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -55289,11 +55289,11 @@
     </row>
     <row r="713">
       <c r="A713" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -55366,11 +55366,11 @@
     </row>
     <row r="714">
       <c r="A714" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -55443,11 +55443,11 @@
     </row>
     <row r="715">
       <c r="A715" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -55520,11 +55520,11 @@
     </row>
     <row r="716">
       <c r="A716" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -55597,11 +55597,11 @@
     </row>
     <row r="717">
       <c r="A717" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -55674,11 +55674,11 @@
     </row>
     <row r="718">
       <c r="A718" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -55751,11 +55751,11 @@
     </row>
     <row r="719">
       <c r="A719" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -55828,11 +55828,11 @@
     </row>
     <row r="720">
       <c r="A720" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -55905,11 +55905,11 @@
     </row>
     <row r="721">
       <c r="A721" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -55982,11 +55982,11 @@
     </row>
     <row r="722">
       <c r="A722" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -56059,11 +56059,11 @@
     </row>
     <row r="723">
       <c r="A723" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -56136,11 +56136,11 @@
     </row>
     <row r="724">
       <c r="A724" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -56213,11 +56213,11 @@
     </row>
     <row r="725">
       <c r="A725" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -56290,11 +56290,11 @@
     </row>
     <row r="726">
       <c r="A726" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -56353,10 +56353,10 @@
         <v>0</v>
       </c>
       <c r="R726" t="n">
-        <v>1635583.23</v>
+        <v>1654249.63</v>
       </c>
       <c r="S726" t="n">
-        <v>-1635583.23</v>
+        <v>-1654249.63</v>
       </c>
       <c r="T726" t="n">
         <v>0</v>
@@ -56367,11 +56367,11 @@
     </row>
     <row r="727">
       <c r="A727" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -56444,11 +56444,11 @@
     </row>
     <row r="728">
       <c r="A728" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -56521,11 +56521,11 @@
     </row>
     <row r="729">
       <c r="A729" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -56598,11 +56598,11 @@
     </row>
     <row r="730">
       <c r="A730" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -56675,11 +56675,11 @@
     </row>
     <row r="731">
       <c r="A731" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -56752,11 +56752,11 @@
     </row>
     <row r="732">
       <c r="A732" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -56829,11 +56829,11 @@
     </row>
     <row r="733">
       <c r="A733" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -56906,11 +56906,11 @@
     </row>
     <row r="734">
       <c r="A734" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -56983,11 +56983,11 @@
     </row>
     <row r="735">
       <c r="A735" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -57060,11 +57060,11 @@
     </row>
     <row r="736">
       <c r="A736" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -57137,11 +57137,11 @@
     </row>
     <row r="737">
       <c r="A737" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -57214,11 +57214,11 @@
     </row>
     <row r="738">
       <c r="A738" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -57291,11 +57291,11 @@
     </row>
     <row r="739">
       <c r="A739" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -57368,11 +57368,11 @@
     </row>
     <row r="740">
       <c r="A740" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -57445,11 +57445,11 @@
     </row>
     <row r="741">
       <c r="A741" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -57522,11 +57522,11 @@
     </row>
     <row r="742">
       <c r="A742" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -57599,11 +57599,11 @@
     </row>
     <row r="743">
       <c r="A743" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -57676,11 +57676,11 @@
     </row>
     <row r="744">
       <c r="A744" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -57753,11 +57753,11 @@
     </row>
     <row r="745">
       <c r="A745" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -57810,16 +57810,16 @@
         <v>0</v>
       </c>
       <c r="P745" t="n">
-        <v>0</v>
+        <v>2432048.79</v>
       </c>
       <c r="Q745" t="n">
-        <v>0</v>
+        <v>-2432048.79</v>
       </c>
       <c r="R745" t="n">
         <v>0</v>
       </c>
       <c r="S745" t="n">
-        <v>0</v>
+        <v>2432048.79</v>
       </c>
       <c r="T745" t="n">
         <v>0</v>
@@ -57830,11 +57830,11 @@
     </row>
     <row r="746">
       <c r="A746" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -57887,16 +57887,16 @@
         <v>20471388.76</v>
       </c>
       <c r="P746" t="n">
-        <v>11664028.3</v>
+        <v>14096077.09</v>
       </c>
       <c r="Q746" t="n">
-        <v>8807360.460000001</v>
+        <v>6375311.670000002</v>
       </c>
       <c r="R746" t="n">
         <v>9603235.9</v>
       </c>
       <c r="S746" t="n">
-        <v>2060792.4</v>
+        <v>4492841.19</v>
       </c>
       <c r="T746" t="n">
         <v>46382823.26</v>
@@ -57907,11 +57907,11 @@
     </row>
     <row r="747">
       <c r="A747" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -57970,10 +57970,10 @@
         <v>-15000</v>
       </c>
       <c r="R747" t="n">
-        <v>0</v>
+        <v>221030.41</v>
       </c>
       <c r="S747" t="n">
-        <v>15000</v>
+        <v>-206030.41</v>
       </c>
       <c r="T747" t="n">
         <v>7222950.51</v>
@@ -57984,11 +57984,11 @@
     </row>
     <row r="748">
       <c r="A748" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -58047,10 +58047,10 @@
         <v>9542918.560000001</v>
       </c>
       <c r="R748" t="n">
-        <v>4146949.64</v>
+        <v>4367980.05</v>
       </c>
       <c r="S748" t="n">
-        <v>1699019.12</v>
+        <v>1477988.71</v>
       </c>
       <c r="T748" t="n">
         <v>27222950.51</v>
@@ -58061,11 +58061,11 @@
     </row>
     <row r="749">
       <c r="A749" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -58130,19 +58130,19 @@
         <v>0</v>
       </c>
       <c r="T749" t="n">
-        <v>0</v>
+        <v>2483827.05</v>
       </c>
       <c r="U749" t="n">
-        <v>0</v>
+        <v>-2483827.05</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -58207,19 +58207,19 @@
         <v>5389734.24</v>
       </c>
       <c r="T750" t="n">
-        <v>44414000</v>
+        <v>46897827.05</v>
       </c>
       <c r="U750" t="n">
-        <v>30208318.24</v>
+        <v>27724491.19</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -58272,16 +58272,16 @@
         <v>0</v>
       </c>
       <c r="P751" t="n">
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="Q751" t="n">
-        <v>0</v>
+        <v>-1080</v>
       </c>
       <c r="R751" t="n">
         <v>0</v>
       </c>
       <c r="S751" t="n">
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="T751" t="n">
         <v>0</v>
@@ -58292,11 +58292,11 @@
     </row>
     <row r="752">
       <c r="A752" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -58349,16 +58349,16 @@
         <v>76455.60000000001</v>
       </c>
       <c r="P752" t="n">
-        <v>37452.6</v>
+        <v>38532.6</v>
       </c>
       <c r="Q752" t="n">
-        <v>39003.00000000001</v>
+        <v>37923.00000000001</v>
       </c>
       <c r="R752" t="n">
         <v>372.6</v>
       </c>
       <c r="S752" t="n">
-        <v>37080</v>
+        <v>38160</v>
       </c>
       <c r="T752" t="n">
         <v>0</v>
@@ -58369,11 +58369,11 @@
     </row>
     <row r="753">
       <c r="A753" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -58426,16 +58426,16 @@
         <v>0</v>
       </c>
       <c r="P753" t="n">
-        <v>1342155.6</v>
+        <v>1611724.95</v>
       </c>
       <c r="Q753" t="n">
-        <v>-1342155.6</v>
+        <v>-1611724.95</v>
       </c>
       <c r="R753" t="n">
         <v>0</v>
       </c>
       <c r="S753" t="n">
-        <v>1342155.6</v>
+        <v>1611724.95</v>
       </c>
       <c r="T753" t="n">
         <v>0</v>
@@ -58446,11 +58446,11 @@
     </row>
     <row r="754">
       <c r="A754" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -58503,16 +58503,16 @@
         <v>17666223.28</v>
       </c>
       <c r="P754" t="n">
-        <v>17396653.93</v>
+        <v>17666223.28</v>
       </c>
       <c r="Q754" t="n">
-        <v>269569.3500000015</v>
+        <v>0</v>
       </c>
       <c r="R754" t="n">
         <v>9748173.800000001</v>
       </c>
       <c r="S754" t="n">
-        <v>7648480.13</v>
+        <v>7918049.48</v>
       </c>
       <c r="T754" t="n">
         <v>0</v>
@@ -58523,11 +58523,11 @@
     </row>
     <row r="755">
       <c r="A755" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -58600,11 +58600,11 @@
     </row>
     <row r="756">
       <c r="A756" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -58677,11 +58677,11 @@
     </row>
     <row r="757">
       <c r="A757" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -58754,11 +58754,11 @@
     </row>
     <row r="758">
       <c r="A758" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -58831,11 +58831,11 @@
     </row>
     <row r="759">
       <c r="A759" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -58908,11 +58908,11 @@
     </row>
     <row r="760">
       <c r="A760" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -58985,11 +58985,11 @@
     </row>
     <row r="761">
       <c r="A761" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -59062,11 +59062,11 @@
     </row>
     <row r="762">
       <c r="A762" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -59139,11 +59139,11 @@
     </row>
     <row r="763">
       <c r="A763" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -59216,11 +59216,11 @@
     </row>
     <row r="764">
       <c r="A764" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -59293,11 +59293,11 @@
     </row>
     <row r="765">
       <c r="A765" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -59370,11 +59370,11 @@
     </row>
     <row r="766">
       <c r="A766" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -59447,11 +59447,11 @@
     </row>
     <row r="767">
       <c r="A767" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -59504,16 +59504,16 @@
         <v>0</v>
       </c>
       <c r="P767" t="n">
-        <v>1805.4</v>
+        <v>5115.3</v>
       </c>
       <c r="Q767" t="n">
-        <v>-1805.4</v>
+        <v>-5115.3</v>
       </c>
       <c r="R767" t="n">
         <v>0</v>
       </c>
       <c r="S767" t="n">
-        <v>1805.4</v>
+        <v>5115.3</v>
       </c>
       <c r="T767" t="n">
         <v>0</v>
@@ -59524,11 +59524,11 @@
     </row>
     <row r="768">
       <c r="A768" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -59581,16 +59581,16 @@
         <v>77180.85000000001</v>
       </c>
       <c r="P768" t="n">
-        <v>65144.85</v>
+        <v>68454.75</v>
       </c>
       <c r="Q768" t="n">
-        <v>12036.00000000001</v>
+        <v>8726.100000000006</v>
       </c>
       <c r="R768" t="n">
         <v>63339.45</v>
       </c>
       <c r="S768" t="n">
-        <v>1805.4</v>
+        <v>5115.3</v>
       </c>
       <c r="T768" t="n">
         <v>0</v>
@@ -59601,11 +59601,11 @@
     </row>
     <row r="769">
       <c r="A769" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -59678,11 +59678,11 @@
     </row>
     <row r="770">
       <c r="A770" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -59755,11 +59755,11 @@
     </row>
     <row r="771">
       <c r="A771" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -59812,16 +59812,16 @@
         <v>0</v>
       </c>
       <c r="P771" t="n">
-        <v>6700</v>
+        <v>22271.5</v>
       </c>
       <c r="Q771" t="n">
-        <v>-6700</v>
+        <v>-22271.5</v>
       </c>
       <c r="R771" t="n">
         <v>34170</v>
       </c>
       <c r="S771" t="n">
-        <v>-27470</v>
+        <v>-11898.5</v>
       </c>
       <c r="T771" t="n">
         <v>0</v>
@@ -59832,11 +59832,11 @@
     </row>
     <row r="772">
       <c r="A772" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -59889,16 +59889,16 @@
         <v>154261.5</v>
       </c>
       <c r="P772" t="n">
-        <v>130650</v>
+        <v>146221.5</v>
       </c>
       <c r="Q772" t="n">
-        <v>23611.5</v>
+        <v>8040</v>
       </c>
       <c r="R772" t="n">
         <v>123950</v>
       </c>
       <c r="S772" t="n">
-        <v>6700</v>
+        <v>22271.5</v>
       </c>
       <c r="T772" t="n">
         <v>0</v>
@@ -59909,11 +59909,11 @@
     </row>
     <row r="773">
       <c r="A773" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -59966,16 +59966,16 @@
         <v>0</v>
       </c>
       <c r="P773" t="n">
-        <v>3685</v>
+        <v>7705</v>
       </c>
       <c r="Q773" t="n">
-        <v>-3685</v>
+        <v>-7705</v>
       </c>
       <c r="R773" t="n">
         <v>21105</v>
       </c>
       <c r="S773" t="n">
-        <v>-17420</v>
+        <v>-13400</v>
       </c>
       <c r="T773" t="n">
         <v>0</v>
@@ -59986,11 +59986,11 @@
     </row>
     <row r="774">
       <c r="A774" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -60043,16 +60043,16 @@
         <v>102007.5</v>
       </c>
       <c r="P774" t="n">
-        <v>97987.5</v>
+        <v>102007.5</v>
       </c>
       <c r="Q774" t="n">
-        <v>4020</v>
+        <v>0</v>
       </c>
       <c r="R774" t="n">
         <v>90282.5</v>
       </c>
       <c r="S774" t="n">
-        <v>7705</v>
+        <v>11725</v>
       </c>
       <c r="T774" t="n">
         <v>0</v>
@@ -60063,11 +60063,11 @@
     </row>
     <row r="775">
       <c r="A775" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -60140,11 +60140,11 @@
     </row>
     <row r="776">
       <c r="A776" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -60217,11 +60217,11 @@
     </row>
     <row r="777">
       <c r="A777" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -60294,11 +60294,11 @@
     </row>
     <row r="778">
       <c r="A778" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -60371,11 +60371,11 @@
     </row>
     <row r="779">
       <c r="A779" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -60428,16 +60428,16 @@
         <v>0</v>
       </c>
       <c r="P779" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q779" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="R779" t="n">
         <v>0</v>
       </c>
       <c r="S779" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T779" t="n">
         <v>0</v>
@@ -60448,11 +60448,11 @@
     </row>
     <row r="780">
       <c r="A780" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -60505,16 +60505,16 @@
         <v>15000</v>
       </c>
       <c r="P780" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="Q780" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="R780" t="n">
         <v>0</v>
       </c>
       <c r="S780" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="T780" t="n">
         <v>0</v>
@@ -60525,11 +60525,11 @@
     </row>
     <row r="781">
       <c r="A781" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -60582,16 +60582,16 @@
         <v>0</v>
       </c>
       <c r="P781" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q781" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="R781" t="n">
         <v>0</v>
       </c>
       <c r="S781" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T781" t="n">
         <v>0</v>
@@ -60602,11 +60602,11 @@
     </row>
     <row r="782">
       <c r="A782" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -60659,16 +60659,16 @@
         <v>15000</v>
       </c>
       <c r="P782" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="Q782" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="R782" t="n">
         <v>0</v>
       </c>
       <c r="S782" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="T782" t="n">
         <v>0</v>
@@ -60679,11 +60679,11 @@
     </row>
     <row r="783">
       <c r="A783" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -60736,16 +60736,16 @@
         <v>0</v>
       </c>
       <c r="P783" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="Q783" t="n">
-        <v>-5000</v>
+        <v>-10000</v>
       </c>
       <c r="R783" t="n">
         <v>0</v>
       </c>
       <c r="S783" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="T783" t="n">
         <v>0</v>
@@ -60756,11 +60756,11 @@
     </row>
     <row r="784">
       <c r="A784" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -60813,16 +60813,16 @@
         <v>15000</v>
       </c>
       <c r="P784" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="Q784" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="R784" t="n">
         <v>0</v>
       </c>
       <c r="S784" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="T784" t="n">
         <v>0</v>
@@ -60833,11 +60833,11 @@
     </row>
     <row r="785">
       <c r="A785" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -60910,11 +60910,11 @@
     </row>
     <row r="786">
       <c r="A786" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -60987,11 +60987,11 @@
     </row>
     <row r="787">
       <c r="A787" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -61064,11 +61064,11 @@
     </row>
     <row r="788">
       <c r="A788" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -61141,11 +61141,11 @@
     </row>
     <row r="789">
       <c r="A789" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -61218,11 +61218,11 @@
     </row>
     <row r="790">
       <c r="A790" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -61295,11 +61295,11 @@
     </row>
     <row r="791">
       <c r="A791" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -61372,11 +61372,11 @@
     </row>
     <row r="792">
       <c r="A792" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -61449,11 +61449,11 @@
     </row>
     <row r="793">
       <c r="A793" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -61526,11 +61526,11 @@
     </row>
     <row r="794">
       <c r="A794" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -61603,11 +61603,11 @@
     </row>
     <row r="795">
       <c r="A795" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -61680,11 +61680,11 @@
     </row>
     <row r="796">
       <c r="A796" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -61757,11 +61757,11 @@
     </row>
     <row r="797">
       <c r="A797" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -61834,11 +61834,11 @@
     </row>
     <row r="798">
       <c r="A798" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -61911,11 +61911,11 @@
     </row>
     <row r="799">
       <c r="A799" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -61988,11 +61988,11 @@
     </row>
     <row r="800">
       <c r="A800" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -62065,11 +62065,11 @@
     </row>
     <row r="801">
       <c r="A801" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -62119,13 +62119,13 @@
         <v>0</v>
       </c>
       <c r="O801" t="n">
-        <v>0</v>
+        <v>3460.35</v>
       </c>
       <c r="P801" t="n">
         <v>0</v>
       </c>
       <c r="Q801" t="n">
-        <v>0</v>
+        <v>3460.35</v>
       </c>
       <c r="R801" t="n">
         <v>26930.55</v>
@@ -62137,16 +62137,16 @@
         <v>0</v>
       </c>
       <c r="U801" t="n">
-        <v>0</v>
+        <v>-3460.35</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -62196,13 +62196,13 @@
         <v>0</v>
       </c>
       <c r="O802" t="n">
-        <v>340017</v>
+        <v>343477.35</v>
       </c>
       <c r="P802" t="n">
         <v>340017</v>
       </c>
       <c r="Q802" t="n">
-        <v>0</v>
+        <v>3460.349999999977</v>
       </c>
       <c r="R802" t="n">
         <v>340017</v>
@@ -62214,16 +62214,16 @@
         <v>0</v>
       </c>
       <c r="U802" t="n">
-        <v>19983</v>
+        <v>16522.65</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -62296,11 +62296,11 @@
     </row>
     <row r="804">
       <c r="A804" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -62373,11 +62373,11 @@
     </row>
     <row r="805">
       <c r="A805" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -62430,16 +62430,16 @@
         <v>0</v>
       </c>
       <c r="P805" t="n">
-        <v>8898</v>
+        <v>15294</v>
       </c>
       <c r="Q805" t="n">
-        <v>-8898</v>
+        <v>-15294</v>
       </c>
       <c r="R805" t="n">
         <v>0</v>
       </c>
       <c r="S805" t="n">
-        <v>8898</v>
+        <v>15294</v>
       </c>
       <c r="T805" t="n">
         <v>0</v>
@@ -62450,11 +62450,11 @@
     </row>
     <row r="806">
       <c r="A806" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -62507,16 +62507,16 @@
         <v>184583</v>
       </c>
       <c r="P806" t="n">
-        <v>171575</v>
+        <v>177971</v>
       </c>
       <c r="Q806" t="n">
-        <v>13008</v>
+        <v>6612</v>
       </c>
       <c r="R806" t="n">
         <v>135326</v>
       </c>
       <c r="S806" t="n">
-        <v>36249</v>
+        <v>42645</v>
       </c>
       <c r="T806" t="n">
         <v>400000</v>
@@ -62527,11 +62527,11 @@
     </row>
     <row r="807">
       <c r="A807" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -62604,11 +62604,11 @@
     </row>
     <row r="808">
       <c r="A808" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -62681,11 +62681,11 @@
     </row>
     <row r="809">
       <c r="A809" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -62758,11 +62758,11 @@
     </row>
     <row r="810">
       <c r="A810" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -62835,11 +62835,11 @@
     </row>
     <row r="811">
       <c r="A811" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -62892,16 +62892,16 @@
         <v>0</v>
       </c>
       <c r="P811" t="n">
-        <v>6204</v>
+        <v>11604</v>
       </c>
       <c r="Q811" t="n">
-        <v>-6204</v>
+        <v>-11604</v>
       </c>
       <c r="R811" t="n">
         <v>0</v>
       </c>
       <c r="S811" t="n">
-        <v>6204</v>
+        <v>11604</v>
       </c>
       <c r="T811" t="n">
         <v>0</v>
@@ -62912,11 +62912,11 @@
     </row>
     <row r="812">
       <c r="A812" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -62969,16 +62969,16 @@
         <v>242268.6</v>
       </c>
       <c r="P812" t="n">
-        <v>40614</v>
+        <v>46014</v>
       </c>
       <c r="Q812" t="n">
-        <v>201654.6</v>
+        <v>196254.6</v>
       </c>
       <c r="R812" t="n">
         <v>29532</v>
       </c>
       <c r="S812" t="n">
-        <v>11082</v>
+        <v>16482</v>
       </c>
       <c r="T812" t="n">
         <v>0</v>
@@ -62989,11 +62989,11 @@
     </row>
     <row r="813">
       <c r="A813" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -63066,11 +63066,11 @@
     </row>
     <row r="814">
       <c r="A814" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -63143,11 +63143,11 @@
     </row>
     <row r="815">
       <c r="A815" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -63220,11 +63220,11 @@
     </row>
     <row r="816">
       <c r="A816" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -63297,11 +63297,11 @@
     </row>
     <row r="817">
       <c r="A817" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -63374,11 +63374,11 @@
     </row>
     <row r="818">
       <c r="A818" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -63451,11 +63451,11 @@
     </row>
     <row r="819">
       <c r="A819" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -63528,11 +63528,11 @@
     </row>
     <row r="820">
       <c r="A820" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -63605,11 +63605,11 @@
     </row>
     <row r="821">
       <c r="A821" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -63682,11 +63682,11 @@
     </row>
     <row r="822">
       <c r="A822" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -63759,11 +63759,11 @@
     </row>
     <row r="823">
       <c r="A823" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>RELEXORC_06-04-2026.csv</t>
+          <t>RELEXORC_07-04-2026.csv</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -63985,7 +63985,7 @@
         <v>46112</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -64071,7 +64071,7 @@
         <v>46112</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -64157,7 +64157,7 @@
         <v>46112</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -64243,7 +64243,7 @@
         <v>46112</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -64329,7 +64329,7 @@
         <v>46112</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -64415,7 +64415,7 @@
         <v>46112</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -64501,7 +64501,7 @@
         <v>46112</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -64587,7 +64587,7 @@
         <v>46112</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -64644,10 +64644,10 @@
         <v>11664028.3</v>
       </c>
       <c r="S9" t="n">
-        <v>11664028.3</v>
+        <v>14096077.09</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2432048.789999999</v>
       </c>
       <c r="U9" t="n">
         <v>9603235.9</v>
@@ -64673,7 +64673,7 @@
         <v>46112</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -64739,10 +64739,10 @@
         <v>4146949.64</v>
       </c>
       <c r="V10" t="n">
-        <v>4146949.64</v>
+        <v>4367980.05</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>221030.4099999997</v>
       </c>
       <c r="X10" t="n">
         <v>29095906.07</v>
@@ -64759,7 +64759,7 @@
         <v>46112</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -64834,10 +64834,10 @@
         <v>30208318.24</v>
       </c>
       <c r="Y11" t="n">
-        <v>30208318.24</v>
+        <v>27724491.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-2483827.049999997</v>
       </c>
     </row>
     <row r="12">
@@ -64845,7 +64845,7 @@
         <v>46112</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -64902,10 +64902,10 @@
         <v>37452.6</v>
       </c>
       <c r="S12" t="n">
-        <v>37452.6</v>
+        <v>38532.6</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="U12" t="n">
         <v>372.6</v>
@@ -64931,7 +64931,7 @@
         <v>46112</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -64988,10 +64988,10 @@
         <v>16054498.33</v>
       </c>
       <c r="S13" t="n">
-        <v>17396653.93</v>
+        <v>17666223.28</v>
       </c>
       <c r="T13" t="n">
-        <v>1342155.6</v>
+        <v>1611724.950000001</v>
       </c>
       <c r="U13" t="n">
         <v>9748173.800000001</v>
@@ -65017,7 +65017,7 @@
         <v>46112</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -65103,7 +65103,7 @@
         <v>46112</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -65189,7 +65189,7 @@
         <v>46112</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -65275,7 +65275,7 @@
         <v>46112</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -65341,10 +65341,10 @@
         <v>4875485.05</v>
       </c>
       <c r="V17" t="n">
-        <v>6531423.23</v>
+        <v>6550089.63</v>
       </c>
       <c r="W17" t="n">
-        <v>1655938.180000001</v>
+        <v>1674604.58</v>
       </c>
       <c r="X17" t="n">
         <v>22791039.49</v>
@@ -65361,7 +65361,7 @@
         <v>46112</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -65447,7 +65447,7 @@
         <v>46112</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -65513,10 +65513,10 @@
         <v>60690650.18</v>
       </c>
       <c r="V19" t="n">
-        <v>77798582.09999999</v>
+        <v>79635166.11</v>
       </c>
       <c r="W19" t="n">
-        <v>17107931.91999999</v>
+        <v>18944515.93</v>
       </c>
       <c r="X19" t="n">
         <v>278444787.27</v>
@@ -65533,7 +65533,7 @@
         <v>46112</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -65619,7 +65619,7 @@
         <v>46112</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -65705,7 +65705,7 @@
         <v>46112</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -65791,7 +65791,7 @@
         <v>46112</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -65877,7 +65877,7 @@
         <v>46112</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -65963,7 +65963,7 @@
         <v>46112</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -66049,7 +66049,7 @@
         <v>46112</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -66135,7 +66135,7 @@
         <v>46112</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -66221,7 +66221,7 @@
         <v>46112</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -66307,7 +66307,7 @@
         <v>46112</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -66393,7 +66393,7 @@
         <v>46112</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -66479,7 +66479,7 @@
         <v>46112</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -66565,7 +66565,7 @@
         <v>46112</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -66651,7 +66651,7 @@
         <v>46112</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -66737,7 +66737,7 @@
         <v>46112</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -66823,7 +66823,7 @@
         <v>46112</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -66909,7 +66909,7 @@
         <v>46112</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -66995,7 +66995,7 @@
         <v>46112</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -67043,10 +67043,10 @@
         <v>340017</v>
       </c>
       <c r="P37" t="n">
-        <v>340017</v>
+        <v>343477.35</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3460.349999999977</v>
       </c>
       <c r="R37" t="n">
         <v>340017</v>
@@ -67070,10 +67070,10 @@
         <v>19983</v>
       </c>
       <c r="Y37" t="n">
-        <v>19983</v>
+        <v>16522.65</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>-3460.349999999999</v>
       </c>
     </row>
     <row r="38">
@@ -67081,7 +67081,7 @@
         <v>46112</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -67167,7 +67167,7 @@
         <v>46112</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -67224,10 +67224,10 @@
         <v>159398</v>
       </c>
       <c r="S39" t="n">
-        <v>171575</v>
+        <v>177971</v>
       </c>
       <c r="T39" t="n">
-        <v>12177</v>
+        <v>18573</v>
       </c>
       <c r="U39" t="n">
         <v>135326</v>
@@ -67253,7 +67253,7 @@
         <v>46112</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -67339,7 +67339,7 @@
         <v>46112</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -67425,7 +67425,7 @@
         <v>46112</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -67482,10 +67482,10 @@
         <v>33222</v>
       </c>
       <c r="S42" t="n">
-        <v>40614</v>
+        <v>46014</v>
       </c>
       <c r="T42" t="n">
-        <v>7392</v>
+        <v>12792</v>
       </c>
       <c r="U42" t="n">
         <v>29532</v>
@@ -67511,7 +67511,7 @@
         <v>46112</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -67597,7 +67597,7 @@
         <v>46112</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -67683,7 +67683,7 @@
         <v>46112</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -67769,7 +67769,7 @@
         <v>46112</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -67855,7 +67855,7 @@
         <v>46112</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -67941,7 +67941,7 @@
         <v>46112</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -68027,7 +68027,7 @@
         <v>46112</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -68113,7 +68113,7 @@
         <v>46112</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -68199,7 +68199,7 @@
         <v>46112</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -68285,7 +68285,7 @@
         <v>46112</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -68342,10 +68342,10 @@
         <v>63339.45</v>
       </c>
       <c r="S52" t="n">
-        <v>65144.85</v>
+        <v>68454.75</v>
       </c>
       <c r="T52" t="n">
-        <v>1805.400000000001</v>
+        <v>5115.300000000003</v>
       </c>
       <c r="U52" t="n">
         <v>63339.45</v>
@@ -68371,7 +68371,7 @@
         <v>46112</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -68457,7 +68457,7 @@
         <v>46112</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -68514,10 +68514,10 @@
         <v>123950</v>
       </c>
       <c r="S54" t="n">
-        <v>130650</v>
+        <v>146221.5</v>
       </c>
       <c r="T54" t="n">
-        <v>6700</v>
+        <v>22271.5</v>
       </c>
       <c r="U54" t="n">
         <v>89780</v>
@@ -68543,7 +68543,7 @@
         <v>46112</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -68600,10 +68600,10 @@
         <v>90282.5</v>
       </c>
       <c r="S55" t="n">
-        <v>97987.5</v>
+        <v>102007.5</v>
       </c>
       <c r="T55" t="n">
-        <v>7705</v>
+        <v>11725</v>
       </c>
       <c r="U55" t="n">
         <v>69177.5</v>
@@ -68629,7 +68629,7 @@
         <v>46112</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -68715,7 +68715,7 @@
         <v>46112</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -68801,7 +68801,7 @@
         <v>46112</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -68858,10 +68858,10 @@
         <v>10000</v>
       </c>
       <c r="S58" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -68887,7 +68887,7 @@
         <v>46112</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -68944,10 +68944,10 @@
         <v>10000</v>
       </c>
       <c r="S59" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
@@ -68973,7 +68973,7 @@
         <v>46112</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -69030,10 +69030,10 @@
         <v>5000</v>
       </c>
       <c r="S60" t="n">
+        <v>15000</v>
+      </c>
+      <c r="T60" t="n">
         <v>10000</v>
-      </c>
-      <c r="T60" t="n">
-        <v>5000</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -69059,7 +69059,7 @@
         <v>46112</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -69145,7 +69145,7 @@
         <v>46112</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -69231,7 +69231,7 @@
         <v>46112</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -69317,7 +69317,7 @@
         <v>46112</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -69403,7 +69403,7 @@
         <v>46112</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -69489,7 +69489,7 @@
         <v>46112</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -69575,7 +69575,7 @@
         <v>46112</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -69661,7 +69661,7 @@
         <v>46112</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -69747,7 +69747,7 @@
         <v>46112</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -69833,7 +69833,7 @@
         <v>46112</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -69919,7 +69919,7 @@
         <v>46112</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -70005,7 +70005,7 @@
         <v>46112</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -70091,7 +70091,7 @@
         <v>46112</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -70177,7 +70177,7 @@
         <v>46112</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -70263,7 +70263,7 @@
         <v>46112</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -70349,7 +70349,7 @@
         <v>46112</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -70435,7 +70435,7 @@
         <v>46112</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -70521,7 +70521,7 @@
         <v>46112</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -70607,7 +70607,7 @@
         <v>46112</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -70693,7 +70693,7 @@
         <v>46112</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -70779,7 +70779,7 @@
         <v>46112</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -70865,7 +70865,7 @@
         <v>46112</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -70951,7 +70951,7 @@
         <v>46112</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -71037,7 +71037,7 @@
         <v>46112</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -71123,7 +71123,7 @@
         <v>46112</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -71209,7 +71209,7 @@
         <v>46112</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -71295,7 +71295,7 @@
         <v>46112</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -71381,7 +71381,7 @@
         <v>46112</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -71467,7 +71467,7 @@
         <v>46112</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -71553,7 +71553,7 @@
         <v>46112</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -71639,7 +71639,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -71725,7 +71725,7 @@
         <v>46112</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -71811,7 +71811,7 @@
         <v>46112</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -71897,7 +71897,7 @@
         <v>46112</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -71983,7 +71983,7 @@
         <v>46112</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -72069,7 +72069,7 @@
         <v>46112</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -72155,7 +72155,7 @@
         <v>46112</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -72241,7 +72241,7 @@
         <v>46112</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -72327,7 +72327,7 @@
         <v>46112</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -72413,7 +72413,7 @@
         <v>46112</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -72499,7 +72499,7 @@
         <v>46112</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -72585,7 +72585,7 @@
         <v>46112</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -72671,7 +72671,7 @@
         <v>46112</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -72757,7 +72757,7 @@
         <v>46112</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -72843,7 +72843,7 @@
         <v>46112</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -72929,7 +72929,7 @@
         <v>46112</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -73015,7 +73015,7 @@
         <v>46112</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -73101,7 +73101,7 @@
         <v>46112</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -73187,7 +73187,7 @@
         <v>46112</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -73273,7 +73273,7 @@
         <v>46112</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -73359,7 +73359,7 @@
         <v>46112</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -73445,7 +73445,7 @@
         <v>46112</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -73531,7 +73531,7 @@
         <v>46112</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -73617,7 +73617,7 @@
         <v>46112</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -73703,7 +73703,7 @@
         <v>46112</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -73789,7 +73789,7 @@
         <v>46112</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -73875,7 +73875,7 @@
         <v>46112</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -73961,7 +73961,7 @@
         <v>46112</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -74047,7 +74047,7 @@
         <v>46112</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -74133,7 +74133,7 @@
         <v>46112</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -74219,7 +74219,7 @@
         <v>46112</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -74305,7 +74305,7 @@
         <v>46112</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -74391,7 +74391,7 @@
         <v>46112</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -74477,7 +74477,7 @@
         <v>46112</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -74563,7 +74563,7 @@
         <v>46112</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -74649,7 +74649,7 @@
         <v>46112</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -74735,7 +74735,7 @@
         <v>46112</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>

--- a/Base_Consolidada_SIAFI.xlsx
+++ b/Base_Consolidada_SIAFI.xlsx
@@ -44432,11 +44432,11 @@
     </row>
     <row r="572">
       <c r="A572" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -44509,11 +44509,11 @@
     </row>
     <row r="573">
       <c r="A573" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -44586,11 +44586,11 @@
     </row>
     <row r="574">
       <c r="A574" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -44663,11 +44663,11 @@
     </row>
     <row r="575">
       <c r="A575" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -44740,11 +44740,11 @@
     </row>
     <row r="576">
       <c r="A576" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -44817,11 +44817,11 @@
     </row>
     <row r="577">
       <c r="A577" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -44894,11 +44894,11 @@
     </row>
     <row r="578">
       <c r="A578" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -44971,11 +44971,11 @@
     </row>
     <row r="579">
       <c r="A579" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -45048,11 +45048,11 @@
     </row>
     <row r="580">
       <c r="A580" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -45125,11 +45125,11 @@
     </row>
     <row r="581">
       <c r="A581" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -45202,11 +45202,11 @@
     </row>
     <row r="582">
       <c r="A582" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -45279,11 +45279,11 @@
     </row>
     <row r="583">
       <c r="A583" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -45356,11 +45356,11 @@
     </row>
     <row r="584">
       <c r="A584" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -45433,11 +45433,11 @@
     </row>
     <row r="585">
       <c r="A585" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -45510,11 +45510,11 @@
     </row>
     <row r="586">
       <c r="A586" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -45587,11 +45587,11 @@
     </row>
     <row r="587">
       <c r="A587" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -45664,11 +45664,11 @@
     </row>
     <row r="588">
       <c r="A588" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -45741,11 +45741,11 @@
     </row>
     <row r="589">
       <c r="A589" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -45818,11 +45818,11 @@
     </row>
     <row r="590">
       <c r="A590" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -45895,11 +45895,11 @@
     </row>
     <row r="591">
       <c r="A591" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -45972,11 +45972,11 @@
     </row>
     <row r="592">
       <c r="A592" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -46049,11 +46049,11 @@
     </row>
     <row r="593">
       <c r="A593" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -46126,11 +46126,11 @@
     </row>
     <row r="594">
       <c r="A594" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -46203,11 +46203,11 @@
     </row>
     <row r="595">
       <c r="A595" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -46280,11 +46280,11 @@
     </row>
     <row r="596">
       <c r="A596" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -46357,11 +46357,11 @@
     </row>
     <row r="597">
       <c r="A597" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -46434,11 +46434,11 @@
     </row>
     <row r="598">
       <c r="A598" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -46511,11 +46511,11 @@
     </row>
     <row r="599">
       <c r="A599" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -46588,11 +46588,11 @@
     </row>
     <row r="600">
       <c r="A600" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -46665,11 +46665,11 @@
     </row>
     <row r="601">
       <c r="A601" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -46742,11 +46742,11 @@
     </row>
     <row r="602">
       <c r="A602" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -46819,11 +46819,11 @@
     </row>
     <row r="603">
       <c r="A603" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -46896,11 +46896,11 @@
     </row>
     <row r="604">
       <c r="A604" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -46973,11 +46973,11 @@
     </row>
     <row r="605">
       <c r="A605" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -47050,11 +47050,11 @@
     </row>
     <row r="606">
       <c r="A606" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -47127,11 +47127,11 @@
     </row>
     <row r="607">
       <c r="A607" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -47204,11 +47204,11 @@
     </row>
     <row r="608">
       <c r="A608" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -47281,11 +47281,11 @@
     </row>
     <row r="609">
       <c r="A609" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -47358,11 +47358,11 @@
     </row>
     <row r="610">
       <c r="A610" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -47435,11 +47435,11 @@
     </row>
     <row r="611">
       <c r="A611" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -47512,11 +47512,11 @@
     </row>
     <row r="612">
       <c r="A612" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -47589,11 +47589,11 @@
     </row>
     <row r="613">
       <c r="A613" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -47666,11 +47666,11 @@
     </row>
     <row r="614">
       <c r="A614" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -47743,11 +47743,11 @@
     </row>
     <row r="615">
       <c r="A615" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -47820,11 +47820,11 @@
     </row>
     <row r="616">
       <c r="A616" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -47897,11 +47897,11 @@
     </row>
     <row r="617">
       <c r="A617" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -47974,11 +47974,11 @@
     </row>
     <row r="618">
       <c r="A618" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -48051,11 +48051,11 @@
     </row>
     <row r="619">
       <c r="A619" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -48128,11 +48128,11 @@
     </row>
     <row r="620">
       <c r="A620" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -48205,11 +48205,11 @@
     </row>
     <row r="621">
       <c r="A621" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -48282,11 +48282,11 @@
     </row>
     <row r="622">
       <c r="A622" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -48359,11 +48359,11 @@
     </row>
     <row r="623">
       <c r="A623" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -48436,11 +48436,11 @@
     </row>
     <row r="624">
       <c r="A624" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -48513,11 +48513,11 @@
     </row>
     <row r="625">
       <c r="A625" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -48590,11 +48590,11 @@
     </row>
     <row r="626">
       <c r="A626" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -48667,11 +48667,11 @@
     </row>
     <row r="627">
       <c r="A627" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -48744,11 +48744,11 @@
     </row>
     <row r="628">
       <c r="A628" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -48821,11 +48821,11 @@
     </row>
     <row r="629">
       <c r="A629" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -48898,11 +48898,11 @@
     </row>
     <row r="630">
       <c r="A630" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -48975,11 +48975,11 @@
     </row>
     <row r="631">
       <c r="A631" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -49052,11 +49052,11 @@
     </row>
     <row r="632">
       <c r="A632" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -49129,11 +49129,11 @@
     </row>
     <row r="633">
       <c r="A633" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -49206,11 +49206,11 @@
     </row>
     <row r="634">
       <c r="A634" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -49283,11 +49283,11 @@
     </row>
     <row r="635">
       <c r="A635" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -49360,11 +49360,11 @@
     </row>
     <row r="636">
       <c r="A636" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -49437,11 +49437,11 @@
     </row>
     <row r="637">
       <c r="A637" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -49514,11 +49514,11 @@
     </row>
     <row r="638">
       <c r="A638" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -49591,11 +49591,11 @@
     </row>
     <row r="639">
       <c r="A639" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -49668,11 +49668,11 @@
     </row>
     <row r="640">
       <c r="A640" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -49745,11 +49745,11 @@
     </row>
     <row r="641">
       <c r="A641" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -49822,11 +49822,11 @@
     </row>
     <row r="642">
       <c r="A642" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -49899,11 +49899,11 @@
     </row>
     <row r="643">
       <c r="A643" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -49976,11 +49976,11 @@
     </row>
     <row r="644">
       <c r="A644" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -50053,11 +50053,11 @@
     </row>
     <row r="645">
       <c r="A645" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -50110,16 +50110,16 @@
         <v>0</v>
       </c>
       <c r="P645" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="Q645" t="n">
-        <v>0</v>
+        <v>-4200</v>
       </c>
       <c r="R645" t="n">
         <v>0</v>
       </c>
       <c r="S645" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="T645" t="n">
         <v>0</v>
@@ -50130,11 +50130,11 @@
     </row>
     <row r="646">
       <c r="A646" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -50187,16 +50187,16 @@
         <v>3126083.6</v>
       </c>
       <c r="P646" t="n">
-        <v>993289</v>
+        <v>997489</v>
       </c>
       <c r="Q646" t="n">
-        <v>2132794.6</v>
+        <v>2128594.6</v>
       </c>
       <c r="R646" t="n">
         <v>993289</v>
       </c>
       <c r="S646" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="T646" t="n">
         <v>0</v>
@@ -50207,11 +50207,11 @@
     </row>
     <row r="647">
       <c r="A647" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -50284,11 +50284,11 @@
     </row>
     <row r="648">
       <c r="A648" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -50361,11 +50361,11 @@
     </row>
     <row r="649">
       <c r="A649" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -50438,11 +50438,11 @@
     </row>
     <row r="650">
       <c r="A650" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -50515,11 +50515,11 @@
     </row>
     <row r="651">
       <c r="A651" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -50592,11 +50592,11 @@
     </row>
     <row r="652">
       <c r="A652" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -50669,11 +50669,11 @@
     </row>
     <row r="653">
       <c r="A653" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -50746,11 +50746,11 @@
     </row>
     <row r="654">
       <c r="A654" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -50823,11 +50823,11 @@
     </row>
     <row r="655">
       <c r="A655" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -50900,11 +50900,11 @@
     </row>
     <row r="656">
       <c r="A656" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -50977,11 +50977,11 @@
     </row>
     <row r="657">
       <c r="A657" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -51054,11 +51054,11 @@
     </row>
     <row r="658">
       <c r="A658" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -51131,11 +51131,11 @@
     </row>
     <row r="659">
       <c r="A659" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -51208,11 +51208,11 @@
     </row>
     <row r="660">
       <c r="A660" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -51285,11 +51285,11 @@
     </row>
     <row r="661">
       <c r="A661" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -51362,11 +51362,11 @@
     </row>
     <row r="662">
       <c r="A662" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -51439,11 +51439,11 @@
     </row>
     <row r="663">
       <c r="A663" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -51516,11 +51516,11 @@
     </row>
     <row r="664">
       <c r="A664" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -51593,11 +51593,11 @@
     </row>
     <row r="665">
       <c r="A665" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -51670,11 +51670,11 @@
     </row>
     <row r="666">
       <c r="A666" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -51747,11 +51747,11 @@
     </row>
     <row r="667">
       <c r="A667" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -51824,11 +51824,11 @@
     </row>
     <row r="668">
       <c r="A668" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -51901,11 +51901,11 @@
     </row>
     <row r="669">
       <c r="A669" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -51978,11 +51978,11 @@
     </row>
     <row r="670">
       <c r="A670" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -52055,11 +52055,11 @@
     </row>
     <row r="671">
       <c r="A671" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -52132,11 +52132,11 @@
     </row>
     <row r="672">
       <c r="A672" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -52209,11 +52209,11 @@
     </row>
     <row r="673">
       <c r="A673" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -52286,11 +52286,11 @@
     </row>
     <row r="674">
       <c r="A674" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -52363,11 +52363,11 @@
     </row>
     <row r="675">
       <c r="A675" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -52440,11 +52440,11 @@
     </row>
     <row r="676">
       <c r="A676" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -52517,11 +52517,11 @@
     </row>
     <row r="677">
       <c r="A677" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -52594,11 +52594,11 @@
     </row>
     <row r="678">
       <c r="A678" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -52671,11 +52671,11 @@
     </row>
     <row r="679">
       <c r="A679" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -52748,11 +52748,11 @@
     </row>
     <row r="680">
       <c r="A680" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -52825,11 +52825,11 @@
     </row>
     <row r="681">
       <c r="A681" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -52902,11 +52902,11 @@
     </row>
     <row r="682">
       <c r="A682" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -52979,11 +52979,11 @@
     </row>
     <row r="683">
       <c r="A683" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -53056,11 +53056,11 @@
     </row>
     <row r="684">
       <c r="A684" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -53133,11 +53133,11 @@
     </row>
     <row r="685">
       <c r="A685" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -53210,11 +53210,11 @@
     </row>
     <row r="686">
       <c r="A686" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -53287,11 +53287,11 @@
     </row>
     <row r="687">
       <c r="A687" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -53364,11 +53364,11 @@
     </row>
     <row r="688">
       <c r="A688" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -53441,11 +53441,11 @@
     </row>
     <row r="689">
       <c r="A689" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -53518,11 +53518,11 @@
     </row>
     <row r="690">
       <c r="A690" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -53595,11 +53595,11 @@
     </row>
     <row r="691">
       <c r="A691" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -53672,11 +53672,11 @@
     </row>
     <row r="692">
       <c r="A692" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -53749,11 +53749,11 @@
     </row>
     <row r="693">
       <c r="A693" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -53826,11 +53826,11 @@
     </row>
     <row r="694">
       <c r="A694" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -53903,11 +53903,11 @@
     </row>
     <row r="695">
       <c r="A695" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -53980,11 +53980,11 @@
     </row>
     <row r="696">
       <c r="A696" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -54057,11 +54057,11 @@
     </row>
     <row r="697">
       <c r="A697" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -54134,11 +54134,11 @@
     </row>
     <row r="698">
       <c r="A698" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -54211,11 +54211,11 @@
     </row>
     <row r="699">
       <c r="A699" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -54274,10 +54274,10 @@
         <v>0</v>
       </c>
       <c r="R699" t="n">
-        <v>6550089.63</v>
+        <v>7195172.54</v>
       </c>
       <c r="S699" t="n">
-        <v>2658870.88</v>
+        <v>2013787.97</v>
       </c>
       <c r="T699" t="n">
         <v>0</v>
@@ -54288,11 +54288,11 @@
     </row>
     <row r="700">
       <c r="A700" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -54365,11 +54365,11 @@
     </row>
     <row r="701">
       <c r="A701" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -54442,11 +54442,11 @@
     </row>
     <row r="702">
       <c r="A702" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -54505,10 +54505,10 @@
         <v>0</v>
       </c>
       <c r="R702" t="n">
-        <v>18916647.74</v>
+        <v>24365573.77</v>
       </c>
       <c r="S702" t="n">
-        <v>-18916647.74</v>
+        <v>-24365573.77</v>
       </c>
       <c r="T702" t="n">
         <v>0</v>
@@ -54519,11 +54519,11 @@
     </row>
     <row r="703">
       <c r="A703" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -54582,10 +54582,10 @@
         <v>0</v>
       </c>
       <c r="R703" t="n">
-        <v>79635166.11</v>
+        <v>85084092.14</v>
       </c>
       <c r="S703" t="n">
-        <v>8477389.619999999</v>
+        <v>3028463.59</v>
       </c>
       <c r="T703" t="n">
         <v>0</v>
@@ -54596,11 +54596,11 @@
     </row>
     <row r="704">
       <c r="A704" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -54673,11 +54673,11 @@
     </row>
     <row r="705">
       <c r="A705" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -54750,11 +54750,11 @@
     </row>
     <row r="706">
       <c r="A706" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -54827,11 +54827,11 @@
     </row>
     <row r="707">
       <c r="A707" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -54904,11 +54904,11 @@
     </row>
     <row r="708">
       <c r="A708" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -54981,11 +54981,11 @@
     </row>
     <row r="709">
       <c r="A709" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -55058,11 +55058,11 @@
     </row>
     <row r="710">
       <c r="A710" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -55135,11 +55135,11 @@
     </row>
     <row r="711">
       <c r="A711" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -55212,11 +55212,11 @@
     </row>
     <row r="712">
       <c r="A712" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -55289,11 +55289,11 @@
     </row>
     <row r="713">
       <c r="A713" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -55366,11 +55366,11 @@
     </row>
     <row r="714">
       <c r="A714" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -55443,11 +55443,11 @@
     </row>
     <row r="715">
       <c r="A715" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -55520,11 +55520,11 @@
     </row>
     <row r="716">
       <c r="A716" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -55597,11 +55597,11 @@
     </row>
     <row r="717">
       <c r="A717" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -55674,11 +55674,11 @@
     </row>
     <row r="718">
       <c r="A718" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -55751,11 +55751,11 @@
     </row>
     <row r="719">
       <c r="A719" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -55828,11 +55828,11 @@
     </row>
     <row r="720">
       <c r="A720" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -55905,11 +55905,11 @@
     </row>
     <row r="721">
       <c r="A721" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -55982,11 +55982,11 @@
     </row>
     <row r="722">
       <c r="A722" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -56059,11 +56059,11 @@
     </row>
     <row r="723">
       <c r="A723" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -56136,11 +56136,11 @@
     </row>
     <row r="724">
       <c r="A724" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -56213,11 +56213,11 @@
     </row>
     <row r="725">
       <c r="A725" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -56290,11 +56290,11 @@
     </row>
     <row r="726">
       <c r="A726" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -56353,10 +56353,10 @@
         <v>0</v>
       </c>
       <c r="R726" t="n">
-        <v>1654249.63</v>
+        <v>2299332.54</v>
       </c>
       <c r="S726" t="n">
-        <v>-1654249.63</v>
+        <v>-2299332.54</v>
       </c>
       <c r="T726" t="n">
         <v>0</v>
@@ -56367,11 +56367,11 @@
     </row>
     <row r="727">
       <c r="A727" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -56444,11 +56444,11 @@
     </row>
     <row r="728">
       <c r="A728" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -56521,11 +56521,11 @@
     </row>
     <row r="729">
       <c r="A729" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -56598,11 +56598,11 @@
     </row>
     <row r="730">
       <c r="A730" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -56652,10 +56652,10 @@
         <v>0</v>
       </c>
       <c r="O730" t="n">
-        <v>0</v>
+        <v>26641.16</v>
       </c>
       <c r="P730" t="n">
-        <v>0</v>
+        <v>26641.16</v>
       </c>
       <c r="Q730" t="n">
         <v>0</v>
@@ -56664,22 +56664,22 @@
         <v>0</v>
       </c>
       <c r="S730" t="n">
-        <v>0</v>
+        <v>26641.16</v>
       </c>
       <c r="T730" t="n">
         <v>0</v>
       </c>
       <c r="U730" t="n">
-        <v>0</v>
+        <v>-26641.16</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -56752,11 +56752,11 @@
     </row>
     <row r="732">
       <c r="A732" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -56829,11 +56829,11 @@
     </row>
     <row r="733">
       <c r="A733" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -56906,11 +56906,11 @@
     </row>
     <row r="734">
       <c r="A734" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -56983,11 +56983,11 @@
     </row>
     <row r="735">
       <c r="A735" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -57060,11 +57060,11 @@
     </row>
     <row r="736">
       <c r="A736" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -57137,11 +57137,11 @@
     </row>
     <row r="737">
       <c r="A737" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -57214,11 +57214,11 @@
     </row>
     <row r="738">
       <c r="A738" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -57291,11 +57291,11 @@
     </row>
     <row r="739">
       <c r="A739" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -57368,11 +57368,11 @@
     </row>
     <row r="740">
       <c r="A740" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -57445,11 +57445,11 @@
     </row>
     <row r="741">
       <c r="A741" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -57522,11 +57522,11 @@
     </row>
     <row r="742">
       <c r="A742" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -57599,11 +57599,11 @@
     </row>
     <row r="743">
       <c r="A743" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -57676,11 +57676,11 @@
     </row>
     <row r="744">
       <c r="A744" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -57753,11 +57753,11 @@
     </row>
     <row r="745">
       <c r="A745" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -57822,19 +57822,19 @@
         <v>2432048.79</v>
       </c>
       <c r="T745" t="n">
-        <v>0</v>
+        <v>6500000</v>
       </c>
       <c r="U745" t="n">
-        <v>0</v>
+        <v>-6500000</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -57899,19 +57899,19 @@
         <v>4492841.19</v>
       </c>
       <c r="T746" t="n">
-        <v>46382823.26</v>
+        <v>52882823.26</v>
       </c>
       <c r="U746" t="n">
-        <v>19401015.72</v>
+        <v>12901015.72</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -57984,11 +57984,11 @@
     </row>
     <row r="748">
       <c r="A748" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -58061,11 +58061,11 @@
     </row>
     <row r="749">
       <c r="A749" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -58130,19 +58130,19 @@
         <v>0</v>
       </c>
       <c r="T749" t="n">
-        <v>2483827.05</v>
+        <v>8983827.050000001</v>
       </c>
       <c r="U749" t="n">
-        <v>-2483827.05</v>
+        <v>-8983827.050000001</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -58207,19 +58207,19 @@
         <v>5389734.24</v>
       </c>
       <c r="T750" t="n">
-        <v>46897827.05</v>
+        <v>53397827.05</v>
       </c>
       <c r="U750" t="n">
-        <v>27724491.19</v>
+        <v>21224491.19</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -58269,34 +58269,34 @@
         <v>0</v>
       </c>
       <c r="O751" t="n">
-        <v>0</v>
+        <v>1620</v>
       </c>
       <c r="P751" t="n">
-        <v>1080</v>
+        <v>1755</v>
       </c>
       <c r="Q751" t="n">
-        <v>-1080</v>
+        <v>-135</v>
       </c>
       <c r="R751" t="n">
         <v>0</v>
       </c>
       <c r="S751" t="n">
-        <v>1080</v>
+        <v>1755</v>
       </c>
       <c r="T751" t="n">
         <v>0</v>
       </c>
       <c r="U751" t="n">
-        <v>0</v>
+        <v>-1620</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -58346,34 +58346,34 @@
         <v>2788800</v>
       </c>
       <c r="O752" t="n">
-        <v>76455.60000000001</v>
+        <v>78075.60000000001</v>
       </c>
       <c r="P752" t="n">
-        <v>38532.6</v>
+        <v>39207.6</v>
       </c>
       <c r="Q752" t="n">
-        <v>37923.00000000001</v>
+        <v>38868.00000000001</v>
       </c>
       <c r="R752" t="n">
         <v>372.6</v>
       </c>
       <c r="S752" t="n">
-        <v>38160</v>
+        <v>38835</v>
       </c>
       <c r="T752" t="n">
         <v>0</v>
       </c>
       <c r="U752" t="n">
-        <v>2712344.4</v>
+        <v>2710724.4</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -58446,11 +58446,11 @@
     </row>
     <row r="754">
       <c r="A754" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -58523,11 +58523,11 @@
     </row>
     <row r="755">
       <c r="A755" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -58600,11 +58600,11 @@
     </row>
     <row r="756">
       <c r="A756" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -58677,11 +58677,11 @@
     </row>
     <row r="757">
       <c r="A757" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -58754,11 +58754,11 @@
     </row>
     <row r="758">
       <c r="A758" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -58831,11 +58831,11 @@
     </row>
     <row r="759">
       <c r="A759" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -58908,11 +58908,11 @@
     </row>
     <row r="760">
       <c r="A760" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -58985,11 +58985,11 @@
     </row>
     <row r="761">
       <c r="A761" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -59062,11 +59062,11 @@
     </row>
     <row r="762">
       <c r="A762" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -59139,11 +59139,11 @@
     </row>
     <row r="763">
       <c r="A763" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -59216,11 +59216,11 @@
     </row>
     <row r="764">
       <c r="A764" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -59293,11 +59293,11 @@
     </row>
     <row r="765">
       <c r="A765" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -59370,11 +59370,11 @@
     </row>
     <row r="766">
       <c r="A766" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -59447,11 +59447,11 @@
     </row>
     <row r="767">
       <c r="A767" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -59504,16 +59504,16 @@
         <v>0</v>
       </c>
       <c r="P767" t="n">
-        <v>5115.3</v>
+        <v>13841.4</v>
       </c>
       <c r="Q767" t="n">
-        <v>-5115.3</v>
+        <v>-13841.4</v>
       </c>
       <c r="R767" t="n">
         <v>0</v>
       </c>
       <c r="S767" t="n">
-        <v>5115.3</v>
+        <v>13841.4</v>
       </c>
       <c r="T767" t="n">
         <v>0</v>
@@ -59524,11 +59524,11 @@
     </row>
     <row r="768">
       <c r="A768" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -59581,16 +59581,16 @@
         <v>77180.85000000001</v>
       </c>
       <c r="P768" t="n">
-        <v>68454.75</v>
+        <v>77180.85000000001</v>
       </c>
       <c r="Q768" t="n">
-        <v>8726.100000000006</v>
+        <v>0</v>
       </c>
       <c r="R768" t="n">
         <v>63339.45</v>
       </c>
       <c r="S768" t="n">
-        <v>5115.3</v>
+        <v>13841.4</v>
       </c>
       <c r="T768" t="n">
         <v>0</v>
@@ -59601,11 +59601,11 @@
     </row>
     <row r="769">
       <c r="A769" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -59678,11 +59678,11 @@
     </row>
     <row r="770">
       <c r="A770" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -59755,11 +59755,11 @@
     </row>
     <row r="771">
       <c r="A771" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -59812,16 +59812,16 @@
         <v>0</v>
       </c>
       <c r="P771" t="n">
-        <v>22271.5</v>
+        <v>30311.5</v>
       </c>
       <c r="Q771" t="n">
-        <v>-22271.5</v>
+        <v>-30311.5</v>
       </c>
       <c r="R771" t="n">
         <v>34170</v>
       </c>
       <c r="S771" t="n">
-        <v>-11898.5</v>
+        <v>-3858.5</v>
       </c>
       <c r="T771" t="n">
         <v>0</v>
@@ -59832,11 +59832,11 @@
     </row>
     <row r="772">
       <c r="A772" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -59889,16 +59889,16 @@
         <v>154261.5</v>
       </c>
       <c r="P772" t="n">
-        <v>146221.5</v>
+        <v>154261.5</v>
       </c>
       <c r="Q772" t="n">
-        <v>8040</v>
+        <v>0</v>
       </c>
       <c r="R772" t="n">
         <v>123950</v>
       </c>
       <c r="S772" t="n">
-        <v>22271.5</v>
+        <v>30311.5</v>
       </c>
       <c r="T772" t="n">
         <v>0</v>
@@ -59909,11 +59909,11 @@
     </row>
     <row r="773">
       <c r="A773" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -59986,11 +59986,11 @@
     </row>
     <row r="774">
       <c r="A774" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -60063,11 +60063,11 @@
     </row>
     <row r="775">
       <c r="A775" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -60140,11 +60140,11 @@
     </row>
     <row r="776">
       <c r="A776" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -60194,13 +60194,13 @@
         <v>0</v>
       </c>
       <c r="O776" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="P776" t="n">
         <v>0</v>
       </c>
       <c r="Q776" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="R776" t="n">
         <v>0</v>
@@ -60212,16 +60212,16 @@
         <v>0</v>
       </c>
       <c r="U776" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -60294,11 +60294,11 @@
     </row>
     <row r="778">
       <c r="A778" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -60371,11 +60371,11 @@
     </row>
     <row r="779">
       <c r="A779" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -60448,11 +60448,11 @@
     </row>
     <row r="780">
       <c r="A780" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -60525,11 +60525,11 @@
     </row>
     <row r="781">
       <c r="A781" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -60602,11 +60602,11 @@
     </row>
     <row r="782">
       <c r="A782" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -60679,11 +60679,11 @@
     </row>
     <row r="783">
       <c r="A783" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -60756,11 +60756,11 @@
     </row>
     <row r="784">
       <c r="A784" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -60833,11 +60833,11 @@
     </row>
     <row r="785">
       <c r="A785" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -60910,11 +60910,11 @@
     </row>
     <row r="786">
       <c r="A786" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -60987,11 +60987,11 @@
     </row>
     <row r="787">
       <c r="A787" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -61064,11 +61064,11 @@
     </row>
     <row r="788">
       <c r="A788" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -61141,11 +61141,11 @@
     </row>
     <row r="789">
       <c r="A789" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -61218,11 +61218,11 @@
     </row>
     <row r="790">
       <c r="A790" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -61272,13 +61272,13 @@
         <v>10000</v>
       </c>
       <c r="O790" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="P790" t="n">
         <v>5000</v>
       </c>
       <c r="Q790" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="R790" t="n">
         <v>5000</v>
@@ -61290,16 +61290,16 @@
         <v>0</v>
       </c>
       <c r="U790" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -61372,11 +61372,11 @@
     </row>
     <row r="792">
       <c r="A792" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -61449,11 +61449,11 @@
     </row>
     <row r="793">
       <c r="A793" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -61526,11 +61526,11 @@
     </row>
     <row r="794">
       <c r="A794" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -61603,11 +61603,11 @@
     </row>
     <row r="795">
       <c r="A795" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -61680,11 +61680,11 @@
     </row>
     <row r="796">
       <c r="A796" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -61757,11 +61757,11 @@
     </row>
     <row r="797">
       <c r="A797" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -61834,11 +61834,11 @@
     </row>
     <row r="798">
       <c r="A798" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -61911,11 +61911,11 @@
     </row>
     <row r="799">
       <c r="A799" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -61988,11 +61988,11 @@
     </row>
     <row r="800">
       <c r="A800" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -62065,11 +62065,11 @@
     </row>
     <row r="801">
       <c r="A801" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -62142,11 +62142,11 @@
     </row>
     <row r="802">
       <c r="A802" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -62219,11 +62219,11 @@
     </row>
     <row r="803">
       <c r="A803" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -62296,11 +62296,11 @@
     </row>
     <row r="804">
       <c r="A804" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -62373,11 +62373,11 @@
     </row>
     <row r="805">
       <c r="A805" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -62430,16 +62430,16 @@
         <v>0</v>
       </c>
       <c r="P805" t="n">
-        <v>15294</v>
+        <v>19980</v>
       </c>
       <c r="Q805" t="n">
-        <v>-15294</v>
+        <v>-19980</v>
       </c>
       <c r="R805" t="n">
         <v>0</v>
       </c>
       <c r="S805" t="n">
-        <v>15294</v>
+        <v>19980</v>
       </c>
       <c r="T805" t="n">
         <v>0</v>
@@ -62450,11 +62450,11 @@
     </row>
     <row r="806">
       <c r="A806" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -62507,16 +62507,16 @@
         <v>184583</v>
       </c>
       <c r="P806" t="n">
-        <v>177971</v>
+        <v>182657</v>
       </c>
       <c r="Q806" t="n">
-        <v>6612</v>
+        <v>1926</v>
       </c>
       <c r="R806" t="n">
         <v>135326</v>
       </c>
       <c r="S806" t="n">
-        <v>42645</v>
+        <v>47331</v>
       </c>
       <c r="T806" t="n">
         <v>400000</v>
@@ -62527,11 +62527,11 @@
     </row>
     <row r="807">
       <c r="A807" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -62604,11 +62604,11 @@
     </row>
     <row r="808">
       <c r="A808" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -62681,11 +62681,11 @@
     </row>
     <row r="809">
       <c r="A809" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -62758,11 +62758,11 @@
     </row>
     <row r="810">
       <c r="A810" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -62835,11 +62835,11 @@
     </row>
     <row r="811">
       <c r="A811" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -62912,11 +62912,11 @@
     </row>
     <row r="812">
       <c r="A812" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -62989,11 +62989,11 @@
     </row>
     <row r="813">
       <c r="A813" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -63066,11 +63066,11 @@
     </row>
     <row r="814">
       <c r="A814" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -63143,11 +63143,11 @@
     </row>
     <row r="815">
       <c r="A815" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -63220,11 +63220,11 @@
     </row>
     <row r="816">
       <c r="A816" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -63297,11 +63297,11 @@
     </row>
     <row r="817">
       <c r="A817" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -63374,11 +63374,11 @@
     </row>
     <row r="818">
       <c r="A818" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -63451,11 +63451,11 @@
     </row>
     <row r="819">
       <c r="A819" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -63528,11 +63528,11 @@
     </row>
     <row r="820">
       <c r="A820" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -63605,11 +63605,11 @@
     </row>
     <row r="821">
       <c r="A821" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -63682,11 +63682,11 @@
     </row>
     <row r="822">
       <c r="A822" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -63759,11 +63759,11 @@
     </row>
     <row r="823">
       <c r="A823" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>RELEXORC_07-04-2026.csv</t>
+          <t>RELEXORC_08-04-2026.csv</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -63813,10 +63813,10 @@
         <v>16930000</v>
       </c>
       <c r="O823" t="n">
-        <v>535261.05</v>
+        <v>561902.21</v>
       </c>
       <c r="P823" t="n">
-        <v>535261.05</v>
+        <v>561902.21</v>
       </c>
       <c r="Q823" t="n">
         <v>0</v>
@@ -63825,13 +63825,13 @@
         <v>535261.05</v>
       </c>
       <c r="S823" t="n">
-        <v>0</v>
+        <v>26641.16</v>
       </c>
       <c r="T823" t="n">
         <v>0</v>
       </c>
       <c r="U823" t="n">
-        <v>16394738.95</v>
+        <v>16368097.79</v>
       </c>
     </row>
   </sheetData>
@@ -63985,7 +63985,7 @@
         <v>46112</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -64071,7 +64071,7 @@
         <v>46112</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -64157,7 +64157,7 @@
         <v>46112</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -64243,7 +64243,7 @@
         <v>46112</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -64329,7 +64329,7 @@
         <v>46112</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -64415,7 +64415,7 @@
         <v>46112</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -64501,7 +64501,7 @@
         <v>46112</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -64587,7 +64587,7 @@
         <v>46112</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -64662,10 +64662,10 @@
         <v>19401015.72</v>
       </c>
       <c r="Y9" t="n">
-        <v>19401015.72</v>
+        <v>12901015.72</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-6499999.999999998</v>
       </c>
     </row>
     <row r="10">
@@ -64673,7 +64673,7 @@
         <v>46112</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -64759,7 +64759,7 @@
         <v>46112</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -64834,10 +64834,10 @@
         <v>30208318.24</v>
       </c>
       <c r="Y11" t="n">
-        <v>27724491.19</v>
+        <v>21224491.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>-2483827.049999997</v>
+        <v>-8983827.049999997</v>
       </c>
     </row>
     <row r="12">
@@ -64845,7 +64845,7 @@
         <v>46112</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -64893,19 +64893,19 @@
         <v>76455.60000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>76455.60000000001</v>
+        <v>78075.60000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1620</v>
       </c>
       <c r="R12" t="n">
         <v>37452.6</v>
       </c>
       <c r="S12" t="n">
-        <v>38532.6</v>
+        <v>39207.6</v>
       </c>
       <c r="T12" t="n">
-        <v>1080</v>
+        <v>1755</v>
       </c>
       <c r="U12" t="n">
         <v>372.6</v>
@@ -64920,10 +64920,10 @@
         <v>2712344.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>2712344.4</v>
+        <v>2710724.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-1620</v>
       </c>
     </row>
     <row r="13">
@@ -64931,7 +64931,7 @@
         <v>46112</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -65017,7 +65017,7 @@
         <v>46112</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -65103,7 +65103,7 @@
         <v>46112</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -65189,7 +65189,7 @@
         <v>46112</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -65275,7 +65275,7 @@
         <v>46112</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -65341,10 +65341,10 @@
         <v>4875485.05</v>
       </c>
       <c r="V17" t="n">
-        <v>6550089.63</v>
+        <v>7195172.54</v>
       </c>
       <c r="W17" t="n">
-        <v>1674604.58</v>
+        <v>2319687.49</v>
       </c>
       <c r="X17" t="n">
         <v>22791039.49</v>
@@ -65361,7 +65361,7 @@
         <v>46112</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -65447,7 +65447,7 @@
         <v>46112</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -65513,10 +65513,10 @@
         <v>60690650.18</v>
       </c>
       <c r="V19" t="n">
-        <v>79635166.11</v>
+        <v>85084092.14</v>
       </c>
       <c r="W19" t="n">
-        <v>18944515.93</v>
+        <v>24393441.96</v>
       </c>
       <c r="X19" t="n">
         <v>278444787.27</v>
@@ -65533,7 +65533,7 @@
         <v>46112</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -65619,7 +65619,7 @@
         <v>46112</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -65705,7 +65705,7 @@
         <v>46112</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -65791,7 +65791,7 @@
         <v>46112</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -65877,7 +65877,7 @@
         <v>46112</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -65963,7 +65963,7 @@
         <v>46112</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -66049,7 +66049,7 @@
         <v>46112</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -66135,7 +66135,7 @@
         <v>46112</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -66221,7 +66221,7 @@
         <v>46112</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -66307,7 +66307,7 @@
         <v>46112</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -66393,7 +66393,7 @@
         <v>46112</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -66479,7 +66479,7 @@
         <v>46112</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -66565,7 +66565,7 @@
         <v>46112</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -66651,7 +66651,7 @@
         <v>46112</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -66737,7 +66737,7 @@
         <v>46112</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -66823,7 +66823,7 @@
         <v>46112</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -66909,7 +66909,7 @@
         <v>46112</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -66995,7 +66995,7 @@
         <v>46112</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -67081,7 +67081,7 @@
         <v>46112</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -67167,7 +67167,7 @@
         <v>46112</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -67224,10 +67224,10 @@
         <v>159398</v>
       </c>
       <c r="S39" t="n">
-        <v>177971</v>
+        <v>182657</v>
       </c>
       <c r="T39" t="n">
-        <v>18573</v>
+        <v>23259</v>
       </c>
       <c r="U39" t="n">
         <v>135326</v>
@@ -67253,7 +67253,7 @@
         <v>46112</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -67339,7 +67339,7 @@
         <v>46112</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -67425,7 +67425,7 @@
         <v>46112</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -67511,7 +67511,7 @@
         <v>46112</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -67597,7 +67597,7 @@
         <v>46112</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -67683,7 +67683,7 @@
         <v>46112</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -67769,7 +67769,7 @@
         <v>46112</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -67855,7 +67855,7 @@
         <v>46112</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -67941,7 +67941,7 @@
         <v>46112</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -68027,7 +68027,7 @@
         <v>46112</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -68113,7 +68113,7 @@
         <v>46112</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -68199,7 +68199,7 @@
         <v>46112</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -68285,7 +68285,7 @@
         <v>46112</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -68342,10 +68342,10 @@
         <v>63339.45</v>
       </c>
       <c r="S52" t="n">
-        <v>68454.75</v>
+        <v>77180.85000000001</v>
       </c>
       <c r="T52" t="n">
-        <v>5115.300000000003</v>
+        <v>13841.40000000001</v>
       </c>
       <c r="U52" t="n">
         <v>63339.45</v>
@@ -68371,7 +68371,7 @@
         <v>46112</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -68457,7 +68457,7 @@
         <v>46112</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -68514,10 +68514,10 @@
         <v>123950</v>
       </c>
       <c r="S54" t="n">
-        <v>146221.5</v>
+        <v>154261.5</v>
       </c>
       <c r="T54" t="n">
-        <v>22271.5</v>
+        <v>30311.5</v>
       </c>
       <c r="U54" t="n">
         <v>89780</v>
@@ -68543,7 +68543,7 @@
         <v>46112</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -68629,7 +68629,7 @@
         <v>46112</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -68677,10 +68677,10 @@
         <v>10000</v>
       </c>
       <c r="P56" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="R56" t="n">
         <v>5000</v>
@@ -68704,10 +68704,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="57">
@@ -68715,7 +68715,7 @@
         <v>46112</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -68801,7 +68801,7 @@
         <v>46112</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -68887,7 +68887,7 @@
         <v>46112</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -68973,7 +68973,7 @@
         <v>46112</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -69059,7 +69059,7 @@
         <v>46112</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -69145,7 +69145,7 @@
         <v>46112</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -69231,7 +69231,7 @@
         <v>46112</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -69317,7 +69317,7 @@
         <v>46112</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -69403,7 +69403,7 @@
         <v>46112</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -69489,7 +69489,7 @@
         <v>46112</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -69575,7 +69575,7 @@
         <v>46112</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -69661,7 +69661,7 @@
         <v>46112</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -69747,7 +69747,7 @@
         <v>46112</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -69833,7 +69833,7 @@
         <v>46112</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -69919,7 +69919,7 @@
         <v>46112</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -70005,7 +70005,7 @@
         <v>46112</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -70091,7 +70091,7 @@
         <v>46112</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -70177,7 +70177,7 @@
         <v>46112</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -70263,7 +70263,7 @@
         <v>46112</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -70349,7 +70349,7 @@
         <v>46112</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -70435,7 +70435,7 @@
         <v>46112</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -70521,7 +70521,7 @@
         <v>46112</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -70607,7 +70607,7 @@
         <v>46112</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -70693,7 +70693,7 @@
         <v>46112</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -70779,7 +70779,7 @@
         <v>46112</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -70865,7 +70865,7 @@
         <v>46112</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -70951,7 +70951,7 @@
         <v>46112</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -71037,7 +71037,7 @@
         <v>46112</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -71123,7 +71123,7 @@
         <v>46112</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -71209,7 +71209,7 @@
         <v>46112</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -71295,7 +71295,7 @@
         <v>46112</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -71381,7 +71381,7 @@
         <v>46112</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -71467,7 +71467,7 @@
         <v>46112</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -71553,7 +71553,7 @@
         <v>46112</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -71639,7 +71639,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -71725,7 +71725,7 @@
         <v>46112</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -71811,7 +71811,7 @@
         <v>46112</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -71897,7 +71897,7 @@
         <v>46112</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -71983,7 +71983,7 @@
         <v>46112</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -72069,7 +72069,7 @@
         <v>46112</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -72155,7 +72155,7 @@
         <v>46112</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -72241,7 +72241,7 @@
         <v>46112</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -72327,7 +72327,7 @@
         <v>46112</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -72413,7 +72413,7 @@
         <v>46112</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -72499,7 +72499,7 @@
         <v>46112</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -72585,7 +72585,7 @@
         <v>46112</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -72671,7 +72671,7 @@
         <v>46112</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -72757,7 +72757,7 @@
         <v>46112</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -72843,7 +72843,7 @@
         <v>46112</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -72929,7 +72929,7 @@
         <v>46112</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -73015,7 +73015,7 @@
         <v>46112</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -73101,7 +73101,7 @@
         <v>46112</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -73187,7 +73187,7 @@
         <v>46112</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -73273,7 +73273,7 @@
         <v>46112</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -73359,7 +73359,7 @@
         <v>46112</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -73445,7 +73445,7 @@
         <v>46112</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -73531,7 +73531,7 @@
         <v>46112</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -73617,7 +73617,7 @@
         <v>46112</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -73703,7 +73703,7 @@
         <v>46112</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -73789,7 +73789,7 @@
         <v>46112</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -73875,7 +73875,7 @@
         <v>46112</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -73961,7 +73961,7 @@
         <v>46112</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -74018,10 +74018,10 @@
         <v>993289</v>
       </c>
       <c r="S118" t="n">
-        <v>993289</v>
+        <v>997489</v>
       </c>
       <c r="T118" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="U118" t="n">
         <v>993289</v>
@@ -74047,7 +74047,7 @@
         <v>46112</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -74133,7 +74133,7 @@
         <v>46112</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -74219,7 +74219,7 @@
         <v>46112</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -74305,7 +74305,7 @@
         <v>46112</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -74391,7 +74391,7 @@
         <v>46112</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -74477,7 +74477,7 @@
         <v>46112</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -74563,7 +74563,7 @@
         <v>46112</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -74649,7 +74649,7 @@
         <v>46112</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -74735,7 +74735,7 @@
         <v>46112</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -74783,19 +74783,19 @@
         <v>535261.05</v>
       </c>
       <c r="P127" t="n">
-        <v>535261.05</v>
+        <v>561902.21</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>26641.15999999992</v>
       </c>
       <c r="R127" t="n">
         <v>535261.05</v>
       </c>
       <c r="S127" t="n">
-        <v>535261.05</v>
+        <v>561902.21</v>
       </c>
       <c r="T127" t="n">
-        <v>0</v>
+        <v>26641.15999999992</v>
       </c>
       <c r="U127" t="n">
         <v>535261.05</v>
@@ -74810,10 +74810,10 @@
         <v>16394738.95</v>
       </c>
       <c r="Y127" t="n">
-        <v>16394738.95</v>
+        <v>16368097.79</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>-26641.16000000015</v>
       </c>
     </row>
   </sheetData>

--- a/Base_Consolidada_SIAFI.xlsx
+++ b/Base_Consolidada_SIAFI.xlsx
@@ -44586,11 +44586,11 @@
     </row>
     <row r="574">
       <c r="A574" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -44663,11 +44663,11 @@
     </row>
     <row r="575">
       <c r="A575" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -44740,11 +44740,11 @@
     </row>
     <row r="576">
       <c r="A576" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -44817,11 +44817,11 @@
     </row>
     <row r="577">
       <c r="A577" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -44894,11 +44894,11 @@
     </row>
     <row r="578">
       <c r="A578" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -44971,11 +44971,11 @@
     </row>
     <row r="579">
       <c r="A579" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -45048,11 +45048,11 @@
     </row>
     <row r="580">
       <c r="A580" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -45125,11 +45125,11 @@
     </row>
     <row r="581">
       <c r="A581" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -45202,11 +45202,11 @@
     </row>
     <row r="582">
       <c r="A582" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -45279,11 +45279,11 @@
     </row>
     <row r="583">
       <c r="A583" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -45356,11 +45356,11 @@
     </row>
     <row r="584">
       <c r="A584" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -45433,11 +45433,11 @@
     </row>
     <row r="585">
       <c r="A585" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -45510,11 +45510,11 @@
     </row>
     <row r="586">
       <c r="A586" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -45587,11 +45587,11 @@
     </row>
     <row r="587">
       <c r="A587" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -45664,11 +45664,11 @@
     </row>
     <row r="588">
       <c r="A588" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -45721,16 +45721,16 @@
         <v>0</v>
       </c>
       <c r="P588" t="n">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="Q588" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="R588" t="n">
         <v>0</v>
       </c>
       <c r="S588" t="n">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="T588" t="n">
         <v>0</v>
@@ -45741,11 +45741,11 @@
     </row>
     <row r="589">
       <c r="A589" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -45798,16 +45798,16 @@
         <v>1305000</v>
       </c>
       <c r="P589" t="n">
-        <v>833400</v>
+        <v>832000</v>
       </c>
       <c r="Q589" t="n">
-        <v>471600</v>
+        <v>473000</v>
       </c>
       <c r="R589" t="n">
         <v>555600</v>
       </c>
       <c r="S589" t="n">
-        <v>277800</v>
+        <v>276400</v>
       </c>
       <c r="T589" t="n">
         <v>0</v>
@@ -45818,11 +45818,11 @@
     </row>
     <row r="590">
       <c r="A590" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -45895,11 +45895,11 @@
     </row>
     <row r="591">
       <c r="A591" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -45972,11 +45972,11 @@
     </row>
     <row r="592">
       <c r="A592" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -46049,11 +46049,11 @@
     </row>
     <row r="593">
       <c r="A593" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -46126,11 +46126,11 @@
     </row>
     <row r="594">
       <c r="A594" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -46203,11 +46203,11 @@
     </row>
     <row r="595">
       <c r="A595" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -46280,11 +46280,11 @@
     </row>
     <row r="596">
       <c r="A596" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -46357,11 +46357,11 @@
     </row>
     <row r="597">
       <c r="A597" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -46434,11 +46434,11 @@
     </row>
     <row r="598">
       <c r="A598" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -46511,11 +46511,11 @@
     </row>
     <row r="599">
       <c r="A599" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -46588,11 +46588,11 @@
     </row>
     <row r="600">
       <c r="A600" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -46665,11 +46665,11 @@
     </row>
     <row r="601">
       <c r="A601" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -46742,11 +46742,11 @@
     </row>
     <row r="602">
       <c r="A602" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -46819,11 +46819,11 @@
     </row>
     <row r="603">
       <c r="A603" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -46896,11 +46896,11 @@
     </row>
     <row r="604">
       <c r="A604" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -46973,11 +46973,11 @@
     </row>
     <row r="605">
       <c r="A605" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -47050,11 +47050,11 @@
     </row>
     <row r="606">
       <c r="A606" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -47127,11 +47127,11 @@
     </row>
     <row r="607">
       <c r="A607" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -47204,11 +47204,11 @@
     </row>
     <row r="608">
       <c r="A608" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -47281,11 +47281,11 @@
     </row>
     <row r="609">
       <c r="A609" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -47358,11 +47358,11 @@
     </row>
     <row r="610">
       <c r="A610" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -47435,11 +47435,11 @@
     </row>
     <row r="611">
       <c r="A611" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -47512,11 +47512,11 @@
     </row>
     <row r="612">
       <c r="A612" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -47589,11 +47589,11 @@
     </row>
     <row r="613">
       <c r="A613" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -47666,11 +47666,11 @@
     </row>
     <row r="614">
       <c r="A614" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -47743,11 +47743,11 @@
     </row>
     <row r="615">
       <c r="A615" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -47800,16 +47800,16 @@
         <v>0</v>
       </c>
       <c r="P615" t="n">
-        <v>0</v>
+        <v>175456</v>
       </c>
       <c r="Q615" t="n">
-        <v>0</v>
+        <v>-175456</v>
       </c>
       <c r="R615" t="n">
         <v>0</v>
       </c>
       <c r="S615" t="n">
-        <v>0</v>
+        <v>175456</v>
       </c>
       <c r="T615" t="n">
         <v>0</v>
@@ -47820,11 +47820,11 @@
     </row>
     <row r="616">
       <c r="A616" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -47877,16 +47877,16 @@
         <v>469806</v>
       </c>
       <c r="P616" t="n">
-        <v>0</v>
+        <v>175456</v>
       </c>
       <c r="Q616" t="n">
-        <v>469806</v>
+        <v>294350</v>
       </c>
       <c r="R616" t="n">
         <v>0</v>
       </c>
       <c r="S616" t="n">
-        <v>0</v>
+        <v>175456</v>
       </c>
       <c r="T616" t="n">
         <v>0</v>
@@ -47897,11 +47897,11 @@
     </row>
     <row r="617">
       <c r="A617" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -47974,11 +47974,11 @@
     </row>
     <row r="618">
       <c r="A618" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -48051,11 +48051,11 @@
     </row>
     <row r="619">
       <c r="A619" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -48128,11 +48128,11 @@
     </row>
     <row r="620">
       <c r="A620" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -48205,11 +48205,11 @@
     </row>
     <row r="621">
       <c r="A621" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -48282,11 +48282,11 @@
     </row>
     <row r="622">
       <c r="A622" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -48359,11 +48359,11 @@
     </row>
     <row r="623">
       <c r="A623" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -48436,11 +48436,11 @@
     </row>
     <row r="624">
       <c r="A624" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -48513,11 +48513,11 @@
     </row>
     <row r="625">
       <c r="A625" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -48590,11 +48590,11 @@
     </row>
     <row r="626">
       <c r="A626" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -48667,11 +48667,11 @@
     </row>
     <row r="627">
       <c r="A627" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -48744,11 +48744,11 @@
     </row>
     <row r="628">
       <c r="A628" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -48821,11 +48821,11 @@
     </row>
     <row r="629">
       <c r="A629" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -48898,11 +48898,11 @@
     </row>
     <row r="630">
       <c r="A630" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -48975,11 +48975,11 @@
     </row>
     <row r="631">
       <c r="A631" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -49052,11 +49052,11 @@
     </row>
     <row r="632">
       <c r="A632" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -49129,11 +49129,11 @@
     </row>
     <row r="633">
       <c r="A633" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -49206,11 +49206,11 @@
     </row>
     <row r="634">
       <c r="A634" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -49283,11 +49283,11 @@
     </row>
     <row r="635">
       <c r="A635" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -49360,11 +49360,11 @@
     </row>
     <row r="636">
       <c r="A636" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -49437,11 +49437,11 @@
     </row>
     <row r="637">
       <c r="A637" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -49514,11 +49514,11 @@
     </row>
     <row r="638">
       <c r="A638" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -49591,11 +49591,11 @@
     </row>
     <row r="639">
       <c r="A639" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -49668,11 +49668,11 @@
     </row>
     <row r="640">
       <c r="A640" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -49745,11 +49745,11 @@
     </row>
     <row r="641">
       <c r="A641" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -49822,11 +49822,11 @@
     </row>
     <row r="642">
       <c r="A642" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -49899,11 +49899,11 @@
     </row>
     <row r="643">
       <c r="A643" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -49976,11 +49976,11 @@
     </row>
     <row r="644">
       <c r="A644" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -50053,11 +50053,11 @@
     </row>
     <row r="645">
       <c r="A645" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -50130,11 +50130,11 @@
     </row>
     <row r="646">
       <c r="A646" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -50187,16 +50187,16 @@
         <v>0</v>
       </c>
       <c r="P646" t="n">
-        <v>4200</v>
+        <v>452802.4</v>
       </c>
       <c r="Q646" t="n">
-        <v>-4200</v>
+        <v>-452802.4</v>
       </c>
       <c r="R646" t="n">
         <v>0</v>
       </c>
       <c r="S646" t="n">
-        <v>4200</v>
+        <v>452802.4</v>
       </c>
       <c r="T646" t="n">
         <v>0</v>
@@ -50207,11 +50207,11 @@
     </row>
     <row r="647">
       <c r="A647" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -50264,16 +50264,16 @@
         <v>3126083.6</v>
       </c>
       <c r="P647" t="n">
-        <v>997489</v>
+        <v>1446091.4</v>
       </c>
       <c r="Q647" t="n">
-        <v>2128594.6</v>
+        <v>1679992.2</v>
       </c>
       <c r="R647" t="n">
         <v>993289</v>
       </c>
       <c r="S647" t="n">
-        <v>4200</v>
+        <v>452802.4</v>
       </c>
       <c r="T647" t="n">
         <v>0</v>
@@ -50284,11 +50284,11 @@
     </row>
     <row r="648">
       <c r="A648" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -50361,11 +50361,11 @@
     </row>
     <row r="649">
       <c r="A649" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -50438,11 +50438,11 @@
     </row>
     <row r="650">
       <c r="A650" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -50515,11 +50515,11 @@
     </row>
     <row r="651">
       <c r="A651" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -50592,11 +50592,11 @@
     </row>
     <row r="652">
       <c r="A652" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -50669,11 +50669,11 @@
     </row>
     <row r="653">
       <c r="A653" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -50746,11 +50746,11 @@
     </row>
     <row r="654">
       <c r="A654" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -50823,11 +50823,11 @@
     </row>
     <row r="655">
       <c r="A655" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -50900,11 +50900,11 @@
     </row>
     <row r="656">
       <c r="A656" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -50977,11 +50977,11 @@
     </row>
     <row r="657">
       <c r="A657" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -51054,11 +51054,11 @@
     </row>
     <row r="658">
       <c r="A658" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -51131,11 +51131,11 @@
     </row>
     <row r="659">
       <c r="A659" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -51208,11 +51208,11 @@
     </row>
     <row r="660">
       <c r="A660" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -51265,16 +51265,16 @@
         <v>0</v>
       </c>
       <c r="P660" t="n">
-        <v>777587.2</v>
+        <v>1510687.7</v>
       </c>
       <c r="Q660" t="n">
-        <v>-777587.2</v>
+        <v>-1510687.7</v>
       </c>
       <c r="R660" t="n">
         <v>0</v>
       </c>
       <c r="S660" t="n">
-        <v>777587.2</v>
+        <v>1510687.7</v>
       </c>
       <c r="T660" t="n">
         <v>0</v>
@@ -51285,11 +51285,11 @@
     </row>
     <row r="661">
       <c r="A661" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -51342,16 +51342,16 @@
         <v>11419975.46</v>
       </c>
       <c r="P661" t="n">
-        <v>5657120.12</v>
+        <v>6390220.62</v>
       </c>
       <c r="Q661" t="n">
-        <v>5762855.340000001</v>
+        <v>5029754.840000001</v>
       </c>
       <c r="R661" t="n">
         <v>3507323.16</v>
       </c>
       <c r="S661" t="n">
-        <v>2149796.96</v>
+        <v>2882897.46</v>
       </c>
       <c r="T661" t="n">
         <v>15000000</v>
@@ -51362,11 +51362,11 @@
     </row>
     <row r="662">
       <c r="A662" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -51439,11 +51439,11 @@
     </row>
     <row r="663">
       <c r="A663" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -51516,11 +51516,11 @@
     </row>
     <row r="664">
       <c r="A664" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -51593,11 +51593,11 @@
     </row>
     <row r="665">
       <c r="A665" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -51670,11 +51670,11 @@
     </row>
     <row r="666">
       <c r="A666" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -51747,11 +51747,11 @@
     </row>
     <row r="667">
       <c r="A667" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -51824,11 +51824,11 @@
     </row>
     <row r="668">
       <c r="A668" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -51901,11 +51901,11 @@
     </row>
     <row r="669">
       <c r="A669" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -51978,11 +51978,11 @@
     </row>
     <row r="670">
       <c r="A670" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -52055,11 +52055,11 @@
     </row>
     <row r="671">
       <c r="A671" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -52132,11 +52132,11 @@
     </row>
     <row r="672">
       <c r="A672" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -52209,11 +52209,11 @@
     </row>
     <row r="673">
       <c r="A673" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -52286,11 +52286,11 @@
     </row>
     <row r="674">
       <c r="A674" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -52363,11 +52363,11 @@
     </row>
     <row r="675">
       <c r="A675" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -52440,11 +52440,11 @@
     </row>
     <row r="676">
       <c r="A676" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -52517,11 +52517,11 @@
     </row>
     <row r="677">
       <c r="A677" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -52594,11 +52594,11 @@
     </row>
     <row r="678">
       <c r="A678" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -52671,11 +52671,11 @@
     </row>
     <row r="679">
       <c r="A679" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -52748,11 +52748,11 @@
     </row>
     <row r="680">
       <c r="A680" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -52825,11 +52825,11 @@
     </row>
     <row r="681">
       <c r="A681" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -52902,11 +52902,11 @@
     </row>
     <row r="682">
       <c r="A682" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -52979,11 +52979,11 @@
     </row>
     <row r="683">
       <c r="A683" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -53056,11 +53056,11 @@
     </row>
     <row r="684">
       <c r="A684" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -53133,11 +53133,11 @@
     </row>
     <row r="685">
       <c r="A685" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -53210,11 +53210,11 @@
     </row>
     <row r="686">
       <c r="A686" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -53287,11 +53287,11 @@
     </row>
     <row r="687">
       <c r="A687" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -53364,11 +53364,11 @@
     </row>
     <row r="688">
       <c r="A688" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -53441,11 +53441,11 @@
     </row>
     <row r="689">
       <c r="A689" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -53518,11 +53518,11 @@
     </row>
     <row r="690">
       <c r="A690" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -53595,11 +53595,11 @@
     </row>
     <row r="691">
       <c r="A691" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -53672,11 +53672,11 @@
     </row>
     <row r="692">
       <c r="A692" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -53749,11 +53749,11 @@
     </row>
     <row r="693">
       <c r="A693" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -53826,11 +53826,11 @@
     </row>
     <row r="694">
       <c r="A694" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -53903,11 +53903,11 @@
     </row>
     <row r="695">
       <c r="A695" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -53980,11 +53980,11 @@
     </row>
     <row r="696">
       <c r="A696" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -54057,11 +54057,11 @@
     </row>
     <row r="697">
       <c r="A697" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -54134,11 +54134,11 @@
     </row>
     <row r="698">
       <c r="A698" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -54211,11 +54211,11 @@
     </row>
     <row r="699">
       <c r="A699" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -54288,11 +54288,11 @@
     </row>
     <row r="700">
       <c r="A700" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -54365,11 +54365,11 @@
     </row>
     <row r="701">
       <c r="A701" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -54442,11 +54442,11 @@
     </row>
     <row r="702">
       <c r="A702" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -54505,10 +54505,10 @@
         <v>0</v>
       </c>
       <c r="R702" t="n">
-        <v>0</v>
+        <v>14714.66</v>
       </c>
       <c r="S702" t="n">
-        <v>0</v>
+        <v>-14714.66</v>
       </c>
       <c r="T702" t="n">
         <v>0</v>
@@ -54519,11 +54519,11 @@
     </row>
     <row r="703">
       <c r="A703" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -54582,10 +54582,10 @@
         <v>0</v>
       </c>
       <c r="R703" t="n">
-        <v>29429.32</v>
+        <v>44143.98</v>
       </c>
       <c r="S703" t="n">
-        <v>14714.66</v>
+        <v>0</v>
       </c>
       <c r="T703" t="n">
         <v>0</v>
@@ -54596,11 +54596,11 @@
     </row>
     <row r="704">
       <c r="A704" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -54659,10 +54659,10 @@
         <v>0</v>
       </c>
       <c r="R704" t="n">
-        <v>24365573.77</v>
+        <v>24382191.67</v>
       </c>
       <c r="S704" t="n">
-        <v>-24365573.77</v>
+        <v>-24382191.67</v>
       </c>
       <c r="T704" t="n">
         <v>0</v>
@@ -54673,11 +54673,11 @@
     </row>
     <row r="705">
       <c r="A705" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -54736,10 +54736,10 @@
         <v>0</v>
       </c>
       <c r="R705" t="n">
-        <v>85084092.14</v>
+        <v>85100710.04000001</v>
       </c>
       <c r="S705" t="n">
-        <v>3028463.59</v>
+        <v>3011845.69</v>
       </c>
       <c r="T705" t="n">
         <v>0</v>
@@ -54750,11 +54750,11 @@
     </row>
     <row r="706">
       <c r="A706" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -54827,11 +54827,11 @@
     </row>
     <row r="707">
       <c r="A707" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -54904,11 +54904,11 @@
     </row>
     <row r="708">
       <c r="A708" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -54981,11 +54981,11 @@
     </row>
     <row r="709">
       <c r="A709" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -55058,11 +55058,11 @@
     </row>
     <row r="710">
       <c r="A710" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -55135,11 +55135,11 @@
     </row>
     <row r="711">
       <c r="A711" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -55212,11 +55212,11 @@
     </row>
     <row r="712">
       <c r="A712" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -55289,11 +55289,11 @@
     </row>
     <row r="713">
       <c r="A713" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -55366,11 +55366,11 @@
     </row>
     <row r="714">
       <c r="A714" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -55443,11 +55443,11 @@
     </row>
     <row r="715">
       <c r="A715" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -55520,11 +55520,11 @@
     </row>
     <row r="716">
       <c r="A716" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -55597,11 +55597,11 @@
     </row>
     <row r="717">
       <c r="A717" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -55674,11 +55674,11 @@
     </row>
     <row r="718">
       <c r="A718" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -55751,11 +55751,11 @@
     </row>
     <row r="719">
       <c r="A719" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -55828,11 +55828,11 @@
     </row>
     <row r="720">
       <c r="A720" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -55891,10 +55891,10 @@
         <v>0</v>
       </c>
       <c r="R720" t="n">
-        <v>0</v>
+        <v>220812.59</v>
       </c>
       <c r="S720" t="n">
-        <v>0</v>
+        <v>-220812.59</v>
       </c>
       <c r="T720" t="n">
         <v>0</v>
@@ -55905,11 +55905,11 @@
     </row>
     <row r="721">
       <c r="A721" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -55968,10 +55968,10 @@
         <v>692827.87</v>
       </c>
       <c r="R721" t="n">
-        <v>0</v>
+        <v>220812.59</v>
       </c>
       <c r="S721" t="n">
-        <v>220812.59</v>
+        <v>0</v>
       </c>
       <c r="T721" t="n">
         <v>0</v>
@@ -55982,11 +55982,11 @@
     </row>
     <row r="722">
       <c r="A722" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -56059,11 +56059,11 @@
     </row>
     <row r="723">
       <c r="A723" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -56136,11 +56136,11 @@
     </row>
     <row r="724">
       <c r="A724" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -56213,11 +56213,11 @@
     </row>
     <row r="725">
       <c r="A725" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -56290,11 +56290,11 @@
     </row>
     <row r="726">
       <c r="A726" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -56367,11 +56367,11 @@
     </row>
     <row r="727">
       <c r="A727" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -56444,11 +56444,11 @@
     </row>
     <row r="728">
       <c r="A728" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -56521,11 +56521,11 @@
     </row>
     <row r="729">
       <c r="A729" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -56598,11 +56598,11 @@
     </row>
     <row r="730">
       <c r="A730" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -56675,11 +56675,11 @@
     </row>
     <row r="731">
       <c r="A731" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -56752,11 +56752,11 @@
     </row>
     <row r="732">
       <c r="A732" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -56806,10 +56806,10 @@
         <v>0</v>
       </c>
       <c r="O732" t="n">
-        <v>26641.16</v>
+        <v>47028.96</v>
       </c>
       <c r="P732" t="n">
-        <v>26641.16</v>
+        <v>47028.96</v>
       </c>
       <c r="Q732" t="n">
         <v>0</v>
@@ -56818,22 +56818,22 @@
         <v>0</v>
       </c>
       <c r="S732" t="n">
-        <v>26641.16</v>
+        <v>47028.96</v>
       </c>
       <c r="T732" t="n">
         <v>0</v>
       </c>
       <c r="U732" t="n">
-        <v>-26641.16</v>
+        <v>-47028.96</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -56906,11 +56906,11 @@
     </row>
     <row r="734">
       <c r="A734" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -56983,11 +56983,11 @@
     </row>
     <row r="735">
       <c r="A735" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -57060,11 +57060,11 @@
     </row>
     <row r="736">
       <c r="A736" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -57137,11 +57137,11 @@
     </row>
     <row r="737">
       <c r="A737" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -57214,11 +57214,11 @@
     </row>
     <row r="738">
       <c r="A738" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -57291,11 +57291,11 @@
     </row>
     <row r="739">
       <c r="A739" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -57368,11 +57368,11 @@
     </row>
     <row r="740">
       <c r="A740" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -57445,11 +57445,11 @@
     </row>
     <row r="741">
       <c r="A741" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -57502,16 +57502,16 @@
         <v>0</v>
       </c>
       <c r="P741" t="n">
-        <v>33458.33</v>
+        <v>40157.4</v>
       </c>
       <c r="Q741" t="n">
-        <v>-33458.33</v>
+        <v>-40157.4</v>
       </c>
       <c r="R741" t="n">
         <v>0</v>
       </c>
       <c r="S741" t="n">
-        <v>33458.33</v>
+        <v>40157.4</v>
       </c>
       <c r="T741" t="n">
         <v>0</v>
@@ -57522,11 +57522,11 @@
     </row>
     <row r="742">
       <c r="A742" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -57579,16 +57579,16 @@
         <v>1405964.1</v>
       </c>
       <c r="P742" t="n">
-        <v>640299.49</v>
+        <v>646998.5600000001</v>
       </c>
       <c r="Q742" t="n">
-        <v>765664.6100000001</v>
+        <v>758965.54</v>
       </c>
       <c r="R742" t="n">
         <v>296021.27</v>
       </c>
       <c r="S742" t="n">
-        <v>344278.22</v>
+        <v>350977.29</v>
       </c>
       <c r="T742" t="n">
         <v>1500000</v>
@@ -57599,11 +57599,11 @@
     </row>
     <row r="743">
       <c r="A743" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -57676,11 +57676,11 @@
     </row>
     <row r="744">
       <c r="A744" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -57753,11 +57753,11 @@
     </row>
     <row r="745">
       <c r="A745" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -57830,11 +57830,11 @@
     </row>
     <row r="746">
       <c r="A746" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -57907,11 +57907,11 @@
     </row>
     <row r="747">
       <c r="A747" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -57984,11 +57984,11 @@
     </row>
     <row r="748">
       <c r="A748" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -58061,11 +58061,11 @@
     </row>
     <row r="749">
       <c r="A749" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -58118,16 +58118,16 @@
         <v>0</v>
       </c>
       <c r="P749" t="n">
-        <v>15000</v>
+        <v>67457.17999999999</v>
       </c>
       <c r="Q749" t="n">
-        <v>-15000</v>
+        <v>-67457.17999999999</v>
       </c>
       <c r="R749" t="n">
         <v>221030.41</v>
       </c>
       <c r="S749" t="n">
-        <v>-206030.41</v>
+        <v>-153573.23</v>
       </c>
       <c r="T749" t="n">
         <v>7222950.51</v>
@@ -58138,11 +58138,11 @@
     </row>
     <row r="750">
       <c r="A750" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -58195,16 +58195,16 @@
         <v>15388887.32</v>
       </c>
       <c r="P750" t="n">
-        <v>5845968.76</v>
+        <v>5898425.94</v>
       </c>
       <c r="Q750" t="n">
-        <v>9542918.560000001</v>
+        <v>9490461.379999999</v>
       </c>
       <c r="R750" t="n">
         <v>4367980.05</v>
       </c>
       <c r="S750" t="n">
-        <v>1477988.71</v>
+        <v>1530445.89</v>
       </c>
       <c r="T750" t="n">
         <v>27222950.51</v>
@@ -58215,11 +58215,11 @@
     </row>
     <row r="751">
       <c r="A751" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -58292,11 +58292,11 @@
     </row>
     <row r="752">
       <c r="A752" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -58369,11 +58369,11 @@
     </row>
     <row r="753">
       <c r="A753" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -58423,34 +58423,34 @@
         <v>0</v>
       </c>
       <c r="O753" t="n">
-        <v>1620</v>
+        <v>2700</v>
       </c>
       <c r="P753" t="n">
-        <v>1755</v>
+        <v>3015</v>
       </c>
       <c r="Q753" t="n">
-        <v>-135</v>
+        <v>-315</v>
       </c>
       <c r="R753" t="n">
         <v>0</v>
       </c>
       <c r="S753" t="n">
-        <v>1755</v>
+        <v>3015</v>
       </c>
       <c r="T753" t="n">
         <v>0</v>
       </c>
       <c r="U753" t="n">
-        <v>-1620</v>
+        <v>-2700</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -58500,34 +58500,34 @@
         <v>2788800</v>
       </c>
       <c r="O754" t="n">
-        <v>78075.60000000001</v>
+        <v>79155.60000000001</v>
       </c>
       <c r="P754" t="n">
-        <v>39207.6</v>
+        <v>40467.6</v>
       </c>
       <c r="Q754" t="n">
-        <v>38868.00000000001</v>
+        <v>38688.00000000001</v>
       </c>
       <c r="R754" t="n">
         <v>372.6</v>
       </c>
       <c r="S754" t="n">
-        <v>38835</v>
+        <v>40095</v>
       </c>
       <c r="T754" t="n">
         <v>0</v>
       </c>
       <c r="U754" t="n">
-        <v>2710724.4</v>
+        <v>2709644.4</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -58600,11 +58600,11 @@
     </row>
     <row r="756">
       <c r="A756" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -58677,11 +58677,11 @@
     </row>
     <row r="757">
       <c r="A757" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -58754,11 +58754,11 @@
     </row>
     <row r="758">
       <c r="A758" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -58831,11 +58831,11 @@
     </row>
     <row r="759">
       <c r="A759" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -58908,11 +58908,11 @@
     </row>
     <row r="760">
       <c r="A760" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -58985,11 +58985,11 @@
     </row>
     <row r="761">
       <c r="A761" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -59062,11 +59062,11 @@
     </row>
     <row r="762">
       <c r="A762" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -59139,11 +59139,11 @@
     </row>
     <row r="763">
       <c r="A763" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -59216,11 +59216,11 @@
     </row>
     <row r="764">
       <c r="A764" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -59293,11 +59293,11 @@
     </row>
     <row r="765">
       <c r="A765" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -59370,11 +59370,11 @@
     </row>
     <row r="766">
       <c r="A766" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -59447,11 +59447,11 @@
     </row>
     <row r="767">
       <c r="A767" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -59524,11 +59524,11 @@
     </row>
     <row r="768">
       <c r="A768" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -59601,11 +59601,11 @@
     </row>
     <row r="769">
       <c r="A769" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -59678,11 +59678,11 @@
     </row>
     <row r="770">
       <c r="A770" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -59755,11 +59755,11 @@
     </row>
     <row r="771">
       <c r="A771" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -59832,11 +59832,11 @@
     </row>
     <row r="772">
       <c r="A772" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -59909,11 +59909,11 @@
     </row>
     <row r="773">
       <c r="A773" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -59986,11 +59986,11 @@
     </row>
     <row r="774">
       <c r="A774" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -60063,11 +60063,11 @@
     </row>
     <row r="775">
       <c r="A775" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -60140,11 +60140,11 @@
     </row>
     <row r="776">
       <c r="A776" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -60217,11 +60217,11 @@
     </row>
     <row r="777">
       <c r="A777" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -60294,11 +60294,11 @@
     </row>
     <row r="778">
       <c r="A778" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -60371,11 +60371,11 @@
     </row>
     <row r="779">
       <c r="A779" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -60448,11 +60448,11 @@
     </row>
     <row r="780">
       <c r="A780" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -60525,11 +60525,11 @@
     </row>
     <row r="781">
       <c r="A781" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -60602,11 +60602,11 @@
     </row>
     <row r="782">
       <c r="A782" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -60679,11 +60679,11 @@
     </row>
     <row r="783">
       <c r="A783" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -60756,11 +60756,11 @@
     </row>
     <row r="784">
       <c r="A784" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -60833,11 +60833,11 @@
     </row>
     <row r="785">
       <c r="A785" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -60910,11 +60910,11 @@
     </row>
     <row r="786">
       <c r="A786" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -60987,11 +60987,11 @@
     </row>
     <row r="787">
       <c r="A787" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -61064,11 +61064,11 @@
     </row>
     <row r="788">
       <c r="A788" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -61141,11 +61141,11 @@
     </row>
     <row r="789">
       <c r="A789" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -61218,11 +61218,11 @@
     </row>
     <row r="790">
       <c r="A790" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -61295,11 +61295,11 @@
     </row>
     <row r="791">
       <c r="A791" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -61372,11 +61372,11 @@
     </row>
     <row r="792">
       <c r="A792" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -61449,11 +61449,11 @@
     </row>
     <row r="793">
       <c r="A793" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -61526,11 +61526,11 @@
     </row>
     <row r="794">
       <c r="A794" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -61603,11 +61603,11 @@
     </row>
     <row r="795">
       <c r="A795" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -61680,11 +61680,11 @@
     </row>
     <row r="796">
       <c r="A796" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -61757,11 +61757,11 @@
     </row>
     <row r="797">
       <c r="A797" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -61834,11 +61834,11 @@
     </row>
     <row r="798">
       <c r="A798" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -61911,11 +61911,11 @@
     </row>
     <row r="799">
       <c r="A799" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -61988,11 +61988,11 @@
     </row>
     <row r="800">
       <c r="A800" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -62065,11 +62065,11 @@
     </row>
     <row r="801">
       <c r="A801" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -62122,16 +62122,16 @@
         <v>0</v>
       </c>
       <c r="P801" t="n">
-        <v>0</v>
+        <v>94956</v>
       </c>
       <c r="Q801" t="n">
-        <v>0</v>
+        <v>-94956</v>
       </c>
       <c r="R801" t="n">
         <v>0</v>
       </c>
       <c r="S801" t="n">
-        <v>0</v>
+        <v>94956</v>
       </c>
       <c r="T801" t="n">
         <v>0</v>
@@ -62142,11 +62142,11 @@
     </row>
     <row r="802">
       <c r="A802" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -62199,16 +62199,16 @@
         <v>872399</v>
       </c>
       <c r="P802" t="n">
-        <v>0</v>
+        <v>94956</v>
       </c>
       <c r="Q802" t="n">
-        <v>872399</v>
+        <v>777443</v>
       </c>
       <c r="R802" t="n">
         <v>0</v>
       </c>
       <c r="S802" t="n">
-        <v>0</v>
+        <v>94956</v>
       </c>
       <c r="T802" t="n">
         <v>0</v>
@@ -62219,11 +62219,11 @@
     </row>
     <row r="803">
       <c r="A803" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -62273,13 +62273,13 @@
         <v>0</v>
       </c>
       <c r="O803" t="n">
-        <v>3460.35</v>
+        <v>7672.95</v>
       </c>
       <c r="P803" t="n">
         <v>0</v>
       </c>
       <c r="Q803" t="n">
-        <v>3460.35</v>
+        <v>7672.95</v>
       </c>
       <c r="R803" t="n">
         <v>26930.55</v>
@@ -62291,16 +62291,16 @@
         <v>0</v>
       </c>
       <c r="U803" t="n">
-        <v>-3460.35</v>
+        <v>-7672.95</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -62350,13 +62350,13 @@
         <v>0</v>
       </c>
       <c r="O804" t="n">
-        <v>343477.35</v>
+        <v>347689.95</v>
       </c>
       <c r="P804" t="n">
         <v>340017</v>
       </c>
       <c r="Q804" t="n">
-        <v>3460.349999999977</v>
+        <v>7672.950000000012</v>
       </c>
       <c r="R804" t="n">
         <v>340017</v>
@@ -62368,16 +62368,16 @@
         <v>0</v>
       </c>
       <c r="U804" t="n">
-        <v>16522.65</v>
+        <v>12310.05</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -62450,11 +62450,11 @@
     </row>
     <row r="806">
       <c r="A806" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -62527,11 +62527,11 @@
     </row>
     <row r="807">
       <c r="A807" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -62584,16 +62584,16 @@
         <v>0</v>
       </c>
       <c r="P807" t="n">
-        <v>19980</v>
+        <v>21720</v>
       </c>
       <c r="Q807" t="n">
-        <v>-19980</v>
+        <v>-21720</v>
       </c>
       <c r="R807" t="n">
         <v>0</v>
       </c>
       <c r="S807" t="n">
-        <v>19980</v>
+        <v>21720</v>
       </c>
       <c r="T807" t="n">
         <v>0</v>
@@ -62604,11 +62604,11 @@
     </row>
     <row r="808">
       <c r="A808" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -62661,16 +62661,16 @@
         <v>184583</v>
       </c>
       <c r="P808" t="n">
-        <v>182657</v>
+        <v>184397</v>
       </c>
       <c r="Q808" t="n">
-        <v>1926</v>
+        <v>186</v>
       </c>
       <c r="R808" t="n">
         <v>135326</v>
       </c>
       <c r="S808" t="n">
-        <v>47331</v>
+        <v>49071</v>
       </c>
       <c r="T808" t="n">
         <v>400000</v>
@@ -62681,11 +62681,11 @@
     </row>
     <row r="809">
       <c r="A809" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -62758,11 +62758,11 @@
     </row>
     <row r="810">
       <c r="A810" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -62835,11 +62835,11 @@
     </row>
     <row r="811">
       <c r="A811" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -62912,11 +62912,11 @@
     </row>
     <row r="812">
       <c r="A812" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -62989,11 +62989,11 @@
     </row>
     <row r="813">
       <c r="A813" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -63046,16 +63046,16 @@
         <v>0</v>
       </c>
       <c r="P813" t="n">
-        <v>11604</v>
+        <v>17904</v>
       </c>
       <c r="Q813" t="n">
-        <v>-11604</v>
+        <v>-17904</v>
       </c>
       <c r="R813" t="n">
         <v>0</v>
       </c>
       <c r="S813" t="n">
-        <v>11604</v>
+        <v>17904</v>
       </c>
       <c r="T813" t="n">
         <v>0</v>
@@ -63066,11 +63066,11 @@
     </row>
     <row r="814">
       <c r="A814" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -63123,16 +63123,16 @@
         <v>242268.6</v>
       </c>
       <c r="P814" t="n">
-        <v>46014</v>
+        <v>52314</v>
       </c>
       <c r="Q814" t="n">
-        <v>196254.6</v>
+        <v>189954.6</v>
       </c>
       <c r="R814" t="n">
         <v>29532</v>
       </c>
       <c r="S814" t="n">
-        <v>16482</v>
+        <v>22782</v>
       </c>
       <c r="T814" t="n">
         <v>0</v>
@@ -63143,11 +63143,11 @@
     </row>
     <row r="815">
       <c r="A815" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -63220,11 +63220,11 @@
     </row>
     <row r="816">
       <c r="A816" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -63297,11 +63297,11 @@
     </row>
     <row r="817">
       <c r="A817" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -63374,11 +63374,11 @@
     </row>
     <row r="818">
       <c r="A818" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -63451,11 +63451,11 @@
     </row>
     <row r="819">
       <c r="A819" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -63528,11 +63528,11 @@
     </row>
     <row r="820">
       <c r="A820" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -63605,11 +63605,11 @@
     </row>
     <row r="821">
       <c r="A821" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -63682,11 +63682,11 @@
     </row>
     <row r="822">
       <c r="A822" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -63759,11 +63759,11 @@
     </row>
     <row r="823">
       <c r="A823" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -63836,11 +63836,11 @@
     </row>
     <row r="824">
       <c r="A824" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -63913,11 +63913,11 @@
     </row>
     <row r="825">
       <c r="A825" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>RELEXORC_08-04-2026.csv</t>
+          <t>RELEXORC_09-04-2026.csv</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -63967,10 +63967,10 @@
         <v>16930000</v>
       </c>
       <c r="O825" t="n">
-        <v>561902.21</v>
+        <v>582290.01</v>
       </c>
       <c r="P825" t="n">
-        <v>561902.21</v>
+        <v>582290.01</v>
       </c>
       <c r="Q825" t="n">
         <v>0</v>
@@ -63979,13 +63979,13 @@
         <v>535261.05</v>
       </c>
       <c r="S825" t="n">
-        <v>26641.16</v>
+        <v>47028.96</v>
       </c>
       <c r="T825" t="n">
         <v>0</v>
       </c>
       <c r="U825" t="n">
-        <v>16368097.79</v>
+        <v>16347709.99</v>
       </c>
     </row>
   </sheetData>
@@ -64139,7 +64139,7 @@
         <v>46112</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -64225,7 +64225,7 @@
         <v>46112</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -64311,7 +64311,7 @@
         <v>46112</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -64397,7 +64397,7 @@
         <v>46112</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -64483,7 +64483,7 @@
         <v>46112</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -64540,10 +64540,10 @@
         <v>640299.49</v>
       </c>
       <c r="S6" t="n">
-        <v>640299.49</v>
+        <v>646998.5600000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>6699.070000000065</v>
       </c>
       <c r="U6" t="n">
         <v>296021.27</v>
@@ -64569,7 +64569,7 @@
         <v>46112</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -64655,7 +64655,7 @@
         <v>46112</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -64741,7 +64741,7 @@
         <v>46112</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -64827,7 +64827,7 @@
         <v>46112</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -64884,10 +64884,10 @@
         <v>5845968.76</v>
       </c>
       <c r="S10" t="n">
-        <v>5845968.76</v>
+        <v>5898425.94</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>52457.18000000063</v>
       </c>
       <c r="U10" t="n">
         <v>4367980.05</v>
@@ -64913,7 +64913,7 @@
         <v>46112</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -64999,7 +64999,7 @@
         <v>46112</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -65047,19 +65047,19 @@
         <v>76455.60000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>78075.60000000001</v>
+        <v>79155.60000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>1620</v>
+        <v>2700</v>
       </c>
       <c r="R12" t="n">
         <v>38532.6</v>
       </c>
       <c r="S12" t="n">
-        <v>39207.6</v>
+        <v>40467.6</v>
       </c>
       <c r="T12" t="n">
-        <v>675</v>
+        <v>1935</v>
       </c>
       <c r="U12" t="n">
         <v>372.6</v>
@@ -65074,10 +65074,10 @@
         <v>2712344.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>2710724.4</v>
+        <v>2709644.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>-1620</v>
+        <v>-2700</v>
       </c>
     </row>
     <row r="13">
@@ -65085,7 +65085,7 @@
         <v>46112</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -65171,7 +65171,7 @@
         <v>46112</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -65257,7 +65257,7 @@
         <v>46112</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -65343,7 +65343,7 @@
         <v>46112</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -65429,7 +65429,7 @@
         <v>46112</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -65515,7 +65515,7 @@
         <v>46112</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -65581,10 +65581,10 @@
         <v>29429.32</v>
       </c>
       <c r="V18" t="n">
-        <v>29429.32</v>
+        <v>44143.98</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>14714.66</v>
       </c>
       <c r="X18" t="n">
         <v>105856.02</v>
@@ -65601,7 +65601,7 @@
         <v>46112</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -65667,10 +65667,10 @@
         <v>79635166.11</v>
       </c>
       <c r="V19" t="n">
-        <v>85084092.14</v>
+        <v>85100710.04000001</v>
       </c>
       <c r="W19" t="n">
-        <v>5448926.030000001</v>
+        <v>5465543.930000007</v>
       </c>
       <c r="X19" t="n">
         <v>278444787.27</v>
@@ -65687,7 +65687,7 @@
         <v>46112</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -65773,7 +65773,7 @@
         <v>46112</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -65859,7 +65859,7 @@
         <v>46112</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -65945,7 +65945,7 @@
         <v>46112</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -66031,7 +66031,7 @@
         <v>46112</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -66117,7 +66117,7 @@
         <v>46112</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -66203,7 +66203,7 @@
         <v>46112</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -66289,7 +66289,7 @@
         <v>46112</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -66355,10 +66355,10 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>220812.59</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>220812.59</v>
       </c>
       <c r="X27" t="n">
         <v>4232604.14</v>
@@ -66375,7 +66375,7 @@
         <v>46112</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -66461,7 +66461,7 @@
         <v>46112</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -66547,7 +66547,7 @@
         <v>46112</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -66633,7 +66633,7 @@
         <v>46112</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -66719,7 +66719,7 @@
         <v>46112</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -66805,7 +66805,7 @@
         <v>46112</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -66891,7 +66891,7 @@
         <v>46112</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -66977,7 +66977,7 @@
         <v>46112</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -67063,7 +67063,7 @@
         <v>46112</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -67120,10 +67120,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>94956</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>94956</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -67149,7 +67149,7 @@
         <v>46112</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -67197,10 +67197,10 @@
         <v>343477.35</v>
       </c>
       <c r="P37" t="n">
-        <v>343477.35</v>
+        <v>347689.95</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4212.600000000035</v>
       </c>
       <c r="R37" t="n">
         <v>340017</v>
@@ -67224,10 +67224,10 @@
         <v>16522.65</v>
       </c>
       <c r="Y37" t="n">
-        <v>16522.65</v>
+        <v>12310.05</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>-4212.600000000002</v>
       </c>
     </row>
     <row r="38">
@@ -67235,7 +67235,7 @@
         <v>46112</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -67321,7 +67321,7 @@
         <v>46112</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -67378,10 +67378,10 @@
         <v>177971</v>
       </c>
       <c r="S39" t="n">
-        <v>182657</v>
+        <v>184397</v>
       </c>
       <c r="T39" t="n">
-        <v>4686</v>
+        <v>6426</v>
       </c>
       <c r="U39" t="n">
         <v>135326</v>
@@ -67407,7 +67407,7 @@
         <v>46112</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -67493,7 +67493,7 @@
         <v>46112</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -67579,7 +67579,7 @@
         <v>46112</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -67636,10 +67636,10 @@
         <v>46014</v>
       </c>
       <c r="S42" t="n">
-        <v>46014</v>
+        <v>52314</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="U42" t="n">
         <v>29532</v>
@@ -67665,7 +67665,7 @@
         <v>46112</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -67751,7 +67751,7 @@
         <v>46112</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -67837,7 +67837,7 @@
         <v>46112</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -67923,7 +67923,7 @@
         <v>46112</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -68009,7 +68009,7 @@
         <v>46112</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -68095,7 +68095,7 @@
         <v>46112</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -68181,7 +68181,7 @@
         <v>46112</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -68267,7 +68267,7 @@
         <v>46112</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -68353,7 +68353,7 @@
         <v>46112</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -68439,7 +68439,7 @@
         <v>46112</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -68525,7 +68525,7 @@
         <v>46112</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -68611,7 +68611,7 @@
         <v>46112</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -68697,7 +68697,7 @@
         <v>46112</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -68783,7 +68783,7 @@
         <v>46112</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -68869,7 +68869,7 @@
         <v>46112</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -68955,7 +68955,7 @@
         <v>46112</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -69041,7 +69041,7 @@
         <v>46112</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -69127,7 +69127,7 @@
         <v>46112</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -69213,7 +69213,7 @@
         <v>46112</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -69299,7 +69299,7 @@
         <v>46112</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -69385,7 +69385,7 @@
         <v>46112</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -69471,7 +69471,7 @@
         <v>46112</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -69557,7 +69557,7 @@
         <v>46112</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -69643,7 +69643,7 @@
         <v>46112</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -69729,7 +69729,7 @@
         <v>46112</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -69815,7 +69815,7 @@
         <v>46112</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -69901,7 +69901,7 @@
         <v>46112</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -69987,7 +69987,7 @@
         <v>46112</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -70073,7 +70073,7 @@
         <v>46112</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -70130,10 +70130,10 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>175456</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>175456</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -70159,7 +70159,7 @@
         <v>46112</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -70245,7 +70245,7 @@
         <v>46112</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -70331,7 +70331,7 @@
         <v>46112</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -70417,7 +70417,7 @@
         <v>46112</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -70503,7 +70503,7 @@
         <v>46112</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -70589,7 +70589,7 @@
         <v>46112</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -70675,7 +70675,7 @@
         <v>46112</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -70761,7 +70761,7 @@
         <v>46112</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -70847,7 +70847,7 @@
         <v>46112</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -70933,7 +70933,7 @@
         <v>46112</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -71019,7 +71019,7 @@
         <v>46112</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -71105,7 +71105,7 @@
         <v>46112</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -71191,7 +71191,7 @@
         <v>46112</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -71277,7 +71277,7 @@
         <v>46112</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -71363,7 +71363,7 @@
         <v>46112</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -71449,7 +71449,7 @@
         <v>46112</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -71535,7 +71535,7 @@
         <v>46112</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -71621,7 +71621,7 @@
         <v>46112</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -71678,10 +71678,10 @@
         <v>833400</v>
       </c>
       <c r="S89" t="n">
-        <v>833400</v>
+        <v>832000</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="U89" t="n">
         <v>555600</v>
@@ -71707,7 +71707,7 @@
         <v>46112</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -71793,7 +71793,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -71879,7 +71879,7 @@
         <v>46112</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -71965,7 +71965,7 @@
         <v>46112</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -72051,7 +72051,7 @@
         <v>46112</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -72137,7 +72137,7 @@
         <v>46112</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -72223,7 +72223,7 @@
         <v>46112</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -72309,7 +72309,7 @@
         <v>46112</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -72395,7 +72395,7 @@
         <v>46112</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -72481,7 +72481,7 @@
         <v>46112</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -72567,7 +72567,7 @@
         <v>46112</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -72653,7 +72653,7 @@
         <v>46112</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -72739,7 +72739,7 @@
         <v>46112</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -72825,7 +72825,7 @@
         <v>46112</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -72911,7 +72911,7 @@
         <v>46112</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -72997,7 +72997,7 @@
         <v>46112</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -73083,7 +73083,7 @@
         <v>46112</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -73169,7 +73169,7 @@
         <v>46112</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -73255,7 +73255,7 @@
         <v>46112</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -73341,7 +73341,7 @@
         <v>46112</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -73427,7 +73427,7 @@
         <v>46112</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -73513,7 +73513,7 @@
         <v>46112</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -73599,7 +73599,7 @@
         <v>46112</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -73685,7 +73685,7 @@
         <v>46112</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -73771,7 +73771,7 @@
         <v>46112</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -73857,7 +73857,7 @@
         <v>46112</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -73943,7 +73943,7 @@
         <v>46112</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -74029,7 +74029,7 @@
         <v>46112</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -74115,7 +74115,7 @@
         <v>46112</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -74172,10 +74172,10 @@
         <v>993289</v>
       </c>
       <c r="S118" t="n">
-        <v>997489</v>
+        <v>1446091.4</v>
       </c>
       <c r="T118" t="n">
-        <v>4200</v>
+        <v>452802.3999999999</v>
       </c>
       <c r="U118" t="n">
         <v>993289</v>
@@ -74201,7 +74201,7 @@
         <v>46112</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -74287,7 +74287,7 @@
         <v>46112</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -74373,7 +74373,7 @@
         <v>46112</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -74459,7 +74459,7 @@
         <v>46112</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -74545,7 +74545,7 @@
         <v>46112</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -74631,7 +74631,7 @@
         <v>46112</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -74717,7 +74717,7 @@
         <v>46112</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -74774,10 +74774,10 @@
         <v>5657120.12</v>
       </c>
       <c r="S125" t="n">
-        <v>5657120.12</v>
+        <v>6390220.62</v>
       </c>
       <c r="T125" t="n">
-        <v>0</v>
+        <v>733100.5</v>
       </c>
       <c r="U125" t="n">
         <v>3507323.16</v>
@@ -74803,7 +74803,7 @@
         <v>46112</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -74889,7 +74889,7 @@
         <v>46112</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -74937,19 +74937,19 @@
         <v>535261.05</v>
       </c>
       <c r="P127" t="n">
-        <v>561902.21</v>
+        <v>582290.01</v>
       </c>
       <c r="Q127" t="n">
-        <v>26641.15999999992</v>
+        <v>47028.95999999996</v>
       </c>
       <c r="R127" t="n">
         <v>535261.05</v>
       </c>
       <c r="S127" t="n">
-        <v>561902.21</v>
+        <v>582290.01</v>
       </c>
       <c r="T127" t="n">
-        <v>26641.15999999992</v>
+        <v>47028.95999999996</v>
       </c>
       <c r="U127" t="n">
         <v>535261.05</v>
@@ -74964,10 +74964,10 @@
         <v>16394738.95</v>
       </c>
       <c r="Y127" t="n">
-        <v>16368097.79</v>
+        <v>16347709.99</v>
       </c>
       <c r="Z127" t="n">
-        <v>-26641.16000000015</v>
+        <v>-47028.95999999903</v>
       </c>
     </row>
   </sheetData>

--- a/Base_Consolidada_SIAFI.xlsx
+++ b/Base_Consolidada_SIAFI.xlsx
@@ -44586,11 +44586,11 @@
     </row>
     <row r="574">
       <c r="A574" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -44663,11 +44663,11 @@
     </row>
     <row r="575">
       <c r="A575" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -44740,11 +44740,11 @@
     </row>
     <row r="576">
       <c r="A576" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -44817,11 +44817,11 @@
     </row>
     <row r="577">
       <c r="A577" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -44894,11 +44894,11 @@
     </row>
     <row r="578">
       <c r="A578" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -44971,11 +44971,11 @@
     </row>
     <row r="579">
       <c r="A579" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -45048,11 +45048,11 @@
     </row>
     <row r="580">
       <c r="A580" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -45125,11 +45125,11 @@
     </row>
     <row r="581">
       <c r="A581" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -45202,11 +45202,11 @@
     </row>
     <row r="582">
       <c r="A582" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -45279,11 +45279,11 @@
     </row>
     <row r="583">
       <c r="A583" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -45356,11 +45356,11 @@
     </row>
     <row r="584">
       <c r="A584" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -45433,11 +45433,11 @@
     </row>
     <row r="585">
       <c r="A585" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -45510,11 +45510,11 @@
     </row>
     <row r="586">
       <c r="A586" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -45587,11 +45587,11 @@
     </row>
     <row r="587">
       <c r="A587" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -45664,11 +45664,11 @@
     </row>
     <row r="588">
       <c r="A588" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -45741,11 +45741,11 @@
     </row>
     <row r="589">
       <c r="A589" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -45818,11 +45818,11 @@
     </row>
     <row r="590">
       <c r="A590" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -45895,11 +45895,11 @@
     </row>
     <row r="591">
       <c r="A591" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -45972,11 +45972,11 @@
     </row>
     <row r="592">
       <c r="A592" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -46049,11 +46049,11 @@
     </row>
     <row r="593">
       <c r="A593" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -46126,11 +46126,11 @@
     </row>
     <row r="594">
       <c r="A594" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -46203,11 +46203,11 @@
     </row>
     <row r="595">
       <c r="A595" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -46280,11 +46280,11 @@
     </row>
     <row r="596">
       <c r="A596" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -46357,11 +46357,11 @@
     </row>
     <row r="597">
       <c r="A597" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -46434,11 +46434,11 @@
     </row>
     <row r="598">
       <c r="A598" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -46511,11 +46511,11 @@
     </row>
     <row r="599">
       <c r="A599" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -46588,11 +46588,11 @@
     </row>
     <row r="600">
       <c r="A600" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -46665,11 +46665,11 @@
     </row>
     <row r="601">
       <c r="A601" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -46742,11 +46742,11 @@
     </row>
     <row r="602">
       <c r="A602" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -46819,11 +46819,11 @@
     </row>
     <row r="603">
       <c r="A603" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -46896,11 +46896,11 @@
     </row>
     <row r="604">
       <c r="A604" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -46973,11 +46973,11 @@
     </row>
     <row r="605">
       <c r="A605" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -47050,11 +47050,11 @@
     </row>
     <row r="606">
       <c r="A606" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -47127,11 +47127,11 @@
     </row>
     <row r="607">
       <c r="A607" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -47204,11 +47204,11 @@
     </row>
     <row r="608">
       <c r="A608" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -47281,11 +47281,11 @@
     </row>
     <row r="609">
       <c r="A609" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -47358,11 +47358,11 @@
     </row>
     <row r="610">
       <c r="A610" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -47435,11 +47435,11 @@
     </row>
     <row r="611">
       <c r="A611" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -47512,11 +47512,11 @@
     </row>
     <row r="612">
       <c r="A612" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -47589,11 +47589,11 @@
     </row>
     <row r="613">
       <c r="A613" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -47666,11 +47666,11 @@
     </row>
     <row r="614">
       <c r="A614" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -47743,11 +47743,11 @@
     </row>
     <row r="615">
       <c r="A615" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -47820,11 +47820,11 @@
     </row>
     <row r="616">
       <c r="A616" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -47897,11 +47897,11 @@
     </row>
     <row r="617">
       <c r="A617" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -47974,11 +47974,11 @@
     </row>
     <row r="618">
       <c r="A618" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -48051,11 +48051,11 @@
     </row>
     <row r="619">
       <c r="A619" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -48128,11 +48128,11 @@
     </row>
     <row r="620">
       <c r="A620" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -48205,11 +48205,11 @@
     </row>
     <row r="621">
       <c r="A621" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -48282,11 +48282,11 @@
     </row>
     <row r="622">
       <c r="A622" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -48359,11 +48359,11 @@
     </row>
     <row r="623">
       <c r="A623" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -48436,11 +48436,11 @@
     </row>
     <row r="624">
       <c r="A624" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -48513,11 +48513,11 @@
     </row>
     <row r="625">
       <c r="A625" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -48590,11 +48590,11 @@
     </row>
     <row r="626">
       <c r="A626" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -48667,11 +48667,11 @@
     </row>
     <row r="627">
       <c r="A627" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -48744,11 +48744,11 @@
     </row>
     <row r="628">
       <c r="A628" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -48821,11 +48821,11 @@
     </row>
     <row r="629">
       <c r="A629" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -48898,11 +48898,11 @@
     </row>
     <row r="630">
       <c r="A630" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -48975,11 +48975,11 @@
     </row>
     <row r="631">
       <c r="A631" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -49052,11 +49052,11 @@
     </row>
     <row r="632">
       <c r="A632" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -49129,11 +49129,11 @@
     </row>
     <row r="633">
       <c r="A633" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -49206,11 +49206,11 @@
     </row>
     <row r="634">
       <c r="A634" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -49283,11 +49283,11 @@
     </row>
     <row r="635">
       <c r="A635" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -49360,11 +49360,11 @@
     </row>
     <row r="636">
       <c r="A636" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -49437,11 +49437,11 @@
     </row>
     <row r="637">
       <c r="A637" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -49514,11 +49514,11 @@
     </row>
     <row r="638">
       <c r="A638" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -49591,11 +49591,11 @@
     </row>
     <row r="639">
       <c r="A639" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -49668,11 +49668,11 @@
     </row>
     <row r="640">
       <c r="A640" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -49745,11 +49745,11 @@
     </row>
     <row r="641">
       <c r="A641" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -49822,11 +49822,11 @@
     </row>
     <row r="642">
       <c r="A642" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -49899,11 +49899,11 @@
     </row>
     <row r="643">
       <c r="A643" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -49976,11 +49976,11 @@
     </row>
     <row r="644">
       <c r="A644" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -50053,11 +50053,11 @@
     </row>
     <row r="645">
       <c r="A645" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -50130,11 +50130,11 @@
     </row>
     <row r="646">
       <c r="A646" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -50207,11 +50207,11 @@
     </row>
     <row r="647">
       <c r="A647" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -50284,11 +50284,11 @@
     </row>
     <row r="648">
       <c r="A648" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -50361,11 +50361,11 @@
     </row>
     <row r="649">
       <c r="A649" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -50438,11 +50438,11 @@
     </row>
     <row r="650">
       <c r="A650" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -50515,11 +50515,11 @@
     </row>
     <row r="651">
       <c r="A651" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -50592,11 +50592,11 @@
     </row>
     <row r="652">
       <c r="A652" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -50669,11 +50669,11 @@
     </row>
     <row r="653">
       <c r="A653" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -50746,11 +50746,11 @@
     </row>
     <row r="654">
       <c r="A654" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -50823,11 +50823,11 @@
     </row>
     <row r="655">
       <c r="A655" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -50900,11 +50900,11 @@
     </row>
     <row r="656">
       <c r="A656" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -50977,11 +50977,11 @@
     </row>
     <row r="657">
       <c r="A657" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -51054,11 +51054,11 @@
     </row>
     <row r="658">
       <c r="A658" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -51131,11 +51131,11 @@
     </row>
     <row r="659">
       <c r="A659" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -51208,11 +51208,11 @@
     </row>
     <row r="660">
       <c r="A660" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -51285,11 +51285,11 @@
     </row>
     <row r="661">
       <c r="A661" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -51362,11 +51362,11 @@
     </row>
     <row r="662">
       <c r="A662" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -51439,11 +51439,11 @@
     </row>
     <row r="663">
       <c r="A663" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -51516,11 +51516,11 @@
     </row>
     <row r="664">
       <c r="A664" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -51593,11 +51593,11 @@
     </row>
     <row r="665">
       <c r="A665" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -51670,11 +51670,11 @@
     </row>
     <row r="666">
       <c r="A666" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -51747,11 +51747,11 @@
     </row>
     <row r="667">
       <c r="A667" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -51824,11 +51824,11 @@
     </row>
     <row r="668">
       <c r="A668" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -51901,11 +51901,11 @@
     </row>
     <row r="669">
       <c r="A669" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -51978,11 +51978,11 @@
     </row>
     <row r="670">
       <c r="A670" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -52055,11 +52055,11 @@
     </row>
     <row r="671">
       <c r="A671" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -52132,11 +52132,11 @@
     </row>
     <row r="672">
       <c r="A672" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -52209,11 +52209,11 @@
     </row>
     <row r="673">
       <c r="A673" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -52286,11 +52286,11 @@
     </row>
     <row r="674">
       <c r="A674" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -52363,11 +52363,11 @@
     </row>
     <row r="675">
       <c r="A675" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -52440,11 +52440,11 @@
     </row>
     <row r="676">
       <c r="A676" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -52517,11 +52517,11 @@
     </row>
     <row r="677">
       <c r="A677" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -52594,11 +52594,11 @@
     </row>
     <row r="678">
       <c r="A678" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -52671,11 +52671,11 @@
     </row>
     <row r="679">
       <c r="A679" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -52695,7 +52695,7 @@
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>339039 - Outros Serviços de Terceiros - Pessoa Jurídica</t>
+          <t>33903965 - Outros Serviços de Terceiros - Pessoa Jurídica</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
@@ -52728,16 +52728,16 @@
         <v>0</v>
       </c>
       <c r="P679" t="n">
-        <v>0</v>
+        <v>1366589.44</v>
       </c>
       <c r="Q679" t="n">
-        <v>0</v>
+        <v>-1366589.44</v>
       </c>
       <c r="R679" t="n">
         <v>0</v>
       </c>
       <c r="S679" t="n">
-        <v>0</v>
+        <v>1366589.44</v>
       </c>
       <c r="T679" t="n">
         <v>0</v>
@@ -52748,11 +52748,11 @@
     </row>
     <row r="680">
       <c r="A680" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -52772,7 +52772,7 @@
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>339039 - Outros Serviços de Terceiros - Pessoa Jurídica</t>
+          <t>33903965 - Outros Serviços de Terceiros - Pessoa Jurídica</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
@@ -52805,16 +52805,16 @@
         <v>1366589.44</v>
       </c>
       <c r="P680" t="n">
-        <v>0</v>
+        <v>1366589.44</v>
       </c>
       <c r="Q680" t="n">
+        <v>0</v>
+      </c>
+      <c r="R680" t="n">
+        <v>0</v>
+      </c>
+      <c r="S680" t="n">
         <v>1366589.44</v>
-      </c>
-      <c r="R680" t="n">
-        <v>0</v>
-      </c>
-      <c r="S680" t="n">
-        <v>0</v>
       </c>
       <c r="T680" t="n">
         <v>0</v>
@@ -52825,11 +52825,11 @@
     </row>
     <row r="681">
       <c r="A681" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -52902,11 +52902,11 @@
     </row>
     <row r="682">
       <c r="A682" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -52979,11 +52979,11 @@
     </row>
     <row r="683">
       <c r="A683" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -53056,11 +53056,11 @@
     </row>
     <row r="684">
       <c r="A684" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -53133,11 +53133,11 @@
     </row>
     <row r="685">
       <c r="A685" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -53210,11 +53210,11 @@
     </row>
     <row r="686">
       <c r="A686" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -53287,11 +53287,11 @@
     </row>
     <row r="687">
       <c r="A687" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -53364,11 +53364,11 @@
     </row>
     <row r="688">
       <c r="A688" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -53441,11 +53441,11 @@
     </row>
     <row r="689">
       <c r="A689" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -53518,11 +53518,11 @@
     </row>
     <row r="690">
       <c r="A690" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -53595,11 +53595,11 @@
     </row>
     <row r="691">
       <c r="A691" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -53672,11 +53672,11 @@
     </row>
     <row r="692">
       <c r="A692" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -53749,11 +53749,11 @@
     </row>
     <row r="693">
       <c r="A693" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -53826,11 +53826,11 @@
     </row>
     <row r="694">
       <c r="A694" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -53903,11 +53903,11 @@
     </row>
     <row r="695">
       <c r="A695" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -53980,11 +53980,11 @@
     </row>
     <row r="696">
       <c r="A696" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -54057,11 +54057,11 @@
     </row>
     <row r="697">
       <c r="A697" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -54134,11 +54134,11 @@
     </row>
     <row r="698">
       <c r="A698" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -54211,11 +54211,11 @@
     </row>
     <row r="699">
       <c r="A699" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -54288,11 +54288,11 @@
     </row>
     <row r="700">
       <c r="A700" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -54365,11 +54365,11 @@
     </row>
     <row r="701">
       <c r="A701" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -54442,11 +54442,11 @@
     </row>
     <row r="702">
       <c r="A702" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -54519,11 +54519,11 @@
     </row>
     <row r="703">
       <c r="A703" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -54596,11 +54596,11 @@
     </row>
     <row r="704">
       <c r="A704" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -54659,10 +54659,10 @@
         <v>0</v>
       </c>
       <c r="R704" t="n">
-        <v>24382191.67</v>
+        <v>24381780.82</v>
       </c>
       <c r="S704" t="n">
-        <v>-24382191.67</v>
+        <v>-24381780.82</v>
       </c>
       <c r="T704" t="n">
         <v>0</v>
@@ -54673,11 +54673,11 @@
     </row>
     <row r="705">
       <c r="A705" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -54736,10 +54736,10 @@
         <v>0</v>
       </c>
       <c r="R705" t="n">
-        <v>85100710.04000001</v>
+        <v>85100299.19</v>
       </c>
       <c r="S705" t="n">
-        <v>3011845.69</v>
+        <v>3012256.54</v>
       </c>
       <c r="T705" t="n">
         <v>0</v>
@@ -54750,11 +54750,11 @@
     </row>
     <row r="706">
       <c r="A706" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -54827,11 +54827,11 @@
     </row>
     <row r="707">
       <c r="A707" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -54904,11 +54904,11 @@
     </row>
     <row r="708">
       <c r="A708" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -54981,11 +54981,11 @@
     </row>
     <row r="709">
       <c r="A709" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -55058,11 +55058,11 @@
     </row>
     <row r="710">
       <c r="A710" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -55135,11 +55135,11 @@
     </row>
     <row r="711">
       <c r="A711" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -55212,11 +55212,11 @@
     </row>
     <row r="712">
       <c r="A712" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -55289,11 +55289,11 @@
     </row>
     <row r="713">
       <c r="A713" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -55366,11 +55366,11 @@
     </row>
     <row r="714">
       <c r="A714" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -55443,11 +55443,11 @@
     </row>
     <row r="715">
       <c r="A715" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -55520,11 +55520,11 @@
     </row>
     <row r="716">
       <c r="A716" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -55597,11 +55597,11 @@
     </row>
     <row r="717">
       <c r="A717" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -55674,11 +55674,11 @@
     </row>
     <row r="718">
       <c r="A718" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -55751,11 +55751,11 @@
     </row>
     <row r="719">
       <c r="A719" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -55828,11 +55828,11 @@
     </row>
     <row r="720">
       <c r="A720" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -55905,11 +55905,11 @@
     </row>
     <row r="721">
       <c r="A721" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -55982,11 +55982,11 @@
     </row>
     <row r="722">
       <c r="A722" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -56059,11 +56059,11 @@
     </row>
     <row r="723">
       <c r="A723" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -56136,11 +56136,11 @@
     </row>
     <row r="724">
       <c r="A724" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -56213,11 +56213,11 @@
     </row>
     <row r="725">
       <c r="A725" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -56290,11 +56290,11 @@
     </row>
     <row r="726">
       <c r="A726" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -56367,11 +56367,11 @@
     </row>
     <row r="727">
       <c r="A727" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -56444,11 +56444,11 @@
     </row>
     <row r="728">
       <c r="A728" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -56521,11 +56521,11 @@
     </row>
     <row r="729">
       <c r="A729" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -56598,11 +56598,11 @@
     </row>
     <row r="730">
       <c r="A730" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -56675,11 +56675,11 @@
     </row>
     <row r="731">
       <c r="A731" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -56752,11 +56752,11 @@
     </row>
     <row r="732">
       <c r="A732" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -56829,11 +56829,11 @@
     </row>
     <row r="733">
       <c r="A733" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -56906,11 +56906,11 @@
     </row>
     <row r="734">
       <c r="A734" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -56983,11 +56983,11 @@
     </row>
     <row r="735">
       <c r="A735" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -57060,11 +57060,11 @@
     </row>
     <row r="736">
       <c r="A736" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -57137,11 +57137,11 @@
     </row>
     <row r="737">
       <c r="A737" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -57214,11 +57214,11 @@
     </row>
     <row r="738">
       <c r="A738" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -57291,11 +57291,11 @@
     </row>
     <row r="739">
       <c r="A739" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -57368,11 +57368,11 @@
     </row>
     <row r="740">
       <c r="A740" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -57445,11 +57445,11 @@
     </row>
     <row r="741">
       <c r="A741" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -57522,11 +57522,11 @@
     </row>
     <row r="742">
       <c r="A742" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -57599,11 +57599,11 @@
     </row>
     <row r="743">
       <c r="A743" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -57676,11 +57676,11 @@
     </row>
     <row r="744">
       <c r="A744" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -57753,11 +57753,11 @@
     </row>
     <row r="745">
       <c r="A745" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -57830,11 +57830,11 @@
     </row>
     <row r="746">
       <c r="A746" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -57907,11 +57907,11 @@
     </row>
     <row r="747">
       <c r="A747" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -57984,11 +57984,11 @@
     </row>
     <row r="748">
       <c r="A748" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -58061,11 +58061,11 @@
     </row>
     <row r="749">
       <c r="A749" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -58138,11 +58138,11 @@
     </row>
     <row r="750">
       <c r="A750" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -58215,11 +58215,11 @@
     </row>
     <row r="751">
       <c r="A751" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -58292,11 +58292,11 @@
     </row>
     <row r="752">
       <c r="A752" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -58369,11 +58369,11 @@
     </row>
     <row r="753">
       <c r="A753" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -58446,11 +58446,11 @@
     </row>
     <row r="754">
       <c r="A754" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -58523,11 +58523,11 @@
     </row>
     <row r="755">
       <c r="A755" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -58600,11 +58600,11 @@
     </row>
     <row r="756">
       <c r="A756" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -58677,11 +58677,11 @@
     </row>
     <row r="757">
       <c r="A757" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -58754,11 +58754,11 @@
     </row>
     <row r="758">
       <c r="A758" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -58831,11 +58831,11 @@
     </row>
     <row r="759">
       <c r="A759" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -58908,11 +58908,11 @@
     </row>
     <row r="760">
       <c r="A760" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -58985,11 +58985,11 @@
     </row>
     <row r="761">
       <c r="A761" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -59062,11 +59062,11 @@
     </row>
     <row r="762">
       <c r="A762" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -59139,11 +59139,11 @@
     </row>
     <row r="763">
       <c r="A763" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -59216,11 +59216,11 @@
     </row>
     <row r="764">
       <c r="A764" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -59293,11 +59293,11 @@
     </row>
     <row r="765">
       <c r="A765" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -59370,11 +59370,11 @@
     </row>
     <row r="766">
       <c r="A766" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -59447,11 +59447,11 @@
     </row>
     <row r="767">
       <c r="A767" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -59524,11 +59524,11 @@
     </row>
     <row r="768">
       <c r="A768" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -59601,11 +59601,11 @@
     </row>
     <row r="769">
       <c r="A769" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -59678,11 +59678,11 @@
     </row>
     <row r="770">
       <c r="A770" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -59755,11 +59755,11 @@
     </row>
     <row r="771">
       <c r="A771" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -59832,11 +59832,11 @@
     </row>
     <row r="772">
       <c r="A772" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -59909,11 +59909,11 @@
     </row>
     <row r="773">
       <c r="A773" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -59986,11 +59986,11 @@
     </row>
     <row r="774">
       <c r="A774" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -60063,11 +60063,11 @@
     </row>
     <row r="775">
       <c r="A775" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -60140,11 +60140,11 @@
     </row>
     <row r="776">
       <c r="A776" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -60217,11 +60217,11 @@
     </row>
     <row r="777">
       <c r="A777" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -60294,11 +60294,11 @@
     </row>
     <row r="778">
       <c r="A778" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -60371,11 +60371,11 @@
     </row>
     <row r="779">
       <c r="A779" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -60448,11 +60448,11 @@
     </row>
     <row r="780">
       <c r="A780" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -60525,11 +60525,11 @@
     </row>
     <row r="781">
       <c r="A781" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -60602,11 +60602,11 @@
     </row>
     <row r="782">
       <c r="A782" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -60679,11 +60679,11 @@
     </row>
     <row r="783">
       <c r="A783" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -60756,11 +60756,11 @@
     </row>
     <row r="784">
       <c r="A784" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -60833,11 +60833,11 @@
     </row>
     <row r="785">
       <c r="A785" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -60910,11 +60910,11 @@
     </row>
     <row r="786">
       <c r="A786" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -60987,11 +60987,11 @@
     </row>
     <row r="787">
       <c r="A787" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -61064,11 +61064,11 @@
     </row>
     <row r="788">
       <c r="A788" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -61141,11 +61141,11 @@
     </row>
     <row r="789">
       <c r="A789" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -61218,11 +61218,11 @@
     </row>
     <row r="790">
       <c r="A790" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -61295,11 +61295,11 @@
     </row>
     <row r="791">
       <c r="A791" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -61372,11 +61372,11 @@
     </row>
     <row r="792">
       <c r="A792" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -61449,11 +61449,11 @@
     </row>
     <row r="793">
       <c r="A793" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -61526,11 +61526,11 @@
     </row>
     <row r="794">
       <c r="A794" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -61603,11 +61603,11 @@
     </row>
     <row r="795">
       <c r="A795" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -61680,11 +61680,11 @@
     </row>
     <row r="796">
       <c r="A796" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -61757,11 +61757,11 @@
     </row>
     <row r="797">
       <c r="A797" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -61834,11 +61834,11 @@
     </row>
     <row r="798">
       <c r="A798" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -61911,11 +61911,11 @@
     </row>
     <row r="799">
       <c r="A799" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -61988,11 +61988,11 @@
     </row>
     <row r="800">
       <c r="A800" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -62065,11 +62065,11 @@
     </row>
     <row r="801">
       <c r="A801" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -62142,11 +62142,11 @@
     </row>
     <row r="802">
       <c r="A802" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -62219,11 +62219,11 @@
     </row>
     <row r="803">
       <c r="A803" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -62296,11 +62296,11 @@
     </row>
     <row r="804">
       <c r="A804" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -62373,11 +62373,11 @@
     </row>
     <row r="805">
       <c r="A805" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -62450,11 +62450,11 @@
     </row>
     <row r="806">
       <c r="A806" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -62527,11 +62527,11 @@
     </row>
     <row r="807">
       <c r="A807" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -62604,11 +62604,11 @@
     </row>
     <row r="808">
       <c r="A808" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -62681,11 +62681,11 @@
     </row>
     <row r="809">
       <c r="A809" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -62758,11 +62758,11 @@
     </row>
     <row r="810">
       <c r="A810" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -62835,11 +62835,11 @@
     </row>
     <row r="811">
       <c r="A811" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -62912,11 +62912,11 @@
     </row>
     <row r="812">
       <c r="A812" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -62989,11 +62989,11 @@
     </row>
     <row r="813">
       <c r="A813" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -63066,11 +63066,11 @@
     </row>
     <row r="814">
       <c r="A814" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -63143,11 +63143,11 @@
     </row>
     <row r="815">
       <c r="A815" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -63220,11 +63220,11 @@
     </row>
     <row r="816">
       <c r="A816" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -63297,11 +63297,11 @@
     </row>
     <row r="817">
       <c r="A817" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -63374,11 +63374,11 @@
     </row>
     <row r="818">
       <c r="A818" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -63451,11 +63451,11 @@
     </row>
     <row r="819">
       <c r="A819" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -63508,16 +63508,16 @@
         <v>0</v>
       </c>
       <c r="P819" t="n">
-        <v>0</v>
+        <v>518000</v>
       </c>
       <c r="Q819" t="n">
-        <v>0</v>
+        <v>-518000</v>
       </c>
       <c r="R819" t="n">
         <v>518000</v>
       </c>
       <c r="S819" t="n">
-        <v>-518000</v>
+        <v>0</v>
       </c>
       <c r="T819" t="n">
         <v>0</v>
@@ -63528,11 +63528,11 @@
     </row>
     <row r="820">
       <c r="A820" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -63585,16 +63585,16 @@
         <v>2253666.68</v>
       </c>
       <c r="P820" t="n">
-        <v>1153409.45</v>
+        <v>1671409.45</v>
       </c>
       <c r="Q820" t="n">
-        <v>1100257.23</v>
+        <v>582257.2300000002</v>
       </c>
       <c r="R820" t="n">
         <v>1036000</v>
       </c>
       <c r="S820" t="n">
-        <v>117409.45</v>
+        <v>635409.45</v>
       </c>
       <c r="T820" t="n">
         <v>0</v>
@@ -63605,11 +63605,11 @@
     </row>
     <row r="821">
       <c r="A821" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -63682,11 +63682,11 @@
     </row>
     <row r="822">
       <c r="A822" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -63759,11 +63759,11 @@
     </row>
     <row r="823">
       <c r="A823" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -63836,11 +63836,11 @@
     </row>
     <row r="824">
       <c r="A824" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -63913,11 +63913,11 @@
     </row>
     <row r="825">
       <c r="A825" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>RELEXORC_10-04-2026_.csv</t>
+          <t>RELEXORC_13-04-2026.csv</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -63999,7 +63999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z127"/>
+  <dimension ref="A1:Z128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64139,7 +64139,7 @@
         <v>46112</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -64225,7 +64225,7 @@
         <v>46112</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -64311,7 +64311,7 @@
         <v>46112</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -64397,7 +64397,7 @@
         <v>46112</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -64483,7 +64483,7 @@
         <v>46112</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -64569,7 +64569,7 @@
         <v>46112</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -64655,7 +64655,7 @@
         <v>46112</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -64741,7 +64741,7 @@
         <v>46112</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -64827,7 +64827,7 @@
         <v>46112</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -64913,7 +64913,7 @@
         <v>46112</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -64999,7 +64999,7 @@
         <v>46112</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -65085,7 +65085,7 @@
         <v>46112</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -65171,7 +65171,7 @@
         <v>46112</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -65257,7 +65257,7 @@
         <v>46112</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -65343,7 +65343,7 @@
         <v>46112</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -65429,7 +65429,7 @@
         <v>46112</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -65515,7 +65515,7 @@
         <v>46112</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -65601,7 +65601,7 @@
         <v>46112</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -65667,10 +65667,10 @@
         <v>79635166.11</v>
       </c>
       <c r="V19" t="n">
-        <v>85100710.04000001</v>
+        <v>85100299.19</v>
       </c>
       <c r="W19" t="n">
-        <v>5465543.930000007</v>
+        <v>5465133.079999998</v>
       </c>
       <c r="X19" t="n">
         <v>278444787.27</v>
@@ -65687,7 +65687,7 @@
         <v>46112</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -65773,7 +65773,7 @@
         <v>46112</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -65859,7 +65859,7 @@
         <v>46112</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -65945,7 +65945,7 @@
         <v>46112</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -66031,7 +66031,7 @@
         <v>46112</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -66117,7 +66117,7 @@
         <v>46112</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -66203,7 +66203,7 @@
         <v>46112</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -66289,7 +66289,7 @@
         <v>46112</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -66375,7 +66375,7 @@
         <v>46112</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -66461,7 +66461,7 @@
         <v>46112</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -66547,7 +66547,7 @@
         <v>46112</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -66633,7 +66633,7 @@
         <v>46112</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -66719,7 +66719,7 @@
         <v>46112</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -66805,7 +66805,7 @@
         <v>46112</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -66891,7 +66891,7 @@
         <v>46112</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -66977,7 +66977,7 @@
         <v>46112</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -67063,7 +67063,7 @@
         <v>46112</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -67149,7 +67149,7 @@
         <v>46112</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -67235,7 +67235,7 @@
         <v>46112</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -67321,7 +67321,7 @@
         <v>46112</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -67407,7 +67407,7 @@
         <v>46112</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -67493,7 +67493,7 @@
         <v>46112</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -67579,7 +67579,7 @@
         <v>46112</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -67665,7 +67665,7 @@
         <v>46112</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -67751,7 +67751,7 @@
         <v>46112</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -67837,7 +67837,7 @@
         <v>46112</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -67894,10 +67894,10 @@
         <v>1153409.45</v>
       </c>
       <c r="S45" t="n">
-        <v>1153409.45</v>
+        <v>1671409.45</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>518000</v>
       </c>
       <c r="U45" t="n">
         <v>518000</v>
@@ -67923,7 +67923,7 @@
         <v>46112</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -68009,7 +68009,7 @@
         <v>46112</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -68095,7 +68095,7 @@
         <v>46112</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -68181,7 +68181,7 @@
         <v>46112</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -68267,7 +68267,7 @@
         <v>46112</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -68353,7 +68353,7 @@
         <v>46112</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -68439,7 +68439,7 @@
         <v>46112</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -68525,7 +68525,7 @@
         <v>46112</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -68611,7 +68611,7 @@
         <v>46112</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -68697,7 +68697,7 @@
         <v>46112</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -68783,7 +68783,7 @@
         <v>46112</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -68869,7 +68869,7 @@
         <v>46112</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -68955,7 +68955,7 @@
         <v>46112</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -69041,7 +69041,7 @@
         <v>46112</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -69127,7 +69127,7 @@
         <v>46112</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -69213,7 +69213,7 @@
         <v>46112</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -69299,7 +69299,7 @@
         <v>46112</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -69385,7 +69385,7 @@
         <v>46112</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -69471,7 +69471,7 @@
         <v>46112</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -69557,7 +69557,7 @@
         <v>46112</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -69643,7 +69643,7 @@
         <v>46112</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -69729,7 +69729,7 @@
         <v>46112</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -69815,7 +69815,7 @@
         <v>46112</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -69901,7 +69901,7 @@
         <v>46112</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -69987,7 +69987,7 @@
         <v>46112</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -70073,7 +70073,7 @@
         <v>46112</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -70159,7 +70159,7 @@
         <v>46112</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -70245,7 +70245,7 @@
         <v>46112</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -70331,7 +70331,7 @@
         <v>46112</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -70417,7 +70417,7 @@
         <v>46112</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -70503,7 +70503,7 @@
         <v>46112</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -70589,7 +70589,7 @@
         <v>46112</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -70675,7 +70675,7 @@
         <v>46112</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -70761,7 +70761,7 @@
         <v>46112</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -70847,7 +70847,7 @@
         <v>46112</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -70933,7 +70933,7 @@
         <v>46112</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -71019,7 +71019,7 @@
         <v>46112</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -71105,7 +71105,7 @@
         <v>46112</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -71191,7 +71191,7 @@
         <v>46112</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -71277,7 +71277,7 @@
         <v>46112</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -71363,7 +71363,7 @@
         <v>46112</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -71449,7 +71449,7 @@
         <v>46112</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -71535,7 +71535,7 @@
         <v>46112</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -71621,7 +71621,7 @@
         <v>46112</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -71707,7 +71707,7 @@
         <v>46112</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -71793,7 +71793,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -71879,7 +71879,7 @@
         <v>46112</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -71965,7 +71965,7 @@
         <v>46112</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -72051,7 +72051,7 @@
         <v>46112</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -72137,7 +72137,7 @@
         <v>46112</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -72223,7 +72223,7 @@
         <v>46112</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -72309,7 +72309,7 @@
         <v>46112</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -72395,7 +72395,7 @@
         <v>46112</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -72481,7 +72481,7 @@
         <v>46112</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -72567,7 +72567,7 @@
         <v>46112</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -72653,7 +72653,7 @@
         <v>46112</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -72739,7 +72739,7 @@
         <v>46112</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -72760,10 +72760,10 @@
         <v>1366589.44</v>
       </c>
       <c r="G102" t="n">
-        <v>1366589.44</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>-1366589.44</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
@@ -72778,19 +72778,19 @@
         <v>1366589.44</v>
       </c>
       <c r="M102" t="n">
-        <v>1366589.44</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>-1366589.44</v>
       </c>
       <c r="O102" t="n">
         <v>1366589.44</v>
       </c>
       <c r="P102" t="n">
-        <v>1366589.44</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>-1366589.44</v>
       </c>
       <c r="R102" t="n">
         <v>0</v>
@@ -72825,7 +72825,7 @@
         <v>46112</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -72834,22 +72834,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>1599116000000000</t>
+          <t>1501201000000000</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>335041 - Contribuições</t>
+          <t>33903965 - Outros Serviços de Terceiros - Pessoa Jurídica</t>
         </is>
       </c>
       <c r="F103" t="n">
         <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>1366589.44</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>1366589.44</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
@@ -72861,31 +72861,31 @@
         <v>0</v>
       </c>
       <c r="L103" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>50000</v>
+        <v>1366589.44</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>1366589.44</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>1366589.44</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>1366589.44</v>
       </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>1366589.44</v>
       </c>
       <c r="T103" t="n">
-        <v>0</v>
+        <v>1366589.44</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
@@ -72897,10 +72897,10 @@
         <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
         <v>0</v>
@@ -72911,7 +72911,7 @@
         <v>46112</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -72925,7 +72925,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>339014 - Diarias - Civil</t>
+          <t>335041 - Contribuições</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -72947,46 +72947,46 @@
         <v>0</v>
       </c>
       <c r="L104" t="n">
-        <v>250000</v>
+        <v>50000</v>
       </c>
       <c r="M104" t="n">
-        <v>250000</v>
+        <v>50000</v>
       </c>
       <c r="N104" t="n">
         <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="T104" t="n">
         <v>0</v>
       </c>
       <c r="U104" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="V104" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="W104" t="n">
         <v>0</v>
       </c>
       <c r="X104" t="n">
-        <v>249721</v>
+        <v>50000</v>
       </c>
       <c r="Y104" t="n">
-        <v>249721</v>
+        <v>50000</v>
       </c>
       <c r="Z104" t="n">
         <v>0</v>
@@ -72997,7 +72997,7 @@
         <v>46112</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -73011,7 +73011,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>33901804 - Auxílio Financeiro A Estudantes</t>
+          <t>339014 - Diarias - Civil</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -73033,46 +73033,46 @@
         <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>3500000</v>
+        <v>250000</v>
       </c>
       <c r="M105" t="n">
-        <v>3500000</v>
+        <v>250000</v>
       </c>
       <c r="N105" t="n">
         <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>2078400</v>
+        <v>279</v>
       </c>
       <c r="P105" t="n">
-        <v>2078400</v>
+        <v>279</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>1128600</v>
+        <v>279</v>
       </c>
       <c r="S105" t="n">
-        <v>1128600</v>
+        <v>279</v>
       </c>
       <c r="T105" t="n">
         <v>0</v>
       </c>
       <c r="U105" t="n">
-        <v>747600</v>
+        <v>279</v>
       </c>
       <c r="V105" t="n">
-        <v>1128600</v>
+        <v>279</v>
       </c>
       <c r="W105" t="n">
-        <v>381000</v>
+        <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>1421600</v>
+        <v>249721</v>
       </c>
       <c r="Y105" t="n">
-        <v>1421600</v>
+        <v>249721</v>
       </c>
       <c r="Z105" t="n">
         <v>0</v>
@@ -73083,7 +73083,7 @@
         <v>46112</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -73097,7 +73097,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>339020 - Auxilio Financeiro a Pesquisadores</t>
+          <t>33901804 - Auxílio Financeiro A Estudantes</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -73119,46 +73119,46 @@
         <v>0</v>
       </c>
       <c r="L106" t="n">
-        <v>850000</v>
+        <v>3500000</v>
       </c>
       <c r="M106" t="n">
-        <v>850000</v>
+        <v>3500000</v>
       </c>
       <c r="N106" t="n">
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>2078400</v>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2078400</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>1128600</v>
       </c>
       <c r="S106" t="n">
-        <v>0</v>
+        <v>1128600</v>
       </c>
       <c r="T106" t="n">
         <v>0</v>
       </c>
       <c r="U106" t="n">
-        <v>0</v>
+        <v>747600</v>
       </c>
       <c r="V106" t="n">
-        <v>0</v>
+        <v>1128600</v>
       </c>
       <c r="W106" t="n">
-        <v>0</v>
+        <v>381000</v>
       </c>
       <c r="X106" t="n">
-        <v>850000</v>
+        <v>1421600</v>
       </c>
       <c r="Y106" t="n">
-        <v>850000</v>
+        <v>1421600</v>
       </c>
       <c r="Z106" t="n">
         <v>0</v>
@@ -73169,7 +73169,7 @@
         <v>46112</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -73183,7 +73183,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>339039 - Outros Serviços de Terceiros - Pessoa Jurídica</t>
+          <t>339020 - Auxilio Financeiro a Pesquisadores</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -73205,28 +73205,28 @@
         <v>0</v>
       </c>
       <c r="L107" t="n">
-        <v>7000000</v>
+        <v>850000</v>
       </c>
       <c r="M107" t="n">
-        <v>7000000</v>
+        <v>850000</v>
       </c>
       <c r="N107" t="n">
         <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>929634.22</v>
+        <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>929634.22</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>929634.22</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>929634.22</v>
+        <v>0</v>
       </c>
       <c r="T107" t="n">
         <v>0</v>
@@ -73235,16 +73235,16 @@
         <v>0</v>
       </c>
       <c r="V107" t="n">
-        <v>267500</v>
+        <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>267500</v>
+        <v>0</v>
       </c>
       <c r="X107" t="n">
-        <v>4429727.67</v>
+        <v>850000</v>
       </c>
       <c r="Y107" t="n">
-        <v>4429727.67</v>
+        <v>850000</v>
       </c>
       <c r="Z107" t="n">
         <v>0</v>
@@ -73255,7 +73255,7 @@
         <v>46112</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -73269,7 +73269,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>339040 - Serviços de Tecnologia da Informação e Comunicação- Pessoa Jurídica</t>
+          <t>339039 - Outros Serviços de Terceiros - Pessoa Jurídica</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -73291,28 +73291,28 @@
         <v>0</v>
       </c>
       <c r="L108" t="n">
-        <v>300000</v>
+        <v>7000000</v>
       </c>
       <c r="M108" t="n">
-        <v>300000</v>
+        <v>7000000</v>
       </c>
       <c r="N108" t="n">
         <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>28932.28</v>
+        <v>929634.22</v>
       </c>
       <c r="P108" t="n">
-        <v>28932.28</v>
+        <v>929634.22</v>
       </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>929634.22</v>
       </c>
       <c r="S108" t="n">
-        <v>0</v>
+        <v>929634.22</v>
       </c>
       <c r="T108" t="n">
         <v>0</v>
@@ -73321,16 +73321,16 @@
         <v>0</v>
       </c>
       <c r="V108" t="n">
-        <v>0</v>
+        <v>267500</v>
       </c>
       <c r="W108" t="n">
-        <v>0</v>
+        <v>267500</v>
       </c>
       <c r="X108" t="n">
-        <v>271067.72</v>
+        <v>4429727.67</v>
       </c>
       <c r="Y108" t="n">
-        <v>271067.72</v>
+        <v>4429727.67</v>
       </c>
       <c r="Z108" t="n">
         <v>0</v>
@@ -73341,7 +73341,7 @@
         <v>46112</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -73350,19 +73350,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2501201000000000</t>
+          <t>1599116000000000</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>339039 - Outros Serviços de Terceiros - Pessoa Jurídica</t>
+          <t>339040 - Serviços de Tecnologia da Informação e Comunicação- Pessoa Jurídica</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>733220.1</v>
+        <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>733220.1</v>
+        <v>0</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -73377,19 +73377,19 @@
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>733220.1</v>
+        <v>300000</v>
       </c>
       <c r="M109" t="n">
-        <v>733220.1</v>
+        <v>300000</v>
       </c>
       <c r="N109" t="n">
         <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>733220.1</v>
+        <v>28932.28</v>
       </c>
       <c r="P109" t="n">
-        <v>733220.1</v>
+        <v>28932.28</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
@@ -73398,10 +73398,10 @@
         <v>0</v>
       </c>
       <c r="S109" t="n">
-        <v>733220.1</v>
+        <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>733220.1</v>
+        <v>0</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -73413,10 +73413,10 @@
         <v>0</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
+        <v>271067.72</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>271067.72</v>
       </c>
       <c r="Z109" t="n">
         <v>0</v>
@@ -73427,28 +73427,28 @@
         <v>46112</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>12364330627020001</t>
+          <t>12364330627010001</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>1570280000000000</t>
+          <t>2501201000000000</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>339030 - Material de Consumo</t>
+          <t>339039 - Outros Serviços de Terceiros - Pessoa Jurídica</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>308272</v>
+        <v>733220.1</v>
       </c>
       <c r="G110" t="n">
-        <v>308272</v>
+        <v>733220.1</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -73463,19 +73463,19 @@
         <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>308272</v>
+        <v>733220.1</v>
       </c>
       <c r="M110" t="n">
-        <v>308272</v>
+        <v>733220.1</v>
       </c>
       <c r="N110" t="n">
         <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>733220.1</v>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>733220.1</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
@@ -73484,10 +73484,10 @@
         <v>0</v>
       </c>
       <c r="S110" t="n">
-        <v>0</v>
+        <v>733220.1</v>
       </c>
       <c r="T110" t="n">
-        <v>0</v>
+        <v>733220.1</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
@@ -73499,10 +73499,10 @@
         <v>0</v>
       </c>
       <c r="X110" t="n">
-        <v>308272</v>
+        <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>308272</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
         <v>0</v>
@@ -73513,7 +73513,7 @@
         <v>46112</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -73527,14 +73527,14 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>339039 - Outros Serviços de Terceiros - Pessoa Jurídica</t>
+          <t>339030 - Material de Consumo</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1150826</v>
+        <v>308272</v>
       </c>
       <c r="G111" t="n">
-        <v>1150826</v>
+        <v>308272</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -73549,10 +73549,10 @@
         <v>0</v>
       </c>
       <c r="L111" t="n">
-        <v>1150826</v>
+        <v>308272</v>
       </c>
       <c r="M111" t="n">
-        <v>1150826</v>
+        <v>308272</v>
       </c>
       <c r="N111" t="n">
         <v>0</v>
@@ -73585,10 +73585,10 @@
         <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>1150826</v>
+        <v>308272</v>
       </c>
       <c r="Y111" t="n">
-        <v>1150826</v>
+        <v>308272</v>
       </c>
       <c r="Z111" t="n">
         <v>0</v>
@@ -73599,7 +73599,7 @@
         <v>46112</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -73608,19 +73608,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>1599116000000000</t>
+          <t>1570280000000000</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>335041 - Contribuições</t>
+          <t>339039 - Outros Serviços de Terceiros - Pessoa Jurídica</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>1150826</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>1150826</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -73635,10 +73635,10 @@
         <v>0</v>
       </c>
       <c r="L112" t="n">
-        <v>2000000</v>
+        <v>1150826</v>
       </c>
       <c r="M112" t="n">
-        <v>2000000</v>
+        <v>1150826</v>
       </c>
       <c r="N112" t="n">
         <v>0</v>
@@ -73671,10 +73671,10 @@
         <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>2000000</v>
+        <v>1150826</v>
       </c>
       <c r="Y112" t="n">
-        <v>2000000</v>
+        <v>1150826</v>
       </c>
       <c r="Z112" t="n">
         <v>0</v>
@@ -73685,7 +73685,7 @@
         <v>46112</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -73699,7 +73699,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>33901401 - Diarias - Civil</t>
+          <t>335041 - Contribuições</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -73721,28 +73721,28 @@
         <v>0</v>
       </c>
       <c r="L113" t="n">
-        <v>30000</v>
+        <v>2000000</v>
       </c>
       <c r="M113" t="n">
-        <v>30000</v>
+        <v>2000000</v>
       </c>
       <c r="N113" t="n">
         <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="T113" t="n">
         <v>0</v>
@@ -73757,10 +73757,10 @@
         <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>29934</v>
+        <v>2000000</v>
       </c>
       <c r="Y113" t="n">
-        <v>29934</v>
+        <v>2000000</v>
       </c>
       <c r="Z113" t="n">
         <v>0</v>
@@ -73771,7 +73771,7 @@
         <v>46112</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -73785,7 +73785,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>33901801 - Auxílio Financeiro A Estudantes</t>
+          <t>33901401 - Diarias - Civil</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -73798,55 +73798,55 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
       </c>
       <c r="L114" t="n">
-        <v>11988000</v>
+        <v>30000</v>
       </c>
       <c r="M114" t="n">
-        <v>11988000</v>
+        <v>30000</v>
       </c>
       <c r="N114" t="n">
         <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>3891000</v>
+        <v>66</v>
       </c>
       <c r="P114" t="n">
-        <v>3891000</v>
+        <v>66</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>1956000</v>
+        <v>66</v>
       </c>
       <c r="S114" t="n">
-        <v>2240200</v>
+        <v>66</v>
       </c>
       <c r="T114" t="n">
-        <v>284200</v>
+        <v>0</v>
       </c>
       <c r="U114" t="n">
-        <v>1955300</v>
+        <v>0</v>
       </c>
       <c r="V114" t="n">
-        <v>1956000</v>
+        <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>8097000</v>
+        <v>29934</v>
       </c>
       <c r="Y114" t="n">
-        <v>8097000</v>
+        <v>29934</v>
       </c>
       <c r="Z114" t="n">
         <v>0</v>
@@ -73857,7 +73857,7 @@
         <v>46112</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -73871,68 +73871,68 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>339036 - Outros Serviços de Terceiros - Pessoa Física</t>
+          <t>33901801 - Auxílio Financeiro A Estudantes</t>
         </is>
       </c>
       <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
         <v>12000</v>
       </c>
-      <c r="G115" t="n">
+      <c r="J115" t="n">
         <v>12000</v>
       </c>
-      <c r="H115" t="n">
-        <v>0</v>
-      </c>
-      <c r="I115" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" t="n">
-        <v>0</v>
-      </c>
       <c r="K115" t="n">
         <v>0</v>
       </c>
       <c r="L115" t="n">
-        <v>12000</v>
+        <v>11988000</v>
       </c>
       <c r="M115" t="n">
-        <v>12000</v>
+        <v>11988000</v>
       </c>
       <c r="N115" t="n">
         <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>12000</v>
+        <v>3891000</v>
       </c>
       <c r="P115" t="n">
-        <v>12000</v>
+        <v>3891000</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>6000</v>
+        <v>1956000</v>
       </c>
       <c r="S115" t="n">
-        <v>6000</v>
+        <v>2240200</v>
       </c>
       <c r="T115" t="n">
-        <v>0</v>
+        <v>284200</v>
       </c>
       <c r="U115" t="n">
-        <v>6000</v>
+        <v>1955300</v>
       </c>
       <c r="V115" t="n">
-        <v>6000</v>
+        <v>1956000</v>
       </c>
       <c r="W115" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="X115" t="n">
-        <v>0</v>
+        <v>8097000</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>8097000</v>
       </c>
       <c r="Z115" t="n">
         <v>0</v>
@@ -73943,7 +73943,7 @@
         <v>46112</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -73957,14 +73957,14 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>33903965 - Outros Serviços de Terceiros - Pessoa Jurídica</t>
+          <t>339036 - Outros Serviços de Terceiros - Pessoa Física</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>2500000</v>
+        <v>12000</v>
       </c>
       <c r="G116" t="n">
-        <v>2500000</v>
+        <v>12000</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -73979,46 +73979,46 @@
         <v>0</v>
       </c>
       <c r="L116" t="n">
-        <v>8470000</v>
+        <v>12000</v>
       </c>
       <c r="M116" t="n">
-        <v>8470000</v>
+        <v>12000</v>
       </c>
       <c r="N116" t="n">
         <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>2195210.31</v>
+        <v>12000</v>
       </c>
       <c r="P116" t="n">
-        <v>2195210.31</v>
+        <v>12000</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>2195210.31</v>
+        <v>6000</v>
       </c>
       <c r="S116" t="n">
-        <v>2195210.31</v>
+        <v>6000</v>
       </c>
       <c r="T116" t="n">
         <v>0</v>
       </c>
       <c r="U116" t="n">
-        <v>2195210.31</v>
+        <v>6000</v>
       </c>
       <c r="V116" t="n">
-        <v>2195210.31</v>
+        <v>6000</v>
       </c>
       <c r="W116" t="n">
         <v>0</v>
       </c>
       <c r="X116" t="n">
-        <v>3627211.32</v>
+        <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>3627211.32</v>
+        <v>0</v>
       </c>
       <c r="Z116" t="n">
         <v>0</v>
@@ -74029,11 +74029,11 @@
         <v>46112</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>12364330627030001</t>
+          <t>12364330627020001</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -74043,14 +74043,14 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>339014 - Diarias - Civil</t>
+          <t>33903965 - Outros Serviços de Terceiros - Pessoa Jurídica</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>2500000</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>2500000</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -74065,46 +74065,46 @@
         <v>0</v>
       </c>
       <c r="L117" t="n">
-        <v>73000</v>
+        <v>8470000</v>
       </c>
       <c r="M117" t="n">
-        <v>73000</v>
+        <v>8470000</v>
       </c>
       <c r="N117" t="n">
         <v>0</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>2195210.31</v>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>2195210.31</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>2195210.31</v>
       </c>
       <c r="S117" t="n">
-        <v>0</v>
+        <v>2195210.31</v>
       </c>
       <c r="T117" t="n">
         <v>0</v>
       </c>
       <c r="U117" t="n">
-        <v>0</v>
+        <v>2195210.31</v>
       </c>
       <c r="V117" t="n">
-        <v>0</v>
+        <v>2195210.31</v>
       </c>
       <c r="W117" t="n">
         <v>0</v>
       </c>
       <c r="X117" t="n">
-        <v>73000</v>
+        <v>3627211.32</v>
       </c>
       <c r="Y117" t="n">
-        <v>73000</v>
+        <v>3627211.32</v>
       </c>
       <c r="Z117" t="n">
         <v>0</v>
@@ -74115,7 +74115,7 @@
         <v>46112</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -74129,7 +74129,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>33901801 - Auxílio Financeiro A Estudantes</t>
+          <t>339014 - Diarias - Civil</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -74151,46 +74151,46 @@
         <v>0</v>
       </c>
       <c r="L118" t="n">
-        <v>5427000</v>
+        <v>73000</v>
       </c>
       <c r="M118" t="n">
-        <v>5427000</v>
+        <v>73000</v>
       </c>
       <c r="N118" t="n">
         <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>3126083.6</v>
+        <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>3126083.6</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>993289</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
-        <v>1446091.4</v>
+        <v>0</v>
       </c>
       <c r="T118" t="n">
-        <v>452802.3999999999</v>
+        <v>0</v>
       </c>
       <c r="U118" t="n">
-        <v>993289</v>
+        <v>0</v>
       </c>
       <c r="V118" t="n">
-        <v>1364891.4</v>
+        <v>0</v>
       </c>
       <c r="W118" t="n">
-        <v>371602.3999999999</v>
+        <v>0</v>
       </c>
       <c r="X118" t="n">
-        <v>2300916.4</v>
+        <v>73000</v>
       </c>
       <c r="Y118" t="n">
-        <v>2300916.4</v>
+        <v>73000</v>
       </c>
       <c r="Z118" t="n">
         <v>0</v>
@@ -74201,7 +74201,7 @@
         <v>46112</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -74215,7 +74215,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>339039 - Outros Serviços de Terceiros - Pessoa Jurídica</t>
+          <t>33901801 - Auxílio Financeiro A Estudantes</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -74228,55 +74228,55 @@
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>321906.57</v>
+        <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>321906.57</v>
+        <v>0</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
       </c>
       <c r="L119" t="n">
-        <v>4678093.43</v>
+        <v>5427000</v>
       </c>
       <c r="M119" t="n">
-        <v>4678093.43</v>
+        <v>5427000</v>
       </c>
       <c r="N119" t="n">
         <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>2601132.4</v>
+        <v>3126083.6</v>
       </c>
       <c r="P119" t="n">
-        <v>2601132.4</v>
+        <v>3126083.6</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>1919999.31</v>
+        <v>993289</v>
       </c>
       <c r="S119" t="n">
-        <v>1919999.31</v>
+        <v>1446091.4</v>
       </c>
       <c r="T119" t="n">
-        <v>0</v>
+        <v>452802.3999999999</v>
       </c>
       <c r="U119" t="n">
-        <v>1278789.54</v>
+        <v>993289</v>
       </c>
       <c r="V119" t="n">
-        <v>1278789.54</v>
+        <v>1364891.4</v>
       </c>
       <c r="W119" t="n">
-        <v>0</v>
+        <v>371602.3999999999</v>
       </c>
       <c r="X119" t="n">
-        <v>1076961.03</v>
+        <v>2300916.4</v>
       </c>
       <c r="Y119" t="n">
-        <v>1076961.03</v>
+        <v>2300916.4</v>
       </c>
       <c r="Z119" t="n">
         <v>0</v>
@@ -74287,7 +74287,7 @@
         <v>46112</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -74301,68 +74301,68 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>33909209 - Despesas De Exercicios Anteriores</t>
+          <t>339039 - Outros Serviços de Terceiros - Pessoa Jurídica</t>
         </is>
       </c>
       <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
         <v>321906.57</v>
       </c>
-      <c r="G120" t="n">
+      <c r="J120" t="n">
         <v>321906.57</v>
       </c>
-      <c r="H120" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" t="n">
-        <v>0</v>
-      </c>
       <c r="K120" t="n">
         <v>0</v>
       </c>
       <c r="L120" t="n">
-        <v>321906.57</v>
+        <v>4678093.43</v>
       </c>
       <c r="M120" t="n">
-        <v>321906.57</v>
+        <v>4678093.43</v>
       </c>
       <c r="N120" t="n">
         <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>141627.67</v>
+        <v>2601132.4</v>
       </c>
       <c r="P120" t="n">
-        <v>141627.67</v>
+        <v>2601132.4</v>
       </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>141627.67</v>
+        <v>1919999.31</v>
       </c>
       <c r="S120" t="n">
-        <v>141627.67</v>
+        <v>1919999.31</v>
       </c>
       <c r="T120" t="n">
         <v>0</v>
       </c>
       <c r="U120" t="n">
-        <v>141627.67</v>
+        <v>1278789.54</v>
       </c>
       <c r="V120" t="n">
-        <v>141627.67</v>
+        <v>1278789.54</v>
       </c>
       <c r="W120" t="n">
         <v>0</v>
       </c>
       <c r="X120" t="n">
-        <v>180278.9</v>
+        <v>1076961.03</v>
       </c>
       <c r="Y120" t="n">
-        <v>180278.9</v>
+        <v>1076961.03</v>
       </c>
       <c r="Z120" t="n">
         <v>0</v>
@@ -74373,11 +74373,11 @@
         <v>46112</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>12364330627190001</t>
+          <t>12364330627030001</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -74387,14 +74387,14 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>339036 - Outros Serviços de Terceiros - Pessoa Física</t>
+          <t>33909209 - Despesas De Exercicios Anteriores</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>321906.57</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>321906.57</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -74409,46 +74409,46 @@
         <v>0</v>
       </c>
       <c r="L121" t="n">
-        <v>82000</v>
+        <v>321906.57</v>
       </c>
       <c r="M121" t="n">
-        <v>82000</v>
+        <v>321906.57</v>
       </c>
       <c r="N121" t="n">
         <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>22151.37</v>
+        <v>141627.67</v>
       </c>
       <c r="P121" t="n">
-        <v>22151.37</v>
+        <v>141627.67</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>5499.9</v>
+        <v>141627.67</v>
       </c>
       <c r="S121" t="n">
-        <v>5499.9</v>
+        <v>141627.67</v>
       </c>
       <c r="T121" t="n">
         <v>0</v>
       </c>
       <c r="U121" t="n">
-        <v>5499.9</v>
+        <v>141627.67</v>
       </c>
       <c r="V121" t="n">
-        <v>5499.9</v>
+        <v>141627.67</v>
       </c>
       <c r="W121" t="n">
         <v>0</v>
       </c>
       <c r="X121" t="n">
-        <v>59848.63</v>
+        <v>180278.9</v>
       </c>
       <c r="Y121" t="n">
-        <v>59848.63</v>
+        <v>180278.9</v>
       </c>
       <c r="Z121" t="n">
         <v>0</v>
@@ -74459,11 +74459,11 @@
         <v>46112</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>12364330627340001</t>
+          <t>12364330627190001</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -74473,14 +74473,14 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>339014 - Diarias - Civil</t>
+          <t>339036 - Outros Serviços de Terceiros - Pessoa Física</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>186000</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>186000</v>
+        <v>0</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -74495,46 +74495,46 @@
         <v>0</v>
       </c>
       <c r="L122" t="n">
-        <v>200000</v>
+        <v>82000</v>
       </c>
       <c r="M122" t="n">
-        <v>200000</v>
+        <v>82000</v>
       </c>
       <c r="N122" t="n">
         <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>76815.89999999999</v>
+        <v>22151.37</v>
       </c>
       <c r="P122" t="n">
-        <v>76815.89999999999</v>
+        <v>22151.37</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>76815.89999999999</v>
+        <v>5499.9</v>
       </c>
       <c r="S122" t="n">
-        <v>76815.89999999999</v>
+        <v>5499.9</v>
       </c>
       <c r="T122" t="n">
         <v>0</v>
       </c>
       <c r="U122" t="n">
-        <v>76815.89999999999</v>
+        <v>5499.9</v>
       </c>
       <c r="V122" t="n">
-        <v>76815.89999999999</v>
+        <v>5499.9</v>
       </c>
       <c r="W122" t="n">
         <v>0</v>
       </c>
       <c r="X122" t="n">
-        <v>123184.1</v>
+        <v>59848.63</v>
       </c>
       <c r="Y122" t="n">
-        <v>123184.1</v>
+        <v>59848.63</v>
       </c>
       <c r="Z122" t="n">
         <v>0</v>
@@ -74545,7 +74545,7 @@
         <v>46112</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -74559,68 +74559,68 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>339018 - Auxílio Financeiro A Estudantes</t>
+          <t>339014 - Diarias - Civil</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>186000</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>186000</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>36000</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>36000</v>
+        <v>0</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
       </c>
       <c r="L123" t="n">
-        <v>64000</v>
+        <v>200000</v>
       </c>
       <c r="M123" t="n">
-        <v>64000</v>
+        <v>200000</v>
       </c>
       <c r="N123" t="n">
         <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
+        <v>76815.89999999999</v>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>76815.89999999999</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>76815.89999999999</v>
       </c>
       <c r="S123" t="n">
-        <v>0</v>
+        <v>76815.89999999999</v>
       </c>
       <c r="T123" t="n">
         <v>0</v>
       </c>
       <c r="U123" t="n">
-        <v>0</v>
+        <v>76815.89999999999</v>
       </c>
       <c r="V123" t="n">
-        <v>0</v>
+        <v>76815.89999999999</v>
       </c>
       <c r="W123" t="n">
         <v>0</v>
       </c>
       <c r="X123" t="n">
-        <v>64000</v>
+        <v>123184.1</v>
       </c>
       <c r="Y123" t="n">
-        <v>64000</v>
+        <v>123184.1</v>
       </c>
       <c r="Z123" t="n">
         <v>0</v>
@@ -74631,7 +74631,7 @@
         <v>46112</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -74645,7 +74645,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>339036 - Outros Serviços de Terceiros - Pessoa Física</t>
+          <t>339018 - Auxílio Financeiro A Estudantes</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -74658,19 +74658,19 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>36000</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>36000</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
       </c>
       <c r="L124" t="n">
-        <v>10000</v>
+        <v>64000</v>
       </c>
       <c r="M124" t="n">
-        <v>10000</v>
+        <v>64000</v>
       </c>
       <c r="N124" t="n">
         <v>0</v>
@@ -74703,10 +74703,10 @@
         <v>0</v>
       </c>
       <c r="X124" t="n">
-        <v>10000</v>
+        <v>64000</v>
       </c>
       <c r="Y124" t="n">
-        <v>10000</v>
+        <v>64000</v>
       </c>
       <c r="Z124" t="n">
         <v>0</v>
@@ -74717,11 +74717,11 @@
         <v>46112</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>12364330628220001</t>
+          <t>12364330627340001</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -74731,7 +74731,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>33903941 - Outros Serviços de Terceiros - Pessoa Jurídica</t>
+          <t>339036 - Outros Serviços de Terceiros - Pessoa Física</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -74744,55 +74744,55 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>2990500.28</v>
+        <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>2990500.28</v>
+        <v>0</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
       </c>
       <c r="L125" t="n">
-        <v>37009499.72</v>
+        <v>10000</v>
       </c>
       <c r="M125" t="n">
-        <v>37009499.72</v>
+        <v>10000</v>
       </c>
       <c r="N125" t="n">
         <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>11419975.46</v>
+        <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>11419975.46</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>5657120.12</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>7116623.94</v>
+        <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>1459503.82</v>
+        <v>0</v>
       </c>
       <c r="U125" t="n">
-        <v>3507323.16</v>
+        <v>0</v>
       </c>
       <c r="V125" t="n">
-        <v>4103146.56</v>
+        <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>595823.3999999999</v>
+        <v>0</v>
       </c>
       <c r="X125" t="n">
-        <v>10589524.26</v>
+        <v>10000</v>
       </c>
       <c r="Y125" t="n">
-        <v>10589524.26</v>
+        <v>10000</v>
       </c>
       <c r="Z125" t="n">
         <v>0</v>
@@ -74803,7 +74803,7 @@
         <v>46112</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -74817,68 +74817,68 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>33909293 - Despesas De Exercicios Anteriores</t>
+          <t>33903941 - Outros Serviços de Terceiros - Pessoa Jurídica</t>
         </is>
       </c>
       <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
         <v>2990500.28</v>
       </c>
-      <c r="G126" t="n">
+      <c r="J126" t="n">
         <v>2990500.28</v>
       </c>
-      <c r="H126" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" t="n">
-        <v>0</v>
-      </c>
       <c r="K126" t="n">
         <v>0</v>
       </c>
       <c r="L126" t="n">
-        <v>2990500.28</v>
+        <v>37009499.72</v>
       </c>
       <c r="M126" t="n">
-        <v>2990500.28</v>
+        <v>37009499.72</v>
       </c>
       <c r="N126" t="n">
         <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>1294906.3</v>
+        <v>11419975.46</v>
       </c>
       <c r="P126" t="n">
-        <v>1294906.3</v>
+        <v>11419975.46</v>
       </c>
       <c r="Q126" t="n">
         <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>1095154.92</v>
+        <v>5657120.12</v>
       </c>
       <c r="S126" t="n">
-        <v>1095154.92</v>
+        <v>7116623.94</v>
       </c>
       <c r="T126" t="n">
-        <v>0</v>
+        <v>1459503.82</v>
       </c>
       <c r="U126" t="n">
-        <v>94702.48</v>
+        <v>3507323.16</v>
       </c>
       <c r="V126" t="n">
-        <v>94702.48</v>
+        <v>4103146.56</v>
       </c>
       <c r="W126" t="n">
-        <v>0</v>
+        <v>595823.3999999999</v>
       </c>
       <c r="X126" t="n">
-        <v>1695593.98</v>
+        <v>10589524.26</v>
       </c>
       <c r="Y126" t="n">
-        <v>1695593.98</v>
+        <v>10589524.26</v>
       </c>
       <c r="Z126" t="n">
         <v>0</v>
@@ -74889,84 +74889,170 @@
         <v>46112</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
+          <t>12364330628220001</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>1599116000000000</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>33909293 - Despesas De Exercicios Anteriores</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>2990500.28</v>
+      </c>
+      <c r="G127" t="n">
+        <v>2990500.28</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>2990500.28</v>
+      </c>
+      <c r="M127" t="n">
+        <v>2990500.28</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>1294906.3</v>
+      </c>
+      <c r="P127" t="n">
+        <v>1294906.3</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>1095154.92</v>
+      </c>
+      <c r="S127" t="n">
+        <v>1095154.92</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="n">
+        <v>94702.48</v>
+      </c>
+      <c r="V127" t="n">
+        <v>94702.48</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0</v>
+      </c>
+      <c r="X127" t="n">
+        <v>1695593.98</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>1695593.98</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
           <t>28846000300020001</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>1599116000000000</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E128" t="inlineStr">
         <is>
           <t>31909106 - Sentenças Judiciais</t>
         </is>
       </c>
-      <c r="F127" t="n">
-        <v>0</v>
-      </c>
-      <c r="G127" t="n">
-        <v>0</v>
-      </c>
-      <c r="H127" t="n">
-        <v>0</v>
-      </c>
-      <c r="I127" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" t="n">
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
         <v>16930000</v>
       </c>
-      <c r="M127" t="n">
+      <c r="M128" t="n">
         <v>16930000</v>
       </c>
-      <c r="N127" t="n">
-        <v>0</v>
-      </c>
-      <c r="O127" t="n">
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
         <v>535261.05</v>
       </c>
-      <c r="P127" t="n">
+      <c r="P128" t="n">
         <v>582290.01</v>
       </c>
-      <c r="Q127" t="n">
+      <c r="Q128" t="n">
         <v>47028.95999999996</v>
       </c>
-      <c r="R127" t="n">
+      <c r="R128" t="n">
         <v>535261.05</v>
       </c>
-      <c r="S127" t="n">
+      <c r="S128" t="n">
         <v>582290.01</v>
       </c>
-      <c r="T127" t="n">
+      <c r="T128" t="n">
         <v>47028.95999999996</v>
       </c>
-      <c r="U127" t="n">
+      <c r="U128" t="n">
         <v>535261.05</v>
       </c>
-      <c r="V127" t="n">
+      <c r="V128" t="n">
         <v>535261.05</v>
       </c>
-      <c r="W127" t="n">
-        <v>0</v>
-      </c>
-      <c r="X127" t="n">
+      <c r="W128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" t="n">
         <v>16394738.95</v>
       </c>
-      <c r="Y127" t="n">
+      <c r="Y128" t="n">
         <v>16347709.99</v>
       </c>
-      <c r="Z127" t="n">
+      <c r="Z128" t="n">
         <v>-47028.95999999903</v>
       </c>
     </row>

--- a/Base_Consolidada_SIAFI.xlsx
+++ b/Base_Consolidada_SIAFI.xlsx
@@ -44586,11 +44586,11 @@
     </row>
     <row r="574">
       <c r="A574" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -44663,11 +44663,11 @@
     </row>
     <row r="575">
       <c r="A575" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -44740,11 +44740,11 @@
     </row>
     <row r="576">
       <c r="A576" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -44817,11 +44817,11 @@
     </row>
     <row r="577">
       <c r="A577" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -44894,11 +44894,11 @@
     </row>
     <row r="578">
       <c r="A578" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -44971,11 +44971,11 @@
     </row>
     <row r="579">
       <c r="A579" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -45048,11 +45048,11 @@
     </row>
     <row r="580">
       <c r="A580" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -45125,11 +45125,11 @@
     </row>
     <row r="581">
       <c r="A581" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -45202,11 +45202,11 @@
     </row>
     <row r="582">
       <c r="A582" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -45279,11 +45279,11 @@
     </row>
     <row r="583">
       <c r="A583" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -45356,11 +45356,11 @@
     </row>
     <row r="584">
       <c r="A584" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -45433,11 +45433,11 @@
     </row>
     <row r="585">
       <c r="A585" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -45510,11 +45510,11 @@
     </row>
     <row r="586">
       <c r="A586" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -45587,11 +45587,11 @@
     </row>
     <row r="587">
       <c r="A587" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -45664,11 +45664,11 @@
     </row>
     <row r="588">
       <c r="A588" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -45741,11 +45741,11 @@
     </row>
     <row r="589">
       <c r="A589" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -45818,11 +45818,11 @@
     </row>
     <row r="590">
       <c r="A590" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -45895,11 +45895,11 @@
     </row>
     <row r="591">
       <c r="A591" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -45972,11 +45972,11 @@
     </row>
     <row r="592">
       <c r="A592" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -46049,11 +46049,11 @@
     </row>
     <row r="593">
       <c r="A593" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -46126,11 +46126,11 @@
     </row>
     <row r="594">
       <c r="A594" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -46203,11 +46203,11 @@
     </row>
     <row r="595">
       <c r="A595" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -46266,25 +46266,25 @@
         <v>-81696</v>
       </c>
       <c r="R595" t="n">
-        <v>1986000</v>
+        <v>1997383.61</v>
       </c>
       <c r="S595" t="n">
-        <v>-1904304</v>
+        <v>-1915687.61</v>
       </c>
       <c r="T595" t="n">
-        <v>0</v>
+        <v>5530000</v>
       </c>
       <c r="U595" t="n">
-        <v>0</v>
+        <v>-5530000</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -46343,25 +46343,25 @@
         <v>4264693.699999999</v>
       </c>
       <c r="R596" t="n">
-        <v>8622057.49</v>
+        <v>8633441.1</v>
       </c>
       <c r="S596" t="n">
-        <v>523460.33</v>
+        <v>512076.72</v>
       </c>
       <c r="T596" t="n">
-        <v>6331411.46</v>
+        <v>11861411.46</v>
       </c>
       <c r="U596" t="n">
-        <v>7354333.68</v>
+        <v>1824333.68</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -46420,10 +46420,10 @@
         <v>0</v>
       </c>
       <c r="R597" t="n">
-        <v>0</v>
+        <v>19833.83</v>
       </c>
       <c r="S597" t="n">
-        <v>0</v>
+        <v>-19833.83</v>
       </c>
       <c r="T597" t="n">
         <v>0</v>
@@ -46434,11 +46434,11 @@
     </row>
     <row r="598">
       <c r="A598" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -46497,10 +46497,10 @@
         <v>592819.21</v>
       </c>
       <c r="R598" t="n">
-        <v>441322.08</v>
+        <v>461155.91</v>
       </c>
       <c r="S598" t="n">
-        <v>223121.17</v>
+        <v>203287.34</v>
       </c>
       <c r="T598" t="n">
         <v>415791.82</v>
@@ -46511,11 +46511,11 @@
     </row>
     <row r="599">
       <c r="A599" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -46588,11 +46588,11 @@
     </row>
     <row r="600">
       <c r="A600" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -46665,11 +46665,11 @@
     </row>
     <row r="601">
       <c r="A601" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -46742,11 +46742,11 @@
     </row>
     <row r="602">
       <c r="A602" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -46819,11 +46819,11 @@
     </row>
     <row r="603">
       <c r="A603" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -46896,11 +46896,11 @@
     </row>
     <row r="604">
       <c r="A604" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -46973,11 +46973,11 @@
     </row>
     <row r="605">
       <c r="A605" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -47050,11 +47050,11 @@
     </row>
     <row r="606">
       <c r="A606" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -47127,11 +47127,11 @@
     </row>
     <row r="607">
       <c r="A607" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -47204,11 +47204,11 @@
     </row>
     <row r="608">
       <c r="A608" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -47281,11 +47281,11 @@
     </row>
     <row r="609">
       <c r="A609" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -47358,11 +47358,11 @@
     </row>
     <row r="610">
       <c r="A610" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -47435,11 +47435,11 @@
     </row>
     <row r="611">
       <c r="A611" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -47512,11 +47512,11 @@
     </row>
     <row r="612">
       <c r="A612" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -47589,11 +47589,11 @@
     </row>
     <row r="613">
       <c r="A613" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -47666,11 +47666,11 @@
     </row>
     <row r="614">
       <c r="A614" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -47743,11 +47743,11 @@
     </row>
     <row r="615">
       <c r="A615" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -47820,11 +47820,11 @@
     </row>
     <row r="616">
       <c r="A616" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -47897,11 +47897,11 @@
     </row>
     <row r="617">
       <c r="A617" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -47974,11 +47974,11 @@
     </row>
     <row r="618">
       <c r="A618" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -48051,11 +48051,11 @@
     </row>
     <row r="619">
       <c r="A619" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -48128,11 +48128,11 @@
     </row>
     <row r="620">
       <c r="A620" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -48205,11 +48205,11 @@
     </row>
     <row r="621">
       <c r="A621" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -48282,11 +48282,11 @@
     </row>
     <row r="622">
       <c r="A622" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -48359,11 +48359,11 @@
     </row>
     <row r="623">
       <c r="A623" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -48436,11 +48436,11 @@
     </row>
     <row r="624">
       <c r="A624" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -48513,11 +48513,11 @@
     </row>
     <row r="625">
       <c r="A625" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -48590,11 +48590,11 @@
     </row>
     <row r="626">
       <c r="A626" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -48667,11 +48667,11 @@
     </row>
     <row r="627">
       <c r="A627" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -48744,11 +48744,11 @@
     </row>
     <row r="628">
       <c r="A628" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -48821,11 +48821,11 @@
     </row>
     <row r="629">
       <c r="A629" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -48898,11 +48898,11 @@
     </row>
     <row r="630">
       <c r="A630" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -48975,11 +48975,11 @@
     </row>
     <row r="631">
       <c r="A631" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -49052,11 +49052,11 @@
     </row>
     <row r="632">
       <c r="A632" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -49129,11 +49129,11 @@
     </row>
     <row r="633">
       <c r="A633" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -49206,11 +49206,11 @@
     </row>
     <row r="634">
       <c r="A634" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -49283,11 +49283,11 @@
     </row>
     <row r="635">
       <c r="A635" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -49360,11 +49360,11 @@
     </row>
     <row r="636">
       <c r="A636" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -49437,11 +49437,11 @@
     </row>
     <row r="637">
       <c r="A637" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -49514,11 +49514,11 @@
     </row>
     <row r="638">
       <c r="A638" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -49591,11 +49591,11 @@
     </row>
     <row r="639">
       <c r="A639" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -49668,11 +49668,11 @@
     </row>
     <row r="640">
       <c r="A640" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -49745,11 +49745,11 @@
     </row>
     <row r="641">
       <c r="A641" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -49822,11 +49822,11 @@
     </row>
     <row r="642">
       <c r="A642" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -49899,11 +49899,11 @@
     </row>
     <row r="643">
       <c r="A643" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -49976,11 +49976,11 @@
     </row>
     <row r="644">
       <c r="A644" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -50053,11 +50053,11 @@
     </row>
     <row r="645">
       <c r="A645" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -50130,11 +50130,11 @@
     </row>
     <row r="646">
       <c r="A646" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -50207,11 +50207,11 @@
     </row>
     <row r="647">
       <c r="A647" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -50284,11 +50284,11 @@
     </row>
     <row r="648">
       <c r="A648" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -50347,10 +50347,10 @@
         <v>0</v>
       </c>
       <c r="R648" t="n">
-        <v>0</v>
+        <v>41752.05</v>
       </c>
       <c r="S648" t="n">
-        <v>0</v>
+        <v>-41752.05</v>
       </c>
       <c r="T648" t="n">
         <v>0</v>
@@ -50361,11 +50361,11 @@
     </row>
     <row r="649">
       <c r="A649" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -50424,10 +50424,10 @@
         <v>681133.0899999999</v>
       </c>
       <c r="R649" t="n">
-        <v>1278789.54</v>
+        <v>1320541.59</v>
       </c>
       <c r="S649" t="n">
-        <v>641209.77</v>
+        <v>599457.72</v>
       </c>
       <c r="T649" t="n">
         <v>1000000</v>
@@ -50438,11 +50438,11 @@
     </row>
     <row r="650">
       <c r="A650" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -50515,11 +50515,11 @@
     </row>
     <row r="651">
       <c r="A651" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -50592,11 +50592,11 @@
     </row>
     <row r="652">
       <c r="A652" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -50655,10 +50655,10 @@
         <v>-5550.49</v>
       </c>
       <c r="R652" t="n">
-        <v>0</v>
+        <v>5550.49</v>
       </c>
       <c r="S652" t="n">
-        <v>5550.49</v>
+        <v>0</v>
       </c>
       <c r="T652" t="n">
         <v>0</v>
@@ -50669,11 +50669,11 @@
     </row>
     <row r="653">
       <c r="A653" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -50732,10 +50732,10 @@
         <v>11100.98</v>
       </c>
       <c r="R653" t="n">
-        <v>5499.9</v>
+        <v>11050.39</v>
       </c>
       <c r="S653" t="n">
-        <v>5550.49</v>
+        <v>0</v>
       </c>
       <c r="T653" t="n">
         <v>0</v>
@@ -50746,11 +50746,11 @@
     </row>
     <row r="654">
       <c r="A654" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -50823,11 +50823,11 @@
     </row>
     <row r="655">
       <c r="A655" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -50900,11 +50900,11 @@
     </row>
     <row r="656">
       <c r="A656" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -50977,11 +50977,11 @@
     </row>
     <row r="657">
       <c r="A657" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -51054,11 +51054,11 @@
     </row>
     <row r="658">
       <c r="A658" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -51131,11 +51131,11 @@
     </row>
     <row r="659">
       <c r="A659" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -51208,11 +51208,11 @@
     </row>
     <row r="660">
       <c r="A660" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -51271,10 +51271,10 @@
         <v>-2237091.02</v>
       </c>
       <c r="R660" t="n">
-        <v>595823.4</v>
+        <v>1163562.62</v>
       </c>
       <c r="S660" t="n">
-        <v>1641267.62</v>
+        <v>1073528.4</v>
       </c>
       <c r="T660" t="n">
         <v>0</v>
@@ -51285,11 +51285,11 @@
     </row>
     <row r="661">
       <c r="A661" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -51348,10 +51348,10 @@
         <v>4303351.52</v>
       </c>
       <c r="R661" t="n">
-        <v>4103146.56</v>
+        <v>4670885.78</v>
       </c>
       <c r="S661" t="n">
-        <v>3013477.38</v>
+        <v>2445738.16</v>
       </c>
       <c r="T661" t="n">
         <v>15000000</v>
@@ -51362,11 +51362,11 @@
     </row>
     <row r="662">
       <c r="A662" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -51439,11 +51439,11 @@
     </row>
     <row r="663">
       <c r="A663" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -51516,11 +51516,11 @@
     </row>
     <row r="664">
       <c r="A664" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -51593,11 +51593,11 @@
     </row>
     <row r="665">
       <c r="A665" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -51670,11 +51670,11 @@
     </row>
     <row r="666">
       <c r="A666" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -51747,11 +51747,11 @@
     </row>
     <row r="667">
       <c r="A667" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -51824,11 +51824,11 @@
     </row>
     <row r="668">
       <c r="A668" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -51901,11 +51901,11 @@
     </row>
     <row r="669">
       <c r="A669" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -51978,11 +51978,11 @@
     </row>
     <row r="670">
       <c r="A670" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -52055,11 +52055,11 @@
     </row>
     <row r="671">
       <c r="A671" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -52132,11 +52132,11 @@
     </row>
     <row r="672">
       <c r="A672" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -52209,11 +52209,11 @@
     </row>
     <row r="673">
       <c r="A673" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -52286,11 +52286,11 @@
     </row>
     <row r="674">
       <c r="A674" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -52363,11 +52363,11 @@
     </row>
     <row r="675">
       <c r="A675" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -52440,11 +52440,11 @@
     </row>
     <row r="676">
       <c r="A676" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -52517,11 +52517,11 @@
     </row>
     <row r="677">
       <c r="A677" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -52594,11 +52594,11 @@
     </row>
     <row r="678">
       <c r="A678" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -52671,11 +52671,11 @@
     </row>
     <row r="679">
       <c r="A679" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -52748,11 +52748,11 @@
     </row>
     <row r="680">
       <c r="A680" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -52825,11 +52825,11 @@
     </row>
     <row r="681">
       <c r="A681" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -52902,11 +52902,11 @@
     </row>
     <row r="682">
       <c r="A682" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -52979,11 +52979,11 @@
     </row>
     <row r="683">
       <c r="A683" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -53056,11 +53056,11 @@
     </row>
     <row r="684">
       <c r="A684" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -53133,11 +53133,11 @@
     </row>
     <row r="685">
       <c r="A685" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -53190,16 +53190,16 @@
         <v>7000</v>
       </c>
       <c r="P685" t="n">
-        <v>401800</v>
+        <v>437500</v>
       </c>
       <c r="Q685" t="n">
-        <v>-394800</v>
+        <v>-430500</v>
       </c>
       <c r="R685" t="n">
         <v>381000</v>
       </c>
       <c r="S685" t="n">
-        <v>20800</v>
+        <v>56500</v>
       </c>
       <c r="T685" t="n">
         <v>0</v>
@@ -53210,11 +53210,11 @@
     </row>
     <row r="686">
       <c r="A686" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -53267,16 +53267,16 @@
         <v>2085400</v>
       </c>
       <c r="P686" t="n">
-        <v>1363400</v>
+        <v>1399100</v>
       </c>
       <c r="Q686" t="n">
-        <v>722000</v>
+        <v>686300</v>
       </c>
       <c r="R686" t="n">
         <v>1128600</v>
       </c>
       <c r="S686" t="n">
-        <v>234800</v>
+        <v>270500</v>
       </c>
       <c r="T686" t="n">
         <v>0</v>
@@ -53287,11 +53287,11 @@
     </row>
     <row r="687">
       <c r="A687" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -53364,11 +53364,11 @@
     </row>
     <row r="688">
       <c r="A688" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -53441,11 +53441,11 @@
     </row>
     <row r="689">
       <c r="A689" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -53504,10 +53504,10 @@
         <v>0</v>
       </c>
       <c r="R689" t="n">
-        <v>267500</v>
+        <v>270645.89</v>
       </c>
       <c r="S689" t="n">
-        <v>-267500</v>
+        <v>-270645.89</v>
       </c>
       <c r="T689" t="n">
         <v>0</v>
@@ -53518,11 +53518,11 @@
     </row>
     <row r="690">
       <c r="A690" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -53581,10 +53581,10 @@
         <v>0</v>
       </c>
       <c r="R690" t="n">
-        <v>267500</v>
+        <v>270645.89</v>
       </c>
       <c r="S690" t="n">
-        <v>662134.22</v>
+        <v>658988.33</v>
       </c>
       <c r="T690" t="n">
         <v>1640638.11</v>
@@ -53595,11 +53595,11 @@
     </row>
     <row r="691">
       <c r="A691" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -53672,11 +53672,11 @@
     </row>
     <row r="692">
       <c r="A692" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -53749,11 +53749,11 @@
     </row>
     <row r="693">
       <c r="A693" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -53826,11 +53826,11 @@
     </row>
     <row r="694">
       <c r="A694" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -53903,11 +53903,11 @@
     </row>
     <row r="695">
       <c r="A695" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -53980,11 +53980,11 @@
     </row>
     <row r="696">
       <c r="A696" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -54057,11 +54057,11 @@
     </row>
     <row r="697">
       <c r="A697" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -54134,11 +54134,11 @@
     </row>
     <row r="698">
       <c r="A698" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -54211,11 +54211,11 @@
     </row>
     <row r="699">
       <c r="A699" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -54288,11 +54288,11 @@
     </row>
     <row r="700">
       <c r="A700" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -54365,11 +54365,11 @@
     </row>
     <row r="701">
       <c r="A701" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -54442,11 +54442,11 @@
     </row>
     <row r="702">
       <c r="A702" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -54519,11 +54519,11 @@
     </row>
     <row r="703">
       <c r="A703" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -54596,11 +54596,11 @@
     </row>
     <row r="704">
       <c r="A704" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -54673,11 +54673,11 @@
     </row>
     <row r="705">
       <c r="A705" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -54750,11 +54750,11 @@
     </row>
     <row r="706">
       <c r="A706" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -54827,11 +54827,11 @@
     </row>
     <row r="707">
       <c r="A707" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -54904,11 +54904,11 @@
     </row>
     <row r="708">
       <c r="A708" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -54981,11 +54981,11 @@
     </row>
     <row r="709">
       <c r="A709" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -55058,11 +55058,11 @@
     </row>
     <row r="710">
       <c r="A710" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -55135,11 +55135,11 @@
     </row>
     <row r="711">
       <c r="A711" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -55212,11 +55212,11 @@
     </row>
     <row r="712">
       <c r="A712" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -55289,11 +55289,11 @@
     </row>
     <row r="713">
       <c r="A713" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -55366,11 +55366,11 @@
     </row>
     <row r="714">
       <c r="A714" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -55443,11 +55443,11 @@
     </row>
     <row r="715">
       <c r="A715" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -55520,11 +55520,11 @@
     </row>
     <row r="716">
       <c r="A716" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -55577,16 +55577,16 @@
         <v>0</v>
       </c>
       <c r="P716" t="n">
-        <v>771216.05</v>
+        <v>811565.0699999999</v>
       </c>
       <c r="Q716" t="n">
-        <v>-771216.05</v>
+        <v>-811565.0699999999</v>
       </c>
       <c r="R716" t="n">
         <v>0</v>
       </c>
       <c r="S716" t="n">
-        <v>771216.05</v>
+        <v>811565.0699999999</v>
       </c>
       <c r="T716" t="n">
         <v>0</v>
@@ -55597,11 +55597,11 @@
     </row>
     <row r="717">
       <c r="A717" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -55654,16 +55654,16 @@
         <v>4215393.26</v>
       </c>
       <c r="P717" t="n">
-        <v>2563101.06</v>
+        <v>2603450.08</v>
       </c>
       <c r="Q717" t="n">
-        <v>1652292.2</v>
+        <v>1611943.18</v>
       </c>
       <c r="R717" t="n">
         <v>1791885.01</v>
       </c>
       <c r="S717" t="n">
-        <v>771216.05</v>
+        <v>811565.0699999999</v>
       </c>
       <c r="T717" t="n">
         <v>0</v>
@@ -55674,11 +55674,11 @@
     </row>
     <row r="718">
       <c r="A718" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -55751,11 +55751,11 @@
     </row>
     <row r="719">
       <c r="A719" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -55828,11 +55828,11 @@
     </row>
     <row r="720">
       <c r="A720" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -55905,11 +55905,11 @@
     </row>
     <row r="721">
       <c r="A721" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -55982,11 +55982,11 @@
     </row>
     <row r="722">
       <c r="A722" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -56059,11 +56059,11 @@
     </row>
     <row r="723">
       <c r="A723" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -56136,11 +56136,11 @@
     </row>
     <row r="724">
       <c r="A724" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -56213,11 +56213,11 @@
     </row>
     <row r="725">
       <c r="A725" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -56290,11 +56290,11 @@
     </row>
     <row r="726">
       <c r="A726" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -56367,11 +56367,11 @@
     </row>
     <row r="727">
       <c r="A727" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -56444,11 +56444,11 @@
     </row>
     <row r="728">
       <c r="A728" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -56521,11 +56521,11 @@
     </row>
     <row r="729">
       <c r="A729" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -56584,10 +56584,10 @@
         <v>19650</v>
       </c>
       <c r="R729" t="n">
-        <v>0</v>
+        <v>876.28</v>
       </c>
       <c r="S729" t="n">
-        <v>73024</v>
+        <v>72147.72</v>
       </c>
       <c r="T729" t="n">
         <v>0</v>
@@ -56598,11 +56598,11 @@
     </row>
     <row r="730">
       <c r="A730" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -56661,10 +56661,10 @@
         <v>0</v>
       </c>
       <c r="R730" t="n">
-        <v>0</v>
+        <v>876.28</v>
       </c>
       <c r="S730" t="n">
-        <v>0</v>
+        <v>-876.28</v>
       </c>
       <c r="T730" t="n">
         <v>0</v>
@@ -56675,11 +56675,11 @@
     </row>
     <row r="731">
       <c r="A731" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -56752,11 +56752,11 @@
     </row>
     <row r="732">
       <c r="A732" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -56806,10 +56806,10 @@
         <v>0</v>
       </c>
       <c r="O732" t="n">
-        <v>47028.96</v>
+        <v>98607.7</v>
       </c>
       <c r="P732" t="n">
-        <v>47028.96</v>
+        <v>98607.7</v>
       </c>
       <c r="Q732" t="n">
         <v>0</v>
@@ -56818,22 +56818,22 @@
         <v>0</v>
       </c>
       <c r="S732" t="n">
-        <v>47028.96</v>
+        <v>98607.7</v>
       </c>
       <c r="T732" t="n">
         <v>0</v>
       </c>
       <c r="U732" t="n">
-        <v>-47028.96</v>
+        <v>-98607.7</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -56906,11 +56906,11 @@
     </row>
     <row r="734">
       <c r="A734" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -56983,11 +56983,11 @@
     </row>
     <row r="735">
       <c r="A735" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -57060,11 +57060,11 @@
     </row>
     <row r="736">
       <c r="A736" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -57137,11 +57137,11 @@
     </row>
     <row r="737">
       <c r="A737" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -57214,11 +57214,11 @@
     </row>
     <row r="738">
       <c r="A738" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -57291,11 +57291,11 @@
     </row>
     <row r="739">
       <c r="A739" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -57368,11 +57368,11 @@
     </row>
     <row r="740">
       <c r="A740" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -57445,11 +57445,11 @@
     </row>
     <row r="741">
       <c r="A741" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -57508,10 +57508,10 @@
         <v>-170265.43</v>
       </c>
       <c r="R741" t="n">
-        <v>0</v>
+        <v>104169.5</v>
       </c>
       <c r="S741" t="n">
-        <v>170265.43</v>
+        <v>66095.92999999999</v>
       </c>
       <c r="T741" t="n">
         <v>0</v>
@@ -57522,11 +57522,11 @@
     </row>
     <row r="742">
       <c r="A742" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -57585,10 +57585,10 @@
         <v>628857.5100000001</v>
       </c>
       <c r="R742" t="n">
-        <v>296021.27</v>
+        <v>400190.77</v>
       </c>
       <c r="S742" t="n">
-        <v>481085.32</v>
+        <v>376915.82</v>
       </c>
       <c r="T742" t="n">
         <v>1500000</v>
@@ -57599,11 +57599,11 @@
     </row>
     <row r="743">
       <c r="A743" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -57676,11 +57676,11 @@
     </row>
     <row r="744">
       <c r="A744" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -57753,11 +57753,11 @@
     </row>
     <row r="745">
       <c r="A745" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -57830,11 +57830,11 @@
     </row>
     <row r="746">
       <c r="A746" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -57907,11 +57907,11 @@
     </row>
     <row r="747">
       <c r="A747" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -57970,10 +57970,10 @@
         <v>-2432048.79</v>
       </c>
       <c r="R747" t="n">
-        <v>0</v>
+        <v>247378.67</v>
       </c>
       <c r="S747" t="n">
-        <v>2432048.79</v>
+        <v>2184670.12</v>
       </c>
       <c r="T747" t="n">
         <v>6500000</v>
@@ -57984,11 +57984,11 @@
     </row>
     <row r="748">
       <c r="A748" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -58047,10 +58047,10 @@
         <v>6375311.670000002</v>
       </c>
       <c r="R748" t="n">
-        <v>9603235.9</v>
+        <v>9850614.57</v>
       </c>
       <c r="S748" t="n">
-        <v>4492841.19</v>
+        <v>4245462.52</v>
       </c>
       <c r="T748" t="n">
         <v>52882823.26</v>
@@ -58061,11 +58061,11 @@
     </row>
     <row r="749">
       <c r="A749" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -58124,10 +58124,10 @@
         <v>-589519.34</v>
       </c>
       <c r="R749" t="n">
-        <v>221030.41</v>
+        <v>455716.57</v>
       </c>
       <c r="S749" t="n">
-        <v>368488.93</v>
+        <v>133802.77</v>
       </c>
       <c r="T749" t="n">
         <v>8888082.390000001</v>
@@ -58138,11 +58138,11 @@
     </row>
     <row r="750">
       <c r="A750" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -58201,10 +58201,10 @@
         <v>8968399.220000001</v>
       </c>
       <c r="R750" t="n">
-        <v>4367980.05</v>
+        <v>4602666.21</v>
       </c>
       <c r="S750" t="n">
-        <v>2052508.05</v>
+        <v>1817821.89</v>
       </c>
       <c r="T750" t="n">
         <v>28888082.39</v>
@@ -58215,11 +58215,11 @@
     </row>
     <row r="751">
       <c r="A751" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -58278,10 +58278,10 @@
         <v>-1228362.35</v>
       </c>
       <c r="R751" t="n">
-        <v>96066.74000000001</v>
+        <v>445162.78</v>
       </c>
       <c r="S751" t="n">
-        <v>1132295.61</v>
+        <v>783199.5699999999</v>
       </c>
       <c r="T751" t="n">
         <v>8983827.050000001</v>
@@ -58292,11 +58292,11 @@
     </row>
     <row r="752">
       <c r="A752" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -58355,10 +58355,10 @@
         <v>4960092.400000002</v>
       </c>
       <c r="R752" t="n">
-        <v>12895559.51</v>
+        <v>13244655.55</v>
       </c>
       <c r="S752" t="n">
-        <v>6522029.85</v>
+        <v>6172933.81</v>
       </c>
       <c r="T752" t="n">
         <v>53397827.05</v>
@@ -58369,11 +58369,11 @@
     </row>
     <row r="753">
       <c r="A753" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -58423,13 +58423,13 @@
         <v>0</v>
       </c>
       <c r="O753" t="n">
-        <v>12816.8</v>
+        <v>14976.8</v>
       </c>
       <c r="P753" t="n">
         <v>6930</v>
       </c>
       <c r="Q753" t="n">
-        <v>5886.799999999999</v>
+        <v>8046.799999999999</v>
       </c>
       <c r="R753" t="n">
         <v>0</v>
@@ -58441,16 +58441,16 @@
         <v>0</v>
       </c>
       <c r="U753" t="n">
-        <v>-12816.8</v>
+        <v>-14976.8</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -58500,13 +58500,13 @@
         <v>2788800</v>
       </c>
       <c r="O754" t="n">
-        <v>89272.39999999999</v>
+        <v>91432.39999999999</v>
       </c>
       <c r="P754" t="n">
         <v>44382.6</v>
       </c>
       <c r="Q754" t="n">
-        <v>44889.8</v>
+        <v>47049.8</v>
       </c>
       <c r="R754" t="n">
         <v>372.6</v>
@@ -58518,16 +58518,16 @@
         <v>0</v>
       </c>
       <c r="U754" t="n">
-        <v>2699527.6</v>
+        <v>2697367.6</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -58586,10 +58586,10 @@
         <v>-1611724.95</v>
       </c>
       <c r="R755" t="n">
-        <v>1161652.61</v>
+        <v>2093554.36</v>
       </c>
       <c r="S755" t="n">
-        <v>450072.34</v>
+        <v>-481829.41</v>
       </c>
       <c r="T755" t="n">
         <v>0</v>
@@ -58600,11 +58600,11 @@
     </row>
     <row r="756">
       <c r="A756" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -58663,10 +58663,10 @@
         <v>0</v>
       </c>
       <c r="R756" t="n">
-        <v>10909826.41</v>
+        <v>11841728.16</v>
       </c>
       <c r="S756" t="n">
-        <v>6756396.87</v>
+        <v>5824495.12</v>
       </c>
       <c r="T756" t="n">
         <v>0</v>
@@ -58677,11 +58677,11 @@
     </row>
     <row r="757">
       <c r="A757" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -58754,11 +58754,11 @@
     </row>
     <row r="758">
       <c r="A758" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -58831,11 +58831,11 @@
     </row>
     <row r="759">
       <c r="A759" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -58908,11 +58908,11 @@
     </row>
     <row r="760">
       <c r="A760" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -58985,11 +58985,11 @@
     </row>
     <row r="761">
       <c r="A761" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -59062,11 +59062,11 @@
     </row>
     <row r="762">
       <c r="A762" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -59139,11 +59139,11 @@
     </row>
     <row r="763">
       <c r="A763" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -59216,11 +59216,11 @@
     </row>
     <row r="764">
       <c r="A764" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -59293,11 +59293,11 @@
     </row>
     <row r="765">
       <c r="A765" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -59370,11 +59370,11 @@
     </row>
     <row r="766">
       <c r="A766" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -59447,11 +59447,11 @@
     </row>
     <row r="767">
       <c r="A767" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -59524,11 +59524,11 @@
     </row>
     <row r="768">
       <c r="A768" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -59601,11 +59601,11 @@
     </row>
     <row r="769">
       <c r="A769" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -59655,13 +59655,13 @@
         <v>0</v>
       </c>
       <c r="O769" t="n">
-        <v>4814.4</v>
+        <v>19408.05</v>
       </c>
       <c r="P769" t="n">
         <v>13841.4</v>
       </c>
       <c r="Q769" t="n">
-        <v>-9027</v>
+        <v>5566.65</v>
       </c>
       <c r="R769" t="n">
         <v>0</v>
@@ -59673,16 +59673,16 @@
         <v>0</v>
       </c>
       <c r="U769" t="n">
-        <v>-4814.4</v>
+        <v>-19408.05</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -59732,13 +59732,13 @@
         <v>0</v>
       </c>
       <c r="O770" t="n">
-        <v>81995.25</v>
+        <v>96588.89999999999</v>
       </c>
       <c r="P770" t="n">
         <v>77180.85000000001</v>
       </c>
       <c r="Q770" t="n">
-        <v>4814.399999999994</v>
+        <v>19408.04999999999</v>
       </c>
       <c r="R770" t="n">
         <v>63339.45</v>
@@ -59750,16 +59750,16 @@
         <v>0</v>
       </c>
       <c r="U770" t="n">
-        <v>137059.95</v>
+        <v>122466.3</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -59809,13 +59809,13 @@
         <v>0</v>
       </c>
       <c r="O771" t="n">
-        <v>0</v>
+        <v>8425.200000000001</v>
       </c>
       <c r="P771" t="n">
         <v>0</v>
       </c>
       <c r="Q771" t="n">
-        <v>0</v>
+        <v>8425.200000000001</v>
       </c>
       <c r="R771" t="n">
         <v>0</v>
@@ -59827,16 +59827,16 @@
         <v>0</v>
       </c>
       <c r="U771" t="n">
-        <v>0</v>
+        <v>-8425.200000000001</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -59886,13 +59886,13 @@
         <v>0</v>
       </c>
       <c r="O772" t="n">
-        <v>10832.4</v>
+        <v>19257.6</v>
       </c>
       <c r="P772" t="n">
         <v>10832.4</v>
       </c>
       <c r="Q772" t="n">
-        <v>0</v>
+        <v>8425.199999999999</v>
       </c>
       <c r="R772" t="n">
         <v>10832.4</v>
@@ -59904,16 +59904,16 @@
         <v>0</v>
       </c>
       <c r="U772" t="n">
-        <v>135746</v>
+        <v>127320.8</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -59986,11 +59986,11 @@
     </row>
     <row r="774">
       <c r="A774" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -60063,11 +60063,11 @@
     </row>
     <row r="775">
       <c r="A775" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -60140,11 +60140,11 @@
     </row>
     <row r="776">
       <c r="A776" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -60217,11 +60217,11 @@
     </row>
     <row r="777">
       <c r="A777" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -60294,11 +60294,11 @@
     </row>
     <row r="778">
       <c r="A778" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -60371,11 +60371,11 @@
     </row>
     <row r="779">
       <c r="A779" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -60448,11 +60448,11 @@
     </row>
     <row r="780">
       <c r="A780" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -60525,11 +60525,11 @@
     </row>
     <row r="781">
       <c r="A781" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -60602,11 +60602,11 @@
     </row>
     <row r="782">
       <c r="A782" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -60679,11 +60679,11 @@
     </row>
     <row r="783">
       <c r="A783" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -60756,11 +60756,11 @@
     </row>
     <row r="784">
       <c r="A784" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -60833,11 +60833,11 @@
     </row>
     <row r="785">
       <c r="A785" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -60910,11 +60910,11 @@
     </row>
     <row r="786">
       <c r="A786" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -60987,11 +60987,11 @@
     </row>
     <row r="787">
       <c r="A787" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -61064,11 +61064,11 @@
     </row>
     <row r="788">
       <c r="A788" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -61141,11 +61141,11 @@
     </row>
     <row r="789">
       <c r="A789" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -61218,11 +61218,11 @@
     </row>
     <row r="790">
       <c r="A790" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -61295,11 +61295,11 @@
     </row>
     <row r="791">
       <c r="A791" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -61372,11 +61372,11 @@
     </row>
     <row r="792">
       <c r="A792" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -61449,11 +61449,11 @@
     </row>
     <row r="793">
       <c r="A793" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -61526,11 +61526,11 @@
     </row>
     <row r="794">
       <c r="A794" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -61603,11 +61603,11 @@
     </row>
     <row r="795">
       <c r="A795" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -61680,11 +61680,11 @@
     </row>
     <row r="796">
       <c r="A796" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -61757,11 +61757,11 @@
     </row>
     <row r="797">
       <c r="A797" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -61834,11 +61834,11 @@
     </row>
     <row r="798">
       <c r="A798" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -61911,11 +61911,11 @@
     </row>
     <row r="799">
       <c r="A799" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -61988,11 +61988,11 @@
     </row>
     <row r="800">
       <c r="A800" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -62065,11 +62065,11 @@
     </row>
     <row r="801">
       <c r="A801" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -62142,11 +62142,11 @@
     </row>
     <row r="802">
       <c r="A802" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -62219,11 +62219,11 @@
     </row>
     <row r="803">
       <c r="A803" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -62296,11 +62296,11 @@
     </row>
     <row r="804">
       <c r="A804" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -62373,11 +62373,11 @@
     </row>
     <row r="805">
       <c r="A805" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -62450,11 +62450,11 @@
     </row>
     <row r="806">
       <c r="A806" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -62527,11 +62527,11 @@
     </row>
     <row r="807">
       <c r="A807" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -62604,11 +62604,11 @@
     </row>
     <row r="808">
       <c r="A808" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -62681,11 +62681,11 @@
     </row>
     <row r="809">
       <c r="A809" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -62758,11 +62758,11 @@
     </row>
     <row r="810">
       <c r="A810" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -62835,11 +62835,11 @@
     </row>
     <row r="811">
       <c r="A811" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -62898,10 +62898,10 @@
         <v>0</v>
       </c>
       <c r="R811" t="n">
-        <v>0</v>
+        <v>48873.78</v>
       </c>
       <c r="S811" t="n">
-        <v>0</v>
+        <v>-48873.78</v>
       </c>
       <c r="T811" t="n">
         <v>0</v>
@@ -62912,11 +62912,11 @@
     </row>
     <row r="812">
       <c r="A812" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -62975,10 +62975,10 @@
         <v>1364129.52</v>
       </c>
       <c r="R812" t="n">
-        <v>637172</v>
+        <v>686045.78</v>
       </c>
       <c r="S812" t="n">
-        <v>650972</v>
+        <v>602098.22</v>
       </c>
       <c r="T812" t="n">
         <v>2000000</v>
@@ -62989,11 +62989,11 @@
     </row>
     <row r="813">
       <c r="A813" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -63066,11 +63066,11 @@
     </row>
     <row r="814">
       <c r="A814" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -63143,11 +63143,11 @@
     </row>
     <row r="815">
       <c r="A815" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -63206,10 +63206,10 @@
         <v>0</v>
       </c>
       <c r="R815" t="n">
-        <v>0</v>
+        <v>244512.48</v>
       </c>
       <c r="S815" t="n">
-        <v>0</v>
+        <v>-244512.48</v>
       </c>
       <c r="T815" t="n">
         <v>0</v>
@@ -63220,11 +63220,11 @@
     </row>
     <row r="816">
       <c r="A816" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -63283,10 +63283,10 @@
         <v>2124079</v>
       </c>
       <c r="R816" t="n">
-        <v>0</v>
+        <v>244512.48</v>
       </c>
       <c r="S816" t="n">
-        <v>1284165.8</v>
+        <v>1039653.32</v>
       </c>
       <c r="T816" t="n">
         <v>16123051.01</v>
@@ -63297,11 +63297,11 @@
     </row>
     <row r="817">
       <c r="A817" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -63360,10 +63360,10 @@
         <v>-1532232.82</v>
       </c>
       <c r="R817" t="n">
-        <v>1517811.82</v>
+        <v>1532232.82</v>
       </c>
       <c r="S817" t="n">
-        <v>14421</v>
+        <v>0</v>
       </c>
       <c r="T817" t="n">
         <v>0</v>
@@ -63374,11 +63374,11 @@
     </row>
     <row r="818">
       <c r="A818" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -63437,10 +63437,10 @@
         <v>2105003.2</v>
       </c>
       <c r="R818" t="n">
-        <v>5138007.48</v>
+        <v>5152428.48</v>
       </c>
       <c r="S818" t="n">
-        <v>1532232.82</v>
+        <v>1517811.82</v>
       </c>
       <c r="T818" t="n">
         <v>2000000</v>
@@ -63451,11 +63451,11 @@
     </row>
     <row r="819">
       <c r="A819" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -63514,10 +63514,10 @@
         <v>-518000</v>
       </c>
       <c r="R819" t="n">
-        <v>518000</v>
+        <v>529506.14</v>
       </c>
       <c r="S819" t="n">
-        <v>0</v>
+        <v>-11506.14</v>
       </c>
       <c r="T819" t="n">
         <v>0</v>
@@ -63528,11 +63528,11 @@
     </row>
     <row r="820">
       <c r="A820" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -63591,10 +63591,10 @@
         <v>582257.2300000002</v>
       </c>
       <c r="R820" t="n">
-        <v>1036000</v>
+        <v>1047506.14</v>
       </c>
       <c r="S820" t="n">
-        <v>635409.45</v>
+        <v>623903.3100000001</v>
       </c>
       <c r="T820" t="n">
         <v>0</v>
@@ -63605,11 +63605,11 @@
     </row>
     <row r="821">
       <c r="A821" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -63668,10 +63668,10 @@
         <v>0</v>
       </c>
       <c r="R821" t="n">
-        <v>1655009.21</v>
+        <v>1728746.99</v>
       </c>
       <c r="S821" t="n">
-        <v>-1655009.21</v>
+        <v>-1728746.99</v>
       </c>
       <c r="T821" t="n">
         <v>0</v>
@@ -63682,11 +63682,11 @@
     </row>
     <row r="822">
       <c r="A822" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -63745,10 +63745,10 @@
         <v>0</v>
       </c>
       <c r="R822" t="n">
-        <v>1664031.21</v>
+        <v>1737768.99</v>
       </c>
       <c r="S822" t="n">
-        <v>1146917.45</v>
+        <v>1073179.67</v>
       </c>
       <c r="T822" t="n">
         <v>0</v>
@@ -63759,11 +63759,11 @@
     </row>
     <row r="823">
       <c r="A823" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -63836,11 +63836,11 @@
     </row>
     <row r="824">
       <c r="A824" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -63913,11 +63913,11 @@
     </row>
     <row r="825">
       <c r="A825" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>RELEXORC_14-04-2026.csv</t>
+          <t>RELEXORC_15-04-2026.csv</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -63967,10 +63967,10 @@
         <v>16930000</v>
       </c>
       <c r="O825" t="n">
-        <v>582290.01</v>
+        <v>633868.75</v>
       </c>
       <c r="P825" t="n">
-        <v>582290.01</v>
+        <v>633868.75</v>
       </c>
       <c r="Q825" t="n">
         <v>0</v>
@@ -63979,13 +63979,13 @@
         <v>535261.05</v>
       </c>
       <c r="S825" t="n">
-        <v>47028.96</v>
+        <v>98607.7</v>
       </c>
       <c r="T825" t="n">
         <v>0</v>
       </c>
       <c r="U825" t="n">
-        <v>16347709.99</v>
+        <v>16296131.25</v>
       </c>
     </row>
   </sheetData>
@@ -64139,7 +64139,7 @@
         <v>46112</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -64225,7 +64225,7 @@
         <v>46112</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -64311,7 +64311,7 @@
         <v>46112</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -64397,7 +64397,7 @@
         <v>46112</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -64483,7 +64483,7 @@
         <v>46112</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -64549,10 +64549,10 @@
         <v>296021.27</v>
       </c>
       <c r="V6" t="n">
-        <v>296021.27</v>
+        <v>400190.77</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>104169.5</v>
       </c>
       <c r="X6" t="n">
         <v>2594035.9</v>
@@ -64569,7 +64569,7 @@
         <v>46112</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -64655,7 +64655,7 @@
         <v>46112</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -64741,7 +64741,7 @@
         <v>46112</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -64807,10 +64807,10 @@
         <v>9603235.9</v>
       </c>
       <c r="V9" t="n">
-        <v>9603235.9</v>
+        <v>9850614.57</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>247378.6699999999</v>
       </c>
       <c r="X9" t="n">
         <v>19401015.72</v>
@@ -64827,7 +64827,7 @@
         <v>46112</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -64893,10 +64893,10 @@
         <v>4367980.05</v>
       </c>
       <c r="V10" t="n">
-        <v>4367980.05</v>
+        <v>4602666.21</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>234686.1600000001</v>
       </c>
       <c r="X10" t="n">
         <v>21872955.56</v>
@@ -64913,7 +64913,7 @@
         <v>46112</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -64979,10 +64979,10 @@
         <v>12799492.77</v>
       </c>
       <c r="V11" t="n">
-        <v>12895559.51</v>
+        <v>13244655.55</v>
       </c>
       <c r="W11" t="n">
-        <v>96066.74000000022</v>
+        <v>445162.7800000012</v>
       </c>
       <c r="X11" t="n">
         <v>27724491.19</v>
@@ -64999,7 +64999,7 @@
         <v>46112</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -65047,10 +65047,10 @@
         <v>76455.60000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>89272.39999999999</v>
+        <v>91432.39999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>12816.79999999999</v>
+        <v>14976.79999999999</v>
       </c>
       <c r="R12" t="n">
         <v>38532.6</v>
@@ -65074,10 +65074,10 @@
         <v>2712344.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>2699527.6</v>
+        <v>2697367.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>-12816.79999999981</v>
+        <v>-14976.79999999981</v>
       </c>
     </row>
     <row r="13">
@@ -65085,7 +65085,7 @@
         <v>46112</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -65151,10 +65151,10 @@
         <v>9748173.800000001</v>
       </c>
       <c r="V13" t="n">
-        <v>10909826.41</v>
+        <v>11841728.16</v>
       </c>
       <c r="W13" t="n">
-        <v>1161652.609999999</v>
+        <v>2093554.359999999</v>
       </c>
       <c r="X13" t="n">
         <v>1045530.35</v>
@@ -65171,7 +65171,7 @@
         <v>46112</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -65257,7 +65257,7 @@
         <v>46112</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -65343,7 +65343,7 @@
         <v>46112</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -65409,10 +65409,10 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>876.28</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>876.28</v>
       </c>
       <c r="X16" t="n">
         <v>1932326</v>
@@ -65429,7 +65429,7 @@
         <v>46112</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -65515,7 +65515,7 @@
         <v>46112</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -65601,7 +65601,7 @@
         <v>46112</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -65687,7 +65687,7 @@
         <v>46112</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -65773,7 +65773,7 @@
         <v>46112</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -65859,7 +65859,7 @@
         <v>46112</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -65945,7 +65945,7 @@
         <v>46112</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -66031,7 +66031,7 @@
         <v>46112</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -66117,7 +66117,7 @@
         <v>46112</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -66174,10 +66174,10 @@
         <v>1791885.01</v>
       </c>
       <c r="S25" t="n">
-        <v>2563101.06</v>
+        <v>2603450.08</v>
       </c>
       <c r="T25" t="n">
-        <v>771216.05</v>
+        <v>811565.0700000001</v>
       </c>
       <c r="U25" t="n">
         <v>1791885.01</v>
@@ -66203,7 +66203,7 @@
         <v>46112</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -66289,7 +66289,7 @@
         <v>46112</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -66375,7 +66375,7 @@
         <v>46112</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -66461,7 +66461,7 @@
         <v>46112</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -66547,7 +66547,7 @@
         <v>46112</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -66633,7 +66633,7 @@
         <v>46112</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -66719,7 +66719,7 @@
         <v>46112</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -66805,7 +66805,7 @@
         <v>46112</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -66891,7 +66891,7 @@
         <v>46112</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -66977,7 +66977,7 @@
         <v>46112</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -67063,7 +67063,7 @@
         <v>46112</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -67149,7 +67149,7 @@
         <v>46112</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -67235,7 +67235,7 @@
         <v>46112</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -67321,7 +67321,7 @@
         <v>46112</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -67407,7 +67407,7 @@
         <v>46112</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -67493,7 +67493,7 @@
         <v>46112</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -67559,10 +67559,10 @@
         <v>637172</v>
       </c>
       <c r="V41" t="n">
-        <v>637172</v>
+        <v>686045.78</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>48873.78000000003</v>
       </c>
       <c r="X41" t="n">
         <v>3347726.48</v>
@@ -67579,7 +67579,7 @@
         <v>46112</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -67665,7 +67665,7 @@
         <v>46112</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -67731,10 +67731,10 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>244512.48</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>244512.48</v>
       </c>
       <c r="X43" t="n">
         <v>4591755.2</v>
@@ -67751,7 +67751,7 @@
         <v>46112</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -67817,10 +67817,10 @@
         <v>3620195.66</v>
       </c>
       <c r="V44" t="n">
-        <v>5138007.48</v>
+        <v>5152428.48</v>
       </c>
       <c r="W44" t="n">
-        <v>1517811.82</v>
+        <v>1532232.82</v>
       </c>
       <c r="X44" t="n">
         <v>7404963.76</v>
@@ -67837,7 +67837,7 @@
         <v>46112</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -67903,10 +67903,10 @@
         <v>518000</v>
       </c>
       <c r="V45" t="n">
-        <v>1036000</v>
+        <v>1047506.14</v>
       </c>
       <c r="W45" t="n">
-        <v>518000</v>
+        <v>529506.14</v>
       </c>
       <c r="X45" t="n">
         <v>5746333.32</v>
@@ -67923,7 +67923,7 @@
         <v>46112</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -67989,10 +67989,10 @@
         <v>9022</v>
       </c>
       <c r="V46" t="n">
-        <v>1664031.21</v>
+        <v>1737768.99</v>
       </c>
       <c r="W46" t="n">
-        <v>1655009.21</v>
+        <v>1728746.99</v>
       </c>
       <c r="X46" t="n">
         <v>683844.08</v>
@@ -68009,7 +68009,7 @@
         <v>46112</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -68095,7 +68095,7 @@
         <v>46112</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -68181,7 +68181,7 @@
         <v>46112</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -68267,7 +68267,7 @@
         <v>46112</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -68353,7 +68353,7 @@
         <v>46112</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -68439,7 +68439,7 @@
         <v>46112</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -68487,10 +68487,10 @@
         <v>77180.85000000001</v>
       </c>
       <c r="P52" t="n">
-        <v>81995.25</v>
+        <v>96588.89999999999</v>
       </c>
       <c r="Q52" t="n">
-        <v>4814.399999999994</v>
+        <v>19408.04999999999</v>
       </c>
       <c r="R52" t="n">
         <v>68454.75</v>
@@ -68514,10 +68514,10 @@
         <v>141874.35</v>
       </c>
       <c r="Y52" t="n">
-        <v>137059.95</v>
+        <v>122466.3</v>
       </c>
       <c r="Z52" t="n">
-        <v>-4814.399999999994</v>
+        <v>-19408.05</v>
       </c>
     </row>
     <row r="53">
@@ -68525,7 +68525,7 @@
         <v>46112</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -68573,10 +68573,10 @@
         <v>10832.4</v>
       </c>
       <c r="P53" t="n">
-        <v>10832.4</v>
+        <v>19257.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>8425.199999999999</v>
       </c>
       <c r="R53" t="n">
         <v>10832.4</v>
@@ -68600,10 +68600,10 @@
         <v>135746</v>
       </c>
       <c r="Y53" t="n">
-        <v>135746</v>
+        <v>127320.8</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>-8425.199999999997</v>
       </c>
     </row>
     <row r="54">
@@ -68611,7 +68611,7 @@
         <v>46112</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -68697,7 +68697,7 @@
         <v>46112</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -68783,7 +68783,7 @@
         <v>46112</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -68869,7 +68869,7 @@
         <v>46112</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -68955,7 +68955,7 @@
         <v>46112</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -69041,7 +69041,7 @@
         <v>46112</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -69127,7 +69127,7 @@
         <v>46112</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -69213,7 +69213,7 @@
         <v>46112</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -69299,7 +69299,7 @@
         <v>46112</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -69385,7 +69385,7 @@
         <v>46112</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -69471,7 +69471,7 @@
         <v>46112</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -69557,7 +69557,7 @@
         <v>46112</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -69643,7 +69643,7 @@
         <v>46112</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -69729,7 +69729,7 @@
         <v>46112</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -69815,7 +69815,7 @@
         <v>46112</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -69901,7 +69901,7 @@
         <v>46112</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -69987,7 +69987,7 @@
         <v>46112</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -70073,7 +70073,7 @@
         <v>46112</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -70159,7 +70159,7 @@
         <v>46112</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -70245,7 +70245,7 @@
         <v>46112</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -70331,7 +70331,7 @@
         <v>46112</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -70417,7 +70417,7 @@
         <v>46112</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -70503,7 +70503,7 @@
         <v>46112</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -70589,7 +70589,7 @@
         <v>46112</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -70675,7 +70675,7 @@
         <v>46112</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -70761,7 +70761,7 @@
         <v>46112</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -70847,7 +70847,7 @@
         <v>46112</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -70933,7 +70933,7 @@
         <v>46112</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -71019,7 +71019,7 @@
         <v>46112</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -71105,7 +71105,7 @@
         <v>46112</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -71191,7 +71191,7 @@
         <v>46112</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -71277,7 +71277,7 @@
         <v>46112</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -71363,7 +71363,7 @@
         <v>46112</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -71449,7 +71449,7 @@
         <v>46112</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -71535,7 +71535,7 @@
         <v>46112</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -71621,7 +71621,7 @@
         <v>46112</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -71707,7 +71707,7 @@
         <v>46112</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -71793,7 +71793,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -71879,7 +71879,7 @@
         <v>46112</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -71965,7 +71965,7 @@
         <v>46112</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -72031,19 +72031,19 @@
         <v>6636057.49</v>
       </c>
       <c r="V93" t="n">
-        <v>8622057.49</v>
+        <v>8633441.1</v>
       </c>
       <c r="W93" t="n">
-        <v>1986000</v>
+        <v>1997383.609999999</v>
       </c>
       <c r="X93" t="n">
         <v>7354333.68</v>
       </c>
       <c r="Y93" t="n">
-        <v>7354333.68</v>
+        <v>1824333.68</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>-5530000</v>
       </c>
     </row>
     <row r="94">
@@ -72051,7 +72051,7 @@
         <v>46112</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -72117,10 +72117,10 @@
         <v>441322.08</v>
       </c>
       <c r="V94" t="n">
-        <v>441322.08</v>
+        <v>461155.91</v>
       </c>
       <c r="W94" t="n">
-        <v>0</v>
+        <v>19833.82999999996</v>
       </c>
       <c r="X94" t="n">
         <v>326945.72</v>
@@ -72137,7 +72137,7 @@
         <v>46112</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -72223,7 +72223,7 @@
         <v>46112</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -72309,7 +72309,7 @@
         <v>46112</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -72395,7 +72395,7 @@
         <v>46112</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -72481,7 +72481,7 @@
         <v>46112</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -72567,7 +72567,7 @@
         <v>46112</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -72653,7 +72653,7 @@
         <v>46112</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -72739,7 +72739,7 @@
         <v>46112</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -72825,7 +72825,7 @@
         <v>46112</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -72911,7 +72911,7 @@
         <v>46112</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -72997,7 +72997,7 @@
         <v>46112</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -73083,7 +73083,7 @@
         <v>46112</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -73140,10 +73140,10 @@
         <v>1128600</v>
       </c>
       <c r="S106" t="n">
-        <v>1363400</v>
+        <v>1399100</v>
       </c>
       <c r="T106" t="n">
-        <v>234800</v>
+        <v>270500</v>
       </c>
       <c r="U106" t="n">
         <v>747600</v>
@@ -73169,7 +73169,7 @@
         <v>46112</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -73255,7 +73255,7 @@
         <v>46112</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -73321,10 +73321,10 @@
         <v>0</v>
       </c>
       <c r="V108" t="n">
-        <v>267500</v>
+        <v>270645.89</v>
       </c>
       <c r="W108" t="n">
-        <v>267500</v>
+        <v>270645.89</v>
       </c>
       <c r="X108" t="n">
         <v>4429727.67</v>
@@ -73341,7 +73341,7 @@
         <v>46112</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -73427,7 +73427,7 @@
         <v>46112</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -73513,7 +73513,7 @@
         <v>46112</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -73599,7 +73599,7 @@
         <v>46112</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -73685,7 +73685,7 @@
         <v>46112</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -73771,7 +73771,7 @@
         <v>46112</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -73857,7 +73857,7 @@
         <v>46112</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -73943,7 +73943,7 @@
         <v>46112</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -74029,7 +74029,7 @@
         <v>46112</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -74115,7 +74115,7 @@
         <v>46112</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -74201,7 +74201,7 @@
         <v>46112</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -74287,7 +74287,7 @@
         <v>46112</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -74353,10 +74353,10 @@
         <v>1278789.54</v>
       </c>
       <c r="V120" t="n">
-        <v>1278789.54</v>
+        <v>1320541.59</v>
       </c>
       <c r="W120" t="n">
-        <v>0</v>
+        <v>41752.05000000005</v>
       </c>
       <c r="X120" t="n">
         <v>1076961.03</v>
@@ -74373,7 +74373,7 @@
         <v>46112</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -74459,7 +74459,7 @@
         <v>46112</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -74525,10 +74525,10 @@
         <v>5499.9</v>
       </c>
       <c r="V122" t="n">
-        <v>5499.9</v>
+        <v>11050.39</v>
       </c>
       <c r="W122" t="n">
-        <v>0</v>
+        <v>5550.49</v>
       </c>
       <c r="X122" t="n">
         <v>59848.63</v>
@@ -74545,7 +74545,7 @@
         <v>46112</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -74631,7 +74631,7 @@
         <v>46112</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -74717,7 +74717,7 @@
         <v>46112</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -74803,7 +74803,7 @@
         <v>46112</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -74869,10 +74869,10 @@
         <v>3507323.16</v>
       </c>
       <c r="V126" t="n">
-        <v>4103146.56</v>
+        <v>4670885.78</v>
       </c>
       <c r="W126" t="n">
-        <v>595823.3999999999</v>
+        <v>1163562.62</v>
       </c>
       <c r="X126" t="n">
         <v>10589524.26</v>
@@ -74889,7 +74889,7 @@
         <v>46112</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -74975,7 +74975,7 @@
         <v>46112</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -75023,19 +75023,19 @@
         <v>535261.05</v>
       </c>
       <c r="P128" t="n">
-        <v>582290.01</v>
+        <v>633868.75</v>
       </c>
       <c r="Q128" t="n">
-        <v>47028.95999999996</v>
+        <v>98607.69999999995</v>
       </c>
       <c r="R128" t="n">
         <v>535261.05</v>
       </c>
       <c r="S128" t="n">
-        <v>582290.01</v>
+        <v>633868.75</v>
       </c>
       <c r="T128" t="n">
-        <v>47028.95999999996</v>
+        <v>98607.69999999995</v>
       </c>
       <c r="U128" t="n">
         <v>535261.05</v>
@@ -75050,10 +75050,10 @@
         <v>16394738.95</v>
       </c>
       <c r="Y128" t="n">
-        <v>16347709.99</v>
+        <v>16296131.25</v>
       </c>
       <c r="Z128" t="n">
-        <v>-47028.95999999903</v>
+        <v>-98607.69999999925</v>
       </c>
     </row>
   </sheetData>

--- a/Base_Consolidada_SIAFI.xlsx
+++ b/Base_Consolidada_SIAFI.xlsx
@@ -63999,7 +63999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z130"/>
+  <dimension ref="A1:AC130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64120,15 +64120,30 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>Bloqueado_Ant</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Bloqueado_Atual</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Variação_Bloqueado</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>Disponível_Ant</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Disponível_Atual</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Variação_Disponível</t>
         </is>
@@ -64211,12 +64226,21 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
         <v>1072500</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AB2" t="n">
         <v>1072500</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AC2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -64297,12 +64321,21 @@
         <v>526440</v>
       </c>
       <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
         <v>12300</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AB3" t="n">
         <v>12300</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AC3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -64383,12 +64416,21 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
         <v>97412</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AB4" t="n">
         <v>97412</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AC4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -64469,12 +64511,21 @@
         <v>20000</v>
       </c>
       <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
         <v>485000</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AB5" t="n">
         <v>485000</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AC5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -64555,12 +64606,21 @@
         <v>281744.6</v>
       </c>
       <c r="X6" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
         <v>2594035.9</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AB6" t="n">
         <v>2594035.9</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AC6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -64649,6 +64709,15 @@
       <c r="Z7" t="n">
         <v>0</v>
       </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -64727,12 +64796,21 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
         <v>15770</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AB8" t="n">
         <v>15770</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AC8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -64813,12 +64891,21 @@
         <v>1329599.219999999</v>
       </c>
       <c r="X9" t="n">
+        <v>46382823.26</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>52882823.26</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="AA9" t="n">
         <v>19401015.72</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AB9" t="n">
         <v>12901015.72</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AC9" t="n">
         <v>-6499999.999999998</v>
       </c>
     </row>
@@ -64899,12 +64986,21 @@
         <v>1462988.71</v>
       </c>
       <c r="X10" t="n">
+        <v>27222950.51</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>28888082.39</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1665131.879999999</v>
+      </c>
+      <c r="AA10" t="n">
         <v>21872955.56</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AB10" t="n">
         <v>20207823.68</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AC10" t="n">
         <v>-1665131.879999999</v>
       </c>
     </row>
@@ -64985,12 +65081,21 @@
         <v>5389734.240000002</v>
       </c>
       <c r="X11" t="n">
+        <v>46897827.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>53397827.05</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="AA11" t="n">
         <v>27724491.19</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AB11" t="n">
         <v>18646285.19</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AC11" t="n">
         <v>-9078206</v>
       </c>
     </row>
@@ -65071,12 +65176,21 @@
         <v>1080</v>
       </c>
       <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
         <v>2712344.4</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AB12" t="n">
         <v>2696107.6</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AC12" t="n">
         <v>-16236.79999999981</v>
       </c>
     </row>
@@ -65157,12 +65271,21 @@
         <v>2593798.539999999</v>
       </c>
       <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
         <v>1045530.35</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AB13" t="n">
         <v>3623736.35</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AC13" t="n">
         <v>2578206</v>
       </c>
     </row>
@@ -65243,12 +65366,21 @@
         <v>864915.1199999999</v>
       </c>
       <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
         <v>10102333.08</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AB14" t="n">
         <v>8763041.26</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AC14" t="n">
         <v>-1339291.82</v>
       </c>
     </row>
@@ -65329,12 +65461,21 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1650000</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AB15" t="n">
         <v>1650000</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AC15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -65415,12 +65556,21 @@
         <v>73024</v>
       </c>
       <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1932326</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AB16" t="n">
         <v>1932326</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AC16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -65501,12 +65651,21 @@
         <v>396970.3500000006</v>
       </c>
       <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
         <v>22791039.49</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AB17" t="n">
         <v>24164795.07</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AC17" t="n">
         <v>1373755.580000002</v>
       </c>
     </row>
@@ -65587,12 +65746,21 @@
         <v>14714.66</v>
       </c>
       <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
         <v>105856.02</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AB18" t="n">
         <v>105856.02</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AC18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -65673,12 +65841,21 @@
         <v>8395377.629999995</v>
       </c>
       <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
         <v>278444787.27</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AB19" t="n">
         <v>278449528.26</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AC19" t="n">
         <v>4740.990000009537</v>
       </c>
     </row>
@@ -65759,12 +65936,21 @@
         <v>213.5100000000093</v>
       </c>
       <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
         <v>3530858.84</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AB20" t="n">
         <v>3544564.98</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AC20" t="n">
         <v>13706.14000000013</v>
       </c>
     </row>
@@ -65853,6 +66039,15 @@
       <c r="Z21" t="n">
         <v>0</v>
       </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -65931,12 +66126,21 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
         <v>139.09</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AB22" t="n">
         <v>139.09</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AC22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -66017,12 +66221,21 @@
         <v>3113406.819999999</v>
       </c>
       <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
         <v>30895406.07</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AB23" t="n">
         <v>30895406.07</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AC23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -66103,12 +66316,21 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
         <v>6594301</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AB24" t="n">
         <v>6594301</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AC24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -66189,12 +66411,21 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
         <v>9332401.09</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AB25" t="n">
         <v>9332401.09</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AC25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -66275,12 +66506,21 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
         <v>452205.65</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AB26" t="n">
         <v>38678.68</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AC26" t="n">
         <v>-413526.97</v>
       </c>
     </row>
@@ -66361,12 +66601,21 @@
         <v>220812.59</v>
       </c>
       <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
         <v>4232604.14</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AB27" t="n">
         <v>4232604.14</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AC27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -66447,12 +66696,21 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
         <v>52328.35</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AB28" t="n">
         <v>29796.8</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AC28" t="n">
         <v>-22531.55</v>
       </c>
     </row>
@@ -66533,12 +66791,21 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
         <v>4050200</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AB29" t="n">
         <v>4050200</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AC29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -66619,12 +66886,21 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
         <v>10000</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AB30" t="n">
         <v>10000</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AC30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -66705,12 +66981,21 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
         <v>18540000</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AB31" t="n">
         <v>18540000</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AC31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -66791,12 +67076,21 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
         <v>500000</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AB32" t="n">
         <v>500000</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AC32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -66877,12 +67171,21 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
         <v>1292593.07</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AB33" t="n">
         <v>1292593.07</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AC33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -66963,12 +67266,21 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
         <v>770000</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="AB34" t="n">
         <v>770000</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AC34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -67049,12 +67361,21 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
         <v>19994</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AB35" t="n">
         <v>19994</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AC35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -67135,12 +67456,21 @@
         <v>94956</v>
       </c>
       <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
         <v>26109.93</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="AB36" t="n">
         <v>26109.93</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AC36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -67221,12 +67551,21 @@
         <v>7672.950000000012</v>
       </c>
       <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
         <v>16522.65</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="AB37" t="n">
         <v>12310.05</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AC37" t="n">
         <v>-4212.600000000002</v>
       </c>
     </row>
@@ -67307,12 +67646,21 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
         <v>34114.1</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AB38" t="n">
         <v>34114.1</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AC38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -67393,12 +67741,21 @@
         <v>24072</v>
       </c>
       <c r="X39" t="n">
+        <v>400000</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>400000</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
         <v>215417</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="AB39" t="n">
         <v>215417</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AC39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -67479,12 +67836,21 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
         <v>15000</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AB40" t="n">
         <v>15000</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AC40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -67565,12 +67931,21 @@
         <v>71015.78000000003</v>
       </c>
       <c r="X41" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
         <v>3347726.48</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="AB41" t="n">
         <v>3347726.48</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AC41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -67651,12 +68026,21 @@
         <v>3690</v>
       </c>
       <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
         <v>1227731.4</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="AB42" t="n">
         <v>1227731.4</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AC42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -67737,12 +68121,21 @@
         <v>1284165.8</v>
       </c>
       <c r="X43" t="n">
+        <v>16123051.01</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>16123051.01</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
         <v>4591755.2</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="AB43" t="n">
         <v>4591755.2</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AC43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -67823,12 +68216,21 @@
         <v>1532232.82</v>
       </c>
       <c r="X44" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
         <v>7404963.76</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="AB44" t="n">
         <v>7404963.76</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AC44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -67909,12 +68311,21 @@
         <v>635409.45</v>
       </c>
       <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
         <v>5746333.32</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="AB45" t="n">
         <v>5746333.32</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AC45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -67995,12 +68406,21 @@
         <v>2221970.44</v>
       </c>
       <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
         <v>683844.08</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="AB46" t="n">
         <v>683844.08</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AC46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -68081,12 +68501,21 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
         <v>10000</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="AB47" t="n">
         <v>10000</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AC47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -68167,12 +68596,21 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
         <v>665000</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="AB48" t="n">
         <v>665000</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="AC48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -68261,6 +68699,15 @@
       <c r="Z49" t="n">
         <v>0</v>
       </c>
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -68347,6 +68794,15 @@
       <c r="Z50" t="n">
         <v>0</v>
       </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -68425,12 +68881,21 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
         <v>9418</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="AB51" t="n">
         <v>9418</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="AC51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -68511,12 +68976,21 @@
         <v>13841.40000000001</v>
       </c>
       <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
         <v>141874.35</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="AB52" t="n">
         <v>122466.3</v>
       </c>
-      <c r="Z52" t="n">
+      <c r="AC52" t="n">
         <v>-19408.05</v>
       </c>
     </row>
@@ -68597,12 +69071,21 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
         <v>135746</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="AB53" t="n">
         <v>127320.8</v>
       </c>
-      <c r="Z53" t="n">
+      <c r="AC53" t="n">
         <v>-8425.199999999997</v>
       </c>
     </row>
@@ -68683,12 +69166,21 @@
         <v>30311.5</v>
       </c>
       <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
         <v>26683.3</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="AB54" t="n">
         <v>23333.3</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="AC54" t="n">
         <v>-3350</v>
       </c>
     </row>
@@ -68769,12 +69261,21 @@
         <v>11725</v>
       </c>
       <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
         <v>17047.7</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="AB55" t="n">
         <v>17047.7</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="AC55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -68858,9 +69359,18 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
         <v>5000</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AC56" t="n">
         <v>5000</v>
       </c>
     </row>
@@ -68941,12 +69451,21 @@
         <v>0</v>
       </c>
       <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="n">
         <v>5000</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="AB57" t="n">
         <v>5000</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="AC57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -69027,12 +69546,21 @@
         <v>0</v>
       </c>
       <c r="X58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="n">
         <v>5000</v>
       </c>
-      <c r="Y58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z58" t="n">
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
         <v>-5000</v>
       </c>
     </row>
@@ -69116,9 +69644,18 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="n">
         <v>5000</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="AC59" t="n">
         <v>5000</v>
       </c>
     </row>
@@ -69199,12 +69736,21 @@
         <v>10000</v>
       </c>
       <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" t="n">
         <v>5000</v>
       </c>
-      <c r="Y60" t="n">
+      <c r="AB60" t="n">
         <v>5000</v>
       </c>
-      <c r="Z60" t="n">
+      <c r="AC60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -69293,6 +69839,15 @@
       <c r="Z61" t="n">
         <v>0</v>
       </c>
+      <c r="AA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -69371,12 +69926,21 @@
         <v>5000</v>
       </c>
       <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
         <v>5000</v>
       </c>
-      <c r="Y62" t="n">
+      <c r="AB62" t="n">
         <v>5000</v>
       </c>
-      <c r="Z62" t="n">
+      <c r="AC62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -69465,6 +70029,15 @@
       <c r="Z63" t="n">
         <v>0</v>
       </c>
+      <c r="AA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -69551,6 +70124,15 @@
       <c r="Z64" t="n">
         <v>0</v>
       </c>
+      <c r="AA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -69637,6 +70219,15 @@
       <c r="Z65" t="n">
         <v>0</v>
       </c>
+      <c r="AA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -69723,6 +70314,15 @@
       <c r="Z66" t="n">
         <v>0</v>
       </c>
+      <c r="AA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -69801,12 +70401,21 @@
         <v>0</v>
       </c>
       <c r="X67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" t="n">
         <v>65296.8</v>
       </c>
-      <c r="Y67" t="n">
+      <c r="AB67" t="n">
         <v>122076.6</v>
       </c>
-      <c r="Z67" t="n">
+      <c r="AC67" t="n">
         <v>56779.8</v>
       </c>
     </row>
@@ -69887,12 +70496,21 @@
         <v>10000</v>
       </c>
       <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA68" t="n">
         <v>5000</v>
       </c>
-      <c r="Y68" t="n">
+      <c r="AB68" t="n">
         <v>5000</v>
       </c>
-      <c r="Z68" t="n">
+      <c r="AC68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -69973,12 +70591,21 @@
         <v>5000</v>
       </c>
       <c r="X69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" t="n">
         <v>10000</v>
       </c>
-      <c r="Y69" t="n">
+      <c r="AB69" t="n">
         <v>10000</v>
       </c>
-      <c r="Z69" t="n">
+      <c r="AC69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -70067,6 +70694,15 @@
       <c r="Z70" t="n">
         <v>0</v>
       </c>
+      <c r="AA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -70153,6 +70789,15 @@
       <c r="Z71" t="n">
         <v>0</v>
       </c>
+      <c r="AA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -70239,6 +70884,15 @@
       <c r="Z72" t="n">
         <v>0</v>
       </c>
+      <c r="AA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -70325,6 +70979,15 @@
       <c r="Z73" t="n">
         <v>0</v>
       </c>
+      <c r="AA73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -70411,6 +71074,15 @@
       <c r="Z74" t="n">
         <v>0</v>
       </c>
+      <c r="AA74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -70497,6 +71169,15 @@
       <c r="Z75" t="n">
         <v>0</v>
       </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -70583,6 +71264,15 @@
       <c r="Z76" t="n">
         <v>0</v>
       </c>
+      <c r="AA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -70669,6 +71359,15 @@
       <c r="Z77" t="n">
         <v>0</v>
       </c>
+      <c r="AA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -70755,6 +71454,15 @@
       <c r="Z78" t="n">
         <v>0</v>
       </c>
+      <c r="AA78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -70841,6 +71549,15 @@
       <c r="Z79" t="n">
         <v>0</v>
       </c>
+      <c r="AA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -70927,6 +71644,15 @@
       <c r="Z80" t="n">
         <v>0</v>
       </c>
+      <c r="AA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -71005,12 +71731,21 @@
         <v>0</v>
       </c>
       <c r="X81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA81" t="n">
         <v>8368410.56</v>
       </c>
-      <c r="Y81" t="n">
+      <c r="AB81" t="n">
         <v>8368410.56</v>
       </c>
-      <c r="Z81" t="n">
+      <c r="AC81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71091,12 +71826,21 @@
         <v>0</v>
       </c>
       <c r="X82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA82" t="n">
         <v>5000000</v>
       </c>
-      <c r="Y82" t="n">
+      <c r="AB82" t="n">
         <v>5000000</v>
       </c>
-      <c r="Z82" t="n">
+      <c r="AC82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71177,12 +71921,21 @@
         <v>0</v>
       </c>
       <c r="X83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA83" t="n">
         <v>199635.07</v>
       </c>
-      <c r="Y83" t="n">
+      <c r="AB83" t="n">
         <v>199635.07</v>
       </c>
-      <c r="Z83" t="n">
+      <c r="AC83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71271,6 +72024,15 @@
       <c r="Z84" t="n">
         <v>0</v>
       </c>
+      <c r="AA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -71349,12 +72111,21 @@
         <v>0</v>
       </c>
       <c r="X85" t="n">
+        <v>1229488.3</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>1229488.3</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA85" t="n">
         <v>61458.63</v>
       </c>
-      <c r="Y85" t="n">
+      <c r="AB85" t="n">
         <v>61458.63</v>
       </c>
-      <c r="Z85" t="n">
+      <c r="AC85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71435,12 +72206,21 @@
         <v>0</v>
       </c>
       <c r="X86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA86" t="n">
         <v>64023.02</v>
       </c>
-      <c r="Y86" t="n">
+      <c r="AB86" t="n">
         <v>64023.02</v>
       </c>
-      <c r="Z86" t="n">
+      <c r="AC86" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71529,6 +72309,15 @@
       <c r="Z87" t="n">
         <v>0</v>
       </c>
+      <c r="AA87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -71607,12 +72396,21 @@
         <v>0</v>
       </c>
       <c r="X88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA88" t="n">
         <v>4695093.84</v>
       </c>
-      <c r="Y88" t="n">
+      <c r="AB88" t="n">
         <v>4695093.84</v>
       </c>
-      <c r="Z88" t="n">
+      <c r="AC88" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71693,12 +72491,21 @@
         <v>0</v>
       </c>
       <c r="X89" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA89" t="n">
         <v>97528</v>
       </c>
-      <c r="Y89" t="n">
+      <c r="AB89" t="n">
         <v>97528</v>
       </c>
-      <c r="Z89" t="n">
+      <c r="AC89" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71779,12 +72586,21 @@
         <v>276400</v>
       </c>
       <c r="X90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA90" t="n">
         <v>895000</v>
       </c>
-      <c r="Y90" t="n">
+      <c r="AB90" t="n">
         <v>895000</v>
       </c>
-      <c r="Z90" t="n">
+      <c r="AC90" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71865,12 +72681,21 @@
         <v>0</v>
       </c>
       <c r="X91" t="n">
+        <v>178148.61</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>178148.61</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA91" t="n">
         <v>86851.39</v>
       </c>
-      <c r="Y91" t="n">
+      <c r="AB91" t="n">
         <v>86851.39</v>
       </c>
-      <c r="Z91" t="n">
+      <c r="AC91" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71951,12 +72776,21 @@
         <v>6000</v>
       </c>
       <c r="X92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA92" t="n">
         <v>502286</v>
       </c>
-      <c r="Y92" t="n">
+      <c r="AB92" t="n">
         <v>502286</v>
       </c>
-      <c r="Z92" t="n">
+      <c r="AC92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72037,12 +72871,21 @@
         <v>0</v>
       </c>
       <c r="X93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA93" t="n">
         <v>1312050</v>
       </c>
-      <c r="Y93" t="n">
+      <c r="AB93" t="n">
         <v>1312050</v>
       </c>
-      <c r="Z93" t="n">
+      <c r="AC93" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72126,9 +72969,18 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
+        <v>11861411.46</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>11861411.46</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB94" t="n">
         <v>1824333.68</v>
       </c>
-      <c r="Z94" t="n">
+      <c r="AC94" t="n">
         <v>1824333.68</v>
       </c>
     </row>
@@ -72209,12 +73061,21 @@
         <v>-6636057.49</v>
       </c>
       <c r="X95" t="n">
+        <v>6331411.46</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>-6331411.46</v>
+      </c>
+      <c r="AA95" t="n">
         <v>7354333.68</v>
       </c>
-      <c r="Y95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z95" t="n">
+      <c r="AB95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC95" t="n">
         <v>-7354333.68</v>
       </c>
     </row>
@@ -72295,12 +73156,21 @@
         <v>223121.17</v>
       </c>
       <c r="X96" t="n">
+        <v>415791.82</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>415791.82</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA96" t="n">
         <v>326945.72</v>
       </c>
-      <c r="Y96" t="n">
+      <c r="AB96" t="n">
         <v>326945.72</v>
       </c>
-      <c r="Z96" t="n">
+      <c r="AC96" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72381,12 +73251,21 @@
         <v>30130.84999999998</v>
       </c>
       <c r="X97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA97" t="n">
         <v>1210721.94</v>
       </c>
-      <c r="Y97" t="n">
+      <c r="AB97" t="n">
         <v>1210721.94</v>
       </c>
-      <c r="Z97" t="n">
+      <c r="AC97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72467,12 +73346,21 @@
         <v>0</v>
       </c>
       <c r="X98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA98" t="n">
         <v>100000</v>
       </c>
-      <c r="Y98" t="n">
+      <c r="AB98" t="n">
         <v>100000</v>
       </c>
-      <c r="Z98" t="n">
+      <c r="AC98" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72553,12 +73441,21 @@
         <v>0</v>
       </c>
       <c r="X99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA99" t="n">
         <v>490280.12</v>
       </c>
-      <c r="Y99" t="n">
+      <c r="AB99" t="n">
         <v>490280.12</v>
       </c>
-      <c r="Z99" t="n">
+      <c r="AC99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72639,12 +73536,21 @@
         <v>0</v>
       </c>
       <c r="X100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA100" t="n">
         <v>958683.8</v>
       </c>
-      <c r="Y100" t="n">
+      <c r="AB100" t="n">
         <v>958683.8</v>
       </c>
-      <c r="Z100" t="n">
+      <c r="AC100" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72725,12 +73631,21 @@
         <v>0</v>
       </c>
       <c r="X101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA101" t="n">
         <v>148969.8</v>
       </c>
-      <c r="Y101" t="n">
+      <c r="AB101" t="n">
         <v>148969.8</v>
       </c>
-      <c r="Z101" t="n">
+      <c r="AC101" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72811,12 +73726,21 @@
         <v>0</v>
       </c>
       <c r="X102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA102" t="n">
         <v>726840.35</v>
       </c>
-      <c r="Y102" t="n">
+      <c r="AB102" t="n">
         <v>726840.35</v>
       </c>
-      <c r="Z102" t="n">
+      <c r="AC102" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72897,12 +73821,21 @@
         <v>0</v>
       </c>
       <c r="X103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA103" t="n">
         <v>1652200</v>
       </c>
-      <c r="Y103" t="n">
+      <c r="AB103" t="n">
         <v>1652200</v>
       </c>
-      <c r="Z103" t="n">
+      <c r="AC103" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72991,6 +73924,15 @@
       <c r="Z104" t="n">
         <v>0</v>
       </c>
+      <c r="AA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -73077,6 +74019,15 @@
       <c r="Z105" t="n">
         <v>0</v>
       </c>
+      <c r="AA105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -73155,12 +74106,21 @@
         <v>0</v>
       </c>
       <c r="X106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" t="n">
         <v>50000</v>
       </c>
-      <c r="Y106" t="n">
+      <c r="AB106" t="n">
         <v>50000</v>
       </c>
-      <c r="Z106" t="n">
+      <c r="AC106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73241,12 +74201,21 @@
         <v>0</v>
       </c>
       <c r="X107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA107" t="n">
         <v>249721</v>
       </c>
-      <c r="Y107" t="n">
+      <c r="AB107" t="n">
         <v>249721</v>
       </c>
-      <c r="Z107" t="n">
+      <c r="AC107" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73327,12 +74296,21 @@
         <v>381000</v>
       </c>
       <c r="X108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA108" t="n">
         <v>1421600</v>
       </c>
-      <c r="Y108" t="n">
+      <c r="AB108" t="n">
         <v>1414600</v>
       </c>
-      <c r="Z108" t="n">
+      <c r="AC108" t="n">
         <v>-7000</v>
       </c>
     </row>
@@ -73413,12 +74391,21 @@
         <v>0</v>
       </c>
       <c r="X109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA109" t="n">
         <v>850000</v>
       </c>
-      <c r="Y109" t="n">
+      <c r="AB109" t="n">
         <v>850000</v>
       </c>
-      <c r="Z109" t="n">
+      <c r="AC109" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73499,12 +74486,21 @@
         <v>929634.22</v>
       </c>
       <c r="X110" t="n">
+        <v>1640638.11</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>1640638.11</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA110" t="n">
         <v>4429727.67</v>
       </c>
-      <c r="Y110" t="n">
+      <c r="AB110" t="n">
         <v>4429727.67</v>
       </c>
-      <c r="Z110" t="n">
+      <c r="AC110" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73585,12 +74581,21 @@
         <v>0</v>
       </c>
       <c r="X111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA111" t="n">
         <v>271067.72</v>
       </c>
-      <c r="Y111" t="n">
+      <c r="AB111" t="n">
         <v>271067.72</v>
       </c>
-      <c r="Z111" t="n">
+      <c r="AC111" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73679,6 +74684,15 @@
       <c r="Z112" t="n">
         <v>0</v>
       </c>
+      <c r="AA112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -73757,12 +74771,21 @@
         <v>0</v>
       </c>
       <c r="X113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA113" t="n">
         <v>308272</v>
       </c>
-      <c r="Y113" t="n">
+      <c r="AB113" t="n">
         <v>308272</v>
       </c>
-      <c r="Z113" t="n">
+      <c r="AC113" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73843,12 +74866,21 @@
         <v>0</v>
       </c>
       <c r="X114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA114" t="n">
         <v>1150826</v>
       </c>
-      <c r="Y114" t="n">
+      <c r="AB114" t="n">
         <v>1150826</v>
       </c>
-      <c r="Z114" t="n">
+      <c r="AC114" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73929,12 +74961,21 @@
         <v>0</v>
       </c>
       <c r="X115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA115" t="n">
         <v>2000000</v>
       </c>
-      <c r="Y115" t="n">
+      <c r="AB115" t="n">
         <v>2000000</v>
       </c>
-      <c r="Z115" t="n">
+      <c r="AC115" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74015,12 +75056,21 @@
         <v>0</v>
       </c>
       <c r="X116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA116" t="n">
         <v>29934</v>
       </c>
-      <c r="Y116" t="n">
+      <c r="AB116" t="n">
         <v>29934</v>
       </c>
-      <c r="Z116" t="n">
+      <c r="AC116" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74101,12 +75151,21 @@
         <v>700</v>
       </c>
       <c r="X117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA117" t="n">
         <v>8097000</v>
       </c>
-      <c r="Y117" t="n">
+      <c r="AB117" t="n">
         <v>8097000</v>
       </c>
-      <c r="Z117" t="n">
+      <c r="AC117" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74195,6 +75254,15 @@
       <c r="Z118" t="n">
         <v>0</v>
       </c>
+      <c r="AA118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -74273,12 +75341,21 @@
         <v>0</v>
       </c>
       <c r="X119" t="n">
+        <v>2647578.37</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>2647578.37</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA119" t="n">
         <v>3627211.32</v>
       </c>
-      <c r="Y119" t="n">
+      <c r="AB119" t="n">
         <v>3627211.32</v>
       </c>
-      <c r="Z119" t="n">
+      <c r="AC119" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74359,12 +75436,21 @@
         <v>0</v>
       </c>
       <c r="X120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA120" t="n">
         <v>73000</v>
       </c>
-      <c r="Y120" t="n">
+      <c r="AB120" t="n">
         <v>73000</v>
       </c>
-      <c r="Z120" t="n">
+      <c r="AC120" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74445,12 +75531,21 @@
         <v>371602.3999999999</v>
       </c>
       <c r="X121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA121" t="n">
         <v>2300916.4</v>
       </c>
-      <c r="Y121" t="n">
+      <c r="AB121" t="n">
         <v>2300916.4</v>
       </c>
-      <c r="Z121" t="n">
+      <c r="AC121" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74531,12 +75626,21 @@
         <v>641209.77</v>
       </c>
       <c r="X122" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA122" t="n">
         <v>1076961.03</v>
       </c>
-      <c r="Y122" t="n">
+      <c r="AB122" t="n">
         <v>1076961.03</v>
       </c>
-      <c r="Z122" t="n">
+      <c r="AC122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74617,12 +75721,21 @@
         <v>0</v>
       </c>
       <c r="X123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA123" t="n">
         <v>180278.9</v>
       </c>
-      <c r="Y123" t="n">
+      <c r="AB123" t="n">
         <v>180278.9</v>
       </c>
-      <c r="Z123" t="n">
+      <c r="AC123" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74703,12 +75816,21 @@
         <v>5550.49</v>
       </c>
       <c r="X124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA124" t="n">
         <v>59848.63</v>
       </c>
-      <c r="Y124" t="n">
+      <c r="AB124" t="n">
         <v>59848.63</v>
       </c>
-      <c r="Z124" t="n">
+      <c r="AC124" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74789,12 +75911,21 @@
         <v>0</v>
       </c>
       <c r="X125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA125" t="n">
         <v>123184.1</v>
       </c>
-      <c r="Y125" t="n">
+      <c r="AB125" t="n">
         <v>123184.1</v>
       </c>
-      <c r="Z125" t="n">
+      <c r="AC125" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74875,12 +76006,21 @@
         <v>0</v>
       </c>
       <c r="X126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA126" t="n">
         <v>64000</v>
       </c>
-      <c r="Y126" t="n">
+      <c r="AB126" t="n">
         <v>64000</v>
       </c>
-      <c r="Z126" t="n">
+      <c r="AC126" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74961,12 +76101,21 @@
         <v>0</v>
       </c>
       <c r="X127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA127" t="n">
         <v>10000</v>
       </c>
-      <c r="Y127" t="n">
+      <c r="AB127" t="n">
         <v>10000</v>
       </c>
-      <c r="Z127" t="n">
+      <c r="AC127" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75047,12 +76196,21 @@
         <v>1382898.62</v>
       </c>
       <c r="X128" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA128" t="n">
         <v>10589524.26</v>
       </c>
-      <c r="Y128" t="n">
+      <c r="AB128" t="n">
         <v>10589524.26</v>
       </c>
-      <c r="Z128" t="n">
+      <c r="AC128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75133,12 +76291,21 @@
         <v>189404.96</v>
       </c>
       <c r="X129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA129" t="n">
         <v>1695593.98</v>
       </c>
-      <c r="Y129" t="n">
+      <c r="AB129" t="n">
         <v>1695593.98</v>
       </c>
-      <c r="Z129" t="n">
+      <c r="AC129" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75219,12 +76386,21 @@
         <v>0</v>
       </c>
       <c r="X130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA130" t="n">
         <v>16394738.95</v>
       </c>
-      <c r="Y130" t="n">
+      <c r="AB130" t="n">
         <v>16272144.64</v>
       </c>
-      <c r="Z130" t="n">
+      <c r="AC130" t="n">
         <v>-122594.3099999987</v>
       </c>
     </row>

--- a/Base_Consolidada_SIAFI.xlsx
+++ b/Base_Consolidada_SIAFI.xlsx
@@ -44586,11 +44586,11 @@
     </row>
     <row r="574">
       <c r="A574" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -44663,11 +44663,11 @@
     </row>
     <row r="575">
       <c r="A575" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -44740,11 +44740,11 @@
     </row>
     <row r="576">
       <c r="A576" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -44817,11 +44817,11 @@
     </row>
     <row r="577">
       <c r="A577" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -44894,11 +44894,11 @@
     </row>
     <row r="578">
       <c r="A578" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -44971,11 +44971,11 @@
     </row>
     <row r="579">
       <c r="A579" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -45048,11 +45048,11 @@
     </row>
     <row r="580">
       <c r="A580" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -45125,11 +45125,11 @@
     </row>
     <row r="581">
       <c r="A581" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -45202,11 +45202,11 @@
     </row>
     <row r="582">
       <c r="A582" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -45279,11 +45279,11 @@
     </row>
     <row r="583">
       <c r="A583" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -45356,11 +45356,11 @@
     </row>
     <row r="584">
       <c r="A584" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -45433,11 +45433,11 @@
     </row>
     <row r="585">
       <c r="A585" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -45510,11 +45510,11 @@
     </row>
     <row r="586">
       <c r="A586" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -45587,11 +45587,11 @@
     </row>
     <row r="587">
       <c r="A587" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -45664,11 +45664,11 @@
     </row>
     <row r="588">
       <c r="A588" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -45741,11 +45741,11 @@
     </row>
     <row r="589">
       <c r="A589" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -45818,11 +45818,11 @@
     </row>
     <row r="590">
       <c r="A590" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -45895,11 +45895,11 @@
     </row>
     <row r="591">
       <c r="A591" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -45972,11 +45972,11 @@
     </row>
     <row r="592">
       <c r="A592" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -46049,11 +46049,11 @@
     </row>
     <row r="593">
       <c r="A593" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -46126,11 +46126,11 @@
     </row>
     <row r="594">
       <c r="A594" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -46203,11 +46203,11 @@
     </row>
     <row r="595">
       <c r="A595" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -46280,11 +46280,11 @@
     </row>
     <row r="596">
       <c r="A596" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -46357,11 +46357,11 @@
     </row>
     <row r="597">
       <c r="A597" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -46434,11 +46434,11 @@
     </row>
     <row r="598">
       <c r="A598" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -46511,11 +46511,11 @@
     </row>
     <row r="599">
       <c r="A599" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -46588,11 +46588,11 @@
     </row>
     <row r="600">
       <c r="A600" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -46665,11 +46665,11 @@
     </row>
     <row r="601">
       <c r="A601" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -46742,11 +46742,11 @@
     </row>
     <row r="602">
       <c r="A602" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -46819,11 +46819,11 @@
     </row>
     <row r="603">
       <c r="A603" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -46896,11 +46896,11 @@
     </row>
     <row r="604">
       <c r="A604" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -46973,11 +46973,11 @@
     </row>
     <row r="605">
       <c r="A605" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -47050,11 +47050,11 @@
     </row>
     <row r="606">
       <c r="A606" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -47127,11 +47127,11 @@
     </row>
     <row r="607">
       <c r="A607" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -47204,11 +47204,11 @@
     </row>
     <row r="608">
       <c r="A608" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -47281,11 +47281,11 @@
     </row>
     <row r="609">
       <c r="A609" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -47358,11 +47358,11 @@
     </row>
     <row r="610">
       <c r="A610" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -47435,11 +47435,11 @@
     </row>
     <row r="611">
       <c r="A611" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -47512,11 +47512,11 @@
     </row>
     <row r="612">
       <c r="A612" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -47589,11 +47589,11 @@
     </row>
     <row r="613">
       <c r="A613" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -47666,11 +47666,11 @@
     </row>
     <row r="614">
       <c r="A614" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -47743,11 +47743,11 @@
     </row>
     <row r="615">
       <c r="A615" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -47820,11 +47820,11 @@
     </row>
     <row r="616">
       <c r="A616" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -47897,11 +47897,11 @@
     </row>
     <row r="617">
       <c r="A617" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -47974,11 +47974,11 @@
     </row>
     <row r="618">
       <c r="A618" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -48051,11 +48051,11 @@
     </row>
     <row r="619">
       <c r="A619" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -48128,11 +48128,11 @@
     </row>
     <row r="620">
       <c r="A620" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -48205,11 +48205,11 @@
     </row>
     <row r="621">
       <c r="A621" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -48282,11 +48282,11 @@
     </row>
     <row r="622">
       <c r="A622" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -48359,11 +48359,11 @@
     </row>
     <row r="623">
       <c r="A623" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -48436,11 +48436,11 @@
     </row>
     <row r="624">
       <c r="A624" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -48513,11 +48513,11 @@
     </row>
     <row r="625">
       <c r="A625" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -48590,11 +48590,11 @@
     </row>
     <row r="626">
       <c r="A626" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -48667,11 +48667,11 @@
     </row>
     <row r="627">
       <c r="A627" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -48744,11 +48744,11 @@
     </row>
     <row r="628">
       <c r="A628" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -48821,11 +48821,11 @@
     </row>
     <row r="629">
       <c r="A629" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -48898,11 +48898,11 @@
     </row>
     <row r="630">
       <c r="A630" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -48975,11 +48975,11 @@
     </row>
     <row r="631">
       <c r="A631" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -49052,11 +49052,11 @@
     </row>
     <row r="632">
       <c r="A632" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -49129,11 +49129,11 @@
     </row>
     <row r="633">
       <c r="A633" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -49206,11 +49206,11 @@
     </row>
     <row r="634">
       <c r="A634" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -49283,11 +49283,11 @@
     </row>
     <row r="635">
       <c r="A635" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -49360,11 +49360,11 @@
     </row>
     <row r="636">
       <c r="A636" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -49437,11 +49437,11 @@
     </row>
     <row r="637">
       <c r="A637" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -49514,11 +49514,11 @@
     </row>
     <row r="638">
       <c r="A638" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -49591,11 +49591,11 @@
     </row>
     <row r="639">
       <c r="A639" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -49668,11 +49668,11 @@
     </row>
     <row r="640">
       <c r="A640" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -49745,11 +49745,11 @@
     </row>
     <row r="641">
       <c r="A641" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -49822,11 +49822,11 @@
     </row>
     <row r="642">
       <c r="A642" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -49899,11 +49899,11 @@
     </row>
     <row r="643">
       <c r="A643" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -49976,11 +49976,11 @@
     </row>
     <row r="644">
       <c r="A644" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -50053,11 +50053,11 @@
     </row>
     <row r="645">
       <c r="A645" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -50130,11 +50130,11 @@
     </row>
     <row r="646">
       <c r="A646" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -50207,11 +50207,11 @@
     </row>
     <row r="647">
       <c r="A647" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -50284,11 +50284,11 @@
     </row>
     <row r="648">
       <c r="A648" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -50361,11 +50361,11 @@
     </row>
     <row r="649">
       <c r="A649" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -50438,11 +50438,11 @@
     </row>
     <row r="650">
       <c r="A650" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -50515,11 +50515,11 @@
     </row>
     <row r="651">
       <c r="A651" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -50592,11 +50592,11 @@
     </row>
     <row r="652">
       <c r="A652" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -50669,11 +50669,11 @@
     </row>
     <row r="653">
       <c r="A653" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -50746,11 +50746,11 @@
     </row>
     <row r="654">
       <c r="A654" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -50823,11 +50823,11 @@
     </row>
     <row r="655">
       <c r="A655" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -50900,11 +50900,11 @@
     </row>
     <row r="656">
       <c r="A656" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -50977,11 +50977,11 @@
     </row>
     <row r="657">
       <c r="A657" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -51054,11 +51054,11 @@
     </row>
     <row r="658">
       <c r="A658" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -51131,11 +51131,11 @@
     </row>
     <row r="659">
       <c r="A659" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -51208,11 +51208,11 @@
     </row>
     <row r="660">
       <c r="A660" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -51285,11 +51285,11 @@
     </row>
     <row r="661">
       <c r="A661" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -51362,11 +51362,11 @@
     </row>
     <row r="662">
       <c r="A662" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -51439,11 +51439,11 @@
     </row>
     <row r="663">
       <c r="A663" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -51516,11 +51516,11 @@
     </row>
     <row r="664">
       <c r="A664" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -51593,11 +51593,11 @@
     </row>
     <row r="665">
       <c r="A665" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -51670,11 +51670,11 @@
     </row>
     <row r="666">
       <c r="A666" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -51747,11 +51747,11 @@
     </row>
     <row r="667">
       <c r="A667" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -51824,11 +51824,11 @@
     </row>
     <row r="668">
       <c r="A668" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -51901,11 +51901,11 @@
     </row>
     <row r="669">
       <c r="A669" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -51978,11 +51978,11 @@
     </row>
     <row r="670">
       <c r="A670" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -52055,11 +52055,11 @@
     </row>
     <row r="671">
       <c r="A671" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -52132,11 +52132,11 @@
     </row>
     <row r="672">
       <c r="A672" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -52209,11 +52209,11 @@
     </row>
     <row r="673">
       <c r="A673" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -52286,11 +52286,11 @@
     </row>
     <row r="674">
       <c r="A674" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -52363,11 +52363,11 @@
     </row>
     <row r="675">
       <c r="A675" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -52440,11 +52440,11 @@
     </row>
     <row r="676">
       <c r="A676" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -52517,11 +52517,11 @@
     </row>
     <row r="677">
       <c r="A677" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -52594,11 +52594,11 @@
     </row>
     <row r="678">
       <c r="A678" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -52671,11 +52671,11 @@
     </row>
     <row r="679">
       <c r="A679" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -52734,10 +52734,10 @@
         <v>-1366589.44</v>
       </c>
       <c r="R679" t="n">
-        <v>124253.58</v>
+        <v>1366589.44</v>
       </c>
       <c r="S679" t="n">
-        <v>1242335.86</v>
+        <v>0</v>
       </c>
       <c r="T679" t="n">
         <v>0</v>
@@ -52748,11 +52748,11 @@
     </row>
     <row r="680">
       <c r="A680" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -52811,10 +52811,10 @@
         <v>0</v>
       </c>
       <c r="R680" t="n">
-        <v>124253.58</v>
+        <v>1366589.44</v>
       </c>
       <c r="S680" t="n">
-        <v>1242335.86</v>
+        <v>0</v>
       </c>
       <c r="T680" t="n">
         <v>0</v>
@@ -52825,11 +52825,11 @@
     </row>
     <row r="681">
       <c r="A681" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -52902,11 +52902,11 @@
     </row>
     <row r="682">
       <c r="A682" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -52979,11 +52979,11 @@
     </row>
     <row r="683">
       <c r="A683" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -53056,11 +53056,11 @@
     </row>
     <row r="684">
       <c r="A684" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -53133,11 +53133,11 @@
     </row>
     <row r="685">
       <c r="A685" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -53210,11 +53210,11 @@
     </row>
     <row r="686">
       <c r="A686" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -53287,11 +53287,11 @@
     </row>
     <row r="687">
       <c r="A687" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -53364,11 +53364,11 @@
     </row>
     <row r="688">
       <c r="A688" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -53441,11 +53441,11 @@
     </row>
     <row r="689">
       <c r="A689" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -53518,11 +53518,11 @@
     </row>
     <row r="690">
       <c r="A690" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -53595,11 +53595,11 @@
     </row>
     <row r="691">
       <c r="A691" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -53672,11 +53672,11 @@
     </row>
     <row r="692">
       <c r="A692" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -53749,11 +53749,11 @@
     </row>
     <row r="693">
       <c r="A693" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -53826,11 +53826,11 @@
     </row>
     <row r="694">
       <c r="A694" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -53903,11 +53903,11 @@
     </row>
     <row r="695">
       <c r="A695" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -53980,11 +53980,11 @@
     </row>
     <row r="696">
       <c r="A696" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -54057,11 +54057,11 @@
     </row>
     <row r="697">
       <c r="A697" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -54134,11 +54134,11 @@
     </row>
     <row r="698">
       <c r="A698" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -54211,11 +54211,11 @@
     </row>
     <row r="699">
       <c r="A699" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -54288,11 +54288,11 @@
     </row>
     <row r="700">
       <c r="A700" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -54365,11 +54365,11 @@
     </row>
     <row r="701">
       <c r="A701" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -54419,34 +54419,34 @@
         <v>32000000</v>
       </c>
       <c r="O701" t="n">
-        <v>7835204.93</v>
+        <v>7563495.42</v>
       </c>
       <c r="P701" t="n">
-        <v>7587092.37</v>
+        <v>7563495.42</v>
       </c>
       <c r="Q701" t="n">
-        <v>248112.5599999996</v>
+        <v>0</v>
       </c>
       <c r="R701" t="n">
-        <v>6947059.98</v>
+        <v>7547516.79</v>
       </c>
       <c r="S701" t="n">
-        <v>640032.39</v>
+        <v>15978.63</v>
       </c>
       <c r="T701" t="n">
         <v>0</v>
       </c>
       <c r="U701" t="n">
-        <v>24164795.07</v>
+        <v>24436504.58</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -54519,11 +54519,11 @@
     </row>
     <row r="703">
       <c r="A703" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -54596,11 +54596,11 @@
     </row>
     <row r="704">
       <c r="A704" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -54659,10 +54659,10 @@
         <v>0</v>
       </c>
       <c r="R704" t="n">
-        <v>27312025.37</v>
+        <v>27382974.41</v>
       </c>
       <c r="S704" t="n">
-        <v>-27316766.36</v>
+        <v>-27387715.4</v>
       </c>
       <c r="T704" t="n">
         <v>0</v>
@@ -54673,11 +54673,11 @@
     </row>
     <row r="705">
       <c r="A705" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -54736,10 +54736,10 @@
         <v>0</v>
       </c>
       <c r="R705" t="n">
-        <v>88030543.73999999</v>
+        <v>88101492.78</v>
       </c>
       <c r="S705" t="n">
-        <v>77271</v>
+        <v>6321.96</v>
       </c>
       <c r="T705" t="n">
         <v>0</v>
@@ -54750,11 +54750,11 @@
     </row>
     <row r="706">
       <c r="A706" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -54813,10 +54813,10 @@
         <v>0</v>
       </c>
       <c r="R706" t="n">
-        <v>213.51</v>
+        <v>470639.11</v>
       </c>
       <c r="S706" t="n">
-        <v>-13919.65</v>
+        <v>-484345.25</v>
       </c>
       <c r="T706" t="n">
         <v>0</v>
@@ -54827,11 +54827,11 @@
     </row>
     <row r="707">
       <c r="A707" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -54890,10 +54890,10 @@
         <v>0</v>
       </c>
       <c r="R707" t="n">
-        <v>985009.42</v>
+        <v>1455435.02</v>
       </c>
       <c r="S707" t="n">
-        <v>470425.6</v>
+        <v>0</v>
       </c>
       <c r="T707" t="n">
         <v>0</v>
@@ -54904,11 +54904,11 @@
     </row>
     <row r="708">
       <c r="A708" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -54981,11 +54981,11 @@
     </row>
     <row r="709">
       <c r="A709" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -55058,11 +55058,11 @@
     </row>
     <row r="710">
       <c r="A710" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -55135,11 +55135,11 @@
     </row>
     <row r="711">
       <c r="A711" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -55212,11 +55212,11 @@
     </row>
     <row r="712">
       <c r="A712" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -55289,11 +55289,11 @@
     </row>
     <row r="713">
       <c r="A713" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -55366,11 +55366,11 @@
     </row>
     <row r="714">
       <c r="A714" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -55443,11 +55443,11 @@
     </row>
     <row r="715">
       <c r="A715" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -55520,11 +55520,11 @@
     </row>
     <row r="716">
       <c r="A716" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -55597,11 +55597,11 @@
     </row>
     <row r="717">
       <c r="A717" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -55674,11 +55674,11 @@
     </row>
     <row r="718">
       <c r="A718" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -55728,13 +55728,13 @@
         <v>0</v>
       </c>
       <c r="O718" t="n">
-        <v>413526.97</v>
+        <v>0</v>
       </c>
       <c r="P718" t="n">
         <v>0</v>
       </c>
       <c r="Q718" t="n">
-        <v>413526.97</v>
+        <v>0</v>
       </c>
       <c r="R718" t="n">
         <v>0</v>
@@ -55746,16 +55746,16 @@
         <v>0</v>
       </c>
       <c r="U718" t="n">
-        <v>-413526.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -55805,13 +55805,13 @@
         <v>452205.65</v>
       </c>
       <c r="O719" t="n">
-        <v>413526.97</v>
+        <v>0</v>
       </c>
       <c r="P719" t="n">
         <v>0</v>
       </c>
       <c r="Q719" t="n">
-        <v>413526.97</v>
+        <v>0</v>
       </c>
       <c r="R719" t="n">
         <v>0</v>
@@ -55823,16 +55823,16 @@
         <v>0</v>
       </c>
       <c r="U719" t="n">
-        <v>38678.68</v>
+        <v>452205.65</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -55905,11 +55905,11 @@
     </row>
     <row r="721">
       <c r="A721" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -55982,11 +55982,11 @@
     </row>
     <row r="722">
       <c r="A722" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -56059,11 +56059,11 @@
     </row>
     <row r="723">
       <c r="A723" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -56136,11 +56136,11 @@
     </row>
     <row r="724">
       <c r="A724" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -56213,11 +56213,11 @@
     </row>
     <row r="725">
       <c r="A725" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -56290,11 +56290,11 @@
     </row>
     <row r="726">
       <c r="A726" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -56367,11 +56367,11 @@
     </row>
     <row r="727">
       <c r="A727" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -56444,11 +56444,11 @@
     </row>
     <row r="728">
       <c r="A728" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -56498,34 +56498,34 @@
         <v>0</v>
       </c>
       <c r="O728" t="n">
-        <v>-1373755.58</v>
+        <v>-1645465.09</v>
       </c>
       <c r="P728" t="n">
-        <v>-1621868.14</v>
+        <v>-1645465.09</v>
       </c>
       <c r="Q728" t="n">
-        <v>248112.5599999998</v>
+        <v>0</v>
       </c>
       <c r="R728" t="n">
-        <v>2051219.98</v>
+        <v>2651676.79</v>
       </c>
       <c r="S728" t="n">
-        <v>-3673088.12</v>
+        <v>-4297141.88</v>
       </c>
       <c r="T728" t="n">
         <v>0</v>
       </c>
       <c r="U728" t="n">
-        <v>1373755.58</v>
+        <v>1645465.09</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -56598,11 +56598,11 @@
     </row>
     <row r="730">
       <c r="A730" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -56675,11 +56675,11 @@
     </row>
     <row r="731">
       <c r="A731" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -56752,11 +56752,11 @@
     </row>
     <row r="732">
       <c r="A732" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -56815,10 +56815,10 @@
         <v>0</v>
       </c>
       <c r="R732" t="n">
-        <v>0</v>
+        <v>20387.8</v>
       </c>
       <c r="S732" t="n">
-        <v>122594.31</v>
+        <v>102206.51</v>
       </c>
       <c r="T732" t="n">
         <v>0</v>
@@ -56829,11 +56829,11 @@
     </row>
     <row r="733">
       <c r="A733" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -56906,11 +56906,11 @@
     </row>
     <row r="734">
       <c r="A734" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -56983,11 +56983,11 @@
     </row>
     <row r="735">
       <c r="A735" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -57060,11 +57060,11 @@
     </row>
     <row r="736">
       <c r="A736" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -57137,11 +57137,11 @@
     </row>
     <row r="737">
       <c r="A737" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -57214,11 +57214,11 @@
     </row>
     <row r="738">
       <c r="A738" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -57291,11 +57291,11 @@
     </row>
     <row r="739">
       <c r="A739" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -57368,11 +57368,11 @@
     </row>
     <row r="740">
       <c r="A740" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -57445,11 +57445,11 @@
     </row>
     <row r="741">
       <c r="A741" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -57522,11 +57522,11 @@
     </row>
     <row r="742">
       <c r="A742" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -57599,11 +57599,11 @@
     </row>
     <row r="743">
       <c r="A743" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -57676,11 +57676,11 @@
     </row>
     <row r="744">
       <c r="A744" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -57753,11 +57753,11 @@
     </row>
     <row r="745">
       <c r="A745" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -57830,11 +57830,11 @@
     </row>
     <row r="746">
       <c r="A746" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -57907,11 +57907,11 @@
     </row>
     <row r="747">
       <c r="A747" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -57984,11 +57984,11 @@
     </row>
     <row r="748">
       <c r="A748" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -58061,11 +58061,11 @@
     </row>
     <row r="749">
       <c r="A749" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -58138,11 +58138,11 @@
     </row>
     <row r="750">
       <c r="A750" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -58215,11 +58215,11 @@
     </row>
     <row r="751">
       <c r="A751" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -58292,11 +58292,11 @@
     </row>
     <row r="752">
       <c r="A752" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -58369,11 +58369,11 @@
     </row>
     <row r="753">
       <c r="A753" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -58423,13 +58423,13 @@
         <v>0</v>
       </c>
       <c r="O753" t="n">
-        <v>16236.8</v>
+        <v>17136.8</v>
       </c>
       <c r="P753" t="n">
         <v>6930</v>
       </c>
       <c r="Q753" t="n">
-        <v>9306.799999999999</v>
+        <v>10206.8</v>
       </c>
       <c r="R753" t="n">
         <v>1080</v>
@@ -58441,16 +58441,16 @@
         <v>0</v>
       </c>
       <c r="U753" t="n">
-        <v>-16236.8</v>
+        <v>-17136.8</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -58500,13 +58500,13 @@
         <v>2788800</v>
       </c>
       <c r="O754" t="n">
-        <v>92692.39999999999</v>
+        <v>93592.39999999999</v>
       </c>
       <c r="P754" t="n">
         <v>44382.6</v>
       </c>
       <c r="Q754" t="n">
-        <v>48309.8</v>
+        <v>49209.8</v>
       </c>
       <c r="R754" t="n">
         <v>1452.6</v>
@@ -58518,16 +58518,16 @@
         <v>0</v>
       </c>
       <c r="U754" t="n">
-        <v>2696107.6</v>
+        <v>2695207.6</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -58600,11 +58600,11 @@
     </row>
     <row r="756">
       <c r="A756" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -58677,11 +58677,11 @@
     </row>
     <row r="757">
       <c r="A757" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -58754,11 +58754,11 @@
     </row>
     <row r="758">
       <c r="A758" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -58831,11 +58831,11 @@
     </row>
     <row r="759">
       <c r="A759" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -58908,11 +58908,11 @@
     </row>
     <row r="760">
       <c r="A760" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -58985,11 +58985,11 @@
     </row>
     <row r="761">
       <c r="A761" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -59062,11 +59062,11 @@
     </row>
     <row r="762">
       <c r="A762" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -59139,11 +59139,11 @@
     </row>
     <row r="763">
       <c r="A763" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -59216,11 +59216,11 @@
     </row>
     <row r="764">
       <c r="A764" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -59293,11 +59293,11 @@
     </row>
     <row r="765">
       <c r="A765" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -59370,11 +59370,11 @@
     </row>
     <row r="766">
       <c r="A766" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -59447,11 +59447,11 @@
     </row>
     <row r="767">
       <c r="A767" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -59524,11 +59524,11 @@
     </row>
     <row r="768">
       <c r="A768" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -59601,11 +59601,11 @@
     </row>
     <row r="769">
       <c r="A769" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -59658,16 +59658,16 @@
         <v>19408.05</v>
       </c>
       <c r="P769" t="n">
-        <v>13841.4</v>
+        <v>22116.15</v>
       </c>
       <c r="Q769" t="n">
-        <v>5566.65</v>
+        <v>-2708.100000000002</v>
       </c>
       <c r="R769" t="n">
         <v>13841.4</v>
       </c>
       <c r="S769" t="n">
-        <v>0</v>
+        <v>8274.75</v>
       </c>
       <c r="T769" t="n">
         <v>0</v>
@@ -59678,11 +59678,11 @@
     </row>
     <row r="770">
       <c r="A770" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -59735,16 +59735,16 @@
         <v>96588.89999999999</v>
       </c>
       <c r="P770" t="n">
-        <v>77180.85000000001</v>
+        <v>85455.60000000001</v>
       </c>
       <c r="Q770" t="n">
-        <v>19408.04999999999</v>
+        <v>11133.29999999999</v>
       </c>
       <c r="R770" t="n">
         <v>77180.85000000001</v>
       </c>
       <c r="S770" t="n">
-        <v>0</v>
+        <v>8274.75</v>
       </c>
       <c r="T770" t="n">
         <v>0</v>
@@ -59755,11 +59755,11 @@
     </row>
     <row r="771">
       <c r="A771" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -59812,16 +59812,16 @@
         <v>8425.200000000001</v>
       </c>
       <c r="P771" t="n">
-        <v>0</v>
+        <v>3610.8</v>
       </c>
       <c r="Q771" t="n">
-        <v>8425.200000000001</v>
+        <v>4814.400000000001</v>
       </c>
       <c r="R771" t="n">
         <v>0</v>
       </c>
       <c r="S771" t="n">
-        <v>0</v>
+        <v>3610.8</v>
       </c>
       <c r="T771" t="n">
         <v>0</v>
@@ -59832,11 +59832,11 @@
     </row>
     <row r="772">
       <c r="A772" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -59889,16 +59889,16 @@
         <v>19257.6</v>
       </c>
       <c r="P772" t="n">
-        <v>10832.4</v>
+        <v>14443.2</v>
       </c>
       <c r="Q772" t="n">
-        <v>8425.199999999999</v>
+        <v>4814.399999999998</v>
       </c>
       <c r="R772" t="n">
         <v>10832.4</v>
       </c>
       <c r="S772" t="n">
-        <v>0</v>
+        <v>3610.8</v>
       </c>
       <c r="T772" t="n">
         <v>0</v>
@@ -59909,11 +59909,11 @@
     </row>
     <row r="773">
       <c r="A773" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -59966,16 +59966,16 @@
         <v>3350</v>
       </c>
       <c r="P773" t="n">
-        <v>30311.5</v>
+        <v>33661.5</v>
       </c>
       <c r="Q773" t="n">
-        <v>-26961.5</v>
+        <v>-30311.5</v>
       </c>
       <c r="R773" t="n">
         <v>64481.5</v>
       </c>
       <c r="S773" t="n">
-        <v>-34170</v>
+        <v>-30820</v>
       </c>
       <c r="T773" t="n">
         <v>0</v>
@@ -59986,11 +59986,11 @@
     </row>
     <row r="774">
       <c r="A774" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -60043,16 +60043,16 @@
         <v>157611.5</v>
       </c>
       <c r="P774" t="n">
-        <v>154261.5</v>
+        <v>157611.5</v>
       </c>
       <c r="Q774" t="n">
-        <v>3350</v>
+        <v>0</v>
       </c>
       <c r="R774" t="n">
         <v>154261.5</v>
       </c>
       <c r="S774" t="n">
-        <v>0</v>
+        <v>3350</v>
       </c>
       <c r="T774" t="n">
         <v>0</v>
@@ -60063,11 +60063,11 @@
     </row>
     <row r="775">
       <c r="A775" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -60140,11 +60140,11 @@
     </row>
     <row r="776">
       <c r="A776" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -60217,11 +60217,11 @@
     </row>
     <row r="777">
       <c r="A777" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -60294,11 +60294,11 @@
     </row>
     <row r="778">
       <c r="A778" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -60371,11 +60371,11 @@
     </row>
     <row r="779">
       <c r="A779" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -60448,11 +60448,11 @@
     </row>
     <row r="780">
       <c r="A780" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -60525,11 +60525,11 @@
     </row>
     <row r="781">
       <c r="A781" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -60602,11 +60602,11 @@
     </row>
     <row r="782">
       <c r="A782" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -60679,11 +60679,11 @@
     </row>
     <row r="783">
       <c r="A783" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -60756,11 +60756,11 @@
     </row>
     <row r="784">
       <c r="A784" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -60833,11 +60833,11 @@
     </row>
     <row r="785">
       <c r="A785" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -60910,11 +60910,11 @@
     </row>
     <row r="786">
       <c r="A786" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -60987,11 +60987,11 @@
     </row>
     <row r="787">
       <c r="A787" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -61064,11 +61064,11 @@
     </row>
     <row r="788">
       <c r="A788" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -61141,11 +61141,11 @@
     </row>
     <row r="789">
       <c r="A789" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -61218,11 +61218,11 @@
     </row>
     <row r="790">
       <c r="A790" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -61295,11 +61295,11 @@
     </row>
     <row r="791">
       <c r="A791" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -61372,11 +61372,11 @@
     </row>
     <row r="792">
       <c r="A792" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -61449,11 +61449,11 @@
     </row>
     <row r="793">
       <c r="A793" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -61526,11 +61526,11 @@
     </row>
     <row r="794">
       <c r="A794" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -61603,11 +61603,11 @@
     </row>
     <row r="795">
       <c r="A795" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -61680,11 +61680,11 @@
     </row>
     <row r="796">
       <c r="A796" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -61757,11 +61757,11 @@
     </row>
     <row r="797">
       <c r="A797" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -61834,11 +61834,11 @@
     </row>
     <row r="798">
       <c r="A798" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -61911,11 +61911,11 @@
     </row>
     <row r="799">
       <c r="A799" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -61988,11 +61988,11 @@
     </row>
     <row r="800">
       <c r="A800" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -62065,11 +62065,11 @@
     </row>
     <row r="801">
       <c r="A801" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -62142,11 +62142,11 @@
     </row>
     <row r="802">
       <c r="A802" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -62219,11 +62219,11 @@
     </row>
     <row r="803">
       <c r="A803" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -62296,11 +62296,11 @@
     </row>
     <row r="804">
       <c r="A804" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -62373,11 +62373,11 @@
     </row>
     <row r="805">
       <c r="A805" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -62450,11 +62450,11 @@
     </row>
     <row r="806">
       <c r="A806" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -62527,11 +62527,11 @@
     </row>
     <row r="807">
       <c r="A807" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -62604,11 +62604,11 @@
     </row>
     <row r="808">
       <c r="A808" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -62681,11 +62681,11 @@
     </row>
     <row r="809">
       <c r="A809" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -62758,11 +62758,11 @@
     </row>
     <row r="810">
       <c r="A810" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -62835,11 +62835,11 @@
     </row>
     <row r="811">
       <c r="A811" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -62912,11 +62912,11 @@
     </row>
     <row r="812">
       <c r="A812" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -62989,11 +62989,11 @@
     </row>
     <row r="813">
       <c r="A813" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -63066,11 +63066,11 @@
     </row>
     <row r="814">
       <c r="A814" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -63143,11 +63143,11 @@
     </row>
     <row r="815">
       <c r="A815" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -63220,11 +63220,11 @@
     </row>
     <row r="816">
       <c r="A816" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -63297,11 +63297,11 @@
     </row>
     <row r="817">
       <c r="A817" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -63374,11 +63374,11 @@
     </row>
     <row r="818">
       <c r="A818" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -63451,11 +63451,11 @@
     </row>
     <row r="819">
       <c r="A819" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -63528,11 +63528,11 @@
     </row>
     <row r="820">
       <c r="A820" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -63605,11 +63605,11 @@
     </row>
     <row r="821">
       <c r="A821" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -63682,11 +63682,11 @@
     </row>
     <row r="822">
       <c r="A822" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -63759,11 +63759,11 @@
     </row>
     <row r="823">
       <c r="A823" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -63836,11 +63836,11 @@
     </row>
     <row r="824">
       <c r="A824" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -63913,11 +63913,11 @@
     </row>
     <row r="825">
       <c r="A825" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>RELEXORC_16-04-2026.csv</t>
+          <t>RELEXORC_17-04-2026.csv</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -63976,10 +63976,10 @@
         <v>0</v>
       </c>
       <c r="R825" t="n">
-        <v>535261.05</v>
+        <v>555648.85</v>
       </c>
       <c r="S825" t="n">
-        <v>122594.31</v>
+        <v>102206.51</v>
       </c>
       <c r="T825" t="n">
         <v>0</v>
@@ -64154,7 +64154,7 @@
         <v>46112</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -64249,7 +64249,7 @@
         <v>46112</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -64344,7 +64344,7 @@
         <v>46112</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -64439,7 +64439,7 @@
         <v>46112</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -64534,7 +64534,7 @@
         <v>46112</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -64629,7 +64629,7 @@
         <v>46112</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -64724,7 +64724,7 @@
         <v>46112</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -64819,7 +64819,7 @@
         <v>46112</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -64914,7 +64914,7 @@
         <v>46112</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -65009,7 +65009,7 @@
         <v>46112</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -65104,7 +65104,7 @@
         <v>46112</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -65152,10 +65152,10 @@
         <v>76455.60000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>92692.39999999999</v>
+        <v>93592.39999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>16236.79999999999</v>
+        <v>17136.79999999999</v>
       </c>
       <c r="R12" t="n">
         <v>38532.6</v>
@@ -65188,10 +65188,10 @@
         <v>2712344.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>2696107.6</v>
+        <v>2695207.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>-16236.79999999981</v>
+        <v>-17136.79999999981</v>
       </c>
     </row>
     <row r="13">
@@ -65199,7 +65199,7 @@
         <v>46112</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -65294,7 +65294,7 @@
         <v>46112</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -65389,7 +65389,7 @@
         <v>46112</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -65484,7 +65484,7 @@
         <v>46112</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -65579,7 +65579,7 @@
         <v>46112</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -65627,28 +65627,28 @@
         <v>9208960.51</v>
       </c>
       <c r="P17" t="n">
-        <v>7835204.93</v>
+        <v>7563495.42</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1373755.58</v>
+        <v>-1645465.09</v>
       </c>
       <c r="R17" t="n">
         <v>9208960.51</v>
       </c>
       <c r="S17" t="n">
-        <v>7587092.37</v>
+        <v>7563495.42</v>
       </c>
       <c r="T17" t="n">
-        <v>-1621868.14</v>
+        <v>-1645465.09</v>
       </c>
       <c r="U17" t="n">
         <v>6550089.63</v>
       </c>
       <c r="V17" t="n">
-        <v>6947059.98</v>
+        <v>7547516.79</v>
       </c>
       <c r="W17" t="n">
-        <v>396970.3500000006</v>
+        <v>997427.1600000001</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -65663,10 +65663,10 @@
         <v>22791039.49</v>
       </c>
       <c r="AB17" t="n">
-        <v>24164795.07</v>
+        <v>24436504.58</v>
       </c>
       <c r="AC17" t="n">
-        <v>1373755.580000002</v>
+        <v>1645465.09</v>
       </c>
     </row>
     <row r="18">
@@ -65674,7 +65674,7 @@
         <v>46112</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -65769,7 +65769,7 @@
         <v>46112</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -65835,10 +65835,10 @@
         <v>79635166.11</v>
       </c>
       <c r="V19" t="n">
-        <v>88030543.73999999</v>
+        <v>88101492.78</v>
       </c>
       <c r="W19" t="n">
-        <v>8395377.629999995</v>
+        <v>8466326.670000002</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -65864,7 +65864,7 @@
         <v>46112</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -65930,10 +65930,10 @@
         <v>984795.91</v>
       </c>
       <c r="V20" t="n">
-        <v>985009.42</v>
+        <v>1455435.02</v>
       </c>
       <c r="W20" t="n">
-        <v>213.5100000000093</v>
+        <v>470639.11</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -65959,7 +65959,7 @@
         <v>46112</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -66054,7 +66054,7 @@
         <v>46112</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -66149,7 +66149,7 @@
         <v>46112</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -66244,7 +66244,7 @@
         <v>46112</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -66339,7 +66339,7 @@
         <v>46112</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -66434,7 +66434,7 @@
         <v>46112</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -66482,10 +66482,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>413526.97</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>413526.97</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -66518,10 +66518,10 @@
         <v>452205.65</v>
       </c>
       <c r="AB26" t="n">
-        <v>38678.68</v>
+        <v>452205.65</v>
       </c>
       <c r="AC26" t="n">
-        <v>-413526.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -66529,7 +66529,7 @@
         <v>46112</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -66624,7 +66624,7 @@
         <v>46112</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -66719,7 +66719,7 @@
         <v>46112</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -66814,7 +66814,7 @@
         <v>46112</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -66909,7 +66909,7 @@
         <v>46112</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -67004,7 +67004,7 @@
         <v>46112</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -67099,7 +67099,7 @@
         <v>46112</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -67194,7 +67194,7 @@
         <v>46112</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -67289,7 +67289,7 @@
         <v>46112</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -67384,7 +67384,7 @@
         <v>46112</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -67479,7 +67479,7 @@
         <v>46112</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -67574,7 +67574,7 @@
         <v>46112</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -67669,7 +67669,7 @@
         <v>46112</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -67764,7 +67764,7 @@
         <v>46112</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -67859,7 +67859,7 @@
         <v>46112</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -67954,7 +67954,7 @@
         <v>46112</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -68049,7 +68049,7 @@
         <v>46112</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -68144,7 +68144,7 @@
         <v>46112</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -68239,7 +68239,7 @@
         <v>46112</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -68334,7 +68334,7 @@
         <v>46112</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -68429,7 +68429,7 @@
         <v>46112</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -68524,7 +68524,7 @@
         <v>46112</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -68619,7 +68619,7 @@
         <v>46112</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -68714,7 +68714,7 @@
         <v>46112</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -68809,7 +68809,7 @@
         <v>46112</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -68904,7 +68904,7 @@
         <v>46112</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -68961,10 +68961,10 @@
         <v>68454.75</v>
       </c>
       <c r="S52" t="n">
-        <v>77180.85000000001</v>
+        <v>85455.60000000001</v>
       </c>
       <c r="T52" t="n">
-        <v>8726.100000000006</v>
+        <v>17000.85000000001</v>
       </c>
       <c r="U52" t="n">
         <v>63339.45</v>
@@ -68999,7 +68999,7 @@
         <v>46112</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -69056,10 +69056,10 @@
         <v>10832.4</v>
       </c>
       <c r="S53" t="n">
-        <v>10832.4</v>
+        <v>14443.2</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>3610.800000000001</v>
       </c>
       <c r="U53" t="n">
         <v>10832.4</v>
@@ -69094,7 +69094,7 @@
         <v>46112</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -69151,10 +69151,10 @@
         <v>146221.5</v>
       </c>
       <c r="S54" t="n">
-        <v>154261.5</v>
+        <v>157611.5</v>
       </c>
       <c r="T54" t="n">
-        <v>8040</v>
+        <v>11390</v>
       </c>
       <c r="U54" t="n">
         <v>123950</v>
@@ -69189,7 +69189,7 @@
         <v>46112</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -69284,7 +69284,7 @@
         <v>46112</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -69379,7 +69379,7 @@
         <v>46112</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -69474,7 +69474,7 @@
         <v>46112</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -69569,7 +69569,7 @@
         <v>46112</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -69664,7 +69664,7 @@
         <v>46112</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -69759,7 +69759,7 @@
         <v>46112</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -69854,7 +69854,7 @@
         <v>46112</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -69949,7 +69949,7 @@
         <v>46112</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -70044,7 +70044,7 @@
         <v>46112</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -70139,7 +70139,7 @@
         <v>46112</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -70234,7 +70234,7 @@
         <v>46112</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -70329,7 +70329,7 @@
         <v>46112</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -70424,7 +70424,7 @@
         <v>46112</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -70519,7 +70519,7 @@
         <v>46112</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -70614,7 +70614,7 @@
         <v>46112</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -70709,7 +70709,7 @@
         <v>46112</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -70804,7 +70804,7 @@
         <v>46112</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -70899,7 +70899,7 @@
         <v>46112</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -70994,7 +70994,7 @@
         <v>46112</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -71089,7 +71089,7 @@
         <v>46112</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -71184,7 +71184,7 @@
         <v>46112</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -71279,7 +71279,7 @@
         <v>46112</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -71374,7 +71374,7 @@
         <v>46112</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -71469,7 +71469,7 @@
         <v>46112</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -71564,7 +71564,7 @@
         <v>46112</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -71659,7 +71659,7 @@
         <v>46112</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -71754,7 +71754,7 @@
         <v>46112</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -71849,7 +71849,7 @@
         <v>46112</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -71944,7 +71944,7 @@
         <v>46112</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -72039,7 +72039,7 @@
         <v>46112</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -72134,7 +72134,7 @@
         <v>46112</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -72229,7 +72229,7 @@
         <v>46112</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -72324,7 +72324,7 @@
         <v>46112</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -72419,7 +72419,7 @@
         <v>46112</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -72514,7 +72514,7 @@
         <v>46112</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -72609,7 +72609,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -72704,7 +72704,7 @@
         <v>46112</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -72799,7 +72799,7 @@
         <v>46112</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -72894,7 +72894,7 @@
         <v>46112</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -72989,7 +72989,7 @@
         <v>46112</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -73084,7 +73084,7 @@
         <v>46112</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -73179,7 +73179,7 @@
         <v>46112</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -73274,7 +73274,7 @@
         <v>46112</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -73369,7 +73369,7 @@
         <v>46112</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -73464,7 +73464,7 @@
         <v>46112</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -73559,7 +73559,7 @@
         <v>46112</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -73654,7 +73654,7 @@
         <v>46112</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -73749,7 +73749,7 @@
         <v>46112</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -73844,7 +73844,7 @@
         <v>46112</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -73939,7 +73939,7 @@
         <v>46112</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -74005,10 +74005,10 @@
         <v>0</v>
       </c>
       <c r="V105" t="n">
-        <v>124253.58</v>
+        <v>1366589.44</v>
       </c>
       <c r="W105" t="n">
-        <v>124253.58</v>
+        <v>1366589.44</v>
       </c>
       <c r="X105" t="n">
         <v>0</v>
@@ -74034,7 +74034,7 @@
         <v>46112</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -74129,7 +74129,7 @@
         <v>46112</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -74224,7 +74224,7 @@
         <v>46112</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -74319,7 +74319,7 @@
         <v>46112</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -74414,7 +74414,7 @@
         <v>46112</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -74509,7 +74509,7 @@
         <v>46112</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -74604,7 +74604,7 @@
         <v>46112</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -74699,7 +74699,7 @@
         <v>46112</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -74794,7 +74794,7 @@
         <v>46112</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -74889,7 +74889,7 @@
         <v>46112</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -74984,7 +74984,7 @@
         <v>46112</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -75079,7 +75079,7 @@
         <v>46112</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -75174,7 +75174,7 @@
         <v>46112</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -75269,7 +75269,7 @@
         <v>46112</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -75364,7 +75364,7 @@
         <v>46112</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -75459,7 +75459,7 @@
         <v>46112</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -75554,7 +75554,7 @@
         <v>46112</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -75649,7 +75649,7 @@
         <v>46112</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -75744,7 +75744,7 @@
         <v>46112</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -75839,7 +75839,7 @@
         <v>46112</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -75934,7 +75934,7 @@
         <v>46112</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -76029,7 +76029,7 @@
         <v>46112</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -76124,7 +76124,7 @@
         <v>46112</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -76219,7 +76219,7 @@
         <v>46112</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -76314,7 +76314,7 @@
         <v>46112</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -76380,10 +76380,10 @@
         <v>535261.05</v>
       </c>
       <c r="V130" t="n">
-        <v>535261.05</v>
+        <v>555648.85</v>
       </c>
       <c r="W130" t="n">
-        <v>0</v>
+        <v>20387.79999999993</v>
       </c>
       <c r="X130" t="n">
         <v>0</v>

--- a/Base_Consolidada_SIAFI.xlsx
+++ b/Base_Consolidada_SIAFI.xlsx
@@ -44586,11 +44586,11 @@
     </row>
     <row r="574">
       <c r="A574" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -44663,11 +44663,11 @@
     </row>
     <row r="575">
       <c r="A575" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -44740,11 +44740,11 @@
     </row>
     <row r="576">
       <c r="A576" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -44817,11 +44817,11 @@
     </row>
     <row r="577">
       <c r="A577" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -44894,11 +44894,11 @@
     </row>
     <row r="578">
       <c r="A578" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -44971,11 +44971,11 @@
     </row>
     <row r="579">
       <c r="A579" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -45048,11 +45048,11 @@
     </row>
     <row r="580">
       <c r="A580" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -45125,11 +45125,11 @@
     </row>
     <row r="581">
       <c r="A581" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -45202,11 +45202,11 @@
     </row>
     <row r="582">
       <c r="A582" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -45279,11 +45279,11 @@
     </row>
     <row r="583">
       <c r="A583" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -45356,11 +45356,11 @@
     </row>
     <row r="584">
       <c r="A584" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -45433,11 +45433,11 @@
     </row>
     <row r="585">
       <c r="A585" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -45510,11 +45510,11 @@
     </row>
     <row r="586">
       <c r="A586" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -45587,11 +45587,11 @@
     </row>
     <row r="587">
       <c r="A587" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -45664,11 +45664,11 @@
     </row>
     <row r="588">
       <c r="A588" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -45741,11 +45741,11 @@
     </row>
     <row r="589">
       <c r="A589" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -45818,11 +45818,11 @@
     </row>
     <row r="590">
       <c r="A590" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -45895,11 +45895,11 @@
     </row>
     <row r="591">
       <c r="A591" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -45972,11 +45972,11 @@
     </row>
     <row r="592">
       <c r="A592" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -46049,11 +46049,11 @@
     </row>
     <row r="593">
       <c r="A593" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -46126,11 +46126,11 @@
     </row>
     <row r="594">
       <c r="A594" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -46203,11 +46203,11 @@
     </row>
     <row r="595">
       <c r="A595" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -46280,11 +46280,11 @@
     </row>
     <row r="596">
       <c r="A596" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -46357,11 +46357,11 @@
     </row>
     <row r="597">
       <c r="A597" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -46414,16 +46414,16 @@
         <v>0</v>
       </c>
       <c r="P597" t="n">
-        <v>0</v>
+        <v>149232.9</v>
       </c>
       <c r="Q597" t="n">
-        <v>0</v>
+        <v>-149232.9</v>
       </c>
       <c r="R597" t="n">
         <v>223121.17</v>
       </c>
       <c r="S597" t="n">
-        <v>-223121.17</v>
+        <v>-73888.27</v>
       </c>
       <c r="T597" t="n">
         <v>0</v>
@@ -46434,11 +46434,11 @@
     </row>
     <row r="598">
       <c r="A598" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -46491,16 +46491,16 @@
         <v>1257262.46</v>
       </c>
       <c r="P598" t="n">
-        <v>664443.25</v>
+        <v>813676.15</v>
       </c>
       <c r="Q598" t="n">
-        <v>592819.21</v>
+        <v>443586.3099999999</v>
       </c>
       <c r="R598" t="n">
         <v>664443.25</v>
       </c>
       <c r="S598" t="n">
-        <v>0</v>
+        <v>149232.9</v>
       </c>
       <c r="T598" t="n">
         <v>415791.82</v>
@@ -46511,11 +46511,11 @@
     </row>
     <row r="599">
       <c r="A599" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -46588,11 +46588,11 @@
     </row>
     <row r="600">
       <c r="A600" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -46665,11 +46665,11 @@
     </row>
     <row r="601">
       <c r="A601" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -46742,11 +46742,11 @@
     </row>
     <row r="602">
       <c r="A602" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -46819,11 +46819,11 @@
     </row>
     <row r="603">
       <c r="A603" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -46896,11 +46896,11 @@
     </row>
     <row r="604">
       <c r="A604" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -46973,11 +46973,11 @@
     </row>
     <row r="605">
       <c r="A605" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -47050,11 +47050,11 @@
     </row>
     <row r="606">
       <c r="A606" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -47127,11 +47127,11 @@
     </row>
     <row r="607">
       <c r="A607" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -47204,11 +47204,11 @@
     </row>
     <row r="608">
       <c r="A608" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -47281,11 +47281,11 @@
     </row>
     <row r="609">
       <c r="A609" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -47358,11 +47358,11 @@
     </row>
     <row r="610">
       <c r="A610" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -47435,11 +47435,11 @@
     </row>
     <row r="611">
       <c r="A611" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -47512,11 +47512,11 @@
     </row>
     <row r="612">
       <c r="A612" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -47589,11 +47589,11 @@
     </row>
     <row r="613">
       <c r="A613" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -47666,11 +47666,11 @@
     </row>
     <row r="614">
       <c r="A614" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -47743,11 +47743,11 @@
     </row>
     <row r="615">
       <c r="A615" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -47820,11 +47820,11 @@
     </row>
     <row r="616">
       <c r="A616" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -47897,11 +47897,11 @@
     </row>
     <row r="617">
       <c r="A617" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -47974,11 +47974,11 @@
     </row>
     <row r="618">
       <c r="A618" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -48051,11 +48051,11 @@
     </row>
     <row r="619">
       <c r="A619" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -48128,11 +48128,11 @@
     </row>
     <row r="620">
       <c r="A620" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -48205,11 +48205,11 @@
     </row>
     <row r="621">
       <c r="A621" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -48282,11 +48282,11 @@
     </row>
     <row r="622">
       <c r="A622" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -48359,11 +48359,11 @@
     </row>
     <row r="623">
       <c r="A623" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -48436,11 +48436,11 @@
     </row>
     <row r="624">
       <c r="A624" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -48513,11 +48513,11 @@
     </row>
     <row r="625">
       <c r="A625" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -48590,11 +48590,11 @@
     </row>
     <row r="626">
       <c r="A626" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -48667,11 +48667,11 @@
     </row>
     <row r="627">
       <c r="A627" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -48744,11 +48744,11 @@
     </row>
     <row r="628">
       <c r="A628" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -48821,11 +48821,11 @@
     </row>
     <row r="629">
       <c r="A629" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -48898,11 +48898,11 @@
     </row>
     <row r="630">
       <c r="A630" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -48975,11 +48975,11 @@
     </row>
     <row r="631">
       <c r="A631" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -49052,11 +49052,11 @@
     </row>
     <row r="632">
       <c r="A632" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -49129,11 +49129,11 @@
     </row>
     <row r="633">
       <c r="A633" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -49206,11 +49206,11 @@
     </row>
     <row r="634">
       <c r="A634" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -49283,11 +49283,11 @@
     </row>
     <row r="635">
       <c r="A635" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -49360,11 +49360,11 @@
     </row>
     <row r="636">
       <c r="A636" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -49437,11 +49437,11 @@
     </row>
     <row r="637">
       <c r="A637" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -49514,11 +49514,11 @@
     </row>
     <row r="638">
       <c r="A638" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -49591,11 +49591,11 @@
     </row>
     <row r="639">
       <c r="A639" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -49668,11 +49668,11 @@
     </row>
     <row r="640">
       <c r="A640" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -49745,11 +49745,11 @@
     </row>
     <row r="641">
       <c r="A641" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -49822,11 +49822,11 @@
     </row>
     <row r="642">
       <c r="A642" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -49899,11 +49899,11 @@
     </row>
     <row r="643">
       <c r="A643" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -49976,11 +49976,11 @@
     </row>
     <row r="644">
       <c r="A644" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -50053,11 +50053,11 @@
     </row>
     <row r="645">
       <c r="A645" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -50130,11 +50130,11 @@
     </row>
     <row r="646">
       <c r="A646" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -50187,16 +50187,16 @@
         <v>0</v>
       </c>
       <c r="P646" t="n">
-        <v>452802.4</v>
+        <v>466102.4</v>
       </c>
       <c r="Q646" t="n">
-        <v>-452802.4</v>
+        <v>-466102.4</v>
       </c>
       <c r="R646" t="n">
         <v>371602.4</v>
       </c>
       <c r="S646" t="n">
-        <v>81200</v>
+        <v>94500</v>
       </c>
       <c r="T646" t="n">
         <v>0</v>
@@ -50207,11 +50207,11 @@
     </row>
     <row r="647">
       <c r="A647" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -50264,16 +50264,16 @@
         <v>3126083.6</v>
       </c>
       <c r="P647" t="n">
-        <v>1446091.4</v>
+        <v>1459391.4</v>
       </c>
       <c r="Q647" t="n">
-        <v>1679992.2</v>
+        <v>1666692.2</v>
       </c>
       <c r="R647" t="n">
         <v>1364891.4</v>
       </c>
       <c r="S647" t="n">
-        <v>81200</v>
+        <v>94500</v>
       </c>
       <c r="T647" t="n">
         <v>0</v>
@@ -50284,11 +50284,11 @@
     </row>
     <row r="648">
       <c r="A648" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -50341,31 +50341,31 @@
         <v>0</v>
       </c>
       <c r="P648" t="n">
-        <v>0</v>
+        <v>141627.67</v>
       </c>
       <c r="Q648" t="n">
-        <v>0</v>
+        <v>-141627.67</v>
       </c>
       <c r="R648" t="n">
         <v>641209.77</v>
       </c>
       <c r="S648" t="n">
-        <v>-641209.77</v>
+        <v>-499582.1</v>
       </c>
       <c r="T648" t="n">
-        <v>0</v>
+        <v>851081.28</v>
       </c>
       <c r="U648" t="n">
-        <v>0</v>
+        <v>-851081.28</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -50418,31 +50418,31 @@
         <v>2601132.4</v>
       </c>
       <c r="P649" t="n">
-        <v>1919999.31</v>
+        <v>2061626.98</v>
       </c>
       <c r="Q649" t="n">
-        <v>681133.0899999999</v>
+        <v>539505.4199999999</v>
       </c>
       <c r="R649" t="n">
         <v>1919999.31</v>
       </c>
       <c r="S649" t="n">
-        <v>0</v>
+        <v>141627.67</v>
       </c>
       <c r="T649" t="n">
-        <v>1000000</v>
+        <v>1851081.28</v>
       </c>
       <c r="U649" t="n">
-        <v>1076961.03</v>
+        <v>225879.75</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -50515,11 +50515,11 @@
     </row>
     <row r="651">
       <c r="A651" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -50592,11 +50592,11 @@
     </row>
     <row r="652">
       <c r="A652" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -50669,11 +50669,11 @@
     </row>
     <row r="653">
       <c r="A653" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -50746,11 +50746,11 @@
     </row>
     <row r="654">
       <c r="A654" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -50823,11 +50823,11 @@
     </row>
     <row r="655">
       <c r="A655" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -50900,11 +50900,11 @@
     </row>
     <row r="656">
       <c r="A656" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -50977,11 +50977,11 @@
     </row>
     <row r="657">
       <c r="A657" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -51054,11 +51054,11 @@
     </row>
     <row r="658">
       <c r="A658" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -51131,11 +51131,11 @@
     </row>
     <row r="659">
       <c r="A659" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -51208,11 +51208,11 @@
     </row>
     <row r="660">
       <c r="A660" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -51285,11 +51285,11 @@
     </row>
     <row r="661">
       <c r="A661" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -51362,11 +51362,11 @@
     </row>
     <row r="662">
       <c r="A662" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -51439,11 +51439,11 @@
     </row>
     <row r="663">
       <c r="A663" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -51516,11 +51516,11 @@
     </row>
     <row r="664">
       <c r="A664" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -51593,11 +51593,11 @@
     </row>
     <row r="665">
       <c r="A665" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -51670,11 +51670,11 @@
     </row>
     <row r="666">
       <c r="A666" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -51747,11 +51747,11 @@
     </row>
     <row r="667">
       <c r="A667" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -51824,11 +51824,11 @@
     </row>
     <row r="668">
       <c r="A668" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -51901,11 +51901,11 @@
     </row>
     <row r="669">
       <c r="A669" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -51978,11 +51978,11 @@
     </row>
     <row r="670">
       <c r="A670" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -52055,11 +52055,11 @@
     </row>
     <row r="671">
       <c r="A671" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -52132,11 +52132,11 @@
     </row>
     <row r="672">
       <c r="A672" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -52209,11 +52209,11 @@
     </row>
     <row r="673">
       <c r="A673" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -52286,11 +52286,11 @@
     </row>
     <row r="674">
       <c r="A674" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -52363,11 +52363,11 @@
     </row>
     <row r="675">
       <c r="A675" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -52440,11 +52440,11 @@
     </row>
     <row r="676">
       <c r="A676" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -52517,11 +52517,11 @@
     </row>
     <row r="677">
       <c r="A677" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -52594,11 +52594,11 @@
     </row>
     <row r="678">
       <c r="A678" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -52671,11 +52671,11 @@
     </row>
     <row r="679">
       <c r="A679" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -52748,11 +52748,11 @@
     </row>
     <row r="680">
       <c r="A680" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -52825,11 +52825,11 @@
     </row>
     <row r="681">
       <c r="A681" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -52902,11 +52902,11 @@
     </row>
     <row r="682">
       <c r="A682" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -52979,11 +52979,11 @@
     </row>
     <row r="683">
       <c r="A683" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -53056,11 +53056,11 @@
     </row>
     <row r="684">
       <c r="A684" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -53133,11 +53133,11 @@
     </row>
     <row r="685">
       <c r="A685" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -53190,16 +53190,16 @@
         <v>7000</v>
       </c>
       <c r="P685" t="n">
-        <v>457300</v>
+        <v>517400</v>
       </c>
       <c r="Q685" t="n">
-        <v>-450300</v>
+        <v>-510400</v>
       </c>
       <c r="R685" t="n">
         <v>381000</v>
       </c>
       <c r="S685" t="n">
-        <v>76300</v>
+        <v>136400</v>
       </c>
       <c r="T685" t="n">
         <v>0</v>
@@ -53210,11 +53210,11 @@
     </row>
     <row r="686">
       <c r="A686" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -53267,16 +53267,16 @@
         <v>2085400</v>
       </c>
       <c r="P686" t="n">
-        <v>1418900</v>
+        <v>1479000</v>
       </c>
       <c r="Q686" t="n">
-        <v>666500</v>
+        <v>606400</v>
       </c>
       <c r="R686" t="n">
         <v>1128600</v>
       </c>
       <c r="S686" t="n">
-        <v>290300</v>
+        <v>350400</v>
       </c>
       <c r="T686" t="n">
         <v>0</v>
@@ -53287,11 +53287,11 @@
     </row>
     <row r="687">
       <c r="A687" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -53364,11 +53364,11 @@
     </row>
     <row r="688">
       <c r="A688" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -53441,11 +53441,11 @@
     </row>
     <row r="689">
       <c r="A689" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -53518,11 +53518,11 @@
     </row>
     <row r="690">
       <c r="A690" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -53595,11 +53595,11 @@
     </row>
     <row r="691">
       <c r="A691" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -53672,11 +53672,11 @@
     </row>
     <row r="692">
       <c r="A692" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -53749,11 +53749,11 @@
     </row>
     <row r="693">
       <c r="A693" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -53826,11 +53826,11 @@
     </row>
     <row r="694">
       <c r="A694" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -53903,11 +53903,11 @@
     </row>
     <row r="695">
       <c r="A695" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -53980,11 +53980,11 @@
     </row>
     <row r="696">
       <c r="A696" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -54057,11 +54057,11 @@
     </row>
     <row r="697">
       <c r="A697" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -54134,11 +54134,11 @@
     </row>
     <row r="698">
       <c r="A698" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -54211,11 +54211,11 @@
     </row>
     <row r="699">
       <c r="A699" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -54288,11 +54288,11 @@
     </row>
     <row r="700">
       <c r="A700" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -54365,11 +54365,11 @@
     </row>
     <row r="701">
       <c r="A701" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -54442,11 +54442,11 @@
     </row>
     <row r="702">
       <c r="A702" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -54519,11 +54519,11 @@
     </row>
     <row r="703">
       <c r="A703" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -54596,11 +54596,11 @@
     </row>
     <row r="704">
       <c r="A704" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -54659,10 +54659,10 @@
         <v>0</v>
       </c>
       <c r="R704" t="n">
-        <v>27382974.41</v>
+        <v>27384345.96</v>
       </c>
       <c r="S704" t="n">
-        <v>-27387715.4</v>
+        <v>-27389086.95</v>
       </c>
       <c r="T704" t="n">
         <v>0</v>
@@ -54673,11 +54673,11 @@
     </row>
     <row r="705">
       <c r="A705" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -54736,10 +54736,10 @@
         <v>0</v>
       </c>
       <c r="R705" t="n">
-        <v>88101492.78</v>
+        <v>88102864.33</v>
       </c>
       <c r="S705" t="n">
-        <v>6321.96</v>
+        <v>4950.41</v>
       </c>
       <c r="T705" t="n">
         <v>0</v>
@@ -54750,11 +54750,11 @@
     </row>
     <row r="706">
       <c r="A706" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -54827,11 +54827,11 @@
     </row>
     <row r="707">
       <c r="A707" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -54904,11 +54904,11 @@
     </row>
     <row r="708">
       <c r="A708" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -54981,11 +54981,11 @@
     </row>
     <row r="709">
       <c r="A709" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -55058,11 +55058,11 @@
     </row>
     <row r="710">
       <c r="A710" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -55135,11 +55135,11 @@
     </row>
     <row r="711">
       <c r="A711" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -55212,11 +55212,11 @@
     </row>
     <row r="712">
       <c r="A712" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -55289,11 +55289,11 @@
     </row>
     <row r="713">
       <c r="A713" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -55366,11 +55366,11 @@
     </row>
     <row r="714">
       <c r="A714" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -55443,11 +55443,11 @@
     </row>
     <row r="715">
       <c r="A715" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -55520,11 +55520,11 @@
     </row>
     <row r="716">
       <c r="A716" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -55597,11 +55597,11 @@
     </row>
     <row r="717">
       <c r="A717" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -55674,11 +55674,11 @@
     </row>
     <row r="718">
       <c r="A718" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -55751,11 +55751,11 @@
     </row>
     <row r="719">
       <c r="A719" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -55828,11 +55828,11 @@
     </row>
     <row r="720">
       <c r="A720" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -55905,11 +55905,11 @@
     </row>
     <row r="721">
       <c r="A721" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -55982,11 +55982,11 @@
     </row>
     <row r="722">
       <c r="A722" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -56059,11 +56059,11 @@
     </row>
     <row r="723">
       <c r="A723" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -56136,11 +56136,11 @@
     </row>
     <row r="724">
       <c r="A724" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -56213,11 +56213,11 @@
     </row>
     <row r="725">
       <c r="A725" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -56290,11 +56290,11 @@
     </row>
     <row r="726">
       <c r="A726" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -56367,11 +56367,11 @@
     </row>
     <row r="727">
       <c r="A727" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -56444,11 +56444,11 @@
     </row>
     <row r="728">
       <c r="A728" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -56521,11 +56521,11 @@
     </row>
     <row r="729">
       <c r="A729" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -56598,11 +56598,11 @@
     </row>
     <row r="730">
       <c r="A730" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -56675,11 +56675,11 @@
     </row>
     <row r="731">
       <c r="A731" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -56752,11 +56752,11 @@
     </row>
     <row r="732">
       <c r="A732" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -56829,11 +56829,11 @@
     </row>
     <row r="733">
       <c r="A733" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -56906,11 +56906,11 @@
     </row>
     <row r="734">
       <c r="A734" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -56983,11 +56983,11 @@
     </row>
     <row r="735">
       <c r="A735" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -57060,11 +57060,11 @@
     </row>
     <row r="736">
       <c r="A736" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -57137,11 +57137,11 @@
     </row>
     <row r="737">
       <c r="A737" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -57214,11 +57214,11 @@
     </row>
     <row r="738">
       <c r="A738" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -57291,11 +57291,11 @@
     </row>
     <row r="739">
       <c r="A739" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -57368,11 +57368,11 @@
     </row>
     <row r="740">
       <c r="A740" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -57445,11 +57445,11 @@
     </row>
     <row r="741">
       <c r="A741" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -57522,11 +57522,11 @@
     </row>
     <row r="742">
       <c r="A742" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -57599,11 +57599,11 @@
     </row>
     <row r="743">
       <c r="A743" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -57676,11 +57676,11 @@
     </row>
     <row r="744">
       <c r="A744" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -57753,11 +57753,11 @@
     </row>
     <row r="745">
       <c r="A745" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -57830,11 +57830,11 @@
     </row>
     <row r="746">
       <c r="A746" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -57907,11 +57907,11 @@
     </row>
     <row r="747">
       <c r="A747" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -57984,11 +57984,11 @@
     </row>
     <row r="748">
       <c r="A748" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -58061,11 +58061,11 @@
     </row>
     <row r="749">
       <c r="A749" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -58118,31 +58118,31 @@
         <v>0</v>
       </c>
       <c r="P749" t="n">
-        <v>616386.34</v>
+        <v>645574.3199999999</v>
       </c>
       <c r="Q749" t="n">
-        <v>-616386.34</v>
+        <v>-645574.3199999999</v>
       </c>
       <c r="R749" t="n">
         <v>1684019.12</v>
       </c>
       <c r="S749" t="n">
-        <v>-1067632.78</v>
+        <v>-1038444.8</v>
       </c>
       <c r="T749" t="n">
-        <v>8888082.390000001</v>
+        <v>8987244.310000001</v>
       </c>
       <c r="U749" t="n">
-        <v>-8888082.390000001</v>
+        <v>-8987244.310000001</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -58195,31 +58195,31 @@
         <v>15388887.32</v>
       </c>
       <c r="P750" t="n">
-        <v>6447355.1</v>
+        <v>6476543.08</v>
       </c>
       <c r="Q750" t="n">
-        <v>8941532.220000001</v>
+        <v>8912344.24</v>
       </c>
       <c r="R750" t="n">
         <v>5830968.76</v>
       </c>
       <c r="S750" t="n">
-        <v>616386.34</v>
+        <v>645574.3199999999</v>
       </c>
       <c r="T750" t="n">
-        <v>28888082.39</v>
+        <v>28987244.31</v>
       </c>
       <c r="U750" t="n">
-        <v>20207823.68</v>
+        <v>20108661.76</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -58292,11 +58292,11 @@
     </row>
     <row r="752">
       <c r="A752" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -58369,11 +58369,11 @@
     </row>
     <row r="753">
       <c r="A753" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -58446,11 +58446,11 @@
     </row>
     <row r="754">
       <c r="A754" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -58523,11 +58523,11 @@
     </row>
     <row r="755">
       <c r="A755" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -58600,11 +58600,11 @@
     </row>
     <row r="756">
       <c r="A756" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -58677,11 +58677,11 @@
     </row>
     <row r="757">
       <c r="A757" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -58754,11 +58754,11 @@
     </row>
     <row r="758">
       <c r="A758" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -58831,11 +58831,11 @@
     </row>
     <row r="759">
       <c r="A759" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -58908,11 +58908,11 @@
     </row>
     <row r="760">
       <c r="A760" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -58985,11 +58985,11 @@
     </row>
     <row r="761">
       <c r="A761" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -59062,11 +59062,11 @@
     </row>
     <row r="762">
       <c r="A762" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -59139,11 +59139,11 @@
     </row>
     <row r="763">
       <c r="A763" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -59216,11 +59216,11 @@
     </row>
     <row r="764">
       <c r="A764" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -59293,11 +59293,11 @@
     </row>
     <row r="765">
       <c r="A765" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -59370,11 +59370,11 @@
     </row>
     <row r="766">
       <c r="A766" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -59447,11 +59447,11 @@
     </row>
     <row r="767">
       <c r="A767" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -59524,11 +59524,11 @@
     </row>
     <row r="768">
       <c r="A768" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -59601,11 +59601,11 @@
     </row>
     <row r="769">
       <c r="A769" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -59678,11 +59678,11 @@
     </row>
     <row r="770">
       <c r="A770" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -59755,11 +59755,11 @@
     </row>
     <row r="771">
       <c r="A771" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -59832,11 +59832,11 @@
     </row>
     <row r="772">
       <c r="A772" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -59909,11 +59909,11 @@
     </row>
     <row r="773">
       <c r="A773" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -59986,11 +59986,11 @@
     </row>
     <row r="774">
       <c r="A774" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -60063,11 +60063,11 @@
     </row>
     <row r="775">
       <c r="A775" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -60140,11 +60140,11 @@
     </row>
     <row r="776">
       <c r="A776" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -60217,11 +60217,11 @@
     </row>
     <row r="777">
       <c r="A777" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -60294,11 +60294,11 @@
     </row>
     <row r="778">
       <c r="A778" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -60371,11 +60371,11 @@
     </row>
     <row r="779">
       <c r="A779" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -60448,11 +60448,11 @@
     </row>
     <row r="780">
       <c r="A780" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -60525,11 +60525,11 @@
     </row>
     <row r="781">
       <c r="A781" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -60602,11 +60602,11 @@
     </row>
     <row r="782">
       <c r="A782" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -60679,11 +60679,11 @@
     </row>
     <row r="783">
       <c r="A783" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -60756,11 +60756,11 @@
     </row>
     <row r="784">
       <c r="A784" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -60833,11 +60833,11 @@
     </row>
     <row r="785">
       <c r="A785" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -60910,11 +60910,11 @@
     </row>
     <row r="786">
       <c r="A786" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -60987,11 +60987,11 @@
     </row>
     <row r="787">
       <c r="A787" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -61064,11 +61064,11 @@
     </row>
     <row r="788">
       <c r="A788" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -61141,11 +61141,11 @@
     </row>
     <row r="789">
       <c r="A789" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -61218,11 +61218,11 @@
     </row>
     <row r="790">
       <c r="A790" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -61295,11 +61295,11 @@
     </row>
     <row r="791">
       <c r="A791" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -61372,11 +61372,11 @@
     </row>
     <row r="792">
       <c r="A792" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -61449,11 +61449,11 @@
     </row>
     <row r="793">
       <c r="A793" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -61526,11 +61526,11 @@
     </row>
     <row r="794">
       <c r="A794" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -61595,19 +61595,19 @@
         <v>0</v>
       </c>
       <c r="T794" t="n">
-        <v>0</v>
+        <v>138840</v>
       </c>
       <c r="U794" t="n">
-        <v>665000</v>
+        <v>526160</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -61680,11 +61680,11 @@
     </row>
     <row r="796">
       <c r="A796" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -61757,11 +61757,11 @@
     </row>
     <row r="797">
       <c r="A797" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -61834,11 +61834,11 @@
     </row>
     <row r="798">
       <c r="A798" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -61911,11 +61911,11 @@
     </row>
     <row r="799">
       <c r="A799" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -61988,11 +61988,11 @@
     </row>
     <row r="800">
       <c r="A800" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -62065,11 +62065,11 @@
     </row>
     <row r="801">
       <c r="A801" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -62142,11 +62142,11 @@
     </row>
     <row r="802">
       <c r="A802" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -62219,11 +62219,11 @@
     </row>
     <row r="803">
       <c r="A803" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -62296,11 +62296,11 @@
     </row>
     <row r="804">
       <c r="A804" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -62373,11 +62373,11 @@
     </row>
     <row r="805">
       <c r="A805" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -62450,11 +62450,11 @@
     </row>
     <row r="806">
       <c r="A806" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -62527,11 +62527,11 @@
     </row>
     <row r="807">
       <c r="A807" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -62604,11 +62604,11 @@
     </row>
     <row r="808">
       <c r="A808" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -62681,11 +62681,11 @@
     </row>
     <row r="809">
       <c r="A809" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -62750,19 +62750,19 @@
         <v>0</v>
       </c>
       <c r="T809" t="n">
-        <v>0</v>
+        <v>138840</v>
       </c>
       <c r="U809" t="n">
-        <v>0</v>
+        <v>-138840</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -62835,11 +62835,11 @@
     </row>
     <row r="811">
       <c r="A811" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -62912,11 +62912,11 @@
     </row>
     <row r="812">
       <c r="A812" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -62989,11 +62989,11 @@
     </row>
     <row r="813">
       <c r="A813" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -63066,11 +63066,11 @@
     </row>
     <row r="814">
       <c r="A814" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -63143,11 +63143,11 @@
     </row>
     <row r="815">
       <c r="A815" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -63220,11 +63220,11 @@
     </row>
     <row r="816">
       <c r="A816" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -63297,11 +63297,11 @@
     </row>
     <row r="817">
       <c r="A817" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -63374,11 +63374,11 @@
     </row>
     <row r="818">
       <c r="A818" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -63451,11 +63451,11 @@
     </row>
     <row r="819">
       <c r="A819" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -63528,11 +63528,11 @@
     </row>
     <row r="820">
       <c r="A820" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -63605,11 +63605,11 @@
     </row>
     <row r="821">
       <c r="A821" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -63682,11 +63682,11 @@
     </row>
     <row r="822">
       <c r="A822" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -63759,11 +63759,11 @@
     </row>
     <row r="823">
       <c r="A823" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -63836,11 +63836,11 @@
     </row>
     <row r="824">
       <c r="A824" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -63913,11 +63913,11 @@
     </row>
     <row r="825">
       <c r="A825" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>RELEXORC_17-04-2026.csv</t>
+          <t>RELEXORC_22-04-2026.csv</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -64154,7 +64154,7 @@
         <v>46112</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -64249,7 +64249,7 @@
         <v>46112</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -64344,7 +64344,7 @@
         <v>46112</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -64439,7 +64439,7 @@
         <v>46112</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -64534,7 +64534,7 @@
         <v>46112</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -64629,7 +64629,7 @@
         <v>46112</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -64724,7 +64724,7 @@
         <v>46112</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -64819,7 +64819,7 @@
         <v>46112</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -64914,7 +64914,7 @@
         <v>46112</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -64971,10 +64971,10 @@
         <v>5845968.76</v>
       </c>
       <c r="S10" t="n">
-        <v>6447355.1</v>
+        <v>6476543.08</v>
       </c>
       <c r="T10" t="n">
-        <v>601386.3399999999</v>
+        <v>630574.3200000003</v>
       </c>
       <c r="U10" t="n">
         <v>4367980.05</v>
@@ -64989,19 +64989,19 @@
         <v>27222950.51</v>
       </c>
       <c r="Y10" t="n">
-        <v>28888082.39</v>
+        <v>28987244.31</v>
       </c>
       <c r="Z10" t="n">
-        <v>1665131.879999999</v>
+        <v>1764293.799999997</v>
       </c>
       <c r="AA10" t="n">
         <v>21872955.56</v>
       </c>
       <c r="AB10" t="n">
-        <v>20207823.68</v>
+        <v>20108661.76</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1665131.879999999</v>
+        <v>-1764293.799999997</v>
       </c>
     </row>
     <row r="11">
@@ -65009,7 +65009,7 @@
         <v>46112</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -65104,7 +65104,7 @@
         <v>46112</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -65199,7 +65199,7 @@
         <v>46112</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -65294,7 +65294,7 @@
         <v>46112</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -65389,7 +65389,7 @@
         <v>46112</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -65484,7 +65484,7 @@
         <v>46112</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -65579,7 +65579,7 @@
         <v>46112</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -65674,7 +65674,7 @@
         <v>46112</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -65769,7 +65769,7 @@
         <v>46112</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -65835,10 +65835,10 @@
         <v>79635166.11</v>
       </c>
       <c r="V19" t="n">
-        <v>88101492.78</v>
+        <v>88102864.33</v>
       </c>
       <c r="W19" t="n">
-        <v>8466326.670000002</v>
+        <v>8467698.219999999</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -65864,7 +65864,7 @@
         <v>46112</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -65959,7 +65959,7 @@
         <v>46112</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -66054,7 +66054,7 @@
         <v>46112</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -66149,7 +66149,7 @@
         <v>46112</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -66244,7 +66244,7 @@
         <v>46112</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -66339,7 +66339,7 @@
         <v>46112</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -66434,7 +66434,7 @@
         <v>46112</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -66529,7 +66529,7 @@
         <v>46112</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -66624,7 +66624,7 @@
         <v>46112</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -66719,7 +66719,7 @@
         <v>46112</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -66814,7 +66814,7 @@
         <v>46112</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -66909,7 +66909,7 @@
         <v>46112</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -67004,7 +67004,7 @@
         <v>46112</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -67099,7 +67099,7 @@
         <v>46112</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -67194,7 +67194,7 @@
         <v>46112</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -67289,7 +67289,7 @@
         <v>46112</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -67384,7 +67384,7 @@
         <v>46112</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -67479,7 +67479,7 @@
         <v>46112</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -67574,7 +67574,7 @@
         <v>46112</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -67669,7 +67669,7 @@
         <v>46112</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -67764,7 +67764,7 @@
         <v>46112</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -67859,7 +67859,7 @@
         <v>46112</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -67954,7 +67954,7 @@
         <v>46112</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -68049,7 +68049,7 @@
         <v>46112</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -68144,7 +68144,7 @@
         <v>46112</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -68239,7 +68239,7 @@
         <v>46112</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -68334,7 +68334,7 @@
         <v>46112</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -68429,7 +68429,7 @@
         <v>46112</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -68524,7 +68524,7 @@
         <v>46112</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -68599,19 +68599,19 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>138840</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>138840</v>
       </c>
       <c r="AA48" t="n">
         <v>665000</v>
       </c>
       <c r="AB48" t="n">
-        <v>665000</v>
+        <v>526160</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>-138840</v>
       </c>
     </row>
     <row r="49">
@@ -68619,7 +68619,7 @@
         <v>46112</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -68714,7 +68714,7 @@
         <v>46112</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -68809,7 +68809,7 @@
         <v>46112</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -68904,7 +68904,7 @@
         <v>46112</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -68999,7 +68999,7 @@
         <v>46112</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -69094,7 +69094,7 @@
         <v>46112</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -69189,7 +69189,7 @@
         <v>46112</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -69284,7 +69284,7 @@
         <v>46112</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -69379,7 +69379,7 @@
         <v>46112</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -69474,7 +69474,7 @@
         <v>46112</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -69569,7 +69569,7 @@
         <v>46112</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -69664,7 +69664,7 @@
         <v>46112</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -69759,7 +69759,7 @@
         <v>46112</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -69854,7 +69854,7 @@
         <v>46112</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -69949,7 +69949,7 @@
         <v>46112</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -70044,7 +70044,7 @@
         <v>46112</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -70139,7 +70139,7 @@
         <v>46112</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -70234,7 +70234,7 @@
         <v>46112</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -70329,7 +70329,7 @@
         <v>46112</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -70424,7 +70424,7 @@
         <v>46112</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -70519,7 +70519,7 @@
         <v>46112</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -70614,7 +70614,7 @@
         <v>46112</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -70709,7 +70709,7 @@
         <v>46112</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -70804,7 +70804,7 @@
         <v>46112</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -70899,7 +70899,7 @@
         <v>46112</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -70994,7 +70994,7 @@
         <v>46112</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -71089,7 +71089,7 @@
         <v>46112</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -71184,7 +71184,7 @@
         <v>46112</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -71279,7 +71279,7 @@
         <v>46112</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -71374,7 +71374,7 @@
         <v>46112</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -71469,7 +71469,7 @@
         <v>46112</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -71564,7 +71564,7 @@
         <v>46112</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -71659,7 +71659,7 @@
         <v>46112</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -71754,7 +71754,7 @@
         <v>46112</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -71849,7 +71849,7 @@
         <v>46112</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -71944,7 +71944,7 @@
         <v>46112</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -72039,7 +72039,7 @@
         <v>46112</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -72134,7 +72134,7 @@
         <v>46112</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -72229,7 +72229,7 @@
         <v>46112</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -72324,7 +72324,7 @@
         <v>46112</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -72419,7 +72419,7 @@
         <v>46112</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -72514,7 +72514,7 @@
         <v>46112</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -72609,7 +72609,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -72704,7 +72704,7 @@
         <v>46112</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -72799,7 +72799,7 @@
         <v>46112</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -72894,7 +72894,7 @@
         <v>46112</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -72989,7 +72989,7 @@
         <v>46112</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -73084,7 +73084,7 @@
         <v>46112</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -73141,10 +73141,10 @@
         <v>664443.25</v>
       </c>
       <c r="S96" t="n">
-        <v>664443.25</v>
+        <v>813676.15</v>
       </c>
       <c r="T96" t="n">
-        <v>0</v>
+        <v>149232.9</v>
       </c>
       <c r="U96" t="n">
         <v>441322.08</v>
@@ -73179,7 +73179,7 @@
         <v>46112</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -73274,7 +73274,7 @@
         <v>46112</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -73369,7 +73369,7 @@
         <v>46112</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -73464,7 +73464,7 @@
         <v>46112</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -73559,7 +73559,7 @@
         <v>46112</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -73654,7 +73654,7 @@
         <v>46112</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -73749,7 +73749,7 @@
         <v>46112</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -73844,7 +73844,7 @@
         <v>46112</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -73939,7 +73939,7 @@
         <v>46112</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -74034,7 +74034,7 @@
         <v>46112</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -74129,7 +74129,7 @@
         <v>46112</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -74224,7 +74224,7 @@
         <v>46112</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -74281,10 +74281,10 @@
         <v>1128600</v>
       </c>
       <c r="S108" t="n">
-        <v>1418900</v>
+        <v>1479000</v>
       </c>
       <c r="T108" t="n">
-        <v>290300</v>
+        <v>350400</v>
       </c>
       <c r="U108" t="n">
         <v>747600</v>
@@ -74319,7 +74319,7 @@
         <v>46112</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -74414,7 +74414,7 @@
         <v>46112</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -74509,7 +74509,7 @@
         <v>46112</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -74604,7 +74604,7 @@
         <v>46112</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -74699,7 +74699,7 @@
         <v>46112</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -74794,7 +74794,7 @@
         <v>46112</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -74889,7 +74889,7 @@
         <v>46112</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -74984,7 +74984,7 @@
         <v>46112</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -75079,7 +75079,7 @@
         <v>46112</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -75174,7 +75174,7 @@
         <v>46112</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -75269,7 +75269,7 @@
         <v>46112</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -75364,7 +75364,7 @@
         <v>46112</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -75459,7 +75459,7 @@
         <v>46112</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -75516,10 +75516,10 @@
         <v>993289</v>
       </c>
       <c r="S121" t="n">
-        <v>1446091.4</v>
+        <v>1459391.4</v>
       </c>
       <c r="T121" t="n">
-        <v>452802.3999999999</v>
+        <v>466102.3999999999</v>
       </c>
       <c r="U121" t="n">
         <v>993289</v>
@@ -75554,7 +75554,7 @@
         <v>46112</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -75611,10 +75611,10 @@
         <v>1919999.31</v>
       </c>
       <c r="S122" t="n">
-        <v>1919999.31</v>
+        <v>2061626.98</v>
       </c>
       <c r="T122" t="n">
-        <v>0</v>
+        <v>141627.6699999999</v>
       </c>
       <c r="U122" t="n">
         <v>1278789.54</v>
@@ -75629,19 +75629,19 @@
         <v>1000000</v>
       </c>
       <c r="Y122" t="n">
-        <v>1000000</v>
+        <v>1851081.28</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>851081.28</v>
       </c>
       <c r="AA122" t="n">
         <v>1076961.03</v>
       </c>
       <c r="AB122" t="n">
-        <v>1076961.03</v>
+        <v>225879.75</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>-851081.28</v>
       </c>
     </row>
     <row r="123">
@@ -75649,7 +75649,7 @@
         <v>46112</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -75744,7 +75744,7 @@
         <v>46112</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -75839,7 +75839,7 @@
         <v>46112</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -75934,7 +75934,7 @@
         <v>46112</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -76029,7 +76029,7 @@
         <v>46112</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -76124,7 +76124,7 @@
         <v>46112</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -76219,7 +76219,7 @@
         <v>46112</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -76314,7 +76314,7 @@
         <v>46112</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>

--- a/Base_Consolidada_SIAFI.xlsx
+++ b/Base_Consolidada_SIAFI.xlsx
@@ -44586,11 +44586,11 @@
     </row>
     <row r="574">
       <c r="A574" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -44663,11 +44663,11 @@
     </row>
     <row r="575">
       <c r="A575" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -44740,11 +44740,11 @@
     </row>
     <row r="576">
       <c r="A576" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -44817,11 +44817,11 @@
     </row>
     <row r="577">
       <c r="A577" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -44894,11 +44894,11 @@
     </row>
     <row r="578">
       <c r="A578" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -44971,11 +44971,11 @@
     </row>
     <row r="579">
       <c r="A579" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -45048,11 +45048,11 @@
     </row>
     <row r="580">
       <c r="A580" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -45125,11 +45125,11 @@
     </row>
     <row r="581">
       <c r="A581" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -45202,11 +45202,11 @@
     </row>
     <row r="582">
       <c r="A582" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -45279,11 +45279,11 @@
     </row>
     <row r="583">
       <c r="A583" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -45356,11 +45356,11 @@
     </row>
     <row r="584">
       <c r="A584" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -45433,11 +45433,11 @@
     </row>
     <row r="585">
       <c r="A585" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -45510,11 +45510,11 @@
     </row>
     <row r="586">
       <c r="A586" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -45587,11 +45587,11 @@
     </row>
     <row r="587">
       <c r="A587" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -45664,11 +45664,11 @@
     </row>
     <row r="588">
       <c r="A588" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -45741,11 +45741,11 @@
     </row>
     <row r="589">
       <c r="A589" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -45818,11 +45818,11 @@
     </row>
     <row r="590">
       <c r="A590" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -45895,11 +45895,11 @@
     </row>
     <row r="591">
       <c r="A591" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -45972,11 +45972,11 @@
     </row>
     <row r="592">
       <c r="A592" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -46049,11 +46049,11 @@
     </row>
     <row r="593">
       <c r="A593" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -46126,11 +46126,11 @@
     </row>
     <row r="594">
       <c r="A594" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -46203,11 +46203,11 @@
     </row>
     <row r="595">
       <c r="A595" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -46257,13 +46257,13 @@
         <v>0</v>
       </c>
       <c r="O595" t="n">
-        <v>0</v>
+        <v>59000</v>
       </c>
       <c r="P595" t="n">
         <v>81696</v>
       </c>
       <c r="Q595" t="n">
-        <v>-81696</v>
+        <v>-22696</v>
       </c>
       <c r="R595" t="n">
         <v>2427764.33</v>
@@ -46275,16 +46275,16 @@
         <v>5530000</v>
       </c>
       <c r="U595" t="n">
-        <v>-5530000</v>
+        <v>-5589000</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -46334,13 +46334,13 @@
         <v>27095956.66</v>
       </c>
       <c r="O596" t="n">
-        <v>13410211.52</v>
+        <v>13469211.52</v>
       </c>
       <c r="P596" t="n">
         <v>9145517.82</v>
       </c>
       <c r="Q596" t="n">
-        <v>4264693.699999999</v>
+        <v>4323693.699999999</v>
       </c>
       <c r="R596" t="n">
         <v>9063821.82</v>
@@ -46352,16 +46352,16 @@
         <v>11861411.46</v>
       </c>
       <c r="U596" t="n">
-        <v>1824333.68</v>
+        <v>1765333.68</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -46434,11 +46434,11 @@
     </row>
     <row r="598">
       <c r="A598" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -46511,11 +46511,11 @@
     </row>
     <row r="599">
       <c r="A599" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -46588,11 +46588,11 @@
     </row>
     <row r="600">
       <c r="A600" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -46665,11 +46665,11 @@
     </row>
     <row r="601">
       <c r="A601" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -46742,11 +46742,11 @@
     </row>
     <row r="602">
       <c r="A602" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -46819,11 +46819,11 @@
     </row>
     <row r="603">
       <c r="A603" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -46896,11 +46896,11 @@
     </row>
     <row r="604">
       <c r="A604" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -46973,11 +46973,11 @@
     </row>
     <row r="605">
       <c r="A605" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -47050,11 +47050,11 @@
     </row>
     <row r="606">
       <c r="A606" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -47127,11 +47127,11 @@
     </row>
     <row r="607">
       <c r="A607" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -47204,11 +47204,11 @@
     </row>
     <row r="608">
       <c r="A608" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -47281,11 +47281,11 @@
     </row>
     <row r="609">
       <c r="A609" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -47358,11 +47358,11 @@
     </row>
     <row r="610">
       <c r="A610" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -47435,11 +47435,11 @@
     </row>
     <row r="611">
       <c r="A611" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -47512,11 +47512,11 @@
     </row>
     <row r="612">
       <c r="A612" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -47589,11 +47589,11 @@
     </row>
     <row r="613">
       <c r="A613" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -47666,11 +47666,11 @@
     </row>
     <row r="614">
       <c r="A614" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -47743,11 +47743,11 @@
     </row>
     <row r="615">
       <c r="A615" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -47820,11 +47820,11 @@
     </row>
     <row r="616">
       <c r="A616" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -47897,11 +47897,11 @@
     </row>
     <row r="617">
       <c r="A617" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -47974,11 +47974,11 @@
     </row>
     <row r="618">
       <c r="A618" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -48051,11 +48051,11 @@
     </row>
     <row r="619">
       <c r="A619" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -48128,11 +48128,11 @@
     </row>
     <row r="620">
       <c r="A620" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -48205,11 +48205,11 @@
     </row>
     <row r="621">
       <c r="A621" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -48282,11 +48282,11 @@
     </row>
     <row r="622">
       <c r="A622" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -48359,11 +48359,11 @@
     </row>
     <row r="623">
       <c r="A623" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -48436,11 +48436,11 @@
     </row>
     <row r="624">
       <c r="A624" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -48513,11 +48513,11 @@
     </row>
     <row r="625">
       <c r="A625" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -48590,11 +48590,11 @@
     </row>
     <row r="626">
       <c r="A626" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -48667,11 +48667,11 @@
     </row>
     <row r="627">
       <c r="A627" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -48744,11 +48744,11 @@
     </row>
     <row r="628">
       <c r="A628" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -48821,11 +48821,11 @@
     </row>
     <row r="629">
       <c r="A629" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -48898,11 +48898,11 @@
     </row>
     <row r="630">
       <c r="A630" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -48975,11 +48975,11 @@
     </row>
     <row r="631">
       <c r="A631" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -49052,11 +49052,11 @@
     </row>
     <row r="632">
       <c r="A632" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -49129,11 +49129,11 @@
     </row>
     <row r="633">
       <c r="A633" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -49206,11 +49206,11 @@
     </row>
     <row r="634">
       <c r="A634" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -49283,11 +49283,11 @@
     </row>
     <row r="635">
       <c r="A635" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -49360,11 +49360,11 @@
     </row>
     <row r="636">
       <c r="A636" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -49437,11 +49437,11 @@
     </row>
     <row r="637">
       <c r="A637" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -49514,11 +49514,11 @@
     </row>
     <row r="638">
       <c r="A638" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -49591,11 +49591,11 @@
     </row>
     <row r="639">
       <c r="A639" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -49668,11 +49668,11 @@
     </row>
     <row r="640">
       <c r="A640" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -49745,11 +49745,11 @@
     </row>
     <row r="641">
       <c r="A641" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -49822,11 +49822,11 @@
     </row>
     <row r="642">
       <c r="A642" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -49891,19 +49891,19 @@
         <v>0</v>
       </c>
       <c r="T642" t="n">
-        <v>0</v>
+        <v>1250000</v>
       </c>
       <c r="U642" t="n">
-        <v>0</v>
+        <v>-1250000</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -49968,19 +49968,19 @@
         <v>0</v>
       </c>
       <c r="T643" t="n">
-        <v>2647578.37</v>
+        <v>3897578.37</v>
       </c>
       <c r="U643" t="n">
-        <v>3627211.32</v>
+        <v>2377211.32</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -50053,11 +50053,11 @@
     </row>
     <row r="645">
       <c r="A645" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -50130,11 +50130,11 @@
     </row>
     <row r="646">
       <c r="A646" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -50207,11 +50207,11 @@
     </row>
     <row r="647">
       <c r="A647" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -50284,11 +50284,11 @@
     </row>
     <row r="648">
       <c r="A648" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -50361,11 +50361,11 @@
     </row>
     <row r="649">
       <c r="A649" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -50438,11 +50438,11 @@
     </row>
     <row r="650">
       <c r="A650" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -50515,11 +50515,11 @@
     </row>
     <row r="651">
       <c r="A651" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -50592,11 +50592,11 @@
     </row>
     <row r="652">
       <c r="A652" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -50669,11 +50669,11 @@
     </row>
     <row r="653">
       <c r="A653" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -50746,11 +50746,11 @@
     </row>
     <row r="654">
       <c r="A654" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -50823,11 +50823,11 @@
     </row>
     <row r="655">
       <c r="A655" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -50900,11 +50900,11 @@
     </row>
     <row r="656">
       <c r="A656" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -50977,11 +50977,11 @@
     </row>
     <row r="657">
       <c r="A657" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -51054,11 +51054,11 @@
     </row>
     <row r="658">
       <c r="A658" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -51131,11 +51131,11 @@
     </row>
     <row r="659">
       <c r="A659" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -51208,11 +51208,11 @@
     </row>
     <row r="660">
       <c r="A660" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -51285,11 +51285,11 @@
     </row>
     <row r="661">
       <c r="A661" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -51362,11 +51362,11 @@
     </row>
     <row r="662">
       <c r="A662" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -51439,11 +51439,11 @@
     </row>
     <row r="663">
       <c r="A663" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -51516,11 +51516,11 @@
     </row>
     <row r="664">
       <c r="A664" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -51593,11 +51593,11 @@
     </row>
     <row r="665">
       <c r="A665" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -51670,11 +51670,11 @@
     </row>
     <row r="666">
       <c r="A666" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -51747,11 +51747,11 @@
     </row>
     <row r="667">
       <c r="A667" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -51824,11 +51824,11 @@
     </row>
     <row r="668">
       <c r="A668" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -51901,11 +51901,11 @@
     </row>
     <row r="669">
       <c r="A669" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -51978,11 +51978,11 @@
     </row>
     <row r="670">
       <c r="A670" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -52055,11 +52055,11 @@
     </row>
     <row r="671">
       <c r="A671" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -52132,11 +52132,11 @@
     </row>
     <row r="672">
       <c r="A672" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -52209,11 +52209,11 @@
     </row>
     <row r="673">
       <c r="A673" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -52286,11 +52286,11 @@
     </row>
     <row r="674">
       <c r="A674" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -52363,11 +52363,11 @@
     </row>
     <row r="675">
       <c r="A675" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -52440,11 +52440,11 @@
     </row>
     <row r="676">
       <c r="A676" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -52517,11 +52517,11 @@
     </row>
     <row r="677">
       <c r="A677" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -52594,11 +52594,11 @@
     </row>
     <row r="678">
       <c r="A678" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -52671,11 +52671,11 @@
     </row>
     <row r="679">
       <c r="A679" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -52748,11 +52748,11 @@
     </row>
     <row r="680">
       <c r="A680" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -52825,11 +52825,11 @@
     </row>
     <row r="681">
       <c r="A681" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -52902,11 +52902,11 @@
     </row>
     <row r="682">
       <c r="A682" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -52979,11 +52979,11 @@
     </row>
     <row r="683">
       <c r="A683" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -53056,11 +53056,11 @@
     </row>
     <row r="684">
       <c r="A684" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -53133,11 +53133,11 @@
     </row>
     <row r="685">
       <c r="A685" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -53190,16 +53190,16 @@
         <v>7000</v>
       </c>
       <c r="P685" t="n">
-        <v>517400</v>
+        <v>551700</v>
       </c>
       <c r="Q685" t="n">
-        <v>-510400</v>
+        <v>-544700</v>
       </c>
       <c r="R685" t="n">
         <v>381000</v>
       </c>
       <c r="S685" t="n">
-        <v>136400</v>
+        <v>170700</v>
       </c>
       <c r="T685" t="n">
         <v>0</v>
@@ -53210,11 +53210,11 @@
     </row>
     <row r="686">
       <c r="A686" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -53267,16 +53267,16 @@
         <v>2085400</v>
       </c>
       <c r="P686" t="n">
-        <v>1479000</v>
+        <v>1513300</v>
       </c>
       <c r="Q686" t="n">
-        <v>606400</v>
+        <v>572100</v>
       </c>
       <c r="R686" t="n">
         <v>1128600</v>
       </c>
       <c r="S686" t="n">
-        <v>350400</v>
+        <v>384700</v>
       </c>
       <c r="T686" t="n">
         <v>0</v>
@@ -53287,11 +53287,11 @@
     </row>
     <row r="687">
       <c r="A687" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -53364,11 +53364,11 @@
     </row>
     <row r="688">
       <c r="A688" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -53441,11 +53441,11 @@
     </row>
     <row r="689">
       <c r="A689" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -53518,11 +53518,11 @@
     </row>
     <row r="690">
       <c r="A690" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -53595,11 +53595,11 @@
     </row>
     <row r="691">
       <c r="A691" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -53672,11 +53672,11 @@
     </row>
     <row r="692">
       <c r="A692" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -53749,11 +53749,11 @@
     </row>
     <row r="693">
       <c r="A693" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -53826,11 +53826,11 @@
     </row>
     <row r="694">
       <c r="A694" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -53903,11 +53903,11 @@
     </row>
     <row r="695">
       <c r="A695" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -53980,11 +53980,11 @@
     </row>
     <row r="696">
       <c r="A696" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -54057,11 +54057,11 @@
     </row>
     <row r="697">
       <c r="A697" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -54134,11 +54134,11 @@
     </row>
     <row r="698">
       <c r="A698" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -54211,11 +54211,11 @@
     </row>
     <row r="699">
       <c r="A699" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -54288,11 +54288,11 @@
     </row>
     <row r="700">
       <c r="A700" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -54365,11 +54365,11 @@
     </row>
     <row r="701">
       <c r="A701" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -54442,11 +54442,11 @@
     </row>
     <row r="702">
       <c r="A702" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -54519,11 +54519,11 @@
     </row>
     <row r="703">
       <c r="A703" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -54596,11 +54596,11 @@
     </row>
     <row r="704">
       <c r="A704" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -54659,10 +54659,10 @@
         <v>0</v>
       </c>
       <c r="R704" t="n">
-        <v>27384345.96</v>
+        <v>27382974.41</v>
       </c>
       <c r="S704" t="n">
-        <v>-27389086.95</v>
+        <v>-27387715.4</v>
       </c>
       <c r="T704" t="n">
         <v>0</v>
@@ -54673,11 +54673,11 @@
     </row>
     <row r="705">
       <c r="A705" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -54736,10 +54736,10 @@
         <v>0</v>
       </c>
       <c r="R705" t="n">
-        <v>88102864.33</v>
+        <v>88101492.78</v>
       </c>
       <c r="S705" t="n">
-        <v>4950.41</v>
+        <v>6321.96</v>
       </c>
       <c r="T705" t="n">
         <v>0</v>
@@ -54750,11 +54750,11 @@
     </row>
     <row r="706">
       <c r="A706" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -54827,11 +54827,11 @@
     </row>
     <row r="707">
       <c r="A707" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -54904,11 +54904,11 @@
     </row>
     <row r="708">
       <c r="A708" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -54981,11 +54981,11 @@
     </row>
     <row r="709">
       <c r="A709" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -55058,11 +55058,11 @@
     </row>
     <row r="710">
       <c r="A710" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -55135,11 +55135,11 @@
     </row>
     <row r="711">
       <c r="A711" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -55212,11 +55212,11 @@
     </row>
     <row r="712">
       <c r="A712" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -55289,11 +55289,11 @@
     </row>
     <row r="713">
       <c r="A713" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -55366,11 +55366,11 @@
     </row>
     <row r="714">
       <c r="A714" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -55443,11 +55443,11 @@
     </row>
     <row r="715">
       <c r="A715" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -55520,11 +55520,11 @@
     </row>
     <row r="716">
       <c r="A716" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -55597,11 +55597,11 @@
     </row>
     <row r="717">
       <c r="A717" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -55674,11 +55674,11 @@
     </row>
     <row r="718">
       <c r="A718" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -55751,11 +55751,11 @@
     </row>
     <row r="719">
       <c r="A719" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -55828,11 +55828,11 @@
     </row>
     <row r="720">
       <c r="A720" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -55905,11 +55905,11 @@
     </row>
     <row r="721">
       <c r="A721" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -55982,11 +55982,11 @@
     </row>
     <row r="722">
       <c r="A722" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -56059,11 +56059,11 @@
     </row>
     <row r="723">
       <c r="A723" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -56136,11 +56136,11 @@
     </row>
     <row r="724">
       <c r="A724" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -56213,11 +56213,11 @@
     </row>
     <row r="725">
       <c r="A725" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -56290,11 +56290,11 @@
     </row>
     <row r="726">
       <c r="A726" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -56367,11 +56367,11 @@
     </row>
     <row r="727">
       <c r="A727" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -56444,11 +56444,11 @@
     </row>
     <row r="728">
       <c r="A728" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -56521,11 +56521,11 @@
     </row>
     <row r="729">
       <c r="A729" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -56598,11 +56598,11 @@
     </row>
     <row r="730">
       <c r="A730" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -56675,11 +56675,11 @@
     </row>
     <row r="731">
       <c r="A731" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -56752,11 +56752,11 @@
     </row>
     <row r="732">
       <c r="A732" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -56829,11 +56829,11 @@
     </row>
     <row r="733">
       <c r="A733" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -56906,11 +56906,11 @@
     </row>
     <row r="734">
       <c r="A734" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -56983,11 +56983,11 @@
     </row>
     <row r="735">
       <c r="A735" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -57060,11 +57060,11 @@
     </row>
     <row r="736">
       <c r="A736" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -57137,11 +57137,11 @@
     </row>
     <row r="737">
       <c r="A737" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -57214,11 +57214,11 @@
     </row>
     <row r="738">
       <c r="A738" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -57291,11 +57291,11 @@
     </row>
     <row r="739">
       <c r="A739" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -57368,11 +57368,11 @@
     </row>
     <row r="740">
       <c r="A740" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -57445,11 +57445,11 @@
     </row>
     <row r="741">
       <c r="A741" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -57502,16 +57502,16 @@
         <v>0</v>
       </c>
       <c r="P741" t="n">
-        <v>170265.43</v>
+        <v>218951.13</v>
       </c>
       <c r="Q741" t="n">
-        <v>-170265.43</v>
+        <v>-218951.13</v>
       </c>
       <c r="R741" t="n">
         <v>281744.6</v>
       </c>
       <c r="S741" t="n">
-        <v>-111479.17</v>
+        <v>-62793.47</v>
       </c>
       <c r="T741" t="n">
         <v>0</v>
@@ -57522,11 +57522,11 @@
     </row>
     <row r="742">
       <c r="A742" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -57579,16 +57579,16 @@
         <v>1405964.1</v>
       </c>
       <c r="P742" t="n">
-        <v>777106.59</v>
+        <v>825792.29</v>
       </c>
       <c r="Q742" t="n">
-        <v>628857.5100000001</v>
+        <v>580171.8100000001</v>
       </c>
       <c r="R742" t="n">
         <v>577765.87</v>
       </c>
       <c r="S742" t="n">
-        <v>199340.72</v>
+        <v>248026.42</v>
       </c>
       <c r="T742" t="n">
         <v>1500000</v>
@@ -57599,11 +57599,11 @@
     </row>
     <row r="743">
       <c r="A743" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -57676,11 +57676,11 @@
     </row>
     <row r="744">
       <c r="A744" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -57753,11 +57753,11 @@
     </row>
     <row r="745">
       <c r="A745" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -57830,11 +57830,11 @@
     </row>
     <row r="746">
       <c r="A746" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -57907,11 +57907,11 @@
     </row>
     <row r="747">
       <c r="A747" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -57984,11 +57984,11 @@
     </row>
     <row r="748">
       <c r="A748" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -58061,11 +58061,11 @@
     </row>
     <row r="749">
       <c r="A749" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -58138,11 +58138,11 @@
     </row>
     <row r="750">
       <c r="A750" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -58215,11 +58215,11 @@
     </row>
     <row r="751">
       <c r="A751" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -58269,13 +58269,13 @@
         <v>-2578206</v>
       </c>
       <c r="O751" t="n">
-        <v>0</v>
+        <v>17676</v>
       </c>
       <c r="P751" t="n">
         <v>1228362.35</v>
       </c>
       <c r="Q751" t="n">
-        <v>-1228362.35</v>
+        <v>-1210686.35</v>
       </c>
       <c r="R751" t="n">
         <v>5389734.24</v>
@@ -58287,16 +58287,16 @@
         <v>8983827.050000001</v>
       </c>
       <c r="U751" t="n">
-        <v>-11562033.05</v>
+        <v>-11579709.05</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -58346,13 +58346,13 @@
         <v>96421794</v>
       </c>
       <c r="O752" t="n">
-        <v>24377681.76</v>
+        <v>24395357.76</v>
       </c>
       <c r="P752" t="n">
         <v>19417589.36</v>
       </c>
       <c r="Q752" t="n">
-        <v>4960092.400000002</v>
+        <v>4977768.400000002</v>
       </c>
       <c r="R752" t="n">
         <v>18189227.01</v>
@@ -58364,16 +58364,16 @@
         <v>53397827.05</v>
       </c>
       <c r="U752" t="n">
-        <v>18646285.19</v>
+        <v>18628609.19</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -58446,11 +58446,11 @@
     </row>
     <row r="754">
       <c r="A754" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -58523,11 +58523,11 @@
     </row>
     <row r="755">
       <c r="A755" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -58600,11 +58600,11 @@
     </row>
     <row r="756">
       <c r="A756" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -58677,11 +58677,11 @@
     </row>
     <row r="757">
       <c r="A757" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -58754,11 +58754,11 @@
     </row>
     <row r="758">
       <c r="A758" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -58831,11 +58831,11 @@
     </row>
     <row r="759">
       <c r="A759" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -58908,11 +58908,11 @@
     </row>
     <row r="760">
       <c r="A760" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -58985,11 +58985,11 @@
     </row>
     <row r="761">
       <c r="A761" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -59062,11 +59062,11 @@
     </row>
     <row r="762">
       <c r="A762" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -59139,11 +59139,11 @@
     </row>
     <row r="763">
       <c r="A763" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -59216,11 +59216,11 @@
     </row>
     <row r="764">
       <c r="A764" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -59293,11 +59293,11 @@
     </row>
     <row r="765">
       <c r="A765" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -59370,11 +59370,11 @@
     </row>
     <row r="766">
       <c r="A766" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -59447,11 +59447,11 @@
     </row>
     <row r="767">
       <c r="A767" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -59524,11 +59524,11 @@
     </row>
     <row r="768">
       <c r="A768" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -59601,11 +59601,11 @@
     </row>
     <row r="769">
       <c r="A769" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -59678,11 +59678,11 @@
     </row>
     <row r="770">
       <c r="A770" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -59755,11 +59755,11 @@
     </row>
     <row r="771">
       <c r="A771" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -59832,11 +59832,11 @@
     </row>
     <row r="772">
       <c r="A772" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -59909,11 +59909,11 @@
     </row>
     <row r="773">
       <c r="A773" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -59972,10 +59972,10 @@
         <v>-30311.5</v>
       </c>
       <c r="R773" t="n">
-        <v>64481.5</v>
+        <v>61472.5</v>
       </c>
       <c r="S773" t="n">
-        <v>-30820</v>
+        <v>-27811</v>
       </c>
       <c r="T773" t="n">
         <v>0</v>
@@ -59986,11 +59986,11 @@
     </row>
     <row r="774">
       <c r="A774" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -60049,10 +60049,10 @@
         <v>0</v>
       </c>
       <c r="R774" t="n">
-        <v>154261.5</v>
+        <v>151252.5</v>
       </c>
       <c r="S774" t="n">
-        <v>3350</v>
+        <v>6359</v>
       </c>
       <c r="T774" t="n">
         <v>0</v>
@@ -60063,11 +60063,11 @@
     </row>
     <row r="775">
       <c r="A775" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -60140,11 +60140,11 @@
     </row>
     <row r="776">
       <c r="A776" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -60217,11 +60217,11 @@
     </row>
     <row r="777">
       <c r="A777" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -60294,11 +60294,11 @@
     </row>
     <row r="778">
       <c r="A778" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -60371,11 +60371,11 @@
     </row>
     <row r="779">
       <c r="A779" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -60448,11 +60448,11 @@
     </row>
     <row r="780">
       <c r="A780" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -60525,11 +60525,11 @@
     </row>
     <row r="781">
       <c r="A781" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -60602,11 +60602,11 @@
     </row>
     <row r="782">
       <c r="A782" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -60679,11 +60679,11 @@
     </row>
     <row r="783">
       <c r="A783" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -60756,11 +60756,11 @@
     </row>
     <row r="784">
       <c r="A784" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -60833,11 +60833,11 @@
     </row>
     <row r="785">
       <c r="A785" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -60910,11 +60910,11 @@
     </row>
     <row r="786">
       <c r="A786" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -60987,11 +60987,11 @@
     </row>
     <row r="787">
       <c r="A787" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -61064,11 +61064,11 @@
     </row>
     <row r="788">
       <c r="A788" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -61141,11 +61141,11 @@
     </row>
     <row r="789">
       <c r="A789" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -61218,11 +61218,11 @@
     </row>
     <row r="790">
       <c r="A790" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -61295,11 +61295,11 @@
     </row>
     <row r="791">
       <c r="A791" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -61372,11 +61372,11 @@
     </row>
     <row r="792">
       <c r="A792" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -61449,11 +61449,11 @@
     </row>
     <row r="793">
       <c r="A793" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -61526,11 +61526,11 @@
     </row>
     <row r="794">
       <c r="A794" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -61603,11 +61603,11 @@
     </row>
     <row r="795">
       <c r="A795" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -61680,11 +61680,11 @@
     </row>
     <row r="796">
       <c r="A796" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -61757,11 +61757,11 @@
     </row>
     <row r="797">
       <c r="A797" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -61834,11 +61834,11 @@
     </row>
     <row r="798">
       <c r="A798" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -61911,11 +61911,11 @@
     </row>
     <row r="799">
       <c r="A799" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -61988,11 +61988,11 @@
     </row>
     <row r="800">
       <c r="A800" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -62065,11 +62065,11 @@
     </row>
     <row r="801">
       <c r="A801" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -62142,11 +62142,11 @@
     </row>
     <row r="802">
       <c r="A802" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -62219,11 +62219,11 @@
     </row>
     <row r="803">
       <c r="A803" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -62296,11 +62296,11 @@
     </row>
     <row r="804">
       <c r="A804" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -62373,11 +62373,11 @@
     </row>
     <row r="805">
       <c r="A805" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -62450,11 +62450,11 @@
     </row>
     <row r="806">
       <c r="A806" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -62527,11 +62527,11 @@
     </row>
     <row r="807">
       <c r="A807" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -62604,11 +62604,11 @@
     </row>
     <row r="808">
       <c r="A808" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -62681,11 +62681,11 @@
     </row>
     <row r="809">
       <c r="A809" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -62758,11 +62758,11 @@
     </row>
     <row r="810">
       <c r="A810" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -62835,11 +62835,11 @@
     </row>
     <row r="811">
       <c r="A811" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -62892,16 +62892,16 @@
         <v>0</v>
       </c>
       <c r="P811" t="n">
-        <v>0</v>
+        <v>44958</v>
       </c>
       <c r="Q811" t="n">
-        <v>0</v>
+        <v>-44958</v>
       </c>
       <c r="R811" t="n">
         <v>71015.78</v>
       </c>
       <c r="S811" t="n">
-        <v>-71015.78</v>
+        <v>-26057.78</v>
       </c>
       <c r="T811" t="n">
         <v>0</v>
@@ -62912,11 +62912,11 @@
     </row>
     <row r="812">
       <c r="A812" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -62969,16 +62969,16 @@
         <v>2652273.52</v>
       </c>
       <c r="P812" t="n">
-        <v>1288144</v>
+        <v>1333102</v>
       </c>
       <c r="Q812" t="n">
-        <v>1364129.52</v>
+        <v>1319171.52</v>
       </c>
       <c r="R812" t="n">
         <v>708187.78</v>
       </c>
       <c r="S812" t="n">
-        <v>579956.22</v>
+        <v>624914.22</v>
       </c>
       <c r="T812" t="n">
         <v>2000000</v>
@@ -62989,11 +62989,11 @@
     </row>
     <row r="813">
       <c r="A813" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -63066,11 +63066,11 @@
     </row>
     <row r="814">
       <c r="A814" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -63143,11 +63143,11 @@
     </row>
     <row r="815">
       <c r="A815" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -63220,11 +63220,11 @@
     </row>
     <row r="816">
       <c r="A816" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -63297,11 +63297,11 @@
     </row>
     <row r="817">
       <c r="A817" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -63374,11 +63374,11 @@
     </row>
     <row r="818">
       <c r="A818" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -63451,11 +63451,11 @@
     </row>
     <row r="819">
       <c r="A819" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -63528,11 +63528,11 @@
     </row>
     <row r="820">
       <c r="A820" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -63605,11 +63605,11 @@
     </row>
     <row r="821">
       <c r="A821" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -63682,11 +63682,11 @@
     </row>
     <row r="822">
       <c r="A822" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -63759,11 +63759,11 @@
     </row>
     <row r="823">
       <c r="A823" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -63836,11 +63836,11 @@
     </row>
     <row r="824">
       <c r="A824" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -63913,11 +63913,11 @@
     </row>
     <row r="825">
       <c r="A825" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>RELEXORC_22-04-2026.csv</t>
+          <t>RELEXORC_23-04-2026.csv</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -64154,7 +64154,7 @@
         <v>46112</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -64249,7 +64249,7 @@
         <v>46112</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -64344,7 +64344,7 @@
         <v>46112</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -64439,7 +64439,7 @@
         <v>46112</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -64534,7 +64534,7 @@
         <v>46112</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -64591,10 +64591,10 @@
         <v>640299.49</v>
       </c>
       <c r="S6" t="n">
-        <v>777106.59</v>
+        <v>825792.29</v>
       </c>
       <c r="T6" t="n">
-        <v>136807.1</v>
+        <v>185492.8</v>
       </c>
       <c r="U6" t="n">
         <v>296021.27</v>
@@ -64629,7 +64629,7 @@
         <v>46112</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -64724,7 +64724,7 @@
         <v>46112</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -64819,7 +64819,7 @@
         <v>46112</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -64914,7 +64914,7 @@
         <v>46112</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -65009,7 +65009,7 @@
         <v>46112</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -65057,10 +65057,10 @@
         <v>24377681.76</v>
       </c>
       <c r="P11" t="n">
-        <v>24377681.76</v>
+        <v>24395357.76</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>17676</v>
       </c>
       <c r="R11" t="n">
         <v>18189227.01</v>
@@ -65093,10 +65093,10 @@
         <v>27724491.19</v>
       </c>
       <c r="AB11" t="n">
-        <v>18646285.19</v>
+        <v>18628609.19</v>
       </c>
       <c r="AC11" t="n">
-        <v>-9078206</v>
+        <v>-9095882</v>
       </c>
     </row>
     <row r="12">
@@ -65104,7 +65104,7 @@
         <v>46112</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -65199,7 +65199,7 @@
         <v>46112</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -65294,7 +65294,7 @@
         <v>46112</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -65389,7 +65389,7 @@
         <v>46112</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -65484,7 +65484,7 @@
         <v>46112</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -65579,7 +65579,7 @@
         <v>46112</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -65674,7 +65674,7 @@
         <v>46112</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -65769,7 +65769,7 @@
         <v>46112</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -65835,10 +65835,10 @@
         <v>79635166.11</v>
       </c>
       <c r="V19" t="n">
-        <v>88102864.33</v>
+        <v>88101492.78</v>
       </c>
       <c r="W19" t="n">
-        <v>8467698.219999999</v>
+        <v>8466326.670000002</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -65864,7 +65864,7 @@
         <v>46112</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -65959,7 +65959,7 @@
         <v>46112</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -66054,7 +66054,7 @@
         <v>46112</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -66149,7 +66149,7 @@
         <v>46112</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -66244,7 +66244,7 @@
         <v>46112</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -66339,7 +66339,7 @@
         <v>46112</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -66434,7 +66434,7 @@
         <v>46112</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -66529,7 +66529,7 @@
         <v>46112</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -66624,7 +66624,7 @@
         <v>46112</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -66719,7 +66719,7 @@
         <v>46112</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -66814,7 +66814,7 @@
         <v>46112</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -66909,7 +66909,7 @@
         <v>46112</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -67004,7 +67004,7 @@
         <v>46112</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -67099,7 +67099,7 @@
         <v>46112</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -67194,7 +67194,7 @@
         <v>46112</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -67289,7 +67289,7 @@
         <v>46112</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -67384,7 +67384,7 @@
         <v>46112</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -67479,7 +67479,7 @@
         <v>46112</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -67574,7 +67574,7 @@
         <v>46112</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -67669,7 +67669,7 @@
         <v>46112</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -67764,7 +67764,7 @@
         <v>46112</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -67859,7 +67859,7 @@
         <v>46112</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -67916,10 +67916,10 @@
         <v>1288144</v>
       </c>
       <c r="S41" t="n">
-        <v>1288144</v>
+        <v>1333102</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>44958</v>
       </c>
       <c r="U41" t="n">
         <v>637172</v>
@@ -67954,7 +67954,7 @@
         <v>46112</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -68049,7 +68049,7 @@
         <v>46112</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -68144,7 +68144,7 @@
         <v>46112</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -68239,7 +68239,7 @@
         <v>46112</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -68334,7 +68334,7 @@
         <v>46112</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -68429,7 +68429,7 @@
         <v>46112</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -68524,7 +68524,7 @@
         <v>46112</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -68619,7 +68619,7 @@
         <v>46112</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -68714,7 +68714,7 @@
         <v>46112</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -68809,7 +68809,7 @@
         <v>46112</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -68904,7 +68904,7 @@
         <v>46112</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -68999,7 +68999,7 @@
         <v>46112</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -69094,7 +69094,7 @@
         <v>46112</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -69160,10 +69160,10 @@
         <v>123950</v>
       </c>
       <c r="V54" t="n">
-        <v>154261.5</v>
+        <v>151252.5</v>
       </c>
       <c r="W54" t="n">
-        <v>30311.5</v>
+        <v>27302.5</v>
       </c>
       <c r="X54" t="n">
         <v>0</v>
@@ -69189,7 +69189,7 @@
         <v>46112</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -69284,7 +69284,7 @@
         <v>46112</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -69379,7 +69379,7 @@
         <v>46112</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -69474,7 +69474,7 @@
         <v>46112</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -69569,7 +69569,7 @@
         <v>46112</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -69664,7 +69664,7 @@
         <v>46112</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -69759,7 +69759,7 @@
         <v>46112</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -69854,7 +69854,7 @@
         <v>46112</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -69949,7 +69949,7 @@
         <v>46112</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -70044,7 +70044,7 @@
         <v>46112</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -70139,7 +70139,7 @@
         <v>46112</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -70234,7 +70234,7 @@
         <v>46112</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -70329,7 +70329,7 @@
         <v>46112</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -70424,7 +70424,7 @@
         <v>46112</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -70519,7 +70519,7 @@
         <v>46112</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -70614,7 +70614,7 @@
         <v>46112</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -70709,7 +70709,7 @@
         <v>46112</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -70804,7 +70804,7 @@
         <v>46112</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -70899,7 +70899,7 @@
         <v>46112</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -70994,7 +70994,7 @@
         <v>46112</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -71089,7 +71089,7 @@
         <v>46112</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -71184,7 +71184,7 @@
         <v>46112</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -71279,7 +71279,7 @@
         <v>46112</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -71374,7 +71374,7 @@
         <v>46112</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -71469,7 +71469,7 @@
         <v>46112</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -71564,7 +71564,7 @@
         <v>46112</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -71659,7 +71659,7 @@
         <v>46112</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -71754,7 +71754,7 @@
         <v>46112</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -71849,7 +71849,7 @@
         <v>46112</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -71944,7 +71944,7 @@
         <v>46112</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -72039,7 +72039,7 @@
         <v>46112</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -72134,7 +72134,7 @@
         <v>46112</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -72229,7 +72229,7 @@
         <v>46112</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -72324,7 +72324,7 @@
         <v>46112</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -72419,7 +72419,7 @@
         <v>46112</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -72514,7 +72514,7 @@
         <v>46112</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -72609,7 +72609,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -72704,7 +72704,7 @@
         <v>46112</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -72799,7 +72799,7 @@
         <v>46112</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -72894,7 +72894,7 @@
         <v>46112</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -72942,10 +72942,10 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>13410211.52</v>
+        <v>13469211.52</v>
       </c>
       <c r="Q94" t="n">
-        <v>13410211.52</v>
+        <v>13469211.52</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
@@ -72978,10 +72978,10 @@
         <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1824333.68</v>
+        <v>1765333.68</v>
       </c>
       <c r="AC94" t="n">
-        <v>1824333.68</v>
+        <v>1765333.68</v>
       </c>
     </row>
     <row r="95">
@@ -72989,7 +72989,7 @@
         <v>46112</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -73084,7 +73084,7 @@
         <v>46112</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -73179,7 +73179,7 @@
         <v>46112</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -73274,7 +73274,7 @@
         <v>46112</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -73369,7 +73369,7 @@
         <v>46112</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -73464,7 +73464,7 @@
         <v>46112</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -73559,7 +73559,7 @@
         <v>46112</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -73654,7 +73654,7 @@
         <v>46112</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -73749,7 +73749,7 @@
         <v>46112</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -73844,7 +73844,7 @@
         <v>46112</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -73939,7 +73939,7 @@
         <v>46112</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -74034,7 +74034,7 @@
         <v>46112</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -74129,7 +74129,7 @@
         <v>46112</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -74224,7 +74224,7 @@
         <v>46112</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -74281,10 +74281,10 @@
         <v>1128600</v>
       </c>
       <c r="S108" t="n">
-        <v>1479000</v>
+        <v>1513300</v>
       </c>
       <c r="T108" t="n">
-        <v>350400</v>
+        <v>384700</v>
       </c>
       <c r="U108" t="n">
         <v>747600</v>
@@ -74319,7 +74319,7 @@
         <v>46112</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -74414,7 +74414,7 @@
         <v>46112</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -74509,7 +74509,7 @@
         <v>46112</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -74604,7 +74604,7 @@
         <v>46112</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -74699,7 +74699,7 @@
         <v>46112</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -74794,7 +74794,7 @@
         <v>46112</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -74889,7 +74889,7 @@
         <v>46112</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -74984,7 +74984,7 @@
         <v>46112</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -75079,7 +75079,7 @@
         <v>46112</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -75174,7 +75174,7 @@
         <v>46112</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -75269,7 +75269,7 @@
         <v>46112</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -75344,19 +75344,19 @@
         <v>2647578.37</v>
       </c>
       <c r="Y119" t="n">
-        <v>2647578.37</v>
+        <v>3897578.37</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1250000</v>
       </c>
       <c r="AA119" t="n">
         <v>3627211.32</v>
       </c>
       <c r="AB119" t="n">
-        <v>3627211.32</v>
+        <v>2377211.32</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>-1250000</v>
       </c>
     </row>
     <row r="120">
@@ -75364,7 +75364,7 @@
         <v>46112</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -75459,7 +75459,7 @@
         <v>46112</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -75554,7 +75554,7 @@
         <v>46112</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -75649,7 +75649,7 @@
         <v>46112</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -75744,7 +75744,7 @@
         <v>46112</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -75839,7 +75839,7 @@
         <v>46112</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -75934,7 +75934,7 @@
         <v>46112</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -76029,7 +76029,7 @@
         <v>46112</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -76124,7 +76124,7 @@
         <v>46112</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -76219,7 +76219,7 @@
         <v>46112</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -76314,7 +76314,7 @@
         <v>46112</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>

--- a/Base_Consolidada_SIAFI.xlsx
+++ b/Base_Consolidada_SIAFI.xlsx
@@ -44586,11 +44586,11 @@
     </row>
     <row r="574">
       <c r="A574" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -44663,11 +44663,11 @@
     </row>
     <row r="575">
       <c r="A575" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -44740,11 +44740,11 @@
     </row>
     <row r="576">
       <c r="A576" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -44817,11 +44817,11 @@
     </row>
     <row r="577">
       <c r="A577" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -44894,11 +44894,11 @@
     </row>
     <row r="578">
       <c r="A578" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -44971,11 +44971,11 @@
     </row>
     <row r="579">
       <c r="A579" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -45048,11 +45048,11 @@
     </row>
     <row r="580">
       <c r="A580" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -45125,11 +45125,11 @@
     </row>
     <row r="581">
       <c r="A581" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -45202,11 +45202,11 @@
     </row>
     <row r="582">
       <c r="A582" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -45279,11 +45279,11 @@
     </row>
     <row r="583">
       <c r="A583" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -45356,11 +45356,11 @@
     </row>
     <row r="584">
       <c r="A584" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -45433,11 +45433,11 @@
     </row>
     <row r="585">
       <c r="A585" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -45510,11 +45510,11 @@
     </row>
     <row r="586">
       <c r="A586" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -45587,11 +45587,11 @@
     </row>
     <row r="587">
       <c r="A587" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -45664,11 +45664,11 @@
     </row>
     <row r="588">
       <c r="A588" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -45741,11 +45741,11 @@
     </row>
     <row r="589">
       <c r="A589" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -45818,11 +45818,11 @@
     </row>
     <row r="590">
       <c r="A590" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -45895,11 +45895,11 @@
     </row>
     <row r="591">
       <c r="A591" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -45972,11 +45972,11 @@
     </row>
     <row r="592">
       <c r="A592" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -46049,11 +46049,11 @@
     </row>
     <row r="593">
       <c r="A593" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -46126,11 +46126,11 @@
     </row>
     <row r="594">
       <c r="A594" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -46203,11 +46203,11 @@
     </row>
     <row r="595">
       <c r="A595" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -46280,11 +46280,11 @@
     </row>
     <row r="596">
       <c r="A596" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -46357,11 +46357,11 @@
     </row>
     <row r="597">
       <c r="A597" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -46434,11 +46434,11 @@
     </row>
     <row r="598">
       <c r="A598" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -46511,11 +46511,11 @@
     </row>
     <row r="599">
       <c r="A599" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -46588,11 +46588,11 @@
     </row>
     <row r="600">
       <c r="A600" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -46665,11 +46665,11 @@
     </row>
     <row r="601">
       <c r="A601" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -46742,11 +46742,11 @@
     </row>
     <row r="602">
       <c r="A602" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -46819,11 +46819,11 @@
     </row>
     <row r="603">
       <c r="A603" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -46896,11 +46896,11 @@
     </row>
     <row r="604">
       <c r="A604" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -46973,11 +46973,11 @@
     </row>
     <row r="605">
       <c r="A605" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -47050,11 +47050,11 @@
     </row>
     <row r="606">
       <c r="A606" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -47127,11 +47127,11 @@
     </row>
     <row r="607">
       <c r="A607" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -47204,11 +47204,11 @@
     </row>
     <row r="608">
       <c r="A608" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -47281,11 +47281,11 @@
     </row>
     <row r="609">
       <c r="A609" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -47358,11 +47358,11 @@
     </row>
     <row r="610">
       <c r="A610" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -47435,11 +47435,11 @@
     </row>
     <row r="611">
       <c r="A611" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -47512,11 +47512,11 @@
     </row>
     <row r="612">
       <c r="A612" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -47589,11 +47589,11 @@
     </row>
     <row r="613">
       <c r="A613" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -47666,11 +47666,11 @@
     </row>
     <row r="614">
       <c r="A614" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -47743,11 +47743,11 @@
     </row>
     <row r="615">
       <c r="A615" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -47820,11 +47820,11 @@
     </row>
     <row r="616">
       <c r="A616" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -47897,11 +47897,11 @@
     </row>
     <row r="617">
       <c r="A617" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -47974,11 +47974,11 @@
     </row>
     <row r="618">
       <c r="A618" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -48051,11 +48051,11 @@
     </row>
     <row r="619">
       <c r="A619" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -48128,11 +48128,11 @@
     </row>
     <row r="620">
       <c r="A620" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -48205,11 +48205,11 @@
     </row>
     <row r="621">
       <c r="A621" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -48282,11 +48282,11 @@
     </row>
     <row r="622">
       <c r="A622" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -48359,11 +48359,11 @@
     </row>
     <row r="623">
       <c r="A623" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -48436,11 +48436,11 @@
     </row>
     <row r="624">
       <c r="A624" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -48513,11 +48513,11 @@
     </row>
     <row r="625">
       <c r="A625" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -48590,11 +48590,11 @@
     </row>
     <row r="626">
       <c r="A626" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -48667,11 +48667,11 @@
     </row>
     <row r="627">
       <c r="A627" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -48744,11 +48744,11 @@
     </row>
     <row r="628">
       <c r="A628" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -48821,11 +48821,11 @@
     </row>
     <row r="629">
       <c r="A629" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -48898,11 +48898,11 @@
     </row>
     <row r="630">
       <c r="A630" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -48975,11 +48975,11 @@
     </row>
     <row r="631">
       <c r="A631" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -49052,11 +49052,11 @@
     </row>
     <row r="632">
       <c r="A632" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -49129,11 +49129,11 @@
     </row>
     <row r="633">
       <c r="A633" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -49206,11 +49206,11 @@
     </row>
     <row r="634">
       <c r="A634" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -49283,11 +49283,11 @@
     </row>
     <row r="635">
       <c r="A635" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -49360,11 +49360,11 @@
     </row>
     <row r="636">
       <c r="A636" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -49437,11 +49437,11 @@
     </row>
     <row r="637">
       <c r="A637" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -49514,11 +49514,11 @@
     </row>
     <row r="638">
       <c r="A638" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -49591,11 +49591,11 @@
     </row>
     <row r="639">
       <c r="A639" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -49668,11 +49668,11 @@
     </row>
     <row r="640">
       <c r="A640" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -49745,11 +49745,11 @@
     </row>
     <row r="641">
       <c r="A641" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -49822,11 +49822,11 @@
     </row>
     <row r="642">
       <c r="A642" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -49899,11 +49899,11 @@
     </row>
     <row r="643">
       <c r="A643" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -49976,11 +49976,11 @@
     </row>
     <row r="644">
       <c r="A644" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -50053,11 +50053,11 @@
     </row>
     <row r="645">
       <c r="A645" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -50130,11 +50130,11 @@
     </row>
     <row r="646">
       <c r="A646" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -50207,11 +50207,11 @@
     </row>
     <row r="647">
       <c r="A647" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -50284,11 +50284,11 @@
     </row>
     <row r="648">
       <c r="A648" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -50361,11 +50361,11 @@
     </row>
     <row r="649">
       <c r="A649" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -50438,11 +50438,11 @@
     </row>
     <row r="650">
       <c r="A650" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -50515,11 +50515,11 @@
     </row>
     <row r="651">
       <c r="A651" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -50592,11 +50592,11 @@
     </row>
     <row r="652">
       <c r="A652" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -50669,11 +50669,11 @@
     </row>
     <row r="653">
       <c r="A653" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -50746,11 +50746,11 @@
     </row>
     <row r="654">
       <c r="A654" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -50823,11 +50823,11 @@
     </row>
     <row r="655">
       <c r="A655" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -50900,11 +50900,11 @@
     </row>
     <row r="656">
       <c r="A656" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -50977,11 +50977,11 @@
     </row>
     <row r="657">
       <c r="A657" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -51054,11 +51054,11 @@
     </row>
     <row r="658">
       <c r="A658" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -51131,11 +51131,11 @@
     </row>
     <row r="659">
       <c r="A659" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -51208,11 +51208,11 @@
     </row>
     <row r="660">
       <c r="A660" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -51285,11 +51285,11 @@
     </row>
     <row r="661">
       <c r="A661" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -51362,11 +51362,11 @@
     </row>
     <row r="662">
       <c r="A662" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -51439,11 +51439,11 @@
     </row>
     <row r="663">
       <c r="A663" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -51516,11 +51516,11 @@
     </row>
     <row r="664">
       <c r="A664" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -51593,11 +51593,11 @@
     </row>
     <row r="665">
       <c r="A665" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -51670,11 +51670,11 @@
     </row>
     <row r="666">
       <c r="A666" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -51747,11 +51747,11 @@
     </row>
     <row r="667">
       <c r="A667" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -51824,11 +51824,11 @@
     </row>
     <row r="668">
       <c r="A668" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -51901,11 +51901,11 @@
     </row>
     <row r="669">
       <c r="A669" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -51978,11 +51978,11 @@
     </row>
     <row r="670">
       <c r="A670" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -52055,11 +52055,11 @@
     </row>
     <row r="671">
       <c r="A671" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -52132,11 +52132,11 @@
     </row>
     <row r="672">
       <c r="A672" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -52209,11 +52209,11 @@
     </row>
     <row r="673">
       <c r="A673" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -52286,11 +52286,11 @@
     </row>
     <row r="674">
       <c r="A674" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -52363,11 +52363,11 @@
     </row>
     <row r="675">
       <c r="A675" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -52440,11 +52440,11 @@
     </row>
     <row r="676">
       <c r="A676" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -52517,11 +52517,11 @@
     </row>
     <row r="677">
       <c r="A677" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -52594,11 +52594,11 @@
     </row>
     <row r="678">
       <c r="A678" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -52671,11 +52671,11 @@
     </row>
     <row r="679">
       <c r="A679" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -52748,11 +52748,11 @@
     </row>
     <row r="680">
       <c r="A680" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -52825,11 +52825,11 @@
     </row>
     <row r="681">
       <c r="A681" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -52902,11 +52902,11 @@
     </row>
     <row r="682">
       <c r="A682" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -52979,11 +52979,11 @@
     </row>
     <row r="683">
       <c r="A683" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -53056,11 +53056,11 @@
     </row>
     <row r="684">
       <c r="A684" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -53133,11 +53133,11 @@
     </row>
     <row r="685">
       <c r="A685" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -53210,11 +53210,11 @@
     </row>
     <row r="686">
       <c r="A686" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -53287,11 +53287,11 @@
     </row>
     <row r="687">
       <c r="A687" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -53364,11 +53364,11 @@
     </row>
     <row r="688">
       <c r="A688" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -53441,11 +53441,11 @@
     </row>
     <row r="689">
       <c r="A689" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -53518,11 +53518,11 @@
     </row>
     <row r="690">
       <c r="A690" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -53595,11 +53595,11 @@
     </row>
     <row r="691">
       <c r="A691" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -53672,11 +53672,11 @@
     </row>
     <row r="692">
       <c r="A692" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -53749,11 +53749,11 @@
     </row>
     <row r="693">
       <c r="A693" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -53826,11 +53826,11 @@
     </row>
     <row r="694">
       <c r="A694" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -53903,11 +53903,11 @@
     </row>
     <row r="695">
       <c r="A695" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -53980,11 +53980,11 @@
     </row>
     <row r="696">
       <c r="A696" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -54057,11 +54057,11 @@
     </row>
     <row r="697">
       <c r="A697" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -54134,11 +54134,11 @@
     </row>
     <row r="698">
       <c r="A698" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -54211,11 +54211,11 @@
     </row>
     <row r="699">
       <c r="A699" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -54288,11 +54288,11 @@
     </row>
     <row r="700">
       <c r="A700" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -54365,11 +54365,11 @@
     </row>
     <row r="701">
       <c r="A701" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -54442,11 +54442,11 @@
     </row>
     <row r="702">
       <c r="A702" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -54519,11 +54519,11 @@
     </row>
     <row r="703">
       <c r="A703" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -54596,11 +54596,11 @@
     </row>
     <row r="704">
       <c r="A704" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -54659,10 +54659,10 @@
         <v>0</v>
       </c>
       <c r="R704" t="n">
-        <v>27382974.41</v>
+        <v>27385817.37</v>
       </c>
       <c r="S704" t="n">
-        <v>-27387715.4</v>
+        <v>-27390558.36</v>
       </c>
       <c r="T704" t="n">
         <v>0</v>
@@ -54673,11 +54673,11 @@
     </row>
     <row r="705">
       <c r="A705" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -54736,10 +54736,10 @@
         <v>0</v>
       </c>
       <c r="R705" t="n">
-        <v>88101492.78</v>
+        <v>88104335.73999999</v>
       </c>
       <c r="S705" t="n">
-        <v>6321.96</v>
+        <v>3479</v>
       </c>
       <c r="T705" t="n">
         <v>0</v>
@@ -54750,11 +54750,11 @@
     </row>
     <row r="706">
       <c r="A706" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -54827,11 +54827,11 @@
     </row>
     <row r="707">
       <c r="A707" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -54904,11 +54904,11 @@
     </row>
     <row r="708">
       <c r="A708" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -54981,11 +54981,11 @@
     </row>
     <row r="709">
       <c r="A709" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -55058,11 +55058,11 @@
     </row>
     <row r="710">
       <c r="A710" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -55135,11 +55135,11 @@
     </row>
     <row r="711">
       <c r="A711" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -55212,11 +55212,11 @@
     </row>
     <row r="712">
       <c r="A712" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -55289,11 +55289,11 @@
     </row>
     <row r="713">
       <c r="A713" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -55366,11 +55366,11 @@
     </row>
     <row r="714">
       <c r="A714" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -55443,11 +55443,11 @@
     </row>
     <row r="715">
       <c r="A715" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -55520,11 +55520,11 @@
     </row>
     <row r="716">
       <c r="A716" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -55597,11 +55597,11 @@
     </row>
     <row r="717">
       <c r="A717" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -55674,11 +55674,11 @@
     </row>
     <row r="718">
       <c r="A718" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -55751,11 +55751,11 @@
     </row>
     <row r="719">
       <c r="A719" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -55828,11 +55828,11 @@
     </row>
     <row r="720">
       <c r="A720" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -55905,11 +55905,11 @@
     </row>
     <row r="721">
       <c r="A721" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -55982,11 +55982,11 @@
     </row>
     <row r="722">
       <c r="A722" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -56059,11 +56059,11 @@
     </row>
     <row r="723">
       <c r="A723" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -56136,11 +56136,11 @@
     </row>
     <row r="724">
       <c r="A724" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -56213,11 +56213,11 @@
     </row>
     <row r="725">
       <c r="A725" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -56290,11 +56290,11 @@
     </row>
     <row r="726">
       <c r="A726" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -56367,11 +56367,11 @@
     </row>
     <row r="727">
       <c r="A727" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -56444,11 +56444,11 @@
     </row>
     <row r="728">
       <c r="A728" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -56521,11 +56521,11 @@
     </row>
     <row r="729">
       <c r="A729" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -56590,19 +56590,19 @@
         <v>0</v>
       </c>
       <c r="T729" t="n">
-        <v>0</v>
+        <v>659217</v>
       </c>
       <c r="U729" t="n">
-        <v>1932326</v>
+        <v>1273109</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -56667,19 +56667,19 @@
         <v>-73024</v>
       </c>
       <c r="T730" t="n">
-        <v>0</v>
+        <v>659217</v>
       </c>
       <c r="U730" t="n">
-        <v>0</v>
+        <v>-659217</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -56752,11 +56752,11 @@
     </row>
     <row r="732">
       <c r="A732" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -56829,11 +56829,11 @@
     </row>
     <row r="733">
       <c r="A733" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -56906,11 +56906,11 @@
     </row>
     <row r="734">
       <c r="A734" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -56983,11 +56983,11 @@
     </row>
     <row r="735">
       <c r="A735" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -57060,11 +57060,11 @@
     </row>
     <row r="736">
       <c r="A736" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -57137,11 +57137,11 @@
     </row>
     <row r="737">
       <c r="A737" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -57214,11 +57214,11 @@
     </row>
     <row r="738">
       <c r="A738" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -57291,11 +57291,11 @@
     </row>
     <row r="739">
       <c r="A739" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -57368,11 +57368,11 @@
     </row>
     <row r="740">
       <c r="A740" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -57445,11 +57445,11 @@
     </row>
     <row r="741">
       <c r="A741" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -57522,11 +57522,11 @@
     </row>
     <row r="742">
       <c r="A742" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -57599,11 +57599,11 @@
     </row>
     <row r="743">
       <c r="A743" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -57676,11 +57676,11 @@
     </row>
     <row r="744">
       <c r="A744" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -57753,11 +57753,11 @@
     </row>
     <row r="745">
       <c r="A745" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -57830,11 +57830,11 @@
     </row>
     <row r="746">
       <c r="A746" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -57907,11 +57907,11 @@
     </row>
     <row r="747">
       <c r="A747" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -57984,11 +57984,11 @@
     </row>
     <row r="748">
       <c r="A748" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -58061,11 +58061,11 @@
     </row>
     <row r="749">
       <c r="A749" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -58118,31 +58118,31 @@
         <v>0</v>
       </c>
       <c r="P749" t="n">
-        <v>645574.3199999999</v>
+        <v>711574.3199999999</v>
       </c>
       <c r="Q749" t="n">
-        <v>-645574.3199999999</v>
+        <v>-711574.3199999999</v>
       </c>
       <c r="R749" t="n">
         <v>1684019.12</v>
       </c>
       <c r="S749" t="n">
-        <v>-1038444.8</v>
+        <v>-972444.8</v>
       </c>
       <c r="T749" t="n">
-        <v>8987244.310000001</v>
+        <v>12071244.31</v>
       </c>
       <c r="U749" t="n">
-        <v>-8987244.310000001</v>
+        <v>-12071244.31</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -58195,31 +58195,31 @@
         <v>15388887.32</v>
       </c>
       <c r="P750" t="n">
-        <v>6476543.08</v>
+        <v>6542543.08</v>
       </c>
       <c r="Q750" t="n">
-        <v>8912344.24</v>
+        <v>8846344.24</v>
       </c>
       <c r="R750" t="n">
         <v>5830968.76</v>
       </c>
       <c r="S750" t="n">
-        <v>645574.3199999999</v>
+        <v>711574.3199999999</v>
       </c>
       <c r="T750" t="n">
-        <v>28987244.31</v>
+        <v>32071244.31</v>
       </c>
       <c r="U750" t="n">
-        <v>20108661.76</v>
+        <v>17024661.76</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -58292,11 +58292,11 @@
     </row>
     <row r="752">
       <c r="A752" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -58369,11 +58369,11 @@
     </row>
     <row r="753">
       <c r="A753" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -58446,11 +58446,11 @@
     </row>
     <row r="754">
       <c r="A754" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -58523,11 +58523,11 @@
     </row>
     <row r="755">
       <c r="A755" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -58600,11 +58600,11 @@
     </row>
     <row r="756">
       <c r="A756" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -58677,11 +58677,11 @@
     </row>
     <row r="757">
       <c r="A757" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -58754,11 +58754,11 @@
     </row>
     <row r="758">
       <c r="A758" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -58831,11 +58831,11 @@
     </row>
     <row r="759">
       <c r="A759" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -58908,11 +58908,11 @@
     </row>
     <row r="760">
       <c r="A760" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -58985,11 +58985,11 @@
     </row>
     <row r="761">
       <c r="A761" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -59062,11 +59062,11 @@
     </row>
     <row r="762">
       <c r="A762" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -59139,11 +59139,11 @@
     </row>
     <row r="763">
       <c r="A763" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -59216,11 +59216,11 @@
     </row>
     <row r="764">
       <c r="A764" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -59293,11 +59293,11 @@
     </row>
     <row r="765">
       <c r="A765" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -59370,11 +59370,11 @@
     </row>
     <row r="766">
       <c r="A766" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -59447,11 +59447,11 @@
     </row>
     <row r="767">
       <c r="A767" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -59524,11 +59524,11 @@
     </row>
     <row r="768">
       <c r="A768" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -59601,11 +59601,11 @@
     </row>
     <row r="769">
       <c r="A769" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -59678,11 +59678,11 @@
     </row>
     <row r="770">
       <c r="A770" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -59755,11 +59755,11 @@
     </row>
     <row r="771">
       <c r="A771" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -59832,11 +59832,11 @@
     </row>
     <row r="772">
       <c r="A772" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -59909,11 +59909,11 @@
     </row>
     <row r="773">
       <c r="A773" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -59986,11 +59986,11 @@
     </row>
     <row r="774">
       <c r="A774" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -60063,11 +60063,11 @@
     </row>
     <row r="775">
       <c r="A775" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -60140,11 +60140,11 @@
     </row>
     <row r="776">
       <c r="A776" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -60217,11 +60217,11 @@
     </row>
     <row r="777">
       <c r="A777" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -60294,11 +60294,11 @@
     </row>
     <row r="778">
       <c r="A778" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -60371,11 +60371,11 @@
     </row>
     <row r="779">
       <c r="A779" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -60448,11 +60448,11 @@
     </row>
     <row r="780">
       <c r="A780" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -60525,11 +60525,11 @@
     </row>
     <row r="781">
       <c r="A781" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -60602,11 +60602,11 @@
     </row>
     <row r="782">
       <c r="A782" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -60679,11 +60679,11 @@
     </row>
     <row r="783">
       <c r="A783" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -60756,11 +60756,11 @@
     </row>
     <row r="784">
       <c r="A784" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -60833,11 +60833,11 @@
     </row>
     <row r="785">
       <c r="A785" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -60910,11 +60910,11 @@
     </row>
     <row r="786">
       <c r="A786" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -60987,11 +60987,11 @@
     </row>
     <row r="787">
       <c r="A787" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -61064,11 +61064,11 @@
     </row>
     <row r="788">
       <c r="A788" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -61141,11 +61141,11 @@
     </row>
     <row r="789">
       <c r="A789" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -61218,11 +61218,11 @@
     </row>
     <row r="790">
       <c r="A790" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -61295,11 +61295,11 @@
     </row>
     <row r="791">
       <c r="A791" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -61372,11 +61372,11 @@
     </row>
     <row r="792">
       <c r="A792" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -61449,11 +61449,11 @@
     </row>
     <row r="793">
       <c r="A793" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -61526,11 +61526,11 @@
     </row>
     <row r="794">
       <c r="A794" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -61603,11 +61603,11 @@
     </row>
     <row r="795">
       <c r="A795" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -61680,11 +61680,11 @@
     </row>
     <row r="796">
       <c r="A796" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -61757,11 +61757,11 @@
     </row>
     <row r="797">
       <c r="A797" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -61834,11 +61834,11 @@
     </row>
     <row r="798">
       <c r="A798" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -61911,11 +61911,11 @@
     </row>
     <row r="799">
       <c r="A799" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -61988,11 +61988,11 @@
     </row>
     <row r="800">
       <c r="A800" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -62065,11 +62065,11 @@
     </row>
     <row r="801">
       <c r="A801" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -62142,11 +62142,11 @@
     </row>
     <row r="802">
       <c r="A802" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -62219,11 +62219,11 @@
     </row>
     <row r="803">
       <c r="A803" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -62296,11 +62296,11 @@
     </row>
     <row r="804">
       <c r="A804" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -62373,11 +62373,11 @@
     </row>
     <row r="805">
       <c r="A805" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -62450,11 +62450,11 @@
     </row>
     <row r="806">
       <c r="A806" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -62527,11 +62527,11 @@
     </row>
     <row r="807">
       <c r="A807" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -62604,11 +62604,11 @@
     </row>
     <row r="808">
       <c r="A808" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -62681,11 +62681,11 @@
     </row>
     <row r="809">
       <c r="A809" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -62758,11 +62758,11 @@
     </row>
     <row r="810">
       <c r="A810" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -62835,11 +62835,11 @@
     </row>
     <row r="811">
       <c r="A811" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -62912,11 +62912,11 @@
     </row>
     <row r="812">
       <c r="A812" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -62989,11 +62989,11 @@
     </row>
     <row r="813">
       <c r="A813" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -63066,11 +63066,11 @@
     </row>
     <row r="814">
       <c r="A814" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -63143,11 +63143,11 @@
     </row>
     <row r="815">
       <c r="A815" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -63220,11 +63220,11 @@
     </row>
     <row r="816">
       <c r="A816" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -63297,11 +63297,11 @@
     </row>
     <row r="817">
       <c r="A817" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -63374,11 +63374,11 @@
     </row>
     <row r="818">
       <c r="A818" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -63451,11 +63451,11 @@
     </row>
     <row r="819">
       <c r="A819" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -63528,11 +63528,11 @@
     </row>
     <row r="820">
       <c r="A820" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -63605,11 +63605,11 @@
     </row>
     <row r="821">
       <c r="A821" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -63682,11 +63682,11 @@
     </row>
     <row r="822">
       <c r="A822" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -63759,11 +63759,11 @@
     </row>
     <row r="823">
       <c r="A823" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -63836,11 +63836,11 @@
     </row>
     <row r="824">
       <c r="A824" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -63913,11 +63913,11 @@
     </row>
     <row r="825">
       <c r="A825" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>RELEXORC_23-04-2026.csv</t>
+          <t>RELEXORC_24-04-2026.csv</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -64154,7 +64154,7 @@
         <v>46112</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -64249,7 +64249,7 @@
         <v>46112</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -64344,7 +64344,7 @@
         <v>46112</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -64439,7 +64439,7 @@
         <v>46112</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -64534,7 +64534,7 @@
         <v>46112</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -64629,7 +64629,7 @@
         <v>46112</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -64724,7 +64724,7 @@
         <v>46112</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -64819,7 +64819,7 @@
         <v>46112</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -64914,7 +64914,7 @@
         <v>46112</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -64971,10 +64971,10 @@
         <v>5845968.76</v>
       </c>
       <c r="S10" t="n">
-        <v>6476543.08</v>
+        <v>6542543.08</v>
       </c>
       <c r="T10" t="n">
-        <v>630574.3200000003</v>
+        <v>696574.3200000003</v>
       </c>
       <c r="U10" t="n">
         <v>4367980.05</v>
@@ -64989,19 +64989,19 @@
         <v>27222950.51</v>
       </c>
       <c r="Y10" t="n">
-        <v>28987244.31</v>
+        <v>32071244.31</v>
       </c>
       <c r="Z10" t="n">
-        <v>1764293.799999997</v>
+        <v>4848293.799999997</v>
       </c>
       <c r="AA10" t="n">
         <v>21872955.56</v>
       </c>
       <c r="AB10" t="n">
-        <v>20108661.76</v>
+        <v>17024661.76</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1764293.799999997</v>
+        <v>-4848293.799999997</v>
       </c>
     </row>
     <row r="11">
@@ -65009,7 +65009,7 @@
         <v>46112</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -65104,7 +65104,7 @@
         <v>46112</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -65199,7 +65199,7 @@
         <v>46112</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -65294,7 +65294,7 @@
         <v>46112</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -65389,7 +65389,7 @@
         <v>46112</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -65484,7 +65484,7 @@
         <v>46112</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -65559,19 +65559,19 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>659217</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>659217</v>
       </c>
       <c r="AA16" t="n">
         <v>1932326</v>
       </c>
       <c r="AB16" t="n">
-        <v>1932326</v>
+        <v>1273109</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>-659217</v>
       </c>
     </row>
     <row r="17">
@@ -65579,7 +65579,7 @@
         <v>46112</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -65674,7 +65674,7 @@
         <v>46112</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -65769,7 +65769,7 @@
         <v>46112</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -65835,10 +65835,10 @@
         <v>79635166.11</v>
       </c>
       <c r="V19" t="n">
-        <v>88101492.78</v>
+        <v>88104335.73999999</v>
       </c>
       <c r="W19" t="n">
-        <v>8466326.670000002</v>
+        <v>8469169.629999995</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -65864,7 +65864,7 @@
         <v>46112</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -65959,7 +65959,7 @@
         <v>46112</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -66054,7 +66054,7 @@
         <v>46112</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -66149,7 +66149,7 @@
         <v>46112</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -66244,7 +66244,7 @@
         <v>46112</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -66339,7 +66339,7 @@
         <v>46112</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -66434,7 +66434,7 @@
         <v>46112</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -66529,7 +66529,7 @@
         <v>46112</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -66624,7 +66624,7 @@
         <v>46112</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -66719,7 +66719,7 @@
         <v>46112</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -66814,7 +66814,7 @@
         <v>46112</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -66909,7 +66909,7 @@
         <v>46112</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -67004,7 +67004,7 @@
         <v>46112</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -67099,7 +67099,7 @@
         <v>46112</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -67194,7 +67194,7 @@
         <v>46112</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -67289,7 +67289,7 @@
         <v>46112</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -67384,7 +67384,7 @@
         <v>46112</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -67479,7 +67479,7 @@
         <v>46112</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -67574,7 +67574,7 @@
         <v>46112</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -67669,7 +67669,7 @@
         <v>46112</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -67764,7 +67764,7 @@
         <v>46112</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -67859,7 +67859,7 @@
         <v>46112</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -67954,7 +67954,7 @@
         <v>46112</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -68049,7 +68049,7 @@
         <v>46112</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -68144,7 +68144,7 @@
         <v>46112</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -68239,7 +68239,7 @@
         <v>46112</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -68334,7 +68334,7 @@
         <v>46112</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -68429,7 +68429,7 @@
         <v>46112</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -68524,7 +68524,7 @@
         <v>46112</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -68619,7 +68619,7 @@
         <v>46112</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -68714,7 +68714,7 @@
         <v>46112</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -68809,7 +68809,7 @@
         <v>46112</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -68904,7 +68904,7 @@
         <v>46112</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -68999,7 +68999,7 @@
         <v>46112</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -69094,7 +69094,7 @@
         <v>46112</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -69189,7 +69189,7 @@
         <v>46112</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -69284,7 +69284,7 @@
         <v>46112</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -69379,7 +69379,7 @@
         <v>46112</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -69474,7 +69474,7 @@
         <v>46112</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -69569,7 +69569,7 @@
         <v>46112</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -69664,7 +69664,7 @@
         <v>46112</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -69759,7 +69759,7 @@
         <v>46112</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -69854,7 +69854,7 @@
         <v>46112</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -69949,7 +69949,7 @@
         <v>46112</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -70044,7 +70044,7 @@
         <v>46112</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -70139,7 +70139,7 @@
         <v>46112</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -70234,7 +70234,7 @@
         <v>46112</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -70329,7 +70329,7 @@
         <v>46112</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -70424,7 +70424,7 @@
         <v>46112</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -70519,7 +70519,7 @@
         <v>46112</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -70614,7 +70614,7 @@
         <v>46112</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -70709,7 +70709,7 @@
         <v>46112</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -70804,7 +70804,7 @@
         <v>46112</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -70899,7 +70899,7 @@
         <v>46112</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -70994,7 +70994,7 @@
         <v>46112</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -71089,7 +71089,7 @@
         <v>46112</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -71184,7 +71184,7 @@
         <v>46112</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -71279,7 +71279,7 @@
         <v>46112</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -71374,7 +71374,7 @@
         <v>46112</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -71469,7 +71469,7 @@
         <v>46112</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -71564,7 +71564,7 @@
         <v>46112</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -71659,7 +71659,7 @@
         <v>46112</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -71754,7 +71754,7 @@
         <v>46112</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -71849,7 +71849,7 @@
         <v>46112</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -71944,7 +71944,7 @@
         <v>46112</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -72039,7 +72039,7 @@
         <v>46112</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -72134,7 +72134,7 @@
         <v>46112</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -72229,7 +72229,7 @@
         <v>46112</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -72324,7 +72324,7 @@
         <v>46112</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -72419,7 +72419,7 @@
         <v>46112</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -72514,7 +72514,7 @@
         <v>46112</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -72609,7 +72609,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -72704,7 +72704,7 @@
         <v>46112</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -72799,7 +72799,7 @@
         <v>46112</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -72894,7 +72894,7 @@
         <v>46112</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -72989,7 +72989,7 @@
         <v>46112</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -73084,7 +73084,7 @@
         <v>46112</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -73179,7 +73179,7 @@
         <v>46112</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -73274,7 +73274,7 @@
         <v>46112</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -73369,7 +73369,7 @@
         <v>46112</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -73464,7 +73464,7 @@
         <v>46112</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -73559,7 +73559,7 @@
         <v>46112</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -73654,7 +73654,7 @@
         <v>46112</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -73749,7 +73749,7 @@
         <v>46112</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -73844,7 +73844,7 @@
         <v>46112</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -73939,7 +73939,7 @@
         <v>46112</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -74034,7 +74034,7 @@
         <v>46112</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -74129,7 +74129,7 @@
         <v>46112</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -74224,7 +74224,7 @@
         <v>46112</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -74319,7 +74319,7 @@
         <v>46112</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -74414,7 +74414,7 @@
         <v>46112</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -74509,7 +74509,7 @@
         <v>46112</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -74604,7 +74604,7 @@
         <v>46112</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -74699,7 +74699,7 @@
         <v>46112</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -74794,7 +74794,7 @@
         <v>46112</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -74889,7 +74889,7 @@
         <v>46112</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -74984,7 +74984,7 @@
         <v>46112</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -75079,7 +75079,7 @@
         <v>46112</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -75174,7 +75174,7 @@
         <v>46112</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -75269,7 +75269,7 @@
         <v>46112</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -75364,7 +75364,7 @@
         <v>46112</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -75459,7 +75459,7 @@
         <v>46112</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -75554,7 +75554,7 @@
         <v>46112</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -75649,7 +75649,7 @@
         <v>46112</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -75744,7 +75744,7 @@
         <v>46112</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -75839,7 +75839,7 @@
         <v>46112</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -75934,7 +75934,7 @@
         <v>46112</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -76029,7 +76029,7 @@
         <v>46112</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -76124,7 +76124,7 @@
         <v>46112</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -76219,7 +76219,7 @@
         <v>46112</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -76314,7 +76314,7 @@
         <v>46112</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>

--- a/Base_Consolidada_SIAFI.xlsx
+++ b/Base_Consolidada_SIAFI.xlsx
@@ -44586,11 +44586,11 @@
     </row>
     <row r="574">
       <c r="A574" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -44663,11 +44663,11 @@
     </row>
     <row r="575">
       <c r="A575" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -44740,11 +44740,11 @@
     </row>
     <row r="576">
       <c r="A576" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -44817,11 +44817,11 @@
     </row>
     <row r="577">
       <c r="A577" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -44894,11 +44894,11 @@
     </row>
     <row r="578">
       <c r="A578" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -44971,11 +44971,11 @@
     </row>
     <row r="579">
       <c r="A579" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -45048,11 +45048,11 @@
     </row>
     <row r="580">
       <c r="A580" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -45125,11 +45125,11 @@
     </row>
     <row r="581">
       <c r="A581" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -45202,11 +45202,11 @@
     </row>
     <row r="582">
       <c r="A582" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -45279,11 +45279,11 @@
     </row>
     <row r="583">
       <c r="A583" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -45336,16 +45336,16 @@
         <v>0</v>
       </c>
       <c r="P583" t="n">
-        <v>0</v>
+        <v>1348665.89</v>
       </c>
       <c r="Q583" t="n">
-        <v>0</v>
+        <v>-1348665.89</v>
       </c>
       <c r="R583" t="n">
         <v>0</v>
       </c>
       <c r="S583" t="n">
-        <v>0</v>
+        <v>1348665.89</v>
       </c>
       <c r="T583" t="n">
         <v>0</v>
@@ -45356,11 +45356,11 @@
     </row>
     <row r="584">
       <c r="A584" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -45433,11 +45433,11 @@
     </row>
     <row r="585">
       <c r="A585" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -45490,16 +45490,16 @@
         <v>3304906.16</v>
       </c>
       <c r="P585" t="n">
-        <v>1956240.27</v>
+        <v>3304906.16</v>
       </c>
       <c r="Q585" t="n">
-        <v>1348665.89</v>
+        <v>0</v>
       </c>
       <c r="R585" t="n">
         <v>1956240.27</v>
       </c>
       <c r="S585" t="n">
-        <v>0</v>
+        <v>1348665.89</v>
       </c>
       <c r="T585" t="n">
         <v>0</v>
@@ -45510,11 +45510,11 @@
     </row>
     <row r="586">
       <c r="A586" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -45587,11 +45587,11 @@
     </row>
     <row r="587">
       <c r="A587" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -45664,11 +45664,11 @@
     </row>
     <row r="588">
       <c r="A588" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -45741,11 +45741,11 @@
     </row>
     <row r="589">
       <c r="A589" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -45818,11 +45818,11 @@
     </row>
     <row r="590">
       <c r="A590" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -45895,11 +45895,11 @@
     </row>
     <row r="591">
       <c r="A591" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -45972,11 +45972,11 @@
     </row>
     <row r="592">
       <c r="A592" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -46049,11 +46049,11 @@
     </row>
     <row r="593">
       <c r="A593" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -46126,11 +46126,11 @@
     </row>
     <row r="594">
       <c r="A594" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -46203,11 +46203,11 @@
     </row>
     <row r="595">
       <c r="A595" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -46260,16 +46260,16 @@
         <v>59000</v>
       </c>
       <c r="P595" t="n">
-        <v>81696</v>
+        <v>273851.88</v>
       </c>
       <c r="Q595" t="n">
-        <v>-22696</v>
+        <v>-214851.88</v>
       </c>
       <c r="R595" t="n">
         <v>2427764.33</v>
       </c>
       <c r="S595" t="n">
-        <v>-2346068.33</v>
+        <v>-2153912.45</v>
       </c>
       <c r="T595" t="n">
         <v>5530000</v>
@@ -46280,11 +46280,11 @@
     </row>
     <row r="596">
       <c r="A596" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -46337,16 +46337,16 @@
         <v>13469211.52</v>
       </c>
       <c r="P596" t="n">
-        <v>9145517.82</v>
+        <v>9337673.699999999</v>
       </c>
       <c r="Q596" t="n">
-        <v>4323693.699999999</v>
+        <v>4131537.82</v>
       </c>
       <c r="R596" t="n">
         <v>9063821.82</v>
       </c>
       <c r="S596" t="n">
-        <v>81696</v>
+        <v>273851.88</v>
       </c>
       <c r="T596" t="n">
         <v>11861411.46</v>
@@ -46357,11 +46357,11 @@
     </row>
     <row r="597">
       <c r="A597" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -46414,16 +46414,16 @@
         <v>0</v>
       </c>
       <c r="P597" t="n">
-        <v>149232.9</v>
+        <v>150986.07</v>
       </c>
       <c r="Q597" t="n">
-        <v>-149232.9</v>
+        <v>-150986.07</v>
       </c>
       <c r="R597" t="n">
         <v>223121.17</v>
       </c>
       <c r="S597" t="n">
-        <v>-73888.27</v>
+        <v>-72135.10000000001</v>
       </c>
       <c r="T597" t="n">
         <v>0</v>
@@ -46434,11 +46434,11 @@
     </row>
     <row r="598">
       <c r="A598" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -46491,16 +46491,16 @@
         <v>1257262.46</v>
       </c>
       <c r="P598" t="n">
-        <v>813676.15</v>
+        <v>815429.3199999999</v>
       </c>
       <c r="Q598" t="n">
-        <v>443586.3099999999</v>
+        <v>441833.14</v>
       </c>
       <c r="R598" t="n">
         <v>664443.25</v>
       </c>
       <c r="S598" t="n">
-        <v>149232.9</v>
+        <v>150986.07</v>
       </c>
       <c r="T598" t="n">
         <v>415791.82</v>
@@ -46511,11 +46511,11 @@
     </row>
     <row r="599">
       <c r="A599" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -46588,11 +46588,11 @@
     </row>
     <row r="600">
       <c r="A600" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -46665,11 +46665,11 @@
     </row>
     <row r="601">
       <c r="A601" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -46742,11 +46742,11 @@
     </row>
     <row r="602">
       <c r="A602" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -46819,11 +46819,11 @@
     </row>
     <row r="603">
       <c r="A603" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -46896,11 +46896,11 @@
     </row>
     <row r="604">
       <c r="A604" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -46973,11 +46973,11 @@
     </row>
     <row r="605">
       <c r="A605" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -47050,11 +47050,11 @@
     </row>
     <row r="606">
       <c r="A606" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -47127,11 +47127,11 @@
     </row>
     <row r="607">
       <c r="A607" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -47204,11 +47204,11 @@
     </row>
     <row r="608">
       <c r="A608" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -47281,11 +47281,11 @@
     </row>
     <row r="609">
       <c r="A609" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -47358,11 +47358,11 @@
     </row>
     <row r="610">
       <c r="A610" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -47435,11 +47435,11 @@
     </row>
     <row r="611">
       <c r="A611" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -47512,11 +47512,11 @@
     </row>
     <row r="612">
       <c r="A612" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -47589,11 +47589,11 @@
     </row>
     <row r="613">
       <c r="A613" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -47666,11 +47666,11 @@
     </row>
     <row r="614">
       <c r="A614" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -47743,11 +47743,11 @@
     </row>
     <row r="615">
       <c r="A615" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -47820,11 +47820,11 @@
     </row>
     <row r="616">
       <c r="A616" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -47897,11 +47897,11 @@
     </row>
     <row r="617">
       <c r="A617" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -47974,11 +47974,11 @@
     </row>
     <row r="618">
       <c r="A618" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -48051,11 +48051,11 @@
     </row>
     <row r="619">
       <c r="A619" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -48128,11 +48128,11 @@
     </row>
     <row r="620">
       <c r="A620" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -48205,11 +48205,11 @@
     </row>
     <row r="621">
       <c r="A621" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -48282,11 +48282,11 @@
     </row>
     <row r="622">
       <c r="A622" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -48359,11 +48359,11 @@
     </row>
     <row r="623">
       <c r="A623" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -48436,11 +48436,11 @@
     </row>
     <row r="624">
       <c r="A624" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -48513,11 +48513,11 @@
     </row>
     <row r="625">
       <c r="A625" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -48590,11 +48590,11 @@
     </row>
     <row r="626">
       <c r="A626" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -48667,11 +48667,11 @@
     </row>
     <row r="627">
       <c r="A627" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -48744,11 +48744,11 @@
     </row>
     <row r="628">
       <c r="A628" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -48821,11 +48821,11 @@
     </row>
     <row r="629">
       <c r="A629" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -48898,11 +48898,11 @@
     </row>
     <row r="630">
       <c r="A630" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -48975,11 +48975,11 @@
     </row>
     <row r="631">
       <c r="A631" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -49052,11 +49052,11 @@
     </row>
     <row r="632">
       <c r="A632" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -49129,11 +49129,11 @@
     </row>
     <row r="633">
       <c r="A633" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -49206,11 +49206,11 @@
     </row>
     <row r="634">
       <c r="A634" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -49283,11 +49283,11 @@
     </row>
     <row r="635">
       <c r="A635" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -49360,11 +49360,11 @@
     </row>
     <row r="636">
       <c r="A636" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -49437,11 +49437,11 @@
     </row>
     <row r="637">
       <c r="A637" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -49514,11 +49514,11 @@
     </row>
     <row r="638">
       <c r="A638" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -49591,11 +49591,11 @@
     </row>
     <row r="639">
       <c r="A639" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -49668,11 +49668,11 @@
     </row>
     <row r="640">
       <c r="A640" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -49745,11 +49745,11 @@
     </row>
     <row r="641">
       <c r="A641" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -49822,11 +49822,11 @@
     </row>
     <row r="642">
       <c r="A642" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -49899,11 +49899,11 @@
     </row>
     <row r="643">
       <c r="A643" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -49976,11 +49976,11 @@
     </row>
     <row r="644">
       <c r="A644" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -50053,11 +50053,11 @@
     </row>
     <row r="645">
       <c r="A645" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -50130,11 +50130,11 @@
     </row>
     <row r="646">
       <c r="A646" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -50207,11 +50207,11 @@
     </row>
     <row r="647">
       <c r="A647" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -50284,11 +50284,11 @@
     </row>
     <row r="648">
       <c r="A648" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -50341,16 +50341,16 @@
         <v>0</v>
       </c>
       <c r="P648" t="n">
-        <v>141627.67</v>
+        <v>321906.56</v>
       </c>
       <c r="Q648" t="n">
-        <v>-141627.67</v>
+        <v>-321906.56</v>
       </c>
       <c r="R648" t="n">
         <v>641209.77</v>
       </c>
       <c r="S648" t="n">
-        <v>-499582.1</v>
+        <v>-319303.21</v>
       </c>
       <c r="T648" t="n">
         <v>851081.28</v>
@@ -50361,11 +50361,11 @@
     </row>
     <row r="649">
       <c r="A649" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -50418,16 +50418,16 @@
         <v>2601132.4</v>
       </c>
       <c r="P649" t="n">
-        <v>2061626.98</v>
+        <v>2241905.87</v>
       </c>
       <c r="Q649" t="n">
-        <v>539505.4199999999</v>
+        <v>359226.5299999998</v>
       </c>
       <c r="R649" t="n">
         <v>1919999.31</v>
       </c>
       <c r="S649" t="n">
-        <v>141627.67</v>
+        <v>321906.56</v>
       </c>
       <c r="T649" t="n">
         <v>1851081.28</v>
@@ -50438,11 +50438,11 @@
     </row>
     <row r="650">
       <c r="A650" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -50515,11 +50515,11 @@
     </row>
     <row r="651">
       <c r="A651" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -50592,11 +50592,11 @@
     </row>
     <row r="652">
       <c r="A652" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -50669,11 +50669,11 @@
     </row>
     <row r="653">
       <c r="A653" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -50746,11 +50746,11 @@
     </row>
     <row r="654">
       <c r="A654" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -50823,11 +50823,11 @@
     </row>
     <row r="655">
       <c r="A655" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -50900,11 +50900,11 @@
     </row>
     <row r="656">
       <c r="A656" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -50977,11 +50977,11 @@
     </row>
     <row r="657">
       <c r="A657" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -51054,11 +51054,11 @@
     </row>
     <row r="658">
       <c r="A658" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -51131,11 +51131,11 @@
     </row>
     <row r="659">
       <c r="A659" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -51208,11 +51208,11 @@
     </row>
     <row r="660">
       <c r="A660" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -51265,16 +51265,16 @@
         <v>0</v>
       </c>
       <c r="P660" t="n">
-        <v>3395990.62</v>
+        <v>3617990.62</v>
       </c>
       <c r="Q660" t="n">
-        <v>-3395990.62</v>
+        <v>-3617990.62</v>
       </c>
       <c r="R660" t="n">
         <v>1382898.62</v>
       </c>
       <c r="S660" t="n">
-        <v>2013092</v>
+        <v>2235092</v>
       </c>
       <c r="T660" t="n">
         <v>0</v>
@@ -51285,11 +51285,11 @@
     </row>
     <row r="661">
       <c r="A661" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -51342,16 +51342,16 @@
         <v>11419975.46</v>
       </c>
       <c r="P661" t="n">
-        <v>8275523.54</v>
+        <v>8497523.539999999</v>
       </c>
       <c r="Q661" t="n">
-        <v>3144451.920000001</v>
+        <v>2922451.920000002</v>
       </c>
       <c r="R661" t="n">
         <v>4890221.78</v>
       </c>
       <c r="S661" t="n">
-        <v>3385301.76</v>
+        <v>3607301.76</v>
       </c>
       <c r="T661" t="n">
         <v>15000000</v>
@@ -51362,11 +51362,11 @@
     </row>
     <row r="662">
       <c r="A662" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -51439,11 +51439,11 @@
     </row>
     <row r="663">
       <c r="A663" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -51516,11 +51516,11 @@
     </row>
     <row r="664">
       <c r="A664" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -51593,11 +51593,11 @@
     </row>
     <row r="665">
       <c r="A665" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -51670,11 +51670,11 @@
     </row>
     <row r="666">
       <c r="A666" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -51747,11 +51747,11 @@
     </row>
     <row r="667">
       <c r="A667" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -51824,11 +51824,11 @@
     </row>
     <row r="668">
       <c r="A668" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -51901,11 +51901,11 @@
     </row>
     <row r="669">
       <c r="A669" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -51978,11 +51978,11 @@
     </row>
     <row r="670">
       <c r="A670" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -52055,11 +52055,11 @@
     </row>
     <row r="671">
       <c r="A671" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -52132,11 +52132,11 @@
     </row>
     <row r="672">
       <c r="A672" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -52209,11 +52209,11 @@
     </row>
     <row r="673">
       <c r="A673" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -52286,11 +52286,11 @@
     </row>
     <row r="674">
       <c r="A674" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -52363,11 +52363,11 @@
     </row>
     <row r="675">
       <c r="A675" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -52440,11 +52440,11 @@
     </row>
     <row r="676">
       <c r="A676" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -52517,11 +52517,11 @@
     </row>
     <row r="677">
       <c r="A677" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -52594,11 +52594,11 @@
     </row>
     <row r="678">
       <c r="A678" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -52671,11 +52671,11 @@
     </row>
     <row r="679">
       <c r="A679" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -52748,11 +52748,11 @@
     </row>
     <row r="680">
       <c r="A680" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -52825,11 +52825,11 @@
     </row>
     <row r="681">
       <c r="A681" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -52902,11 +52902,11 @@
     </row>
     <row r="682">
       <c r="A682" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -52979,11 +52979,11 @@
     </row>
     <row r="683">
       <c r="A683" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -53056,11 +53056,11 @@
     </row>
     <row r="684">
       <c r="A684" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -53133,11 +53133,11 @@
     </row>
     <row r="685">
       <c r="A685" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -53210,11 +53210,11 @@
     </row>
     <row r="686">
       <c r="A686" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -53287,11 +53287,11 @@
     </row>
     <row r="687">
       <c r="A687" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -53364,11 +53364,11 @@
     </row>
     <row r="688">
       <c r="A688" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -53441,11 +53441,11 @@
     </row>
     <row r="689">
       <c r="A689" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -53518,11 +53518,11 @@
     </row>
     <row r="690">
       <c r="A690" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -53595,11 +53595,11 @@
     </row>
     <row r="691">
       <c r="A691" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -53672,11 +53672,11 @@
     </row>
     <row r="692">
       <c r="A692" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -53749,11 +53749,11 @@
     </row>
     <row r="693">
       <c r="A693" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -53826,11 +53826,11 @@
     </row>
     <row r="694">
       <c r="A694" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -53903,11 +53903,11 @@
     </row>
     <row r="695">
       <c r="A695" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -53980,11 +53980,11 @@
     </row>
     <row r="696">
       <c r="A696" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -54057,11 +54057,11 @@
     </row>
     <row r="697">
       <c r="A697" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -54134,11 +54134,11 @@
     </row>
     <row r="698">
       <c r="A698" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -54211,11 +54211,11 @@
     </row>
     <row r="699">
       <c r="A699" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -54288,11 +54288,11 @@
     </row>
     <row r="700">
       <c r="A700" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -54365,11 +54365,11 @@
     </row>
     <row r="701">
       <c r="A701" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -54442,11 +54442,11 @@
     </row>
     <row r="702">
       <c r="A702" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -54519,11 +54519,11 @@
     </row>
     <row r="703">
       <c r="A703" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -54596,11 +54596,11 @@
     </row>
     <row r="704">
       <c r="A704" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -54673,11 +54673,11 @@
     </row>
     <row r="705">
       <c r="A705" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -54750,11 +54750,11 @@
     </row>
     <row r="706">
       <c r="A706" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -54827,11 +54827,11 @@
     </row>
     <row r="707">
       <c r="A707" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -54904,11 +54904,11 @@
     </row>
     <row r="708">
       <c r="A708" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -54981,11 +54981,11 @@
     </row>
     <row r="709">
       <c r="A709" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -55058,11 +55058,11 @@
     </row>
     <row r="710">
       <c r="A710" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -55135,11 +55135,11 @@
     </row>
     <row r="711">
       <c r="A711" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -55212,11 +55212,11 @@
     </row>
     <row r="712">
       <c r="A712" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -55289,11 +55289,11 @@
     </row>
     <row r="713">
       <c r="A713" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -55366,11 +55366,11 @@
     </row>
     <row r="714">
       <c r="A714" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -55443,11 +55443,11 @@
     </row>
     <row r="715">
       <c r="A715" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -55520,11 +55520,11 @@
     </row>
     <row r="716">
       <c r="A716" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -55597,11 +55597,11 @@
     </row>
     <row r="717">
       <c r="A717" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -55674,11 +55674,11 @@
     </row>
     <row r="718">
       <c r="A718" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -55751,11 +55751,11 @@
     </row>
     <row r="719">
       <c r="A719" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -55828,11 +55828,11 @@
     </row>
     <row r="720">
       <c r="A720" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -55905,11 +55905,11 @@
     </row>
     <row r="721">
       <c r="A721" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -55982,11 +55982,11 @@
     </row>
     <row r="722">
       <c r="A722" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -56059,11 +56059,11 @@
     </row>
     <row r="723">
       <c r="A723" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -56136,11 +56136,11 @@
     </row>
     <row r="724">
       <c r="A724" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -56213,11 +56213,11 @@
     </row>
     <row r="725">
       <c r="A725" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -56290,11 +56290,11 @@
     </row>
     <row r="726">
       <c r="A726" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -56367,11 +56367,11 @@
     </row>
     <row r="727">
       <c r="A727" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -56444,11 +56444,11 @@
     </row>
     <row r="728">
       <c r="A728" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -56521,11 +56521,11 @@
     </row>
     <row r="729">
       <c r="A729" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -56598,11 +56598,11 @@
     </row>
     <row r="730">
       <c r="A730" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -56675,11 +56675,11 @@
     </row>
     <row r="731">
       <c r="A731" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -56752,11 +56752,11 @@
     </row>
     <row r="732">
       <c r="A732" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -56829,11 +56829,11 @@
     </row>
     <row r="733">
       <c r="A733" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -56906,11 +56906,11 @@
     </row>
     <row r="734">
       <c r="A734" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -56983,11 +56983,11 @@
     </row>
     <row r="735">
       <c r="A735" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -57060,11 +57060,11 @@
     </row>
     <row r="736">
       <c r="A736" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -57137,11 +57137,11 @@
     </row>
     <row r="737">
       <c r="A737" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -57214,11 +57214,11 @@
     </row>
     <row r="738">
       <c r="A738" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -57291,11 +57291,11 @@
     </row>
     <row r="739">
       <c r="A739" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -57368,11 +57368,11 @@
     </row>
     <row r="740">
       <c r="A740" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -57445,11 +57445,11 @@
     </row>
     <row r="741">
       <c r="A741" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -57522,11 +57522,11 @@
     </row>
     <row r="742">
       <c r="A742" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -57599,11 +57599,11 @@
     </row>
     <row r="743">
       <c r="A743" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -57676,11 +57676,11 @@
     </row>
     <row r="744">
       <c r="A744" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -57753,11 +57753,11 @@
     </row>
     <row r="745">
       <c r="A745" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -57830,11 +57830,11 @@
     </row>
     <row r="746">
       <c r="A746" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -57887,16 +57887,16 @@
         <v>0</v>
       </c>
       <c r="P746" t="n">
-        <v>0</v>
+        <v>1863</v>
       </c>
       <c r="Q746" t="n">
-        <v>0</v>
+        <v>-1863</v>
       </c>
       <c r="R746" t="n">
         <v>0</v>
       </c>
       <c r="S746" t="n">
-        <v>0</v>
+        <v>1863</v>
       </c>
       <c r="T746" t="n">
         <v>0</v>
@@ -57907,11 +57907,11 @@
     </row>
     <row r="747">
       <c r="A747" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -57984,11 +57984,11 @@
     </row>
     <row r="748">
       <c r="A748" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -58061,11 +58061,11 @@
     </row>
     <row r="749">
       <c r="A749" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -58118,16 +58118,16 @@
         <v>0</v>
       </c>
       <c r="P749" t="n">
-        <v>711574.3199999999</v>
+        <v>810074.16</v>
       </c>
       <c r="Q749" t="n">
-        <v>-711574.3199999999</v>
+        <v>-810074.16</v>
       </c>
       <c r="R749" t="n">
         <v>1684019.12</v>
       </c>
       <c r="S749" t="n">
-        <v>-972444.8</v>
+        <v>-873944.96</v>
       </c>
       <c r="T749" t="n">
         <v>12071244.31</v>
@@ -58138,11 +58138,11 @@
     </row>
     <row r="750">
       <c r="A750" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -58195,16 +58195,16 @@
         <v>15388887.32</v>
       </c>
       <c r="P750" t="n">
-        <v>6542543.08</v>
+        <v>6641042.92</v>
       </c>
       <c r="Q750" t="n">
-        <v>8846344.24</v>
+        <v>8747844.4</v>
       </c>
       <c r="R750" t="n">
         <v>5830968.76</v>
       </c>
       <c r="S750" t="n">
-        <v>711574.3199999999</v>
+        <v>810074.16</v>
       </c>
       <c r="T750" t="n">
         <v>32071244.31</v>
@@ -58215,11 +58215,11 @@
     </row>
     <row r="751">
       <c r="A751" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -58292,11 +58292,11 @@
     </row>
     <row r="752">
       <c r="A752" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -58369,11 +58369,11 @@
     </row>
     <row r="753">
       <c r="A753" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -58426,16 +58426,16 @@
         <v>17136.8</v>
       </c>
       <c r="P753" t="n">
-        <v>6930</v>
+        <v>9462.6</v>
       </c>
       <c r="Q753" t="n">
-        <v>10206.8</v>
+        <v>7674.199999999999</v>
       </c>
       <c r="R753" t="n">
         <v>1080</v>
       </c>
       <c r="S753" t="n">
-        <v>5850</v>
+        <v>8382.6</v>
       </c>
       <c r="T753" t="n">
         <v>0</v>
@@ -58446,11 +58446,11 @@
     </row>
     <row r="754">
       <c r="A754" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -58503,16 +58503,16 @@
         <v>93592.39999999999</v>
       </c>
       <c r="P754" t="n">
-        <v>44382.6</v>
+        <v>46915.2</v>
       </c>
       <c r="Q754" t="n">
-        <v>49209.8</v>
+        <v>46677.2</v>
       </c>
       <c r="R754" t="n">
         <v>1452.6</v>
       </c>
       <c r="S754" t="n">
-        <v>42930</v>
+        <v>45462.6</v>
       </c>
       <c r="T754" t="n">
         <v>0</v>
@@ -58523,11 +58523,11 @@
     </row>
     <row r="755">
       <c r="A755" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -58600,11 +58600,11 @@
     </row>
     <row r="756">
       <c r="A756" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -58677,11 +58677,11 @@
     </row>
     <row r="757">
       <c r="A757" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -58754,11 +58754,11 @@
     </row>
     <row r="758">
       <c r="A758" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -58831,11 +58831,11 @@
     </row>
     <row r="759">
       <c r="A759" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -58908,11 +58908,11 @@
     </row>
     <row r="760">
       <c r="A760" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -58965,16 +58965,16 @@
         <v>4230</v>
       </c>
       <c r="P760" t="n">
-        <v>2367</v>
+        <v>4230</v>
       </c>
       <c r="Q760" t="n">
-        <v>1863</v>
+        <v>0</v>
       </c>
       <c r="R760" t="n">
         <v>2367</v>
       </c>
       <c r="S760" t="n">
-        <v>0</v>
+        <v>1863</v>
       </c>
       <c r="T760" t="n">
         <v>0</v>
@@ -58985,11 +58985,11 @@
     </row>
     <row r="761">
       <c r="A761" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -59062,11 +59062,11 @@
     </row>
     <row r="762">
       <c r="A762" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -59139,11 +59139,11 @@
     </row>
     <row r="763">
       <c r="A763" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -59216,11 +59216,11 @@
     </row>
     <row r="764">
       <c r="A764" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -59293,11 +59293,11 @@
     </row>
     <row r="765">
       <c r="A765" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -59370,11 +59370,11 @@
     </row>
     <row r="766">
       <c r="A766" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -59447,11 +59447,11 @@
     </row>
     <row r="767">
       <c r="A767" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -59524,11 +59524,11 @@
     </row>
     <row r="768">
       <c r="A768" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -59601,11 +59601,11 @@
     </row>
     <row r="769">
       <c r="A769" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -59678,11 +59678,11 @@
     </row>
     <row r="770">
       <c r="A770" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -59755,11 +59755,11 @@
     </row>
     <row r="771">
       <c r="A771" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -59832,11 +59832,11 @@
     </row>
     <row r="772">
       <c r="A772" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -59909,11 +59909,11 @@
     </row>
     <row r="773">
       <c r="A773" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -59963,10 +59963,10 @@
         <v>0</v>
       </c>
       <c r="O773" t="n">
-        <v>3350</v>
+        <v>341</v>
       </c>
       <c r="P773" t="n">
-        <v>33661.5</v>
+        <v>30652.5</v>
       </c>
       <c r="Q773" t="n">
         <v>-30311.5</v>
@@ -59975,22 +59975,22 @@
         <v>61472.5</v>
       </c>
       <c r="S773" t="n">
-        <v>-27811</v>
+        <v>-30820</v>
       </c>
       <c r="T773" t="n">
         <v>0</v>
       </c>
       <c r="U773" t="n">
-        <v>-3350</v>
+        <v>-341</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -60040,10 +60040,10 @@
         <v>0</v>
       </c>
       <c r="O774" t="n">
-        <v>157611.5</v>
+        <v>154602.5</v>
       </c>
       <c r="P774" t="n">
-        <v>157611.5</v>
+        <v>154602.5</v>
       </c>
       <c r="Q774" t="n">
         <v>0</v>
@@ -60052,22 +60052,22 @@
         <v>151252.5</v>
       </c>
       <c r="S774" t="n">
-        <v>6359</v>
+        <v>3350</v>
       </c>
       <c r="T774" t="n">
         <v>0</v>
       </c>
       <c r="U774" t="n">
-        <v>23333.3</v>
+        <v>26342.3</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -60140,11 +60140,11 @@
     </row>
     <row r="776">
       <c r="A776" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -60217,11 +60217,11 @@
     </row>
     <row r="777">
       <c r="A777" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -60294,11 +60294,11 @@
     </row>
     <row r="778">
       <c r="A778" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -60371,11 +60371,11 @@
     </row>
     <row r="779">
       <c r="A779" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -60448,11 +60448,11 @@
     </row>
     <row r="780">
       <c r="A780" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -60525,11 +60525,11 @@
     </row>
     <row r="781">
       <c r="A781" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -60602,11 +60602,11 @@
     </row>
     <row r="782">
       <c r="A782" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -60679,11 +60679,11 @@
     </row>
     <row r="783">
       <c r="A783" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -60756,11 +60756,11 @@
     </row>
     <row r="784">
       <c r="A784" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -60833,11 +60833,11 @@
     </row>
     <row r="785">
       <c r="A785" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -60910,11 +60910,11 @@
     </row>
     <row r="786">
       <c r="A786" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -60987,11 +60987,11 @@
     </row>
     <row r="787">
       <c r="A787" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -61064,11 +61064,11 @@
     </row>
     <row r="788">
       <c r="A788" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -61141,11 +61141,11 @@
     </row>
     <row r="789">
       <c r="A789" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -61218,11 +61218,11 @@
     </row>
     <row r="790">
       <c r="A790" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -61295,11 +61295,11 @@
     </row>
     <row r="791">
       <c r="A791" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -61372,11 +61372,11 @@
     </row>
     <row r="792">
       <c r="A792" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -61449,11 +61449,11 @@
     </row>
     <row r="793">
       <c r="A793" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -61526,11 +61526,11 @@
     </row>
     <row r="794">
       <c r="A794" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -61603,11 +61603,11 @@
     </row>
     <row r="795">
       <c r="A795" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -61680,11 +61680,11 @@
     </row>
     <row r="796">
       <c r="A796" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -61757,11 +61757,11 @@
     </row>
     <row r="797">
       <c r="A797" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -61834,11 +61834,11 @@
     </row>
     <row r="798">
       <c r="A798" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -61911,11 +61911,11 @@
     </row>
     <row r="799">
       <c r="A799" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -61988,11 +61988,11 @@
     </row>
     <row r="800">
       <c r="A800" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -62065,11 +62065,11 @@
     </row>
     <row r="801">
       <c r="A801" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -62142,11 +62142,11 @@
     </row>
     <row r="802">
       <c r="A802" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -62219,11 +62219,11 @@
     </row>
     <row r="803">
       <c r="A803" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -62296,11 +62296,11 @@
     </row>
     <row r="804">
       <c r="A804" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -62373,11 +62373,11 @@
     </row>
     <row r="805">
       <c r="A805" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -62450,11 +62450,11 @@
     </row>
     <row r="806">
       <c r="A806" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -62527,11 +62527,11 @@
     </row>
     <row r="807">
       <c r="A807" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -62604,11 +62604,11 @@
     </row>
     <row r="808">
       <c r="A808" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -62681,11 +62681,11 @@
     </row>
     <row r="809">
       <c r="A809" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -62758,11 +62758,11 @@
     </row>
     <row r="810">
       <c r="A810" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -62835,11 +62835,11 @@
     </row>
     <row r="811">
       <c r="A811" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -62912,11 +62912,11 @@
     </row>
     <row r="812">
       <c r="A812" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -62989,11 +62989,11 @@
     </row>
     <row r="813">
       <c r="A813" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -63046,16 +63046,16 @@
         <v>0</v>
       </c>
       <c r="P813" t="n">
-        <v>38535</v>
+        <v>49335</v>
       </c>
       <c r="Q813" t="n">
-        <v>-38535</v>
+        <v>-49335</v>
       </c>
       <c r="R813" t="n">
         <v>3690</v>
       </c>
       <c r="S813" t="n">
-        <v>34845</v>
+        <v>45645</v>
       </c>
       <c r="T813" t="n">
         <v>0</v>
@@ -63066,11 +63066,11 @@
     </row>
     <row r="814">
       <c r="A814" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -63123,16 +63123,16 @@
         <v>242268.6</v>
       </c>
       <c r="P814" t="n">
-        <v>72945</v>
+        <v>83745</v>
       </c>
       <c r="Q814" t="n">
-        <v>169323.6</v>
+        <v>158523.6</v>
       </c>
       <c r="R814" t="n">
         <v>33222</v>
       </c>
       <c r="S814" t="n">
-        <v>39723</v>
+        <v>50523</v>
       </c>
       <c r="T814" t="n">
         <v>0</v>
@@ -63143,11 +63143,11 @@
     </row>
     <row r="815">
       <c r="A815" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -63220,11 +63220,11 @@
     </row>
     <row r="816">
       <c r="A816" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -63297,11 +63297,11 @@
     </row>
     <row r="817">
       <c r="A817" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -63374,11 +63374,11 @@
     </row>
     <row r="818">
       <c r="A818" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -63451,11 +63451,11 @@
     </row>
     <row r="819">
       <c r="A819" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -63528,11 +63528,11 @@
     </row>
     <row r="820">
       <c r="A820" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -63605,11 +63605,11 @@
     </row>
     <row r="821">
       <c r="A821" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -63682,11 +63682,11 @@
     </row>
     <row r="822">
       <c r="A822" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -63759,11 +63759,11 @@
     </row>
     <row r="823">
       <c r="A823" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -63836,11 +63836,11 @@
     </row>
     <row r="824">
       <c r="A824" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -63913,11 +63913,11 @@
     </row>
     <row r="825">
       <c r="A825" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>RELEXORC_24-04-2026.csv</t>
+          <t>RELEXORC_27-04-2026.csv</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -64154,7 +64154,7 @@
         <v>46112</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -64249,7 +64249,7 @@
         <v>46112</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -64344,7 +64344,7 @@
         <v>46112</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -64439,7 +64439,7 @@
         <v>46112</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -64534,7 +64534,7 @@
         <v>46112</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -64629,7 +64629,7 @@
         <v>46112</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -64724,7 +64724,7 @@
         <v>46112</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -64781,10 +64781,10 @@
         <v>2367</v>
       </c>
       <c r="S8" t="n">
-        <v>2367</v>
+        <v>4230</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1863</v>
       </c>
       <c r="U8" t="n">
         <v>2367</v>
@@ -64819,7 +64819,7 @@
         <v>46112</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -64914,7 +64914,7 @@
         <v>46112</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -64971,10 +64971,10 @@
         <v>5845968.76</v>
       </c>
       <c r="S10" t="n">
-        <v>6542543.08</v>
+        <v>6641042.92</v>
       </c>
       <c r="T10" t="n">
-        <v>696574.3200000003</v>
+        <v>795074.1600000001</v>
       </c>
       <c r="U10" t="n">
         <v>4367980.05</v>
@@ -65009,7 +65009,7 @@
         <v>46112</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -65104,7 +65104,7 @@
         <v>46112</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -65161,10 +65161,10 @@
         <v>38532.6</v>
       </c>
       <c r="S12" t="n">
-        <v>44382.6</v>
+        <v>46915.2</v>
       </c>
       <c r="T12" t="n">
-        <v>5850</v>
+        <v>8382.599999999999</v>
       </c>
       <c r="U12" t="n">
         <v>372.6</v>
@@ -65199,7 +65199,7 @@
         <v>46112</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -65294,7 +65294,7 @@
         <v>46112</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -65389,7 +65389,7 @@
         <v>46112</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -65484,7 +65484,7 @@
         <v>46112</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -65579,7 +65579,7 @@
         <v>46112</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -65674,7 +65674,7 @@
         <v>46112</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -65769,7 +65769,7 @@
         <v>46112</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -65864,7 +65864,7 @@
         <v>46112</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -65959,7 +65959,7 @@
         <v>46112</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -66054,7 +66054,7 @@
         <v>46112</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -66149,7 +66149,7 @@
         <v>46112</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -66244,7 +66244,7 @@
         <v>46112</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -66339,7 +66339,7 @@
         <v>46112</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -66434,7 +66434,7 @@
         <v>46112</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -66529,7 +66529,7 @@
         <v>46112</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -66624,7 +66624,7 @@
         <v>46112</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -66719,7 +66719,7 @@
         <v>46112</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -66814,7 +66814,7 @@
         <v>46112</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -66909,7 +66909,7 @@
         <v>46112</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -67004,7 +67004,7 @@
         <v>46112</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -67099,7 +67099,7 @@
         <v>46112</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -67194,7 +67194,7 @@
         <v>46112</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -67289,7 +67289,7 @@
         <v>46112</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -67384,7 +67384,7 @@
         <v>46112</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -67479,7 +67479,7 @@
         <v>46112</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -67574,7 +67574,7 @@
         <v>46112</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -67669,7 +67669,7 @@
         <v>46112</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -67764,7 +67764,7 @@
         <v>46112</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -67859,7 +67859,7 @@
         <v>46112</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -67954,7 +67954,7 @@
         <v>46112</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -68011,10 +68011,10 @@
         <v>46014</v>
       </c>
       <c r="S42" t="n">
-        <v>72945</v>
+        <v>83745</v>
       </c>
       <c r="T42" t="n">
-        <v>26931</v>
+        <v>37731</v>
       </c>
       <c r="U42" t="n">
         <v>29532</v>
@@ -68049,7 +68049,7 @@
         <v>46112</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -68144,7 +68144,7 @@
         <v>46112</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -68239,7 +68239,7 @@
         <v>46112</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -68334,7 +68334,7 @@
         <v>46112</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -68429,7 +68429,7 @@
         <v>46112</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -68524,7 +68524,7 @@
         <v>46112</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -68619,7 +68619,7 @@
         <v>46112</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -68714,7 +68714,7 @@
         <v>46112</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -68809,7 +68809,7 @@
         <v>46112</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -68904,7 +68904,7 @@
         <v>46112</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -68999,7 +68999,7 @@
         <v>46112</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -69094,7 +69094,7 @@
         <v>46112</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -69142,19 +69142,19 @@
         <v>154261.5</v>
       </c>
       <c r="P54" t="n">
-        <v>157611.5</v>
+        <v>154602.5</v>
       </c>
       <c r="Q54" t="n">
-        <v>3350</v>
+        <v>341</v>
       </c>
       <c r="R54" t="n">
         <v>146221.5</v>
       </c>
       <c r="S54" t="n">
-        <v>157611.5</v>
+        <v>154602.5</v>
       </c>
       <c r="T54" t="n">
-        <v>11390</v>
+        <v>8381</v>
       </c>
       <c r="U54" t="n">
         <v>123950</v>
@@ -69178,10 +69178,10 @@
         <v>26683.3</v>
       </c>
       <c r="AB54" t="n">
-        <v>23333.3</v>
+        <v>26342.3</v>
       </c>
       <c r="AC54" t="n">
-        <v>-3350</v>
+        <v>-341</v>
       </c>
     </row>
     <row r="55">
@@ -69189,7 +69189,7 @@
         <v>46112</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -69284,7 +69284,7 @@
         <v>46112</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -69379,7 +69379,7 @@
         <v>46112</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -69474,7 +69474,7 @@
         <v>46112</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -69569,7 +69569,7 @@
         <v>46112</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -69664,7 +69664,7 @@
         <v>46112</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -69759,7 +69759,7 @@
         <v>46112</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -69854,7 +69854,7 @@
         <v>46112</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -69949,7 +69949,7 @@
         <v>46112</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -70044,7 +70044,7 @@
         <v>46112</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -70139,7 +70139,7 @@
         <v>46112</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -70234,7 +70234,7 @@
         <v>46112</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -70329,7 +70329,7 @@
         <v>46112</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -70424,7 +70424,7 @@
         <v>46112</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -70519,7 +70519,7 @@
         <v>46112</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -70614,7 +70614,7 @@
         <v>46112</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -70709,7 +70709,7 @@
         <v>46112</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -70804,7 +70804,7 @@
         <v>46112</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -70899,7 +70899,7 @@
         <v>46112</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -70994,7 +70994,7 @@
         <v>46112</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -71089,7 +71089,7 @@
         <v>46112</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -71184,7 +71184,7 @@
         <v>46112</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -71279,7 +71279,7 @@
         <v>46112</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -71374,7 +71374,7 @@
         <v>46112</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -71469,7 +71469,7 @@
         <v>46112</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -71564,7 +71564,7 @@
         <v>46112</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -71659,7 +71659,7 @@
         <v>46112</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -71754,7 +71754,7 @@
         <v>46112</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -71849,7 +71849,7 @@
         <v>46112</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -71944,7 +71944,7 @@
         <v>46112</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -72039,7 +72039,7 @@
         <v>46112</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -72134,7 +72134,7 @@
         <v>46112</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -72229,7 +72229,7 @@
         <v>46112</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -72324,7 +72324,7 @@
         <v>46112</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -72381,10 +72381,10 @@
         <v>1956240.27</v>
       </c>
       <c r="S88" t="n">
-        <v>1956240.27</v>
+        <v>3304906.16</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>1348665.89</v>
       </c>
       <c r="U88" t="n">
         <v>1956240.27</v>
@@ -72419,7 +72419,7 @@
         <v>46112</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -72514,7 +72514,7 @@
         <v>46112</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -72609,7 +72609,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -72704,7 +72704,7 @@
         <v>46112</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -72799,7 +72799,7 @@
         <v>46112</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -72894,7 +72894,7 @@
         <v>46112</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -72951,10 +72951,10 @@
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>9145517.82</v>
+        <v>9337673.699999999</v>
       </c>
       <c r="T94" t="n">
-        <v>9145517.82</v>
+        <v>9337673.699999999</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -72989,7 +72989,7 @@
         <v>46112</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -73084,7 +73084,7 @@
         <v>46112</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -73141,10 +73141,10 @@
         <v>664443.25</v>
       </c>
       <c r="S96" t="n">
-        <v>813676.15</v>
+        <v>815429.3199999999</v>
       </c>
       <c r="T96" t="n">
-        <v>149232.9</v>
+        <v>150986.0699999999</v>
       </c>
       <c r="U96" t="n">
         <v>441322.08</v>
@@ -73179,7 +73179,7 @@
         <v>46112</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -73274,7 +73274,7 @@
         <v>46112</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -73369,7 +73369,7 @@
         <v>46112</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -73464,7 +73464,7 @@
         <v>46112</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -73559,7 +73559,7 @@
         <v>46112</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -73654,7 +73654,7 @@
         <v>46112</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -73749,7 +73749,7 @@
         <v>46112</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -73844,7 +73844,7 @@
         <v>46112</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -73939,7 +73939,7 @@
         <v>46112</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -74034,7 +74034,7 @@
         <v>46112</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -74129,7 +74129,7 @@
         <v>46112</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -74224,7 +74224,7 @@
         <v>46112</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -74319,7 +74319,7 @@
         <v>46112</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -74414,7 +74414,7 @@
         <v>46112</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -74509,7 +74509,7 @@
         <v>46112</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -74604,7 +74604,7 @@
         <v>46112</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -74699,7 +74699,7 @@
         <v>46112</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -74794,7 +74794,7 @@
         <v>46112</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -74889,7 +74889,7 @@
         <v>46112</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -74984,7 +74984,7 @@
         <v>46112</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -75079,7 +75079,7 @@
         <v>46112</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -75174,7 +75174,7 @@
         <v>46112</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -75269,7 +75269,7 @@
         <v>46112</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -75364,7 +75364,7 @@
         <v>46112</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -75459,7 +75459,7 @@
         <v>46112</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -75554,7 +75554,7 @@
         <v>46112</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -75611,10 +75611,10 @@
         <v>1919999.31</v>
       </c>
       <c r="S122" t="n">
-        <v>2061626.98</v>
+        <v>2241905.87</v>
       </c>
       <c r="T122" t="n">
-        <v>141627.6699999999</v>
+        <v>321906.5600000001</v>
       </c>
       <c r="U122" t="n">
         <v>1278789.54</v>
@@ -75649,7 +75649,7 @@
         <v>46112</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -75744,7 +75744,7 @@
         <v>46112</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -75839,7 +75839,7 @@
         <v>46112</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -75934,7 +75934,7 @@
         <v>46112</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -76029,7 +76029,7 @@
         <v>46112</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -76124,7 +76124,7 @@
         <v>46112</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -76181,10 +76181,10 @@
         <v>5657120.12</v>
       </c>
       <c r="S128" t="n">
-        <v>8275523.54</v>
+        <v>8497523.539999999</v>
       </c>
       <c r="T128" t="n">
-        <v>2618403.42</v>
+        <v>2840403.419999999</v>
       </c>
       <c r="U128" t="n">
         <v>3507323.16</v>
@@ -76219,7 +76219,7 @@
         <v>46112</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -76314,7 +76314,7 @@
         <v>46112</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>

--- a/Base_Consolidada_SIAFI.xlsx
+++ b/Base_Consolidada_SIAFI.xlsx
@@ -44586,11 +44586,11 @@
     </row>
     <row r="574">
       <c r="A574" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -44663,11 +44663,11 @@
     </row>
     <row r="575">
       <c r="A575" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -44740,11 +44740,11 @@
     </row>
     <row r="576">
       <c r="A576" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -44817,11 +44817,11 @@
     </row>
     <row r="577">
       <c r="A577" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -44894,11 +44894,11 @@
     </row>
     <row r="578">
       <c r="A578" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -44971,11 +44971,11 @@
     </row>
     <row r="579">
       <c r="A579" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -45048,11 +45048,11 @@
     </row>
     <row r="580">
       <c r="A580" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -45125,11 +45125,11 @@
     </row>
     <row r="581">
       <c r="A581" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -45202,11 +45202,11 @@
     </row>
     <row r="582">
       <c r="A582" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -45279,11 +45279,11 @@
     </row>
     <row r="583">
       <c r="A583" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -45356,11 +45356,11 @@
     </row>
     <row r="584">
       <c r="A584" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -45433,11 +45433,11 @@
     </row>
     <row r="585">
       <c r="A585" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -45510,11 +45510,11 @@
     </row>
     <row r="586">
       <c r="A586" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -45587,11 +45587,11 @@
     </row>
     <row r="587">
       <c r="A587" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -45664,11 +45664,11 @@
     </row>
     <row r="588">
       <c r="A588" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -45741,11 +45741,11 @@
     </row>
     <row r="589">
       <c r="A589" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -45818,11 +45818,11 @@
     </row>
     <row r="590">
       <c r="A590" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -45895,11 +45895,11 @@
     </row>
     <row r="591">
       <c r="A591" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -45972,11 +45972,11 @@
     </row>
     <row r="592">
       <c r="A592" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -46049,11 +46049,11 @@
     </row>
     <row r="593">
       <c r="A593" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -46126,11 +46126,11 @@
     </row>
     <row r="594">
       <c r="A594" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -46203,11 +46203,11 @@
     </row>
     <row r="595">
       <c r="A595" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -46260,16 +46260,16 @@
         <v>59000</v>
       </c>
       <c r="P595" t="n">
-        <v>273851.88</v>
+        <v>354060.21</v>
       </c>
       <c r="Q595" t="n">
-        <v>-214851.88</v>
+        <v>-295060.21</v>
       </c>
       <c r="R595" t="n">
         <v>2427764.33</v>
       </c>
       <c r="S595" t="n">
-        <v>-2153912.45</v>
+        <v>-2073704.12</v>
       </c>
       <c r="T595" t="n">
         <v>5530000</v>
@@ -46280,11 +46280,11 @@
     </row>
     <row r="596">
       <c r="A596" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -46337,16 +46337,16 @@
         <v>13469211.52</v>
       </c>
       <c r="P596" t="n">
-        <v>9337673.699999999</v>
+        <v>9417882.029999999</v>
       </c>
       <c r="Q596" t="n">
-        <v>4131537.82</v>
+        <v>4051329.49</v>
       </c>
       <c r="R596" t="n">
         <v>9063821.82</v>
       </c>
       <c r="S596" t="n">
-        <v>273851.88</v>
+        <v>354060.21</v>
       </c>
       <c r="T596" t="n">
         <v>11861411.46</v>
@@ -46357,11 +46357,11 @@
     </row>
     <row r="597">
       <c r="A597" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -46434,11 +46434,11 @@
     </row>
     <row r="598">
       <c r="A598" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -46511,11 +46511,11 @@
     </row>
     <row r="599">
       <c r="A599" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -46588,11 +46588,11 @@
     </row>
     <row r="600">
       <c r="A600" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -46665,11 +46665,11 @@
     </row>
     <row r="601">
       <c r="A601" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -46742,11 +46742,11 @@
     </row>
     <row r="602">
       <c r="A602" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -46819,11 +46819,11 @@
     </row>
     <row r="603">
       <c r="A603" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -46896,11 +46896,11 @@
     </row>
     <row r="604">
       <c r="A604" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -46959,10 +46959,10 @@
         <v>0</v>
       </c>
       <c r="R604" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="S604" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T604" t="n">
         <v>0</v>
@@ -46973,11 +46973,11 @@
     </row>
     <row r="605">
       <c r="A605" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -47050,11 +47050,11 @@
     </row>
     <row r="606">
       <c r="A606" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -47127,11 +47127,11 @@
     </row>
     <row r="607">
       <c r="A607" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -47204,11 +47204,11 @@
     </row>
     <row r="608">
       <c r="A608" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -47281,11 +47281,11 @@
     </row>
     <row r="609">
       <c r="A609" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -47358,11 +47358,11 @@
     </row>
     <row r="610">
       <c r="A610" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -47435,11 +47435,11 @@
     </row>
     <row r="611">
       <c r="A611" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -47512,11 +47512,11 @@
     </row>
     <row r="612">
       <c r="A612" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -47589,11 +47589,11 @@
     </row>
     <row r="613">
       <c r="A613" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -47666,11 +47666,11 @@
     </row>
     <row r="614">
       <c r="A614" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -47743,11 +47743,11 @@
     </row>
     <row r="615">
       <c r="A615" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -47820,11 +47820,11 @@
     </row>
     <row r="616">
       <c r="A616" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -47897,11 +47897,11 @@
     </row>
     <row r="617">
       <c r="A617" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -47960,10 +47960,10 @@
         <v>-5000</v>
       </c>
       <c r="R617" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="S617" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T617" t="n">
         <v>0</v>
@@ -47974,11 +47974,11 @@
     </row>
     <row r="618">
       <c r="A618" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -48037,10 +48037,10 @@
         <v>0</v>
       </c>
       <c r="R618" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="S618" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T618" t="n">
         <v>0</v>
@@ -48051,11 +48051,11 @@
     </row>
     <row r="619">
       <c r="A619" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -48114,10 +48114,10 @@
         <v>-5000</v>
       </c>
       <c r="R619" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="S619" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T619" t="n">
         <v>0</v>
@@ -48128,11 +48128,11 @@
     </row>
     <row r="620">
       <c r="A620" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -48191,10 +48191,10 @@
         <v>0</v>
       </c>
       <c r="R620" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="S620" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T620" t="n">
         <v>0</v>
@@ -48205,11 +48205,11 @@
     </row>
     <row r="621">
       <c r="A621" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -48268,10 +48268,10 @@
         <v>0</v>
       </c>
       <c r="R621" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="S621" t="n">
-        <v>-5000</v>
+        <v>-10000</v>
       </c>
       <c r="T621" t="n">
         <v>0</v>
@@ -48282,11 +48282,11 @@
     </row>
     <row r="622">
       <c r="A622" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -48345,10 +48345,10 @@
         <v>0</v>
       </c>
       <c r="R622" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="S622" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T622" t="n">
         <v>0</v>
@@ -48359,11 +48359,11 @@
     </row>
     <row r="623">
       <c r="A623" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -48422,10 +48422,10 @@
         <v>0</v>
       </c>
       <c r="R623" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="S623" t="n">
-        <v>-5000</v>
+        <v>-10000</v>
       </c>
       <c r="T623" t="n">
         <v>0</v>
@@ -48436,11 +48436,11 @@
     </row>
     <row r="624">
       <c r="A624" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -48499,10 +48499,10 @@
         <v>0</v>
       </c>
       <c r="R624" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="S624" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T624" t="n">
         <v>0</v>
@@ -48513,11 +48513,11 @@
     </row>
     <row r="625">
       <c r="A625" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -48590,11 +48590,11 @@
     </row>
     <row r="626">
       <c r="A626" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -48667,11 +48667,11 @@
     </row>
     <row r="627">
       <c r="A627" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -48744,11 +48744,11 @@
     </row>
     <row r="628">
       <c r="A628" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -48821,11 +48821,11 @@
     </row>
     <row r="629">
       <c r="A629" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -48884,10 +48884,10 @@
         <v>-5000</v>
       </c>
       <c r="R629" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="S629" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T629" t="n">
         <v>0</v>
@@ -48898,11 +48898,11 @@
     </row>
     <row r="630">
       <c r="A630" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -48961,10 +48961,10 @@
         <v>0</v>
       </c>
       <c r="R630" t="n">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="S630" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T630" t="n">
         <v>0</v>
@@ -48975,11 +48975,11 @@
     </row>
     <row r="631">
       <c r="A631" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -49052,11 +49052,11 @@
     </row>
     <row r="632">
       <c r="A632" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -49129,11 +49129,11 @@
     </row>
     <row r="633">
       <c r="A633" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -49206,11 +49206,11 @@
     </row>
     <row r="634">
       <c r="A634" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -49283,11 +49283,11 @@
     </row>
     <row r="635">
       <c r="A635" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -49360,11 +49360,11 @@
     </row>
     <row r="636">
       <c r="A636" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -49437,11 +49437,11 @@
     </row>
     <row r="637">
       <c r="A637" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -49500,10 +49500,10 @@
         <v>0</v>
       </c>
       <c r="R637" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="S637" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="T637" t="n">
         <v>0</v>
@@ -49514,11 +49514,11 @@
     </row>
     <row r="638">
       <c r="A638" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -49591,11 +49591,11 @@
     </row>
     <row r="639">
       <c r="A639" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -49668,11 +49668,11 @@
     </row>
     <row r="640">
       <c r="A640" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -49745,11 +49745,11 @@
     </row>
     <row r="641">
       <c r="A641" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -49822,11 +49822,11 @@
     </row>
     <row r="642">
       <c r="A642" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -49899,11 +49899,11 @@
     </row>
     <row r="643">
       <c r="A643" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -49976,11 +49976,11 @@
     </row>
     <row r="644">
       <c r="A644" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -50053,11 +50053,11 @@
     </row>
     <row r="645">
       <c r="A645" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -50130,11 +50130,11 @@
     </row>
     <row r="646">
       <c r="A646" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -50207,11 +50207,11 @@
     </row>
     <row r="647">
       <c r="A647" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -50284,11 +50284,11 @@
     </row>
     <row r="648">
       <c r="A648" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -50361,11 +50361,11 @@
     </row>
     <row r="649">
       <c r="A649" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -50438,11 +50438,11 @@
     </row>
     <row r="650">
       <c r="A650" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -50501,10 +50501,10 @@
         <v>-66</v>
       </c>
       <c r="R650" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="S650" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="T650" t="n">
         <v>0</v>
@@ -50515,11 +50515,11 @@
     </row>
     <row r="651">
       <c r="A651" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -50592,11 +50592,11 @@
     </row>
     <row r="652">
       <c r="A652" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -50649,16 +50649,16 @@
         <v>0</v>
       </c>
       <c r="P652" t="n">
-        <v>11100.98</v>
+        <v>16651.47</v>
       </c>
       <c r="Q652" t="n">
-        <v>-11100.98</v>
+        <v>-16651.47</v>
       </c>
       <c r="R652" t="n">
         <v>5550.49</v>
       </c>
       <c r="S652" t="n">
-        <v>5550.49</v>
+        <v>11100.98</v>
       </c>
       <c r="T652" t="n">
         <v>0</v>
@@ -50669,11 +50669,11 @@
     </row>
     <row r="653">
       <c r="A653" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -50726,16 +50726,16 @@
         <v>22151.37</v>
       </c>
       <c r="P653" t="n">
-        <v>16600.88</v>
+        <v>22151.37</v>
       </c>
       <c r="Q653" t="n">
-        <v>5550.489999999998</v>
+        <v>0</v>
       </c>
       <c r="R653" t="n">
         <v>11050.39</v>
       </c>
       <c r="S653" t="n">
-        <v>5550.49</v>
+        <v>11100.98</v>
       </c>
       <c r="T653" t="n">
         <v>0</v>
@@ -50746,11 +50746,11 @@
     </row>
     <row r="654">
       <c r="A654" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -50823,11 +50823,11 @@
     </row>
     <row r="655">
       <c r="A655" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -50900,11 +50900,11 @@
     </row>
     <row r="656">
       <c r="A656" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -50977,11 +50977,11 @@
     </row>
     <row r="657">
       <c r="A657" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -51054,11 +51054,11 @@
     </row>
     <row r="658">
       <c r="A658" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -51131,11 +51131,11 @@
     </row>
     <row r="659">
       <c r="A659" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -51208,11 +51208,11 @@
     </row>
     <row r="660">
       <c r="A660" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -51285,11 +51285,11 @@
     </row>
     <row r="661">
       <c r="A661" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -51362,11 +51362,11 @@
     </row>
     <row r="662">
       <c r="A662" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -51439,11 +51439,11 @@
     </row>
     <row r="663">
       <c r="A663" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -51502,10 +51502,10 @@
         <v>-5000</v>
       </c>
       <c r="R663" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="S663" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T663" t="n">
         <v>0</v>
@@ -51516,11 +51516,11 @@
     </row>
     <row r="664">
       <c r="A664" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -51593,11 +51593,11 @@
     </row>
     <row r="665">
       <c r="A665" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -51670,11 +51670,11 @@
     </row>
     <row r="666">
       <c r="A666" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -51747,11 +51747,11 @@
     </row>
     <row r="667">
       <c r="A667" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -51824,11 +51824,11 @@
     </row>
     <row r="668">
       <c r="A668" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -51901,11 +51901,11 @@
     </row>
     <row r="669">
       <c r="A669" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -51978,11 +51978,11 @@
     </row>
     <row r="670">
       <c r="A670" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -52055,11 +52055,11 @@
     </row>
     <row r="671">
       <c r="A671" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -52132,11 +52132,11 @@
     </row>
     <row r="672">
       <c r="A672" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -52209,11 +52209,11 @@
     </row>
     <row r="673">
       <c r="A673" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -52286,11 +52286,11 @@
     </row>
     <row r="674">
       <c r="A674" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -52363,11 +52363,11 @@
     </row>
     <row r="675">
       <c r="A675" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -52440,11 +52440,11 @@
     </row>
     <row r="676">
       <c r="A676" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -52517,11 +52517,11 @@
     </row>
     <row r="677">
       <c r="A677" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -52594,11 +52594,11 @@
     </row>
     <row r="678">
       <c r="A678" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -52671,11 +52671,11 @@
     </row>
     <row r="679">
       <c r="A679" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -52748,11 +52748,11 @@
     </row>
     <row r="680">
       <c r="A680" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -52825,11 +52825,11 @@
     </row>
     <row r="681">
       <c r="A681" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -52902,11 +52902,11 @@
     </row>
     <row r="682">
       <c r="A682" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -52979,11 +52979,11 @@
     </row>
     <row r="683">
       <c r="A683" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -53056,11 +53056,11 @@
     </row>
     <row r="684">
       <c r="A684" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -53133,11 +53133,11 @@
     </row>
     <row r="685">
       <c r="A685" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -53190,16 +53190,16 @@
         <v>7000</v>
       </c>
       <c r="P685" t="n">
-        <v>551700</v>
+        <v>553900</v>
       </c>
       <c r="Q685" t="n">
-        <v>-544700</v>
+        <v>-546900</v>
       </c>
       <c r="R685" t="n">
         <v>381000</v>
       </c>
       <c r="S685" t="n">
-        <v>170700</v>
+        <v>172900</v>
       </c>
       <c r="T685" t="n">
         <v>0</v>
@@ -53210,11 +53210,11 @@
     </row>
     <row r="686">
       <c r="A686" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -53267,16 +53267,16 @@
         <v>2085400</v>
       </c>
       <c r="P686" t="n">
-        <v>1513300</v>
+        <v>1515500</v>
       </c>
       <c r="Q686" t="n">
-        <v>572100</v>
+        <v>569900</v>
       </c>
       <c r="R686" t="n">
         <v>1128600</v>
       </c>
       <c r="S686" t="n">
-        <v>384700</v>
+        <v>386900</v>
       </c>
       <c r="T686" t="n">
         <v>0</v>
@@ -53287,11 +53287,11 @@
     </row>
     <row r="687">
       <c r="A687" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -53364,11 +53364,11 @@
     </row>
     <row r="688">
       <c r="A688" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -53441,11 +53441,11 @@
     </row>
     <row r="689">
       <c r="A689" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -53518,11 +53518,11 @@
     </row>
     <row r="690">
       <c r="A690" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -53595,11 +53595,11 @@
     </row>
     <row r="691">
       <c r="A691" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -53672,11 +53672,11 @@
     </row>
     <row r="692">
       <c r="A692" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -53749,11 +53749,11 @@
     </row>
     <row r="693">
       <c r="A693" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -53826,11 +53826,11 @@
     </row>
     <row r="694">
       <c r="A694" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -53903,11 +53903,11 @@
     </row>
     <row r="695">
       <c r="A695" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -53980,11 +53980,11 @@
     </row>
     <row r="696">
       <c r="A696" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -54057,11 +54057,11 @@
     </row>
     <row r="697">
       <c r="A697" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -54134,11 +54134,11 @@
     </row>
     <row r="698">
       <c r="A698" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -54211,11 +54211,11 @@
     </row>
     <row r="699">
       <c r="A699" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -54288,11 +54288,11 @@
     </row>
     <row r="700">
       <c r="A700" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -54365,11 +54365,11 @@
     </row>
     <row r="701">
       <c r="A701" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -54419,10 +54419,10 @@
         <v>32000000</v>
       </c>
       <c r="O701" t="n">
-        <v>7563495.42</v>
+        <v>10225424.25</v>
       </c>
       <c r="P701" t="n">
-        <v>7563495.42</v>
+        <v>10225424.25</v>
       </c>
       <c r="Q701" t="n">
         <v>0</v>
@@ -54431,22 +54431,22 @@
         <v>7547516.79</v>
       </c>
       <c r="S701" t="n">
-        <v>15978.63</v>
+        <v>2677907.46</v>
       </c>
       <c r="T701" t="n">
         <v>0</v>
       </c>
       <c r="U701" t="n">
-        <v>24436504.58</v>
+        <v>21774575.75</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -54496,10 +54496,10 @@
         <v>0</v>
       </c>
       <c r="O702" t="n">
-        <v>0</v>
+        <v>14714.66</v>
       </c>
       <c r="P702" t="n">
-        <v>0</v>
+        <v>14714.66</v>
       </c>
       <c r="Q702" t="n">
         <v>0</v>
@@ -54508,22 +54508,22 @@
         <v>14714.66</v>
       </c>
       <c r="S702" t="n">
+        <v>0</v>
+      </c>
+      <c r="T702" t="n">
+        <v>0</v>
+      </c>
+      <c r="U702" t="n">
         <v>-14714.66</v>
-      </c>
-      <c r="T702" t="n">
-        <v>0</v>
-      </c>
-      <c r="U702" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -54573,10 +54573,10 @@
         <v>150000</v>
       </c>
       <c r="O703" t="n">
-        <v>44143.98</v>
+        <v>58858.64</v>
       </c>
       <c r="P703" t="n">
-        <v>44143.98</v>
+        <v>58858.64</v>
       </c>
       <c r="Q703" t="n">
         <v>0</v>
@@ -54585,22 +54585,22 @@
         <v>44143.98</v>
       </c>
       <c r="S703" t="n">
-        <v>0</v>
+        <v>14714.66</v>
       </c>
       <c r="T703" t="n">
         <v>0</v>
       </c>
       <c r="U703" t="n">
-        <v>105856.02</v>
+        <v>91141.36</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -54650,10 +54650,10 @@
         <v>0</v>
       </c>
       <c r="O704" t="n">
-        <v>-4740.99</v>
+        <v>27897863.37</v>
       </c>
       <c r="P704" t="n">
-        <v>-4740.99</v>
+        <v>27897863.37</v>
       </c>
       <c r="Q704" t="n">
         <v>0</v>
@@ -54662,22 +54662,22 @@
         <v>27385817.37</v>
       </c>
       <c r="S704" t="n">
-        <v>-27390558.36</v>
+        <v>512046</v>
       </c>
       <c r="T704" t="n">
         <v>0</v>
       </c>
       <c r="U704" t="n">
-        <v>4740.99</v>
+        <v>-27897863.37</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -54727,10 +54727,10 @@
         <v>366557343</v>
       </c>
       <c r="O705" t="n">
-        <v>88107814.73999999</v>
+        <v>116010419.1</v>
       </c>
       <c r="P705" t="n">
-        <v>88107814.73999999</v>
+        <v>116010419.1</v>
       </c>
       <c r="Q705" t="n">
         <v>0</v>
@@ -54739,22 +54739,22 @@
         <v>88104335.73999999</v>
       </c>
       <c r="S705" t="n">
-        <v>3479</v>
+        <v>27906083.36</v>
       </c>
       <c r="T705" t="n">
         <v>0</v>
       </c>
       <c r="U705" t="n">
-        <v>278449528.26</v>
+        <v>250546923.9</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -54804,10 +54804,10 @@
         <v>0</v>
       </c>
       <c r="O706" t="n">
-        <v>-13706.14</v>
+        <v>457365.29</v>
       </c>
       <c r="P706" t="n">
-        <v>-13706.14</v>
+        <v>457365.29</v>
       </c>
       <c r="Q706" t="n">
         <v>0</v>
@@ -54816,22 +54816,22 @@
         <v>470639.11</v>
       </c>
       <c r="S706" t="n">
-        <v>-484345.25</v>
+        <v>-13273.82</v>
       </c>
       <c r="T706" t="n">
         <v>0</v>
       </c>
       <c r="U706" t="n">
-        <v>13706.14</v>
+        <v>-457365.29</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -54881,10 +54881,10 @@
         <v>5000000</v>
       </c>
       <c r="O707" t="n">
-        <v>1455435.02</v>
+        <v>1926506.45</v>
       </c>
       <c r="P707" t="n">
-        <v>1455435.02</v>
+        <v>1926506.45</v>
       </c>
       <c r="Q707" t="n">
         <v>0</v>
@@ -54893,22 +54893,22 @@
         <v>1455435.02</v>
       </c>
       <c r="S707" t="n">
-        <v>0</v>
+        <v>471071.43</v>
       </c>
       <c r="T707" t="n">
         <v>0</v>
       </c>
       <c r="U707" t="n">
-        <v>3544564.98</v>
+        <v>3073493.55</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -54981,11 +54981,11 @@
     </row>
     <row r="709">
       <c r="A709" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -55058,11 +55058,11 @@
     </row>
     <row r="710">
       <c r="A710" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -55135,11 +55135,11 @@
     </row>
     <row r="711">
       <c r="A711" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -55212,11 +55212,11 @@
     </row>
     <row r="712">
       <c r="A712" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -55266,10 +55266,10 @@
         <v>0</v>
       </c>
       <c r="O712" t="n">
-        <v>0</v>
+        <v>3189347.02</v>
       </c>
       <c r="P712" t="n">
-        <v>0</v>
+        <v>3189347.02</v>
       </c>
       <c r="Q712" t="n">
         <v>0</v>
@@ -55278,22 +55278,22 @@
         <v>3113406.82</v>
       </c>
       <c r="S712" t="n">
-        <v>-3113406.82</v>
+        <v>75940.2</v>
       </c>
       <c r="T712" t="n">
         <v>0</v>
       </c>
       <c r="U712" t="n">
-        <v>0</v>
+        <v>-3189347.02</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -55343,10 +55343,10 @@
         <v>40260000</v>
       </c>
       <c r="O713" t="n">
-        <v>9364593.93</v>
+        <v>12553940.95</v>
       </c>
       <c r="P713" t="n">
-        <v>9364593.93</v>
+        <v>12553940.95</v>
       </c>
       <c r="Q713" t="n">
         <v>0</v>
@@ -55355,22 +55355,22 @@
         <v>9364593.93</v>
       </c>
       <c r="S713" t="n">
-        <v>0</v>
+        <v>3189347.02</v>
       </c>
       <c r="T713" t="n">
         <v>0</v>
       </c>
       <c r="U713" t="n">
-        <v>30895406.07</v>
+        <v>27706059.05</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -55420,10 +55420,10 @@
         <v>0</v>
       </c>
       <c r="O714" t="n">
-        <v>0</v>
+        <v>389111</v>
       </c>
       <c r="P714" t="n">
-        <v>0</v>
+        <v>389111</v>
       </c>
       <c r="Q714" t="n">
         <v>0</v>
@@ -55432,22 +55432,22 @@
         <v>419159</v>
       </c>
       <c r="S714" t="n">
-        <v>-419159</v>
+        <v>-30048</v>
       </c>
       <c r="T714" t="n">
         <v>0</v>
       </c>
       <c r="U714" t="n">
-        <v>0</v>
+        <v>-389111</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -55497,10 +55497,10 @@
         <v>7700000</v>
       </c>
       <c r="O715" t="n">
-        <v>1105699</v>
+        <v>1494810</v>
       </c>
       <c r="P715" t="n">
-        <v>1105699</v>
+        <v>1494810</v>
       </c>
       <c r="Q715" t="n">
         <v>0</v>
@@ -55509,22 +55509,22 @@
         <v>1105699</v>
       </c>
       <c r="S715" t="n">
-        <v>0</v>
+        <v>389111</v>
       </c>
       <c r="T715" t="n">
         <v>0</v>
       </c>
       <c r="U715" t="n">
-        <v>6594301</v>
+        <v>6205190</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -55583,10 +55583,10 @@
         <v>-811565.0699999999</v>
       </c>
       <c r="R716" t="n">
-        <v>0</v>
+        <v>811565.0699999999</v>
       </c>
       <c r="S716" t="n">
-        <v>811565.0699999999</v>
+        <v>0</v>
       </c>
       <c r="T716" t="n">
         <v>0</v>
@@ -55597,11 +55597,11 @@
     </row>
     <row r="717">
       <c r="A717" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -55660,10 +55660,10 @@
         <v>1611943.18</v>
       </c>
       <c r="R717" t="n">
-        <v>1791885.01</v>
+        <v>2603450.08</v>
       </c>
       <c r="S717" t="n">
-        <v>811565.0699999999</v>
+        <v>0</v>
       </c>
       <c r="T717" t="n">
         <v>0</v>
@@ -55674,11 +55674,11 @@
     </row>
     <row r="718">
       <c r="A718" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -55751,11 +55751,11 @@
     </row>
     <row r="719">
       <c r="A719" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -55828,11 +55828,11 @@
     </row>
     <row r="720">
       <c r="A720" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -55897,19 +55897,19 @@
         <v>-220812.59</v>
       </c>
       <c r="T720" t="n">
-        <v>0</v>
+        <v>276508.8</v>
       </c>
       <c r="U720" t="n">
-        <v>0</v>
+        <v>-276508.8</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -55974,19 +55974,19 @@
         <v>0</v>
       </c>
       <c r="T721" t="n">
-        <v>0</v>
+        <v>276508.8</v>
       </c>
       <c r="U721" t="n">
-        <v>4232604.14</v>
+        <v>3956095.34</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -56059,11 +56059,11 @@
     </row>
     <row r="723">
       <c r="A723" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -56136,11 +56136,11 @@
     </row>
     <row r="724">
       <c r="A724" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -56213,11 +56213,11 @@
     </row>
     <row r="725">
       <c r="A725" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -56290,11 +56290,11 @@
     </row>
     <row r="726">
       <c r="A726" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -56367,11 +56367,11 @@
     </row>
     <row r="727">
       <c r="A727" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -56444,11 +56444,11 @@
     </row>
     <row r="728">
       <c r="A728" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -56498,10 +56498,10 @@
         <v>0</v>
       </c>
       <c r="O728" t="n">
-        <v>-1645465.09</v>
+        <v>1016463.74</v>
       </c>
       <c r="P728" t="n">
-        <v>-1645465.09</v>
+        <v>1016463.74</v>
       </c>
       <c r="Q728" t="n">
         <v>0</v>
@@ -56510,22 +56510,22 @@
         <v>2651676.79</v>
       </c>
       <c r="S728" t="n">
-        <v>-4297141.88</v>
+        <v>-1635213.05</v>
       </c>
       <c r="T728" t="n">
         <v>0</v>
       </c>
       <c r="U728" t="n">
-        <v>1645465.09</v>
+        <v>-1016463.74</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -56578,16 +56578,16 @@
         <v>92674</v>
       </c>
       <c r="P729" t="n">
-        <v>73024</v>
+        <v>92674</v>
       </c>
       <c r="Q729" t="n">
-        <v>19650</v>
+        <v>0</v>
       </c>
       <c r="R729" t="n">
         <v>73024</v>
       </c>
       <c r="S729" t="n">
-        <v>0</v>
+        <v>19650</v>
       </c>
       <c r="T729" t="n">
         <v>659217</v>
@@ -56598,11 +56598,11 @@
     </row>
     <row r="730">
       <c r="A730" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -56655,16 +56655,16 @@
         <v>0</v>
       </c>
       <c r="P730" t="n">
-        <v>0</v>
+        <v>19650</v>
       </c>
       <c r="Q730" t="n">
-        <v>0</v>
+        <v>-19650</v>
       </c>
       <c r="R730" t="n">
         <v>73024</v>
       </c>
       <c r="S730" t="n">
-        <v>-73024</v>
+        <v>-53374</v>
       </c>
       <c r="T730" t="n">
         <v>659217</v>
@@ -56675,11 +56675,11 @@
     </row>
     <row r="731">
       <c r="A731" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -56752,11 +56752,11 @@
     </row>
     <row r="732">
       <c r="A732" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -56806,10 +56806,10 @@
         <v>0</v>
       </c>
       <c r="O732" t="n">
-        <v>122594.31</v>
+        <v>132249.44</v>
       </c>
       <c r="P732" t="n">
-        <v>122594.31</v>
+        <v>132249.44</v>
       </c>
       <c r="Q732" t="n">
         <v>0</v>
@@ -56818,22 +56818,22 @@
         <v>20387.8</v>
       </c>
       <c r="S732" t="n">
-        <v>102206.51</v>
+        <v>111861.64</v>
       </c>
       <c r="T732" t="n">
         <v>0</v>
       </c>
       <c r="U732" t="n">
-        <v>-122594.31</v>
+        <v>-132249.44</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -56906,11 +56906,11 @@
     </row>
     <row r="734">
       <c r="A734" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -56983,11 +56983,11 @@
     </row>
     <row r="735">
       <c r="A735" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -57060,11 +57060,11 @@
     </row>
     <row r="736">
       <c r="A736" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -57137,11 +57137,11 @@
     </row>
     <row r="737">
       <c r="A737" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -57214,11 +57214,11 @@
     </row>
     <row r="738">
       <c r="A738" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -57291,11 +57291,11 @@
     </row>
     <row r="739">
       <c r="A739" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -57354,10 +57354,10 @@
         <v>-5000</v>
       </c>
       <c r="R739" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="S739" t="n">
-        <v>-15000</v>
+        <v>-20000</v>
       </c>
       <c r="T739" t="n">
         <v>0</v>
@@ -57368,11 +57368,11 @@
     </row>
     <row r="740">
       <c r="A740" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -57431,10 +57431,10 @@
         <v>0</v>
       </c>
       <c r="R740" t="n">
-        <v>110000</v>
+        <v>115000</v>
       </c>
       <c r="S740" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T740" t="n">
         <v>0</v>
@@ -57445,11 +57445,11 @@
     </row>
     <row r="741">
       <c r="A741" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -57522,11 +57522,11 @@
     </row>
     <row r="742">
       <c r="A742" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -57599,11 +57599,11 @@
     </row>
     <row r="743">
       <c r="A743" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -57676,11 +57676,11 @@
     </row>
     <row r="744">
       <c r="A744" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -57753,11 +57753,11 @@
     </row>
     <row r="745">
       <c r="A745" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -57830,11 +57830,11 @@
     </row>
     <row r="746">
       <c r="A746" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -57907,11 +57907,11 @@
     </row>
     <row r="747">
       <c r="A747" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -57984,11 +57984,11 @@
     </row>
     <row r="748">
       <c r="A748" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -58061,11 +58061,11 @@
     </row>
     <row r="749">
       <c r="A749" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -58118,16 +58118,16 @@
         <v>0</v>
       </c>
       <c r="P749" t="n">
-        <v>810074.16</v>
+        <v>1231903.16</v>
       </c>
       <c r="Q749" t="n">
-        <v>-810074.16</v>
+        <v>-1231903.16</v>
       </c>
       <c r="R749" t="n">
-        <v>1684019.12</v>
+        <v>1699019.12</v>
       </c>
       <c r="S749" t="n">
-        <v>-873944.96</v>
+        <v>-467115.96</v>
       </c>
       <c r="T749" t="n">
         <v>12071244.31</v>
@@ -58138,11 +58138,11 @@
     </row>
     <row r="750">
       <c r="A750" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -58195,16 +58195,16 @@
         <v>15388887.32</v>
       </c>
       <c r="P750" t="n">
-        <v>6641042.92</v>
+        <v>7062871.92</v>
       </c>
       <c r="Q750" t="n">
-        <v>8747844.4</v>
+        <v>8326015.4</v>
       </c>
       <c r="R750" t="n">
-        <v>5830968.76</v>
+        <v>5845968.76</v>
       </c>
       <c r="S750" t="n">
-        <v>810074.16</v>
+        <v>1216903.16</v>
       </c>
       <c r="T750" t="n">
         <v>32071244.31</v>
@@ -58215,11 +58215,11 @@
     </row>
     <row r="751">
       <c r="A751" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -58292,11 +58292,11 @@
     </row>
     <row r="752">
       <c r="A752" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -58369,11 +58369,11 @@
     </row>
     <row r="753">
       <c r="A753" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -58426,16 +58426,16 @@
         <v>17136.8</v>
       </c>
       <c r="P753" t="n">
-        <v>9462.6</v>
+        <v>12522.6</v>
       </c>
       <c r="Q753" t="n">
-        <v>7674.199999999999</v>
+        <v>4614.199999999999</v>
       </c>
       <c r="R753" t="n">
         <v>1080</v>
       </c>
       <c r="S753" t="n">
-        <v>8382.6</v>
+        <v>11442.6</v>
       </c>
       <c r="T753" t="n">
         <v>0</v>
@@ -58446,11 +58446,11 @@
     </row>
     <row r="754">
       <c r="A754" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -58503,16 +58503,16 @@
         <v>93592.39999999999</v>
       </c>
       <c r="P754" t="n">
-        <v>46915.2</v>
+        <v>49975.2</v>
       </c>
       <c r="Q754" t="n">
-        <v>46677.2</v>
+        <v>43617.2</v>
       </c>
       <c r="R754" t="n">
         <v>1452.6</v>
       </c>
       <c r="S754" t="n">
-        <v>45462.6</v>
+        <v>48522.6</v>
       </c>
       <c r="T754" t="n">
         <v>0</v>
@@ -58523,11 +58523,11 @@
     </row>
     <row r="755">
       <c r="A755" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -58600,11 +58600,11 @@
     </row>
     <row r="756">
       <c r="A756" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -58677,11 +58677,11 @@
     </row>
     <row r="757">
       <c r="A757" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -58754,11 +58754,11 @@
     </row>
     <row r="758">
       <c r="A758" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -58831,11 +58831,11 @@
     </row>
     <row r="759">
       <c r="A759" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -58908,11 +58908,11 @@
     </row>
     <row r="760">
       <c r="A760" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -58985,11 +58985,11 @@
     </row>
     <row r="761">
       <c r="A761" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -59062,11 +59062,11 @@
     </row>
     <row r="762">
       <c r="A762" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -59139,11 +59139,11 @@
     </row>
     <row r="763">
       <c r="A763" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -59216,11 +59216,11 @@
     </row>
     <row r="764">
       <c r="A764" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -59293,11 +59293,11 @@
     </row>
     <row r="765">
       <c r="A765" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -59370,11 +59370,11 @@
     </row>
     <row r="766">
       <c r="A766" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -59447,11 +59447,11 @@
     </row>
     <row r="767">
       <c r="A767" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -59524,11 +59524,11 @@
     </row>
     <row r="768">
       <c r="A768" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -59601,11 +59601,11 @@
     </row>
     <row r="769">
       <c r="A769" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -59678,11 +59678,11 @@
     </row>
     <row r="770">
       <c r="A770" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -59755,11 +59755,11 @@
     </row>
     <row r="771">
       <c r="A771" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -59832,11 +59832,11 @@
     </row>
     <row r="772">
       <c r="A772" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -59909,11 +59909,11 @@
     </row>
     <row r="773">
       <c r="A773" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -59986,11 +59986,11 @@
     </row>
     <row r="774">
       <c r="A774" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -60063,11 +60063,11 @@
     </row>
     <row r="775">
       <c r="A775" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -60140,11 +60140,11 @@
     </row>
     <row r="776">
       <c r="A776" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -60217,11 +60217,11 @@
     </row>
     <row r="777">
       <c r="A777" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -60294,11 +60294,11 @@
     </row>
     <row r="778">
       <c r="A778" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -60371,11 +60371,11 @@
     </row>
     <row r="779">
       <c r="A779" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -60448,11 +60448,11 @@
     </row>
     <row r="780">
       <c r="A780" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -60525,11 +60525,11 @@
     </row>
     <row r="781">
       <c r="A781" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -60588,10 +60588,10 @@
         <v>-5000</v>
       </c>
       <c r="R781" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="S781" t="n">
-        <v>-5000</v>
+        <v>-10000</v>
       </c>
       <c r="T781" t="n">
         <v>0</v>
@@ -60602,11 +60602,11 @@
     </row>
     <row r="782">
       <c r="A782" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -60665,10 +60665,10 @@
         <v>0</v>
       </c>
       <c r="R782" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="S782" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T782" t="n">
         <v>0</v>
@@ -60679,11 +60679,11 @@
     </row>
     <row r="783">
       <c r="A783" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -60742,10 +60742,10 @@
         <v>-5000</v>
       </c>
       <c r="R783" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="S783" t="n">
-        <v>-5000</v>
+        <v>-10000</v>
       </c>
       <c r="T783" t="n">
         <v>0</v>
@@ -60756,11 +60756,11 @@
     </row>
     <row r="784">
       <c r="A784" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -60819,10 +60819,10 @@
         <v>0</v>
       </c>
       <c r="R784" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="S784" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T784" t="n">
         <v>0</v>
@@ -60833,11 +60833,11 @@
     </row>
     <row r="785">
       <c r="A785" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -60896,10 +60896,10 @@
         <v>-10000</v>
       </c>
       <c r="R785" t="n">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="S785" t="n">
-        <v>5000</v>
+        <v>-5000</v>
       </c>
       <c r="T785" t="n">
         <v>0</v>
@@ -60910,11 +60910,11 @@
     </row>
     <row r="786">
       <c r="A786" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -60973,10 +60973,10 @@
         <v>0</v>
       </c>
       <c r="R786" t="n">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="S786" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T786" t="n">
         <v>0</v>
@@ -60987,11 +60987,11 @@
     </row>
     <row r="787">
       <c r="A787" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -61050,10 +61050,10 @@
         <v>-5000</v>
       </c>
       <c r="R787" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="S787" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T787" t="n">
         <v>0</v>
@@ -61064,11 +61064,11 @@
     </row>
     <row r="788">
       <c r="A788" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -61127,10 +61127,10 @@
         <v>0</v>
       </c>
       <c r="R788" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="S788" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T788" t="n">
         <v>0</v>
@@ -61141,11 +61141,11 @@
     </row>
     <row r="789">
       <c r="A789" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -61218,11 +61218,11 @@
     </row>
     <row r="790">
       <c r="A790" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -61295,11 +61295,11 @@
     </row>
     <row r="791">
       <c r="A791" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -61372,11 +61372,11 @@
     </row>
     <row r="792">
       <c r="A792" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -61449,11 +61449,11 @@
     </row>
     <row r="793">
       <c r="A793" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -61526,11 +61526,11 @@
     </row>
     <row r="794">
       <c r="A794" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -61603,11 +61603,11 @@
     </row>
     <row r="795">
       <c r="A795" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -61680,11 +61680,11 @@
     </row>
     <row r="796">
       <c r="A796" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -61757,11 +61757,11 @@
     </row>
     <row r="797">
       <c r="A797" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -61834,11 +61834,11 @@
     </row>
     <row r="798">
       <c r="A798" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -61911,11 +61911,11 @@
     </row>
     <row r="799">
       <c r="A799" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -61988,11 +61988,11 @@
     </row>
     <row r="800">
       <c r="A800" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -62065,11 +62065,11 @@
     </row>
     <row r="801">
       <c r="A801" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -62142,11 +62142,11 @@
     </row>
     <row r="802">
       <c r="A802" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -62219,11 +62219,11 @@
     </row>
     <row r="803">
       <c r="A803" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -62296,11 +62296,11 @@
     </row>
     <row r="804">
       <c r="A804" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -62373,11 +62373,11 @@
     </row>
     <row r="805">
       <c r="A805" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -62450,11 +62450,11 @@
     </row>
     <row r="806">
       <c r="A806" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -62527,11 +62527,11 @@
     </row>
     <row r="807">
       <c r="A807" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -62590,10 +62590,10 @@
         <v>-21840</v>
       </c>
       <c r="R807" t="n">
-        <v>24072</v>
+        <v>49191</v>
       </c>
       <c r="S807" t="n">
-        <v>-2232</v>
+        <v>-27351</v>
       </c>
       <c r="T807" t="n">
         <v>0</v>
@@ -62604,11 +62604,11 @@
     </row>
     <row r="808">
       <c r="A808" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -62667,10 +62667,10 @@
         <v>66</v>
       </c>
       <c r="R808" t="n">
-        <v>159398</v>
+        <v>184517</v>
       </c>
       <c r="S808" t="n">
-        <v>25119</v>
+        <v>0</v>
       </c>
       <c r="T808" t="n">
         <v>400000</v>
@@ -62681,11 +62681,11 @@
     </row>
     <row r="809">
       <c r="A809" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -62758,11 +62758,11 @@
     </row>
     <row r="810">
       <c r="A810" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -62835,11 +62835,11 @@
     </row>
     <row r="811">
       <c r="A811" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -62912,11 +62912,11 @@
     </row>
     <row r="812">
       <c r="A812" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -62989,11 +62989,11 @@
     </row>
     <row r="813">
       <c r="A813" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -63046,16 +63046,16 @@
         <v>0</v>
       </c>
       <c r="P813" t="n">
-        <v>49335</v>
+        <v>64635</v>
       </c>
       <c r="Q813" t="n">
-        <v>-49335</v>
+        <v>-64635</v>
       </c>
       <c r="R813" t="n">
-        <v>3690</v>
+        <v>12138</v>
       </c>
       <c r="S813" t="n">
-        <v>45645</v>
+        <v>52497</v>
       </c>
       <c r="T813" t="n">
         <v>0</v>
@@ -63066,11 +63066,11 @@
     </row>
     <row r="814">
       <c r="A814" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -63123,16 +63123,16 @@
         <v>242268.6</v>
       </c>
       <c r="P814" t="n">
-        <v>83745</v>
+        <v>99045</v>
       </c>
       <c r="Q814" t="n">
-        <v>158523.6</v>
+        <v>143223.6</v>
       </c>
       <c r="R814" t="n">
-        <v>33222</v>
+        <v>41670</v>
       </c>
       <c r="S814" t="n">
-        <v>50523</v>
+        <v>57375</v>
       </c>
       <c r="T814" t="n">
         <v>0</v>
@@ -63143,11 +63143,11 @@
     </row>
     <row r="815">
       <c r="A815" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -63220,11 +63220,11 @@
     </row>
     <row r="816">
       <c r="A816" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -63297,11 +63297,11 @@
     </row>
     <row r="817">
       <c r="A817" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -63374,11 +63374,11 @@
     </row>
     <row r="818">
       <c r="A818" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -63451,11 +63451,11 @@
     </row>
     <row r="819">
       <c r="A819" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -63528,11 +63528,11 @@
     </row>
     <row r="820">
       <c r="A820" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -63605,11 +63605,11 @@
     </row>
     <row r="821">
       <c r="A821" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -63682,11 +63682,11 @@
     </row>
     <row r="822">
       <c r="A822" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -63759,11 +63759,11 @@
     </row>
     <row r="823">
       <c r="A823" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -63836,11 +63836,11 @@
     </row>
     <row r="824">
       <c r="A824" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -63913,11 +63913,11 @@
     </row>
     <row r="825">
       <c r="A825" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>RELEXORC_27-04-2026.csv</t>
+          <t>RELEXORC_28-04-2026.csv</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -63967,10 +63967,10 @@
         <v>16930000</v>
       </c>
       <c r="O825" t="n">
-        <v>657855.36</v>
+        <v>667510.49</v>
       </c>
       <c r="P825" t="n">
-        <v>657855.36</v>
+        <v>667510.49</v>
       </c>
       <c r="Q825" t="n">
         <v>0</v>
@@ -63979,13 +63979,13 @@
         <v>555648.85</v>
       </c>
       <c r="S825" t="n">
-        <v>102206.51</v>
+        <v>111861.64</v>
       </c>
       <c r="T825" t="n">
         <v>0</v>
       </c>
       <c r="U825" t="n">
-        <v>16272144.64</v>
+        <v>16262489.51</v>
       </c>
     </row>
   </sheetData>
@@ -64154,7 +64154,7 @@
         <v>46112</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -64249,7 +64249,7 @@
         <v>46112</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -64344,7 +64344,7 @@
         <v>46112</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -64439,7 +64439,7 @@
         <v>46112</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -64505,10 +64505,10 @@
         <v>90000</v>
       </c>
       <c r="V5" t="n">
-        <v>110000</v>
+        <v>115000</v>
       </c>
       <c r="W5" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -64534,7 +64534,7 @@
         <v>46112</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -64629,7 +64629,7 @@
         <v>46112</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -64724,7 +64724,7 @@
         <v>46112</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -64819,7 +64819,7 @@
         <v>46112</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -64914,7 +64914,7 @@
         <v>46112</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -64971,19 +64971,19 @@
         <v>5845968.76</v>
       </c>
       <c r="S10" t="n">
-        <v>6641042.92</v>
+        <v>7062871.92</v>
       </c>
       <c r="T10" t="n">
-        <v>795074.1600000001</v>
+        <v>1216903.16</v>
       </c>
       <c r="U10" t="n">
         <v>4367980.05</v>
       </c>
       <c r="V10" t="n">
-        <v>5830968.76</v>
+        <v>5845968.76</v>
       </c>
       <c r="W10" t="n">
-        <v>1462988.71</v>
+        <v>1477988.71</v>
       </c>
       <c r="X10" t="n">
         <v>27222950.51</v>
@@ -65009,7 +65009,7 @@
         <v>46112</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -65104,7 +65104,7 @@
         <v>46112</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -65161,10 +65161,10 @@
         <v>38532.6</v>
       </c>
       <c r="S12" t="n">
-        <v>46915.2</v>
+        <v>49975.2</v>
       </c>
       <c r="T12" t="n">
-        <v>8382.599999999999</v>
+        <v>11442.6</v>
       </c>
       <c r="U12" t="n">
         <v>372.6</v>
@@ -65199,7 +65199,7 @@
         <v>46112</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -65294,7 +65294,7 @@
         <v>46112</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -65389,7 +65389,7 @@
         <v>46112</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -65484,7 +65484,7 @@
         <v>46112</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -65541,10 +65541,10 @@
         <v>73024</v>
       </c>
       <c r="S16" t="n">
-        <v>73024</v>
+        <v>92674</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>19650</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -65579,7 +65579,7 @@
         <v>46112</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -65627,19 +65627,19 @@
         <v>9208960.51</v>
       </c>
       <c r="P17" t="n">
-        <v>7563495.42</v>
+        <v>10225424.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1645465.09</v>
+        <v>1016463.74</v>
       </c>
       <c r="R17" t="n">
         <v>9208960.51</v>
       </c>
       <c r="S17" t="n">
-        <v>7563495.42</v>
+        <v>10225424.25</v>
       </c>
       <c r="T17" t="n">
-        <v>-1645465.09</v>
+        <v>1016463.74</v>
       </c>
       <c r="U17" t="n">
         <v>6550089.63</v>
@@ -65663,10 +65663,10 @@
         <v>22791039.49</v>
       </c>
       <c r="AB17" t="n">
-        <v>24436504.58</v>
+        <v>21774575.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>1645465.09</v>
+        <v>-1016463.739999998</v>
       </c>
     </row>
     <row r="18">
@@ -65674,7 +65674,7 @@
         <v>46112</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -65722,19 +65722,19 @@
         <v>44143.98</v>
       </c>
       <c r="P18" t="n">
-        <v>44143.98</v>
+        <v>58858.64</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>14714.66</v>
       </c>
       <c r="R18" t="n">
         <v>44143.98</v>
       </c>
       <c r="S18" t="n">
-        <v>44143.98</v>
+        <v>58858.64</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>14714.66</v>
       </c>
       <c r="U18" t="n">
         <v>29429.32</v>
@@ -65758,10 +65758,10 @@
         <v>105856.02</v>
       </c>
       <c r="AB18" t="n">
-        <v>105856.02</v>
+        <v>91141.36</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>-14714.66</v>
       </c>
     </row>
     <row r="19">
@@ -65769,7 +65769,7 @@
         <v>46112</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -65817,19 +65817,19 @@
         <v>88112555.73</v>
       </c>
       <c r="P19" t="n">
-        <v>88107814.73999999</v>
+        <v>116010419.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4740.990000009537</v>
+        <v>27897863.36999999</v>
       </c>
       <c r="R19" t="n">
         <v>88112555.73</v>
       </c>
       <c r="S19" t="n">
-        <v>88107814.73999999</v>
+        <v>116010419.1</v>
       </c>
       <c r="T19" t="n">
-        <v>-4740.990000009537</v>
+        <v>27897863.36999999</v>
       </c>
       <c r="U19" t="n">
         <v>79635166.11</v>
@@ -65853,10 +65853,10 @@
         <v>278444787.27</v>
       </c>
       <c r="AB19" t="n">
-        <v>278449528.26</v>
+        <v>250546923.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>4740.990000009537</v>
+        <v>-27897863.36999997</v>
       </c>
     </row>
     <row r="20">
@@ -65864,7 +65864,7 @@
         <v>46112</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -65912,19 +65912,19 @@
         <v>1469141.16</v>
       </c>
       <c r="P20" t="n">
-        <v>1455435.02</v>
+        <v>1926506.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>-13706.1399999999</v>
+        <v>457365.29</v>
       </c>
       <c r="R20" t="n">
         <v>1469141.16</v>
       </c>
       <c r="S20" t="n">
-        <v>1455435.02</v>
+        <v>1926506.45</v>
       </c>
       <c r="T20" t="n">
-        <v>-13706.1399999999</v>
+        <v>457365.29</v>
       </c>
       <c r="U20" t="n">
         <v>984795.91</v>
@@ -65948,10 +65948,10 @@
         <v>3530858.84</v>
       </c>
       <c r="AB20" t="n">
-        <v>3544564.98</v>
+        <v>3073493.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>13706.14000000013</v>
+        <v>-457365.29</v>
       </c>
     </row>
     <row r="21">
@@ -65959,7 +65959,7 @@
         <v>46112</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -66054,7 +66054,7 @@
         <v>46112</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -66149,7 +66149,7 @@
         <v>46112</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -66197,19 +66197,19 @@
         <v>9364593.93</v>
       </c>
       <c r="P23" t="n">
-        <v>9364593.93</v>
+        <v>12553940.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3189347.02</v>
       </c>
       <c r="R23" t="n">
         <v>9364593.93</v>
       </c>
       <c r="S23" t="n">
-        <v>9364593.93</v>
+        <v>12553940.95</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3189347.02</v>
       </c>
       <c r="U23" t="n">
         <v>6251187.11</v>
@@ -66233,10 +66233,10 @@
         <v>30895406.07</v>
       </c>
       <c r="AB23" t="n">
-        <v>30895406.07</v>
+        <v>27706059.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>-3189347.02</v>
       </c>
     </row>
     <row r="24">
@@ -66244,7 +66244,7 @@
         <v>46112</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -66292,19 +66292,19 @@
         <v>1105699</v>
       </c>
       <c r="P24" t="n">
-        <v>1105699</v>
+        <v>1494810</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>389111</v>
       </c>
       <c r="R24" t="n">
         <v>1105699</v>
       </c>
       <c r="S24" t="n">
-        <v>1105699</v>
+        <v>1494810</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>389111</v>
       </c>
       <c r="U24" t="n">
         <v>1105699</v>
@@ -66328,10 +66328,10 @@
         <v>6594301</v>
       </c>
       <c r="AB24" t="n">
-        <v>6594301</v>
+        <v>6205190</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>-389111</v>
       </c>
     </row>
     <row r="25">
@@ -66339,7 +66339,7 @@
         <v>46112</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -66405,10 +66405,10 @@
         <v>1791885.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1791885.01</v>
+        <v>2603450.08</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>811565.0700000001</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -66434,7 +66434,7 @@
         <v>46112</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -66529,7 +66529,7 @@
         <v>46112</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -66604,19 +66604,19 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>276508.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>276508.8</v>
       </c>
       <c r="AA27" t="n">
         <v>4232604.14</v>
       </c>
       <c r="AB27" t="n">
-        <v>4232604.14</v>
+        <v>3956095.34</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>-276508.7999999998</v>
       </c>
     </row>
     <row r="28">
@@ -66624,7 +66624,7 @@
         <v>46112</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -66719,7 +66719,7 @@
         <v>46112</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -66814,7 +66814,7 @@
         <v>46112</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -66909,7 +66909,7 @@
         <v>46112</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -67004,7 +67004,7 @@
         <v>46112</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -67099,7 +67099,7 @@
         <v>46112</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -67194,7 +67194,7 @@
         <v>46112</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -67289,7 +67289,7 @@
         <v>46112</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -67384,7 +67384,7 @@
         <v>46112</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -67479,7 +67479,7 @@
         <v>46112</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -67574,7 +67574,7 @@
         <v>46112</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -67669,7 +67669,7 @@
         <v>46112</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -67735,10 +67735,10 @@
         <v>135326</v>
       </c>
       <c r="V39" t="n">
-        <v>159398</v>
+        <v>184517</v>
       </c>
       <c r="W39" t="n">
-        <v>24072</v>
+        <v>49191</v>
       </c>
       <c r="X39" t="n">
         <v>400000</v>
@@ -67764,7 +67764,7 @@
         <v>46112</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -67859,7 +67859,7 @@
         <v>46112</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -67954,7 +67954,7 @@
         <v>46112</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -68011,19 +68011,19 @@
         <v>46014</v>
       </c>
       <c r="S42" t="n">
-        <v>83745</v>
+        <v>99045</v>
       </c>
       <c r="T42" t="n">
-        <v>37731</v>
+        <v>53031</v>
       </c>
       <c r="U42" t="n">
         <v>29532</v>
       </c>
       <c r="V42" t="n">
-        <v>33222</v>
+        <v>41670</v>
       </c>
       <c r="W42" t="n">
-        <v>3690</v>
+        <v>12138</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -68049,7 +68049,7 @@
         <v>46112</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -68144,7 +68144,7 @@
         <v>46112</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -68239,7 +68239,7 @@
         <v>46112</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -68334,7 +68334,7 @@
         <v>46112</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -68429,7 +68429,7 @@
         <v>46112</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -68524,7 +68524,7 @@
         <v>46112</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -68619,7 +68619,7 @@
         <v>46112</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -68714,7 +68714,7 @@
         <v>46112</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -68809,7 +68809,7 @@
         <v>46112</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -68904,7 +68904,7 @@
         <v>46112</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -68999,7 +68999,7 @@
         <v>46112</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -69094,7 +69094,7 @@
         <v>46112</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -69189,7 +69189,7 @@
         <v>46112</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -69284,7 +69284,7 @@
         <v>46112</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -69379,7 +69379,7 @@
         <v>46112</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -69474,7 +69474,7 @@
         <v>46112</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -69569,7 +69569,7 @@
         <v>46112</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -69635,10 +69635,10 @@
         <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="W59" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="X59" t="n">
         <v>0</v>
@@ -69664,7 +69664,7 @@
         <v>46112</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -69730,10 +69730,10 @@
         <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="W60" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="X60" t="n">
         <v>0</v>
@@ -69759,7 +69759,7 @@
         <v>46112</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -69825,10 +69825,10 @@
         <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="W61" t="n">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="X61" t="n">
         <v>0</v>
@@ -69854,7 +69854,7 @@
         <v>46112</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -69920,10 +69920,10 @@
         <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="W62" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="X62" t="n">
         <v>0</v>
@@ -69949,7 +69949,7 @@
         <v>46112</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -70044,7 +70044,7 @@
         <v>46112</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -70139,7 +70139,7 @@
         <v>46112</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -70234,7 +70234,7 @@
         <v>46112</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -70300,10 +70300,10 @@
         <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="X66" t="n">
         <v>0</v>
@@ -70329,7 +70329,7 @@
         <v>46112</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -70424,7 +70424,7 @@
         <v>46112</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -70519,7 +70519,7 @@
         <v>46112</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -70614,7 +70614,7 @@
         <v>46112</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -70709,7 +70709,7 @@
         <v>46112</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -70804,7 +70804,7 @@
         <v>46112</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -70899,7 +70899,7 @@
         <v>46112</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -70965,10 +70965,10 @@
         <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="W73" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="X73" t="n">
         <v>0</v>
@@ -70994,7 +70994,7 @@
         <v>46112</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -71060,10 +71060,10 @@
         <v>5000</v>
       </c>
       <c r="V74" t="n">
+        <v>10000</v>
+      </c>
+      <c r="W74" t="n">
         <v>5000</v>
-      </c>
-      <c r="W74" t="n">
-        <v>0</v>
       </c>
       <c r="X74" t="n">
         <v>0</v>
@@ -71089,7 +71089,7 @@
         <v>46112</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -71155,10 +71155,10 @@
         <v>0</v>
       </c>
       <c r="V75" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="W75" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="X75" t="n">
         <v>0</v>
@@ -71184,7 +71184,7 @@
         <v>46112</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -71250,10 +71250,10 @@
         <v>0</v>
       </c>
       <c r="V76" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="W76" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="X76" t="n">
         <v>0</v>
@@ -71279,7 +71279,7 @@
         <v>46112</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -71374,7 +71374,7 @@
         <v>46112</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -71469,7 +71469,7 @@
         <v>46112</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -71535,10 +71535,10 @@
         <v>10000</v>
       </c>
       <c r="V79" t="n">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="W79" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="X79" t="n">
         <v>0</v>
@@ -71564,7 +71564,7 @@
         <v>46112</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -71659,7 +71659,7 @@
         <v>46112</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -71754,7 +71754,7 @@
         <v>46112</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -71849,7 +71849,7 @@
         <v>46112</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -71944,7 +71944,7 @@
         <v>46112</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -72039,7 +72039,7 @@
         <v>46112</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -72134,7 +72134,7 @@
         <v>46112</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -72229,7 +72229,7 @@
         <v>46112</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -72324,7 +72324,7 @@
         <v>46112</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -72419,7 +72419,7 @@
         <v>46112</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -72514,7 +72514,7 @@
         <v>46112</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -72609,7 +72609,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -72704,7 +72704,7 @@
         <v>46112</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -72799,7 +72799,7 @@
         <v>46112</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -72894,7 +72894,7 @@
         <v>46112</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -72951,10 +72951,10 @@
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>9337673.699999999</v>
+        <v>9417882.029999999</v>
       </c>
       <c r="T94" t="n">
-        <v>9337673.699999999</v>
+        <v>9417882.029999999</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -72989,7 +72989,7 @@
         <v>46112</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -73084,7 +73084,7 @@
         <v>46112</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -73179,7 +73179,7 @@
         <v>46112</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -73274,7 +73274,7 @@
         <v>46112</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -73369,7 +73369,7 @@
         <v>46112</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -73464,7 +73464,7 @@
         <v>46112</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -73559,7 +73559,7 @@
         <v>46112</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -73654,7 +73654,7 @@
         <v>46112</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -73749,7 +73749,7 @@
         <v>46112</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -73844,7 +73844,7 @@
         <v>46112</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -73939,7 +73939,7 @@
         <v>46112</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -74034,7 +74034,7 @@
         <v>46112</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -74129,7 +74129,7 @@
         <v>46112</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -74224,7 +74224,7 @@
         <v>46112</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -74281,10 +74281,10 @@
         <v>1128600</v>
       </c>
       <c r="S108" t="n">
-        <v>1513300</v>
+        <v>1515500</v>
       </c>
       <c r="T108" t="n">
-        <v>384700</v>
+        <v>386900</v>
       </c>
       <c r="U108" t="n">
         <v>747600</v>
@@ -74319,7 +74319,7 @@
         <v>46112</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -74414,7 +74414,7 @@
         <v>46112</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -74509,7 +74509,7 @@
         <v>46112</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -74604,7 +74604,7 @@
         <v>46112</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -74699,7 +74699,7 @@
         <v>46112</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -74794,7 +74794,7 @@
         <v>46112</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -74889,7 +74889,7 @@
         <v>46112</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -74984,7 +74984,7 @@
         <v>46112</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -75050,10 +75050,10 @@
         <v>0</v>
       </c>
       <c r="V116" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="W116" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="X116" t="n">
         <v>0</v>
@@ -75079,7 +75079,7 @@
         <v>46112</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -75174,7 +75174,7 @@
         <v>46112</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -75269,7 +75269,7 @@
         <v>46112</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -75364,7 +75364,7 @@
         <v>46112</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -75459,7 +75459,7 @@
         <v>46112</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -75554,7 +75554,7 @@
         <v>46112</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -75649,7 +75649,7 @@
         <v>46112</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -75744,7 +75744,7 @@
         <v>46112</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -75801,10 +75801,10 @@
         <v>5499.9</v>
       </c>
       <c r="S124" t="n">
-        <v>16600.88</v>
+        <v>22151.37</v>
       </c>
       <c r="T124" t="n">
-        <v>11100.98</v>
+        <v>16651.47</v>
       </c>
       <c r="U124" t="n">
         <v>5499.9</v>
@@ -75839,7 +75839,7 @@
         <v>46112</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -75934,7 +75934,7 @@
         <v>46112</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -76029,7 +76029,7 @@
         <v>46112</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -76124,7 +76124,7 @@
         <v>46112</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -76219,7 +76219,7 @@
         <v>46112</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -76314,7 +76314,7 @@
         <v>46112</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -76362,19 +76362,19 @@
         <v>535261.05</v>
       </c>
       <c r="P130" t="n">
-        <v>657855.36</v>
+        <v>667510.49</v>
       </c>
       <c r="Q130" t="n">
-        <v>122594.3099999999</v>
+        <v>132249.4399999999</v>
       </c>
       <c r="R130" t="n">
         <v>535261.05</v>
       </c>
       <c r="S130" t="n">
-        <v>657855.36</v>
+        <v>667510.49</v>
       </c>
       <c r="T130" t="n">
-        <v>122594.3099999999</v>
+        <v>132249.4399999999</v>
       </c>
       <c r="U130" t="n">
         <v>535261.05</v>
@@ -76398,10 +76398,10 @@
         <v>16394738.95</v>
       </c>
       <c r="AB130" t="n">
-        <v>16272144.64</v>
+        <v>16262489.51</v>
       </c>
       <c r="AC130" t="n">
-        <v>-122594.3099999987</v>
+        <v>-132249.4399999995</v>
       </c>
     </row>
   </sheetData>

--- a/Base_Consolidada_SIAFI.xlsx
+++ b/Base_Consolidada_SIAFI.xlsx
@@ -21,16 +21,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -434,114 +422,114 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Data Extração</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Arquivo Origem</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Mês Referência</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Programa de Trabalho</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fonte de Recurso</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Natureza da Despesa</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Tipo Movimento</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Dotação Inicial</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Dotação Suplementar</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Dotação Especial</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Reduções</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Destaque Recebido</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Destaque Concedido</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Autorizado</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Empenhado</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Liquidado</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>A Liquidar</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Pago</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>A Pagar</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Bloqueado</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Disponível</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +606,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -695,7 +683,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -772,7 +760,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -849,7 +837,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -926,7 +914,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1003,7 +991,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1080,7 +1068,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1157,7 +1145,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1234,7 +1222,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1311,7 +1299,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1388,7 +1376,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1465,7 +1453,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1542,7 +1530,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1619,7 +1607,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1696,7 +1684,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1773,7 +1761,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1850,7 +1838,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1927,7 +1915,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -2004,7 +1992,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -2081,7 +2069,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -2158,7 +2146,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -2235,7 +2223,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -2312,7 +2300,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -2389,7 +2377,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -2466,7 +2454,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -2543,7 +2531,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -2620,7 +2608,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -2697,7 +2685,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -2774,7 +2762,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -2851,7 +2839,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -2928,7 +2916,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -3005,7 +2993,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -3082,7 +3070,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -3159,7 +3147,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -3236,7 +3224,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -3313,7 +3301,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -3390,7 +3378,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,7 +3455,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -3544,7 +3532,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -3621,7 +3609,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -3698,7 +3686,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -3775,7 +3763,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -3852,7 +3840,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -3929,7 +3917,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -4006,7 +3994,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -4083,7 +4071,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -4160,7 +4148,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -4237,7 +4225,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -4314,7 +4302,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -4391,7 +4379,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -4468,7 +4456,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -4545,7 +4533,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -4622,7 +4610,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -4699,7 +4687,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -4776,7 +4764,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -4853,7 +4841,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -4930,7 +4918,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -5007,7 +4995,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -5084,7 +5072,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -5161,7 +5149,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -5238,7 +5226,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -5315,7 +5303,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -5392,7 +5380,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -5469,7 +5457,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -5546,7 +5534,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -5623,7 +5611,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -5700,7 +5688,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -5777,7 +5765,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -5854,7 +5842,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -5931,7 +5919,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -6008,7 +5996,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -6085,7 +6073,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -6162,7 +6150,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -6239,7 +6227,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -6316,7 +6304,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -6393,7 +6381,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -6470,7 +6458,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -6547,7 +6535,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -6624,7 +6612,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -6701,7 +6689,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -6778,7 +6766,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -6855,7 +6843,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -6932,7 +6920,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -7009,7 +6997,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -7086,7 +7074,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -7163,7 +7151,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -7240,7 +7228,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -7317,7 +7305,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -7394,7 +7382,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -7471,7 +7459,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -7548,7 +7536,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -7625,7 +7613,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -7702,7 +7690,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -7779,7 +7767,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -7856,7 +7844,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -7933,7 +7921,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -8010,7 +7998,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -8087,7 +8075,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -8164,7 +8152,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -8241,7 +8229,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -8318,7 +8306,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -8395,7 +8383,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -8472,7 +8460,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -8549,7 +8537,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -8626,7 +8614,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -8703,7 +8691,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -8780,7 +8768,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -8857,7 +8845,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -8934,7 +8922,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -9011,7 +8999,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -9088,7 +9076,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -9165,7 +9153,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -9242,7 +9230,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -9319,7 +9307,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -9396,7 +9384,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -9473,7 +9461,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -9550,7 +9538,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -9627,7 +9615,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -9704,7 +9692,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -9781,7 +9769,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -9858,7 +9846,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -9935,7 +9923,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B124" t="inlineStr">
@@ -10012,7 +10000,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B125" t="inlineStr">
@@ -10089,7 +10077,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -10166,7 +10154,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -10243,7 +10231,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -10320,7 +10308,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -10397,7 +10385,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B130" t="inlineStr">
@@ -10474,7 +10462,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B131" t="inlineStr">
@@ -10551,7 +10539,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B132" t="inlineStr">
@@ -10628,7 +10616,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B133" t="inlineStr">
@@ -10705,7 +10693,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B134" t="inlineStr">
@@ -10782,7 +10770,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B135" t="inlineStr">
@@ -10859,7 +10847,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B136" t="inlineStr">
@@ -10936,7 +10924,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B137" t="inlineStr">
@@ -11013,7 +11001,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B138" t="inlineStr">
@@ -11090,7 +11078,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B139" t="inlineStr">
@@ -11167,7 +11155,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B140" t="inlineStr">
@@ -11244,7 +11232,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B141" t="inlineStr">
@@ -11321,7 +11309,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B142" t="inlineStr">
@@ -11398,7 +11386,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B143" t="inlineStr">
@@ -11475,7 +11463,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B144" t="inlineStr">
@@ -11552,7 +11540,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B145" t="inlineStr">
@@ -11629,7 +11617,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B146" t="inlineStr">
@@ -11706,7 +11694,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B147" t="inlineStr">
@@ -11783,7 +11771,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B148" t="inlineStr">
@@ -11860,7 +11848,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B149" t="inlineStr">
@@ -11937,7 +11925,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B150" t="inlineStr">
@@ -12014,7 +12002,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B151" t="inlineStr">
@@ -12091,7 +12079,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B152" t="inlineStr">
@@ -12168,7 +12156,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B153" t="inlineStr">
@@ -12245,7 +12233,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B154" t="inlineStr">
@@ -12322,7 +12310,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B155" t="inlineStr">
@@ -12399,7 +12387,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B156" t="inlineStr">
@@ -12476,7 +12464,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B157" t="inlineStr">
@@ -12553,7 +12541,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B158" t="inlineStr">
@@ -12630,7 +12618,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B159" t="inlineStr">
@@ -12707,7 +12695,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B160" t="inlineStr">
@@ -12784,7 +12772,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B161" t="inlineStr">
@@ -12861,7 +12849,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B162" t="inlineStr">
@@ -12938,7 +12926,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B163" t="inlineStr">
@@ -13015,7 +13003,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B164" t="inlineStr">
@@ -13092,7 +13080,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B165" t="inlineStr">
@@ -13169,7 +13157,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B166" t="inlineStr">
@@ -13246,7 +13234,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B167" t="inlineStr">
@@ -13323,7 +13311,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B168" t="inlineStr">
@@ -13400,7 +13388,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B169" t="inlineStr">
@@ -13477,7 +13465,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B170" t="inlineStr">
@@ -13554,7 +13542,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B171" t="inlineStr">
@@ -13631,7 +13619,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B172" t="inlineStr">
@@ -13708,7 +13696,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B173" t="inlineStr">
@@ -13785,7 +13773,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B174" t="inlineStr">
@@ -13862,7 +13850,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B175" t="inlineStr">
@@ -13939,7 +13927,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B176" t="inlineStr">
@@ -14016,7 +14004,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B177" t="inlineStr">
@@ -14093,7 +14081,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B178" t="inlineStr">
@@ -14170,7 +14158,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B179" t="inlineStr">
@@ -14247,7 +14235,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B180" t="inlineStr">
@@ -14324,7 +14312,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B181" t="inlineStr">
@@ -14401,7 +14389,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B182" t="inlineStr">
@@ -14478,7 +14466,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B183" t="inlineStr">
@@ -14555,7 +14543,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B184" t="inlineStr">
@@ -14632,7 +14620,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B185" t="inlineStr">
@@ -14709,7 +14697,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B186" t="inlineStr">
@@ -14786,7 +14774,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B187" t="inlineStr">
@@ -14863,7 +14851,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B188" t="inlineStr">
@@ -14940,7 +14928,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B189" t="inlineStr">
@@ -15017,7 +15005,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B190" t="inlineStr">
@@ -15094,7 +15082,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B191" t="inlineStr">
@@ -15171,7 +15159,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B192" t="inlineStr">
@@ -15248,7 +15236,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B193" t="inlineStr">
@@ -15325,7 +15313,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B194" t="inlineStr">
@@ -15402,7 +15390,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B195" t="inlineStr">
@@ -15479,7 +15467,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B196" t="inlineStr">
@@ -15556,7 +15544,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B197" t="inlineStr">
@@ -15633,7 +15621,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B198" t="inlineStr">
@@ -15710,7 +15698,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B199" t="inlineStr">
@@ -15787,7 +15775,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B200" t="inlineStr">
@@ -15864,7 +15852,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B201" t="inlineStr">
@@ -15941,7 +15929,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B202" t="inlineStr">
@@ -16018,7 +16006,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B203" t="inlineStr">
@@ -16095,7 +16083,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B204" t="inlineStr">
@@ -16172,7 +16160,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B205" t="inlineStr">
@@ -16249,7 +16237,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B206" t="inlineStr">
@@ -16326,7 +16314,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B207" t="inlineStr">
@@ -16403,7 +16391,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B208" t="inlineStr">
@@ -16480,7 +16468,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B209" t="inlineStr">
@@ -16557,7 +16545,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B210" t="inlineStr">
@@ -16634,7 +16622,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B211" t="inlineStr">
@@ -16711,7 +16699,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B212" t="inlineStr">
@@ -16788,7 +16776,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B213" t="inlineStr">
@@ -16865,7 +16853,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B214" t="inlineStr">
@@ -16942,7 +16930,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B215" t="inlineStr">
@@ -17019,7 +17007,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B216" t="inlineStr">
@@ -17096,7 +17084,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B217" t="inlineStr">
@@ -17173,7 +17161,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B218" t="inlineStr">
@@ -17250,7 +17238,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B219" t="inlineStr">
@@ -17327,7 +17315,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B220" t="inlineStr">
@@ -17404,7 +17392,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B221" t="inlineStr">
@@ -17481,7 +17469,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B222" t="inlineStr">
@@ -17558,7 +17546,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B223" t="inlineStr">
@@ -17635,7 +17623,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B224" t="inlineStr">
@@ -17712,7 +17700,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B225" t="inlineStr">
@@ -17789,7 +17777,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B226" t="inlineStr">
@@ -17866,7 +17854,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B227" t="inlineStr">
@@ -17943,7 +17931,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B228" t="inlineStr">
@@ -18020,7 +18008,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B229" t="inlineStr">
@@ -18097,7 +18085,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B230" t="inlineStr">
@@ -18174,7 +18162,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B231" t="inlineStr">
@@ -18251,7 +18239,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B232" t="inlineStr">
@@ -18328,7 +18316,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B233" t="inlineStr">
@@ -18405,7 +18393,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B234" t="inlineStr">
@@ -18482,7 +18470,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B235" t="inlineStr">
@@ -18559,7 +18547,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B236" t="inlineStr">
@@ -18636,7 +18624,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B237" t="inlineStr">
@@ -18713,7 +18701,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B238" t="inlineStr">
@@ -18790,7 +18778,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B239" t="inlineStr">
@@ -18867,7 +18855,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B240" t="inlineStr">
@@ -18944,7 +18932,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B241" t="inlineStr">
@@ -19021,7 +19009,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B242" t="inlineStr">
@@ -19098,7 +19086,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B243" t="inlineStr">
@@ -19175,7 +19163,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B244" t="inlineStr">
@@ -19252,7 +19240,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B245" t="inlineStr">
@@ -19329,7 +19317,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B246" t="inlineStr">
@@ -19406,7 +19394,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B247" t="inlineStr">
@@ -19483,7 +19471,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B248" t="inlineStr">
@@ -19560,7 +19548,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B249" t="inlineStr">
@@ -19637,7 +19625,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B250" t="inlineStr">
@@ -19714,7 +19702,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B251" t="inlineStr">
@@ -19791,7 +19779,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B252" t="inlineStr">
@@ -19868,7 +19856,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B253" t="inlineStr">
@@ -19945,7 +19933,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B254" t="inlineStr">
@@ -20022,7 +20010,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B255" t="inlineStr">
@@ -20099,7 +20087,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B256" t="inlineStr">
@@ -20176,7 +20164,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B257" t="inlineStr">
@@ -20253,7 +20241,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B258" t="inlineStr">
@@ -20330,7 +20318,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B259" t="inlineStr">
@@ -20407,7 +20395,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B260" t="inlineStr">
@@ -20484,7 +20472,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B261" t="inlineStr">
@@ -20561,7 +20549,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B262" t="inlineStr">
@@ -20638,7 +20626,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B263" t="inlineStr">
@@ -20715,7 +20703,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B264" t="inlineStr">
@@ -20792,7 +20780,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B265" t="inlineStr">
@@ -20869,7 +20857,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B266" t="inlineStr">
@@ -20946,7 +20934,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B267" t="inlineStr">
@@ -21023,7 +21011,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B268" t="inlineStr">
@@ -21100,7 +21088,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B269" t="inlineStr">
@@ -21177,7 +21165,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B270" t="inlineStr">
@@ -21254,7 +21242,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B271" t="inlineStr">
@@ -21331,7 +21319,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B272" t="inlineStr">
@@ -21408,7 +21396,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B273" t="inlineStr">
@@ -21485,7 +21473,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B274" t="inlineStr">
@@ -21562,7 +21550,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B275" t="inlineStr">
@@ -21639,7 +21627,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B276" t="inlineStr">
@@ -21716,7 +21704,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B277" t="inlineStr">
@@ -21793,7 +21781,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B278" t="inlineStr">
@@ -21870,7 +21858,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B279" t="inlineStr">
@@ -21947,7 +21935,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B280" t="inlineStr">
@@ -22024,7 +22012,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B281" t="inlineStr">
@@ -22101,7 +22089,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B282" t="inlineStr">
@@ -22178,7 +22166,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B283" t="inlineStr">
@@ -22255,7 +22243,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B284" t="inlineStr">
@@ -22332,7 +22320,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B285" t="inlineStr">
@@ -22409,7 +22397,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B286" t="inlineStr">
@@ -22486,7 +22474,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B287" t="inlineStr">
@@ -22563,7 +22551,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B288" t="inlineStr">
@@ -22640,7 +22628,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B289" t="inlineStr">
@@ -22717,7 +22705,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B290" t="inlineStr">
@@ -22794,7 +22782,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B291" t="inlineStr">
@@ -22871,7 +22859,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B292" t="inlineStr">
@@ -22948,7 +22936,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B293" t="inlineStr">
@@ -23025,7 +23013,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B294" t="inlineStr">
@@ -23102,7 +23090,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B295" t="inlineStr">
@@ -23179,7 +23167,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B296" t="inlineStr">
@@ -23256,7 +23244,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B297" t="inlineStr">
@@ -23333,7 +23321,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B298" t="inlineStr">
@@ -23410,7 +23398,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B299" t="inlineStr">
@@ -23487,7 +23475,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B300" t="inlineStr">
@@ -23564,7 +23552,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B301" t="inlineStr">
@@ -23641,7 +23629,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B302" t="inlineStr">
@@ -23718,7 +23706,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B303" t="inlineStr">
@@ -23795,7 +23783,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B304" t="inlineStr">
@@ -23872,7 +23860,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B305" t="inlineStr">
@@ -23949,7 +23937,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B306" t="inlineStr">
@@ -24026,7 +24014,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B307" t="inlineStr">
@@ -24103,7 +24091,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B308" t="inlineStr">
@@ -24180,7 +24168,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B309" t="inlineStr">
@@ -24257,7 +24245,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B310" t="inlineStr">
@@ -24334,7 +24322,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B311" t="inlineStr">
@@ -24411,7 +24399,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B312" t="inlineStr">
@@ -24488,7 +24476,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B313" t="inlineStr">
@@ -24565,7 +24553,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B314" t="inlineStr">
@@ -24642,7 +24630,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B315" t="inlineStr">
@@ -24719,7 +24707,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B316" t="inlineStr">
@@ -24796,7 +24784,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="n">
+      <c r="A317" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B317" t="inlineStr">
@@ -24873,7 +24861,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="2" t="n">
+      <c r="A318" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B318" t="inlineStr">
@@ -24950,7 +24938,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="2" t="n">
+      <c r="A319" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B319" t="inlineStr">
@@ -25027,7 +25015,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="2" t="n">
+      <c r="A320" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B320" t="inlineStr">
@@ -25104,7 +25092,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="2" t="n">
+      <c r="A321" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B321" t="inlineStr">
@@ -25181,7 +25169,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="2" t="n">
+      <c r="A322" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B322" t="inlineStr">
@@ -25258,7 +25246,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="2" t="n">
+      <c r="A323" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B323" t="inlineStr">
@@ -25335,7 +25323,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="2" t="n">
+      <c r="A324" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B324" t="inlineStr">
@@ -25412,7 +25400,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="2" t="n">
+      <c r="A325" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B325" t="inlineStr">
@@ -25489,7 +25477,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="2" t="n">
+      <c r="A326" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B326" t="inlineStr">
@@ -25566,7 +25554,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="2" t="n">
+      <c r="A327" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B327" t="inlineStr">
@@ -25643,7 +25631,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="2" t="n">
+      <c r="A328" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B328" t="inlineStr">
@@ -25720,7 +25708,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="2" t="n">
+      <c r="A329" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B329" t="inlineStr">
@@ -25797,7 +25785,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="2" t="n">
+      <c r="A330" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B330" t="inlineStr">
@@ -25874,7 +25862,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="2" t="n">
+      <c r="A331" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B331" t="inlineStr">
@@ -25951,7 +25939,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="n">
+      <c r="A332" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B332" t="inlineStr">
@@ -26028,7 +26016,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="2" t="n">
+      <c r="A333" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B333" t="inlineStr">
@@ -26105,7 +26093,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="2" t="n">
+      <c r="A334" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B334" t="inlineStr">
@@ -26182,7 +26170,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="2" t="n">
+      <c r="A335" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B335" t="inlineStr">
@@ -26259,7 +26247,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="2" t="n">
+      <c r="A336" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B336" t="inlineStr">
@@ -26336,7 +26324,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="2" t="n">
+      <c r="A337" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B337" t="inlineStr">
@@ -26413,7 +26401,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="2" t="n">
+      <c r="A338" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B338" t="inlineStr">
@@ -26490,7 +26478,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="2" t="n">
+      <c r="A339" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B339" t="inlineStr">
@@ -26567,7 +26555,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="2" t="n">
+      <c r="A340" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B340" t="inlineStr">
@@ -26644,7 +26632,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="2" t="n">
+      <c r="A341" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B341" t="inlineStr">
@@ -26721,7 +26709,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="2" t="n">
+      <c r="A342" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B342" t="inlineStr">
@@ -26798,7 +26786,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="2" t="n">
+      <c r="A343" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B343" t="inlineStr">
@@ -26875,7 +26863,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="2" t="n">
+      <c r="A344" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B344" t="inlineStr">
@@ -26952,7 +26940,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="2" t="n">
+      <c r="A345" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B345" t="inlineStr">
@@ -27029,7 +27017,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="2" t="n">
+      <c r="A346" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B346" t="inlineStr">
@@ -27106,7 +27094,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="2" t="n">
+      <c r="A347" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B347" t="inlineStr">
@@ -27183,7 +27171,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="2" t="n">
+      <c r="A348" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B348" t="inlineStr">
@@ -27260,7 +27248,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="2" t="n">
+      <c r="A349" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B349" t="inlineStr">
@@ -27337,7 +27325,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="2" t="n">
+      <c r="A350" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B350" t="inlineStr">
@@ -27414,7 +27402,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="2" t="n">
+      <c r="A351" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B351" t="inlineStr">
@@ -27491,7 +27479,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="2" t="n">
+      <c r="A352" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B352" t="inlineStr">
@@ -27568,7 +27556,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="2" t="n">
+      <c r="A353" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B353" t="inlineStr">
@@ -27645,7 +27633,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="2" t="n">
+      <c r="A354" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B354" t="inlineStr">
@@ -27722,7 +27710,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="2" t="n">
+      <c r="A355" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B355" t="inlineStr">
@@ -27799,7 +27787,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="2" t="n">
+      <c r="A356" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B356" t="inlineStr">
@@ -27876,7 +27864,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="2" t="n">
+      <c r="A357" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B357" t="inlineStr">
@@ -27953,7 +27941,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="2" t="n">
+      <c r="A358" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B358" t="inlineStr">
@@ -28030,7 +28018,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="2" t="n">
+      <c r="A359" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B359" t="inlineStr">
@@ -28107,7 +28095,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="2" t="n">
+      <c r="A360" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B360" t="inlineStr">
@@ -28184,7 +28172,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="2" t="n">
+      <c r="A361" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B361" t="inlineStr">
@@ -28261,7 +28249,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="2" t="n">
+      <c r="A362" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B362" t="inlineStr">
@@ -28338,7 +28326,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="2" t="n">
+      <c r="A363" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B363" t="inlineStr">
@@ -28415,7 +28403,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="2" t="n">
+      <c r="A364" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B364" t="inlineStr">
@@ -28492,7 +28480,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="2" t="n">
+      <c r="A365" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B365" t="inlineStr">
@@ -28569,7 +28557,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="2" t="n">
+      <c r="A366" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B366" t="inlineStr">
@@ -28646,7 +28634,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="2" t="n">
+      <c r="A367" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B367" t="inlineStr">
@@ -28723,7 +28711,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="2" t="n">
+      <c r="A368" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B368" t="inlineStr">
@@ -28800,7 +28788,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="2" t="n">
+      <c r="A369" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B369" t="inlineStr">
@@ -28877,7 +28865,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="2" t="n">
+      <c r="A370" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B370" t="inlineStr">
@@ -28954,7 +28942,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="2" t="n">
+      <c r="A371" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B371" t="inlineStr">
@@ -29031,7 +29019,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="2" t="n">
+      <c r="A372" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B372" t="inlineStr">
@@ -29108,7 +29096,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="2" t="n">
+      <c r="A373" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B373" t="inlineStr">
@@ -29185,7 +29173,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="2" t="n">
+      <c r="A374" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B374" t="inlineStr">
@@ -29262,7 +29250,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="2" t="n">
+      <c r="A375" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B375" t="inlineStr">
@@ -29339,7 +29327,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="2" t="n">
+      <c r="A376" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B376" t="inlineStr">
@@ -29416,7 +29404,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="2" t="n">
+      <c r="A377" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B377" t="inlineStr">
@@ -29493,7 +29481,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="2" t="n">
+      <c r="A378" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B378" t="inlineStr">
@@ -29570,7 +29558,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="2" t="n">
+      <c r="A379" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B379" t="inlineStr">
@@ -29647,7 +29635,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="2" t="n">
+      <c r="A380" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B380" t="inlineStr">
@@ -29724,7 +29712,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="2" t="n">
+      <c r="A381" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B381" t="inlineStr">
@@ -29801,7 +29789,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="2" t="n">
+      <c r="A382" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B382" t="inlineStr">
@@ -29878,7 +29866,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="2" t="n">
+      <c r="A383" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B383" t="inlineStr">
@@ -29955,7 +29943,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="2" t="n">
+      <c r="A384" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B384" t="inlineStr">
@@ -30032,7 +30020,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="2" t="n">
+      <c r="A385" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B385" t="inlineStr">
@@ -30109,7 +30097,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="2" t="n">
+      <c r="A386" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B386" t="inlineStr">
@@ -30186,7 +30174,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="2" t="n">
+      <c r="A387" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B387" t="inlineStr">
@@ -30263,7 +30251,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="2" t="n">
+      <c r="A388" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B388" t="inlineStr">
@@ -30340,7 +30328,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="2" t="n">
+      <c r="A389" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B389" t="inlineStr">
@@ -30417,7 +30405,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="2" t="n">
+      <c r="A390" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B390" t="inlineStr">
@@ -30494,7 +30482,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="2" t="n">
+      <c r="A391" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B391" t="inlineStr">
@@ -30571,7 +30559,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="2" t="n">
+      <c r="A392" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B392" t="inlineStr">
@@ -30648,7 +30636,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="2" t="n">
+      <c r="A393" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B393" t="inlineStr">
@@ -30725,7 +30713,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="2" t="n">
+      <c r="A394" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B394" t="inlineStr">
@@ -30802,7 +30790,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="2" t="n">
+      <c r="A395" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B395" t="inlineStr">
@@ -30879,7 +30867,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="2" t="n">
+      <c r="A396" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B396" t="inlineStr">
@@ -30956,7 +30944,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="2" t="n">
+      <c r="A397" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B397" t="inlineStr">
@@ -31033,7 +31021,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="2" t="n">
+      <c r="A398" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B398" t="inlineStr">
@@ -31110,7 +31098,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="2" t="n">
+      <c r="A399" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B399" t="inlineStr">
@@ -31187,7 +31175,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="2" t="n">
+      <c r="A400" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B400" t="inlineStr">
@@ -31264,7 +31252,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="2" t="n">
+      <c r="A401" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B401" t="inlineStr">
@@ -31341,7 +31329,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="2" t="n">
+      <c r="A402" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B402" t="inlineStr">
@@ -31418,7 +31406,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="2" t="n">
+      <c r="A403" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B403" t="inlineStr">
@@ -31495,7 +31483,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="2" t="n">
+      <c r="A404" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B404" t="inlineStr">
@@ -31572,7 +31560,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="2" t="n">
+      <c r="A405" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B405" t="inlineStr">
@@ -31649,7 +31637,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="2" t="n">
+      <c r="A406" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B406" t="inlineStr">
@@ -31726,7 +31714,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="2" t="n">
+      <c r="A407" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B407" t="inlineStr">
@@ -31803,7 +31791,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="2" t="n">
+      <c r="A408" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B408" t="inlineStr">
@@ -31880,7 +31868,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="2" t="n">
+      <c r="A409" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B409" t="inlineStr">
@@ -31957,7 +31945,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="2" t="n">
+      <c r="A410" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B410" t="inlineStr">
@@ -32034,7 +32022,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="2" t="n">
+      <c r="A411" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B411" t="inlineStr">
@@ -32111,7 +32099,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="2" t="n">
+      <c r="A412" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B412" t="inlineStr">
@@ -32188,7 +32176,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="2" t="n">
+      <c r="A413" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B413" t="inlineStr">
@@ -32265,7 +32253,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="2" t="n">
+      <c r="A414" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B414" t="inlineStr">
@@ -32342,7 +32330,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="2" t="n">
+      <c r="A415" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B415" t="inlineStr">
@@ -32419,7 +32407,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="2" t="n">
+      <c r="A416" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B416" t="inlineStr">
@@ -32496,7 +32484,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="2" t="n">
+      <c r="A417" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B417" t="inlineStr">
@@ -32573,7 +32561,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="2" t="n">
+      <c r="A418" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B418" t="inlineStr">
@@ -32650,7 +32638,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="2" t="n">
+      <c r="A419" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B419" t="inlineStr">
@@ -32727,7 +32715,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="2" t="n">
+      <c r="A420" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B420" t="inlineStr">
@@ -32804,7 +32792,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="2" t="n">
+      <c r="A421" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B421" t="inlineStr">
@@ -32881,7 +32869,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="2" t="n">
+      <c r="A422" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B422" t="inlineStr">
@@ -32958,7 +32946,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="2" t="n">
+      <c r="A423" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B423" t="inlineStr">
@@ -33035,7 +33023,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="2" t="n">
+      <c r="A424" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B424" t="inlineStr">
@@ -33112,7 +33100,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="2" t="n">
+      <c r="A425" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B425" t="inlineStr">
@@ -33189,7 +33177,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="2" t="n">
+      <c r="A426" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B426" t="inlineStr">
@@ -33266,7 +33254,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="2" t="n">
+      <c r="A427" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B427" t="inlineStr">
@@ -33343,7 +33331,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="2" t="n">
+      <c r="A428" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B428" t="inlineStr">
@@ -33420,7 +33408,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="2" t="n">
+      <c r="A429" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B429" t="inlineStr">
@@ -33497,7 +33485,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="2" t="n">
+      <c r="A430" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B430" t="inlineStr">
@@ -33574,7 +33562,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="2" t="n">
+      <c r="A431" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B431" t="inlineStr">
@@ -33651,7 +33639,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="2" t="n">
+      <c r="A432" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B432" t="inlineStr">
@@ -33728,7 +33716,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="2" t="n">
+      <c r="A433" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B433" t="inlineStr">
@@ -33805,7 +33793,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="2" t="n">
+      <c r="A434" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B434" t="inlineStr">
@@ -33882,7 +33870,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="2" t="n">
+      <c r="A435" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B435" t="inlineStr">
@@ -33959,7 +33947,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="2" t="n">
+      <c r="A436" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B436" t="inlineStr">
@@ -34036,7 +34024,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="2" t="n">
+      <c r="A437" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B437" t="inlineStr">
@@ -34113,7 +34101,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="2" t="n">
+      <c r="A438" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B438" t="inlineStr">
@@ -34190,7 +34178,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="2" t="n">
+      <c r="A439" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B439" t="inlineStr">
@@ -34267,7 +34255,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="2" t="n">
+      <c r="A440" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B440" t="inlineStr">
@@ -34344,7 +34332,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="2" t="n">
+      <c r="A441" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B441" t="inlineStr">
@@ -34421,7 +34409,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="2" t="n">
+      <c r="A442" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B442" t="inlineStr">
@@ -34498,7 +34486,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="2" t="n">
+      <c r="A443" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B443" t="inlineStr">
@@ -34575,7 +34563,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="2" t="n">
+      <c r="A444" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B444" t="inlineStr">
@@ -34652,7 +34640,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="2" t="n">
+      <c r="A445" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B445" t="inlineStr">
@@ -34729,7 +34717,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="2" t="n">
+      <c r="A446" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B446" t="inlineStr">
@@ -34806,7 +34794,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="2" t="n">
+      <c r="A447" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B447" t="inlineStr">
@@ -34883,7 +34871,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="2" t="n">
+      <c r="A448" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B448" t="inlineStr">
@@ -34960,7 +34948,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="2" t="n">
+      <c r="A449" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B449" t="inlineStr">
@@ -35037,7 +35025,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="2" t="n">
+      <c r="A450" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B450" t="inlineStr">
@@ -35114,7 +35102,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="2" t="n">
+      <c r="A451" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B451" t="inlineStr">
@@ -35191,7 +35179,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="2" t="n">
+      <c r="A452" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B452" t="inlineStr">
@@ -35268,7 +35256,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="2" t="n">
+      <c r="A453" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B453" t="inlineStr">
@@ -35345,7 +35333,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="2" t="n">
+      <c r="A454" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B454" t="inlineStr">
@@ -35422,7 +35410,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="2" t="n">
+      <c r="A455" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B455" t="inlineStr">
@@ -35499,7 +35487,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="2" t="n">
+      <c r="A456" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B456" t="inlineStr">
@@ -35576,7 +35564,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="2" t="n">
+      <c r="A457" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B457" t="inlineStr">
@@ -35653,7 +35641,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="2" t="n">
+      <c r="A458" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B458" t="inlineStr">
@@ -35730,7 +35718,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="2" t="n">
+      <c r="A459" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B459" t="inlineStr">
@@ -35807,7 +35795,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="2" t="n">
+      <c r="A460" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B460" t="inlineStr">
@@ -35884,7 +35872,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="2" t="n">
+      <c r="A461" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B461" t="inlineStr">
@@ -35961,7 +35949,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="2" t="n">
+      <c r="A462" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B462" t="inlineStr">
@@ -36038,7 +36026,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="2" t="n">
+      <c r="A463" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B463" t="inlineStr">
@@ -36115,7 +36103,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="2" t="n">
+      <c r="A464" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B464" t="inlineStr">
@@ -36192,7 +36180,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="2" t="n">
+      <c r="A465" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B465" t="inlineStr">
@@ -36269,7 +36257,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="2" t="n">
+      <c r="A466" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B466" t="inlineStr">
@@ -36346,7 +36334,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="2" t="n">
+      <c r="A467" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B467" t="inlineStr">
@@ -36423,7 +36411,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="2" t="n">
+      <c r="A468" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B468" t="inlineStr">
@@ -36500,7 +36488,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="2" t="n">
+      <c r="A469" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B469" t="inlineStr">
@@ -36577,7 +36565,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="2" t="n">
+      <c r="A470" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B470" t="inlineStr">
@@ -36654,7 +36642,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="2" t="n">
+      <c r="A471" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B471" t="inlineStr">
@@ -36731,7 +36719,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="2" t="n">
+      <c r="A472" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B472" t="inlineStr">
@@ -36808,7 +36796,7 @@
       </c>
     </row>
  